--- a/project_documents/parameterDirectory.xlsx
+++ b/project_documents/parameterDirectory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabian/Documents/GitHub/HPVScreeningProject/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabian/Documents/DPhil Work/Academic Work/EnglandCervicalScreeningProject/project_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F816E9-5CD6-FD45-B2EF-A389AAAFED89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17100" activeTab="2" xr2:uid="{9CDCC384-B02C-4946-8A51-C0AA91FF93D1}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17100" activeTab="7" xr2:uid="{9CDCC384-B02C-4946-8A51-C0AA91FF93D1}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -2566,6 +2566,63 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2599,63 +2656,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2708,23 +2708,86 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2746,12 +2809,6 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2761,62 +2818,20 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2832,21 +2847,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3742,29 +3742,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="B2" s="205" t="s">
+      <c r="B2" s="188" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="209" t="s">
+      <c r="C2" s="192" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="215" t="s">
+      <c r="D2" s="200" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="216"/>
-      <c r="F2" s="217" t="s">
+      <c r="E2" s="201"/>
+      <c r="F2" s="202" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="217"/>
-      <c r="H2" s="217"/>
-      <c r="I2" s="216"/>
-      <c r="J2" s="207" t="s">
+      <c r="G2" s="202"/>
+      <c r="H2" s="202"/>
+      <c r="I2" s="201"/>
+      <c r="J2" s="190" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="206"/>
-      <c r="C3" s="210"/>
+      <c r="B3" s="189"/>
+      <c r="C3" s="193"/>
       <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
@@ -3783,10 +3783,10 @@
       <c r="I3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="208"/>
+      <c r="J3" s="191"/>
     </row>
     <row r="4" spans="1:10" s="83" customFormat="1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="200" t="s">
+      <c r="A4" s="204" t="s">
         <v>93</v>
       </c>
       <c r="B4" s="78" t="s">
@@ -3810,7 +3810,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" s="83" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A5" s="200"/>
+      <c r="A5" s="204"/>
       <c r="B5" s="84" t="s">
         <v>18</v>
       </c>
@@ -3832,7 +3832,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" s="83" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A6" s="200"/>
+      <c r="A6" s="204"/>
       <c r="B6" s="84" t="s">
         <v>22</v>
       </c>
@@ -3852,7 +3852,7 @@
       <c r="J6" s="86"/>
     </row>
     <row r="7" spans="1:10" s="83" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="200"/>
+      <c r="A7" s="204"/>
       <c r="B7" s="84" t="s">
         <v>109</v>
       </c>
@@ -3872,7 +3872,7 @@
       <c r="J7" s="86"/>
     </row>
     <row r="8" spans="1:10" s="83" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A8" s="200"/>
+      <c r="A8" s="204"/>
       <c r="B8" s="84" t="s">
         <v>23</v>
       </c>
@@ -3916,7 +3916,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="104" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A10" s="201" t="s">
+      <c r="A10" s="205" t="s">
         <v>95</v>
       </c>
       <c r="B10" s="99" t="s">
@@ -3940,41 +3940,41 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="104" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="201"/>
-      <c r="B11" s="203" t="s">
+      <c r="A11" s="205"/>
+      <c r="B11" s="196" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="211" t="s">
+      <c r="C11" s="194" t="s">
         <v>43</v>
       </c>
       <c r="D11" s="102" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="E11" s="203" t="s">
+      <c r="E11" s="196" t="s">
         <v>244</v>
       </c>
       <c r="F11" s="102"/>
       <c r="G11" s="103"/>
       <c r="H11" s="103"/>
       <c r="I11" s="99"/>
-      <c r="J11" s="213"/>
+      <c r="J11" s="198"/>
     </row>
     <row r="12" spans="1:10" s="104" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="201"/>
-      <c r="B12" s="204"/>
-      <c r="C12" s="212"/>
+      <c r="A12" s="205"/>
+      <c r="B12" s="197"/>
+      <c r="C12" s="195"/>
       <c r="D12" s="102" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="E12" s="204"/>
+      <c r="E12" s="197"/>
       <c r="F12" s="102"/>
       <c r="G12" s="103"/>
       <c r="H12" s="103"/>
       <c r="I12" s="99"/>
-      <c r="J12" s="214"/>
+      <c r="J12" s="199"/>
     </row>
     <row r="13" spans="1:10" s="109" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A13" s="202" t="s">
+      <c r="A13" s="206" t="s">
         <v>96</v>
       </c>
       <c r="B13" s="105" t="s">
@@ -3996,7 +3996,7 @@
       <c r="J13" s="107"/>
     </row>
     <row r="14" spans="1:10" s="109" customFormat="1" ht="188" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="202"/>
+      <c r="A14" s="206"/>
       <c r="B14" s="105" t="s">
         <v>38</v>
       </c>
@@ -4018,7 +4018,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" s="109" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="202"/>
+      <c r="A15" s="206"/>
       <c r="B15" s="105" t="s">
         <v>48</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="J15" s="107"/>
     </row>
     <row r="16" spans="1:10" s="109" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A16" s="202"/>
+      <c r="A16" s="206"/>
       <c r="B16" s="105" t="s">
         <v>51</v>
       </c>
@@ -4060,7 +4060,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" s="109" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="202"/>
+      <c r="A17" s="206"/>
       <c r="B17" s="105" t="s">
         <v>55</v>
       </c>
@@ -4080,7 +4080,7 @@
       <c r="J17" s="107"/>
     </row>
     <row r="18" spans="1:10" s="109" customFormat="1" ht="120" x14ac:dyDescent="0.2">
-      <c r="A18" s="202"/>
+      <c r="A18" s="206"/>
       <c r="B18" s="105" t="s">
         <v>60</v>
       </c>
@@ -4104,7 +4104,7 @@
       <c r="J18" s="107"/>
     </row>
     <row r="19" spans="1:10" s="109" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A19" s="202"/>
+      <c r="A19" s="206"/>
       <c r="B19" s="105" t="s">
         <v>64</v>
       </c>
@@ -4128,7 +4128,7 @@
       <c r="J19" s="107"/>
     </row>
     <row r="20" spans="1:10" s="109" customFormat="1" ht="115" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="202"/>
+      <c r="A20" s="206"/>
       <c r="B20" s="105" t="s">
         <v>67</v>
       </c>
@@ -4148,51 +4148,51 @@
       <c r="J20" s="111"/>
     </row>
     <row r="21" spans="1:10" s="109" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="202"/>
+      <c r="A21" s="206"/>
       <c r="B21" s="112" t="s">
         <v>103</v>
       </c>
-      <c r="C21" s="191" t="s">
+      <c r="C21" s="210" t="s">
         <v>106</v>
       </c>
       <c r="D21" s="111" t="s">
         <v>173</v>
       </c>
-      <c r="E21" s="188" t="s">
+      <c r="E21" s="207" t="s">
         <v>107</v>
       </c>
       <c r="F21" s="113"/>
       <c r="G21" s="114"/>
       <c r="H21" s="114"/>
-      <c r="I21" s="188" t="s">
+      <c r="I21" s="207" t="s">
         <v>175</v>
       </c>
-      <c r="J21" s="194" t="s">
+      <c r="J21" s="213" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="109" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="202"/>
+      <c r="A22" s="206"/>
       <c r="B22" s="115" t="s">
         <v>105</v>
       </c>
-      <c r="C22" s="192"/>
+      <c r="C22" s="211"/>
       <c r="D22" s="114" t="s">
         <v>174</v>
       </c>
-      <c r="E22" s="189"/>
+      <c r="E22" s="208"/>
       <c r="F22" s="111"/>
       <c r="G22" s="107"/>
       <c r="H22" s="107"/>
-      <c r="I22" s="189"/>
-      <c r="J22" s="195"/>
+      <c r="I22" s="208"/>
+      <c r="J22" s="214"/>
     </row>
     <row r="23" spans="1:10" s="109" customFormat="1" ht="180" x14ac:dyDescent="0.2">
-      <c r="A23" s="202"/>
+      <c r="A23" s="206"/>
       <c r="B23" s="105" t="s">
         <v>104</v>
       </c>
-      <c r="C23" s="193"/>
+      <c r="C23" s="212"/>
       <c r="D23" s="111" t="s">
         <v>326</v>
       </c>
@@ -4202,8 +4202,8 @@
       <c r="F23" s="187"/>
       <c r="G23" s="107"/>
       <c r="H23" s="107"/>
-      <c r="I23" s="190"/>
-      <c r="J23" s="196"/>
+      <c r="I23" s="209"/>
+      <c r="J23" s="215"/>
     </row>
     <row r="24" spans="1:10" s="109" customFormat="1" ht="255" x14ac:dyDescent="0.2">
       <c r="A24" s="185"/>
@@ -4412,7 +4412,7 @@
       <c r="J32" s="117"/>
     </row>
     <row r="33" spans="1:10" s="134" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="199" t="s">
+      <c r="A33" s="203" t="s">
         <v>249</v>
       </c>
       <c r="B33" s="130" t="s">
@@ -4431,12 +4431,12 @@
       <c r="G33" s="133"/>
       <c r="H33" s="133"/>
       <c r="I33" s="130"/>
-      <c r="J33" s="197" t="s">
+      <c r="J33" s="216" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="134" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A34" s="199"/>
+      <c r="A34" s="203"/>
       <c r="B34" s="130" t="s">
         <v>114</v>
       </c>
@@ -4453,10 +4453,20 @@
       <c r="G34" s="133"/>
       <c r="H34" s="133"/>
       <c r="I34" s="130"/>
-      <c r="J34" s="198"/>
+      <c r="J34" s="217"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="J21:J23"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B11:B12"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="C2:C3"/>
@@ -4465,16 +4475,6 @@
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="J21:J23"/>
-    <mergeCell ref="J33:J34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7352,84 +7352,84 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="253" t="s">
+      <c r="B2" s="252" t="s">
         <v>160</v>
       </c>
-      <c r="C2" s="255" t="s">
+      <c r="C2" s="238" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="257"/>
-      <c r="G2" s="270" t="s">
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="250" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="253" t="s">
+      <c r="H2" s="252" t="s">
         <v>273</v>
       </c>
-      <c r="I2" s="255" t="s">
+      <c r="I2" s="238" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="256"/>
-      <c r="K2" s="265"/>
+      <c r="J2" s="239"/>
+      <c r="K2" s="240"/>
     </row>
     <row r="3" spans="1:21" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="254"/>
-      <c r="C3" s="258"/>
-      <c r="D3" s="259"/>
-      <c r="E3" s="259"/>
-      <c r="F3" s="260"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="254"/>
-      <c r="I3" s="258"/>
-      <c r="J3" s="259"/>
-      <c r="K3" s="266"/>
+      <c r="B3" s="253"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="255"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="253"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="243"/>
     </row>
     <row r="4" spans="1:21" s="120" customFormat="1" ht="270" x14ac:dyDescent="0.2">
       <c r="A4" s="138"/>
       <c r="B4" s="140" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="261" t="s">
+      <c r="C4" s="256" t="s">
         <v>314</v>
       </c>
-      <c r="D4" s="262"/>
-      <c r="E4" s="262"/>
-      <c r="F4" s="263"/>
+      <c r="D4" s="257"/>
+      <c r="E4" s="257"/>
+      <c r="F4" s="258"/>
       <c r="G4" s="141" t="s">
         <v>280</v>
       </c>
       <c r="H4" s="142" t="s">
         <v>281</v>
       </c>
-      <c r="I4" s="267" t="s">
+      <c r="I4" s="247" t="s">
         <v>309</v>
       </c>
-      <c r="J4" s="268"/>
-      <c r="K4" s="269"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="249"/>
     </row>
     <row r="5" spans="1:21" s="120" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="138"/>
       <c r="B5" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="235" t="s">
+      <c r="C5" s="244" t="s">
         <v>315</v>
       </c>
-      <c r="D5" s="236"/>
-      <c r="E5" s="236"/>
-      <c r="F5" s="264"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="246"/>
       <c r="G5" s="143">
         <v>0.8</v>
       </c>
       <c r="H5" s="144" t="s">
         <v>325</v>
       </c>
-      <c r="I5" s="238" t="s">
+      <c r="I5" s="235" t="s">
         <v>279</v>
       </c>
-      <c r="J5" s="239"/>
-      <c r="K5" s="240"/>
+      <c r="J5" s="236"/>
+      <c r="K5" s="237"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
@@ -7439,23 +7439,23 @@
       <c r="B6" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="C6" s="235" t="s">
+      <c r="C6" s="244" t="s">
         <v>316</v>
       </c>
-      <c r="D6" s="236"/>
-      <c r="E6" s="236"/>
-      <c r="F6" s="264"/>
+      <c r="D6" s="245"/>
+      <c r="E6" s="245"/>
+      <c r="F6" s="246"/>
       <c r="G6" s="143">
         <v>0.8</v>
       </c>
       <c r="H6" s="145" t="s">
         <v>325</v>
       </c>
-      <c r="I6" s="238" t="s">
+      <c r="I6" s="235" t="s">
         <v>278</v>
       </c>
-      <c r="J6" s="239"/>
-      <c r="K6" s="240"/>
+      <c r="J6" s="236"/>
+      <c r="K6" s="237"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
@@ -7465,21 +7465,21 @@
       <c r="B7" s="93" t="s">
         <v>311</v>
       </c>
-      <c r="C7" s="235" t="s">
+      <c r="C7" s="244" t="s">
         <v>312</v>
       </c>
-      <c r="D7" s="236"/>
-      <c r="E7" s="236"/>
-      <c r="F7" s="264"/>
+      <c r="D7" s="245"/>
+      <c r="E7" s="245"/>
+      <c r="F7" s="246"/>
       <c r="G7" s="143">
         <v>1</v>
       </c>
       <c r="H7" s="145"/>
-      <c r="I7" s="238" t="s">
+      <c r="I7" s="235" t="s">
         <v>313</v>
       </c>
-      <c r="J7" s="239"/>
-      <c r="K7" s="240"/>
+      <c r="J7" s="236"/>
+      <c r="K7" s="237"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
@@ -7489,21 +7489,21 @@
       <c r="B8" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="235" t="s">
+      <c r="C8" s="244" t="s">
         <v>275</v>
       </c>
-      <c r="D8" s="236"/>
-      <c r="E8" s="236"/>
-      <c r="F8" s="264"/>
+      <c r="D8" s="245"/>
+      <c r="E8" s="245"/>
+      <c r="F8" s="246"/>
       <c r="G8" s="143">
         <v>1</v>
       </c>
       <c r="H8" s="144" t="s">
         <v>276</v>
       </c>
-      <c r="I8" s="238"/>
-      <c r="J8" s="239"/>
-      <c r="K8" s="240"/>
+      <c r="I8" s="235"/>
+      <c r="J8" s="236"/>
+      <c r="K8" s="237"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
@@ -7513,23 +7513,23 @@
       <c r="B9" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="C9" s="235" t="s">
+      <c r="C9" s="244" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="236"/>
-      <c r="E9" s="236"/>
-      <c r="F9" s="264"/>
+      <c r="D9" s="245"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="246"/>
       <c r="G9" s="143">
         <v>0.95</v>
       </c>
       <c r="H9" s="144" t="s">
         <v>325</v>
       </c>
-      <c r="I9" s="235" t="s">
+      <c r="I9" s="244" t="s">
         <v>274</v>
       </c>
-      <c r="J9" s="236"/>
-      <c r="K9" s="237"/>
+      <c r="J9" s="245"/>
+      <c r="K9" s="261"/>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -7539,21 +7539,21 @@
       <c r="B10" s="93" t="s">
         <v>167</v>
       </c>
-      <c r="C10" s="235" t="s">
+      <c r="C10" s="244" t="s">
         <v>170</v>
       </c>
-      <c r="D10" s="236"/>
-      <c r="E10" s="236"/>
-      <c r="F10" s="264"/>
+      <c r="D10" s="245"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="246"/>
       <c r="G10" s="146">
         <v>0.9</v>
       </c>
       <c r="H10" s="144"/>
-      <c r="I10" s="238" t="s">
+      <c r="I10" s="235" t="s">
         <v>277</v>
       </c>
-      <c r="J10" s="239"/>
-      <c r="K10" s="240"/>
+      <c r="J10" s="236"/>
+      <c r="K10" s="237"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -7563,21 +7563,21 @@
       <c r="B11" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="C11" s="235" t="s">
+      <c r="C11" s="244" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="236"/>
-      <c r="E11" s="236"/>
-      <c r="F11" s="264"/>
+      <c r="D11" s="245"/>
+      <c r="E11" s="245"/>
+      <c r="F11" s="246"/>
       <c r="G11" s="146">
         <v>0.9</v>
       </c>
       <c r="H11" s="145"/>
-      <c r="I11" s="238" t="s">
+      <c r="I11" s="235" t="s">
         <v>277</v>
       </c>
-      <c r="J11" s="239"/>
-      <c r="K11" s="240"/>
+      <c r="J11" s="236"/>
+      <c r="K11" s="237"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -7608,28 +7608,28 @@
       <c r="U13" s="150"/>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="245" t="s">
+      <c r="B14" s="266" t="s">
         <v>268</v>
       </c>
-      <c r="C14" s="246"/>
-      <c r="D14" s="246"/>
-      <c r="E14" s="246"/>
-      <c r="F14" s="246"/>
-      <c r="G14" s="246"/>
-      <c r="H14" s="246"/>
-      <c r="I14" s="246"/>
-      <c r="J14" s="246"/>
-      <c r="K14" s="246"/>
-      <c r="L14" s="246"/>
-      <c r="M14" s="246"/>
-      <c r="N14" s="246"/>
-      <c r="O14" s="246"/>
-      <c r="P14" s="246"/>
-      <c r="Q14" s="246"/>
-      <c r="R14" s="246"/>
-      <c r="S14" s="246"/>
-      <c r="T14" s="246"/>
-      <c r="U14" s="247"/>
+      <c r="C14" s="267"/>
+      <c r="D14" s="267"/>
+      <c r="E14" s="267"/>
+      <c r="F14" s="267"/>
+      <c r="G14" s="267"/>
+      <c r="H14" s="267"/>
+      <c r="I14" s="267"/>
+      <c r="J14" s="267"/>
+      <c r="K14" s="267"/>
+      <c r="L14" s="267"/>
+      <c r="M14" s="267"/>
+      <c r="N14" s="267"/>
+      <c r="O14" s="267"/>
+      <c r="P14" s="267"/>
+      <c r="Q14" s="267"/>
+      <c r="R14" s="267"/>
+      <c r="S14" s="267"/>
+      <c r="T14" s="267"/>
+      <c r="U14" s="268"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B15" s="151"/>
@@ -7654,34 +7654,34 @@
       <c r="U15" s="154"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B16" s="243" t="s">
+      <c r="B16" s="264" t="s">
         <v>264</v>
       </c>
-      <c r="C16" s="244"/>
-      <c r="D16" s="244"/>
-      <c r="E16" s="244"/>
-      <c r="F16" s="244"/>
-      <c r="G16" s="244"/>
-      <c r="H16" s="244"/>
-      <c r="I16" s="244"/>
-      <c r="J16" s="244"/>
-      <c r="K16" s="244"/>
-      <c r="L16" s="244"/>
-      <c r="M16" s="244"/>
-      <c r="N16" s="244"/>
-      <c r="O16" s="244"/>
-      <c r="P16" s="244"/>
-      <c r="Q16" s="244"/>
-      <c r="R16" s="244"/>
-      <c r="S16" s="244"/>
-      <c r="T16" s="244"/>
-      <c r="U16" s="252"/>
+      <c r="C16" s="265"/>
+      <c r="D16" s="265"/>
+      <c r="E16" s="265"/>
+      <c r="F16" s="265"/>
+      <c r="G16" s="265"/>
+      <c r="H16" s="265"/>
+      <c r="I16" s="265"/>
+      <c r="J16" s="265"/>
+      <c r="K16" s="265"/>
+      <c r="L16" s="265"/>
+      <c r="M16" s="265"/>
+      <c r="N16" s="265"/>
+      <c r="O16" s="265"/>
+      <c r="P16" s="265"/>
+      <c r="Q16" s="265"/>
+      <c r="R16" s="265"/>
+      <c r="S16" s="265"/>
+      <c r="T16" s="265"/>
+      <c r="U16" s="271"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B17" s="248" t="s">
+      <c r="B17" s="259" t="s">
         <v>260</v>
       </c>
-      <c r="C17" s="249"/>
+      <c r="C17" s="260"/>
       <c r="D17" s="161">
         <v>2008</v>
       </c>
@@ -7738,10 +7738,10 @@
       </c>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18" s="250" t="s">
+      <c r="B18" s="269" t="s">
         <v>261</v>
       </c>
-      <c r="C18" s="251"/>
+      <c r="C18" s="270"/>
       <c r="D18" s="162">
         <v>0.86</v>
       </c>
@@ -7798,10 +7798,10 @@
       </c>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B19" s="250" t="s">
+      <c r="B19" s="269" t="s">
         <v>262</v>
       </c>
-      <c r="C19" s="251"/>
+      <c r="C19" s="270"/>
       <c r="D19" s="162">
         <f>78/86</f>
         <v>0.90697674418604646</v>
@@ -7873,10 +7873,10 @@
       </c>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B20" s="250" t="s">
+      <c r="B20" s="269" t="s">
         <v>263</v>
       </c>
-      <c r="C20" s="251"/>
+      <c r="C20" s="270"/>
       <c r="D20" s="162">
         <v>1</v>
       </c>
@@ -7955,17 +7955,17 @@
       <c r="U21" s="154"/>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B22" s="243" t="s">
+      <c r="B22" s="264" t="s">
         <v>267</v>
       </c>
-      <c r="C22" s="244"/>
-      <c r="D22" s="244"/>
-      <c r="E22" s="244"/>
-      <c r="F22" s="244"/>
-      <c r="G22" s="244"/>
-      <c r="H22" s="244"/>
-      <c r="I22" s="244"/>
-      <c r="J22" s="244"/>
+      <c r="C22" s="265"/>
+      <c r="D22" s="265"/>
+      <c r="E22" s="265"/>
+      <c r="F22" s="265"/>
+      <c r="G22" s="265"/>
+      <c r="H22" s="265"/>
+      <c r="I22" s="265"/>
+      <c r="J22" s="265"/>
       <c r="K22" s="156"/>
       <c r="L22" s="156"/>
       <c r="M22" s="156"/>
@@ -7979,10 +7979,10 @@
       <c r="U22" s="157"/>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B23" s="248" t="s">
+      <c r="B23" s="259" t="s">
         <v>260</v>
       </c>
-      <c r="C23" s="249"/>
+      <c r="C23" s="260"/>
       <c r="D23" s="161">
         <v>2019</v>
       </c>
@@ -8017,10 +8017,10 @@
       <c r="U23" s="154"/>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B24" s="248" t="s">
+      <c r="B24" s="259" t="s">
         <v>261</v>
       </c>
-      <c r="C24" s="249"/>
+      <c r="C24" s="260"/>
       <c r="D24" s="162">
         <f>E24</f>
         <v>0.53</v>
@@ -8058,10 +8058,10 @@
       <c r="U24" s="154"/>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B25" s="248" t="s">
+      <c r="B25" s="259" t="s">
         <v>262</v>
       </c>
-      <c r="C25" s="249"/>
+      <c r="C25" s="260"/>
       <c r="D25" s="162">
         <f>E25</f>
         <v>0.35830985915492958</v>
@@ -8099,10 +8099,10 @@
       <c r="U25" s="154"/>
     </row>
     <row r="26" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="241" t="s">
+      <c r="B26" s="262" t="s">
         <v>263</v>
       </c>
-      <c r="C26" s="242"/>
+      <c r="C26" s="263"/>
       <c r="D26" s="168">
         <v>0</v>
       </c>
@@ -8167,26 +8167,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="I10:K10"/>
     <mergeCell ref="B26:C26"/>
@@ -8199,6 +8179,26 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B16:U16"/>
     <mergeCell ref="I11:K11"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8244,13 +8244,13 @@
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="278" t="s">
+      <c r="B3" s="272" t="s">
         <v>253</v>
       </c>
-      <c r="C3" s="279"/>
-      <c r="D3" s="279"/>
-      <c r="E3" s="279"/>
-      <c r="F3" s="280"/>
+      <c r="C3" s="273"/>
+      <c r="D3" s="273"/>
+      <c r="E3" s="273"/>
+      <c r="F3" s="274"/>
       <c r="G3" s="171"/>
       <c r="H3" s="67"/>
     </row>
@@ -8277,13 +8277,13 @@
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="278" t="s">
+      <c r="B5" s="272" t="s">
         <v>270</v>
       </c>
-      <c r="C5" s="279"/>
-      <c r="D5" s="279"/>
-      <c r="E5" s="279"/>
-      <c r="F5" s="280"/>
+      <c r="C5" s="273"/>
+      <c r="D5" s="273"/>
+      <c r="E5" s="273"/>
+      <c r="F5" s="274"/>
       <c r="G5" s="171"/>
       <c r="H5" s="67"/>
     </row>
@@ -8312,13 +8312,13 @@
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="278" t="s">
+      <c r="B7" s="272" t="s">
         <v>283</v>
       </c>
-      <c r="C7" s="279"/>
-      <c r="D7" s="279"/>
-      <c r="E7" s="279"/>
-      <c r="F7" s="280"/>
+      <c r="C7" s="273"/>
+      <c r="D7" s="273"/>
+      <c r="E7" s="273"/>
+      <c r="F7" s="274"/>
       <c r="G7" s="171"/>
       <c r="H7" s="67"/>
     </row>
@@ -8335,7 +8335,7 @@
       <c r="E8" s="182" t="s">
         <v>306</v>
       </c>
-      <c r="F8" s="277" t="s">
+      <c r="F8" s="275" t="s">
         <v>308</v>
       </c>
       <c r="G8" s="171"/>
@@ -8354,7 +8354,7 @@
       <c r="E9" s="182" t="s">
         <v>307</v>
       </c>
-      <c r="F9" s="277"/>
+      <c r="F9" s="275"/>
       <c r="G9" s="171"/>
       <c r="H9" s="67"/>
     </row>
@@ -8371,11 +8371,11 @@
       <c r="E10" s="172" t="s">
         <v>284</v>
       </c>
-      <c r="F10" s="277"/>
-      <c r="G10" s="275">
+      <c r="F10" s="275"/>
+      <c r="G10" s="280">
         <v>3</v>
       </c>
-      <c r="H10" s="273">
+      <c r="H10" s="278">
         <f>H6*G10</f>
         <v>18</v>
       </c>
@@ -8393,9 +8393,9 @@
       <c r="E11" s="172" t="s">
         <v>284</v>
       </c>
-      <c r="F11" s="277"/>
-      <c r="G11" s="275"/>
-      <c r="H11" s="273"/>
+      <c r="F11" s="275"/>
+      <c r="G11" s="280"/>
+      <c r="H11" s="278"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" s="68" t="s">
@@ -8410,9 +8410,9 @@
       <c r="E12" s="172" t="s">
         <v>292</v>
       </c>
-      <c r="F12" s="277"/>
-      <c r="G12" s="275"/>
-      <c r="H12" s="273"/>
+      <c r="F12" s="275"/>
+      <c r="G12" s="280"/>
+      <c r="H12" s="278"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B13" s="68" t="s">
@@ -8427,18 +8427,18 @@
       <c r="E13" s="172" t="s">
         <v>285</v>
       </c>
-      <c r="F13" s="277"/>
-      <c r="G13" s="275"/>
-      <c r="H13" s="273"/>
+      <c r="F13" s="275"/>
+      <c r="G13" s="280"/>
+      <c r="H13" s="278"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="278" t="s">
+      <c r="B14" s="272" t="s">
         <v>323</v>
       </c>
-      <c r="C14" s="279"/>
-      <c r="D14" s="279"/>
-      <c r="E14" s="279"/>
-      <c r="F14" s="280"/>
+      <c r="C14" s="273"/>
+      <c r="D14" s="273"/>
+      <c r="E14" s="273"/>
+      <c r="F14" s="274"/>
       <c r="G14" s="180"/>
       <c r="H14" s="67"/>
     </row>
@@ -8455,13 +8455,13 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="277" t="s">
+      <c r="F15" s="275" t="s">
         <v>291</v>
       </c>
-      <c r="G15" s="275">
+      <c r="G15" s="280">
         <v>2</v>
       </c>
-      <c r="H15" s="273">
+      <c r="H15" s="278">
         <f>H10*G15</f>
         <v>36</v>
       </c>
@@ -8479,9 +8479,9 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="277"/>
-      <c r="G16" s="275"/>
-      <c r="H16" s="273"/>
+      <c r="F16" s="275"/>
+      <c r="G16" s="280"/>
+      <c r="H16" s="278"/>
     </row>
     <row r="17" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="69" t="s">
@@ -8496,9 +8496,9 @@
       <c r="E17" s="70">
         <v>0</v>
       </c>
-      <c r="F17" s="281"/>
-      <c r="G17" s="276"/>
-      <c r="H17" s="274"/>
+      <c r="F17" s="276"/>
+      <c r="G17" s="281"/>
+      <c r="H17" s="279"/>
     </row>
     <row r="18" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
@@ -8543,38 +8543,33 @@
       <c r="G24" s="234"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C27" s="272" t="s">
+      <c r="C27" s="277" t="s">
         <v>320</v>
       </c>
-      <c r="D27" s="272"/>
-      <c r="E27" s="272"/>
-      <c r="F27" s="272"/>
-      <c r="G27" s="272"/>
-      <c r="H27" s="272"/>
+      <c r="D27" s="277"/>
+      <c r="E27" s="277"/>
+      <c r="F27" s="277"/>
+      <c r="G27" s="277"/>
+      <c r="H27" s="277"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C28" s="272"/>
-      <c r="D28" s="272"/>
-      <c r="E28" s="272"/>
-      <c r="F28" s="272"/>
-      <c r="G28" s="272"/>
-      <c r="H28" s="272"/>
+      <c r="C28" s="277"/>
+      <c r="D28" s="277"/>
+      <c r="E28" s="277"/>
+      <c r="F28" s="277"/>
+      <c r="G28" s="277"/>
+      <c r="H28" s="277"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C29" s="272"/>
-      <c r="D29" s="272"/>
-      <c r="E29" s="272"/>
-      <c r="F29" s="272"/>
-      <c r="G29" s="272"/>
-      <c r="H29" s="272"/>
+      <c r="C29" s="277"/>
+      <c r="D29" s="277"/>
+      <c r="E29" s="277"/>
+      <c r="F29" s="277"/>
+      <c r="G29" s="277"/>
+      <c r="H29" s="277"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="C27:H29"/>
     <mergeCell ref="H10:H13"/>
     <mergeCell ref="H15:H17"/>
@@ -8582,7 +8577,13 @@
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="F8:F13"/>
     <mergeCell ref="C22:G24"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="B14:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/project_documents/parameterDirectory.xlsx
+++ b/project_documents/parameterDirectory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabian/Documents/DPhil Work/Academic Work/EnglandCervicalScreeningProject/project_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F816E9-5CD6-FD45-B2EF-A389AAAFED89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B1E46E-D74E-1E48-80C2-A84FF8A184A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17100" activeTab="7" xr2:uid="{9CDCC384-B02C-4946-8A51-C0AA91FF93D1}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17100" activeTab="2" xr2:uid="{9CDCC384-B02C-4946-8A51-C0AA91FF93D1}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -185,9 +185,6 @@
     <t>Distribution of sexual debut ages, split by female and male sexes</t>
   </si>
   <si>
-    <t>f: N(16,3.1^2), m: N(16,4.1^2)</t>
-  </si>
-  <si>
     <t>mixing</t>
   </si>
   <si>
@@ -252,9 +249,6 @@
   </si>
   <si>
     <t>These parameters don't matter when we have only 1 cluster</t>
-  </si>
-  <si>
-    <t>Little literature exists on sexual debut age, but this is consistnet with other modelling and the scant information available online which suggests in the UK most debut is at age 16 with about a third of both boys' and girls'  debuts before 16.</t>
   </si>
   <si>
     <t>f_cross_layer, m_cross_layer</t>
@@ -1144,6 +1138,12 @@
   </si>
   <si>
     <t>0,0.20,  0.23, 0.20, 0.18, 0.25, 0.25</t>
+  </si>
+  <si>
+    <t>f: ExponNormal(2.041,14.862,1.245), m: ExponNormal(1.792,14.600,1.455)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natsal 3 (see analysis code in GitHub)                </t>
   </si>
 </sst>
 </file>
@@ -2566,6 +2566,129 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2590,12 +2713,6 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2611,90 +2728,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2704,7 +2737,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2716,33 +2755,84 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2757,96 +2847,6 @@
     </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3272,11 +3272,11 @@
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="218" t="s">
+      <c r="B4" s="199" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="218"/>
-      <c r="D4" s="218"/>
+      <c r="C4" s="199"/>
+      <c r="D4" s="199"/>
     </row>
     <row r="5" spans="2:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="13" t="s">
@@ -3286,18 +3286,18 @@
         <v>3</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="48" t="s">
         <v>177</v>
-      </c>
-      <c r="C6" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="43" customHeight="1" x14ac:dyDescent="0.2">
@@ -3311,69 +3311,69 @@
     </row>
     <row r="8" spans="2:4" ht="98" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="68" x14ac:dyDescent="0.2">
       <c r="B10" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="34" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="219" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" s="219"/>
-      <c r="D13" s="219"/>
+      <c r="B13" s="200" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="200"/>
+      <c r="D13" s="200"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="219"/>
-      <c r="C14" s="219"/>
-      <c r="D14" s="219"/>
+      <c r="B14" s="200"/>
+      <c r="C14" s="200"/>
+      <c r="D14" s="200"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="219"/>
-      <c r="C15" s="219"/>
-      <c r="D15" s="219"/>
+      <c r="B15" s="200"/>
+      <c r="C15" s="200"/>
+      <c r="D15" s="200"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="219"/>
-      <c r="C16" s="219"/>
-      <c r="D16" s="219"/>
+      <c r="B16" s="200"/>
+      <c r="C16" s="200"/>
+      <c r="D16" s="200"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3400,229 +3400,229 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="222" t="s">
-        <v>237</v>
-      </c>
-      <c r="C3" s="222"/>
-      <c r="D3" s="222"/>
-      <c r="E3" s="222"/>
-      <c r="F3" s="222"/>
+      <c r="B3" s="203" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" s="203"/>
+      <c r="D3" s="203"/>
+      <c r="E3" s="203"/>
+      <c r="F3" s="203"/>
     </row>
     <row r="5" spans="2:6" ht="35" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" s="54" t="s">
+        <v>197</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="B6" s="205" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="56" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="F6" s="49"/>
+    </row>
+    <row r="7" spans="2:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="B7" s="206"/>
+      <c r="C7" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="D7" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>199</v>
+      </c>
+      <c r="F7" s="50"/>
+    </row>
+    <row r="8" spans="2:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="B8" s="206"/>
+      <c r="C8" s="63" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="F8" s="50"/>
+    </row>
+    <row r="9" spans="2:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="B9" s="206"/>
+      <c r="C9" s="63" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="50"/>
+    </row>
+    <row r="10" spans="2:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="B10" s="207" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="58" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>202</v>
+      </c>
+      <c r="F10" s="51" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="B11" s="207"/>
+      <c r="C11" s="64" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="B12" s="207"/>
+      <c r="C12" s="64" t="s">
+        <v>194</v>
+      </c>
+      <c r="D12" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>203</v>
+      </c>
+      <c r="F12" s="51" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="B13" s="208" t="s">
         <v>180</v>
       </c>
-      <c r="C5" s="61" t="s">
-        <v>184</v>
-      </c>
-      <c r="D5" s="55" t="s">
-        <v>190</v>
-      </c>
-      <c r="E5" s="54" t="s">
-        <v>199</v>
-      </c>
-      <c r="F5" s="54" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B6" s="224" t="s">
-        <v>185</v>
-      </c>
-      <c r="C6" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="D6" s="56" t="s">
-        <v>191</v>
-      </c>
-      <c r="E6" s="49" t="s">
-        <v>200</v>
-      </c>
-      <c r="F6" s="49"/>
-    </row>
-    <row r="7" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" s="225"/>
-      <c r="C7" s="63" t="s">
-        <v>187</v>
-      </c>
-      <c r="D7" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" s="50" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="50"/>
-    </row>
-    <row r="8" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B8" s="225"/>
-      <c r="C8" s="63" t="s">
-        <v>188</v>
-      </c>
-      <c r="D8" s="57" t="s">
-        <v>192</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="F8" s="50"/>
-    </row>
-    <row r="9" spans="2:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="B9" s="225"/>
-      <c r="C9" s="63" t="s">
-        <v>189</v>
-      </c>
-      <c r="D9" s="57" t="s">
-        <v>194</v>
-      </c>
-      <c r="E9" s="50" t="s">
-        <v>203</v>
-      </c>
-      <c r="F9" s="50"/>
-    </row>
-    <row r="10" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B10" s="226" t="s">
+      <c r="C13" s="65" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="E13" s="52" t="s">
+        <v>205</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="B14" s="208"/>
+      <c r="C14" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="59" t="s">
+        <v>217</v>
+      </c>
+      <c r="E14" s="52" t="s">
+        <v>219</v>
+      </c>
+      <c r="F14" s="52" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="B15" s="208"/>
+      <c r="C15" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="59" t="s">
+        <v>218</v>
+      </c>
+      <c r="E15" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="F15" s="52" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="B16" s="209" t="s">
         <v>181</v>
       </c>
-      <c r="C10" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="D10" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="E10" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B11" s="226"/>
-      <c r="C11" s="64" t="s">
-        <v>195</v>
-      </c>
-      <c r="D11" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="E11" s="51" t="s">
-        <v>206</v>
-      </c>
-      <c r="F11" s="51" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B12" s="226"/>
-      <c r="C12" s="64" t="s">
+      <c r="C16" s="66" t="s">
         <v>196</v>
       </c>
-      <c r="D12" s="58" t="s">
-        <v>217</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>205</v>
-      </c>
-      <c r="F12" s="51" t="s">
+      <c r="D16" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="E16" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="F16" s="53"/>
+    </row>
+    <row r="17" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B17" s="209"/>
+      <c r="C17" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="D17" s="60" t="s">
+        <v>211</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>208</v>
+      </c>
+      <c r="F17" s="53" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B13" s="227" t="s">
-        <v>182</v>
-      </c>
-      <c r="C13" s="65" t="s">
-        <v>140</v>
-      </c>
-      <c r="D13" s="59" t="s">
-        <v>218</v>
-      </c>
-      <c r="E13" s="52" t="s">
-        <v>207</v>
-      </c>
-      <c r="F13" s="52" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B14" s="227"/>
-      <c r="C14" s="65" t="s">
+    <row r="18" spans="2:11" ht="135" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="209"/>
+      <c r="C18" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="D14" s="59" t="s">
-        <v>219</v>
-      </c>
-      <c r="E14" s="52" t="s">
-        <v>221</v>
-      </c>
-      <c r="F14" s="52" t="s">
+      <c r="D18" s="60" t="s">
+        <v>240</v>
+      </c>
+      <c r="E18" s="53" t="s">
+        <v>209</v>
+      </c>
+      <c r="F18" s="77" t="s">
+        <v>241</v>
+      </c>
+      <c r="G18" s="76" t="s">
         <v>236</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B15" s="227"/>
-      <c r="C15" s="65" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15" s="59" t="s">
-        <v>220</v>
-      </c>
-      <c r="E15" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="F15" s="52" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B16" s="228" t="s">
-        <v>183</v>
-      </c>
-      <c r="C16" s="66" t="s">
-        <v>198</v>
-      </c>
-      <c r="D16" s="60" t="s">
-        <v>212</v>
-      </c>
-      <c r="E16" s="53" t="s">
-        <v>209</v>
-      </c>
-      <c r="F16" s="53"/>
-    </row>
-    <row r="17" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B17" s="228"/>
-      <c r="C17" s="66" t="s">
-        <v>141</v>
-      </c>
-      <c r="D17" s="60" t="s">
-        <v>213</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>210</v>
-      </c>
-      <c r="F17" s="53" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" ht="135" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="228"/>
-      <c r="C18" s="66" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="60" t="s">
-        <v>242</v>
-      </c>
-      <c r="E18" s="53" t="s">
-        <v>211</v>
-      </c>
-      <c r="F18" s="77" t="s">
-        <v>243</v>
-      </c>
-      <c r="G18" s="76" t="s">
-        <v>238</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -3630,64 +3630,64 @@
       <c r="K18" s="5"/>
     </row>
     <row r="19" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B19" s="228"/>
+      <c r="B19" s="209"/>
       <c r="C19" s="66" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D19" s="60" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F19" s="53"/>
     </row>
     <row r="21" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
+        <v>220</v>
+      </c>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="B22" s="210" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="72" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" s="201" t="s">
         <v>222</v>
       </c>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B22" s="229" t="s">
-        <v>140</v>
-      </c>
-      <c r="C22" s="72" t="s">
-        <v>124</v>
-      </c>
-      <c r="D22" s="220" t="s">
+      <c r="E22" s="202"/>
+    </row>
+    <row r="23" spans="2:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="211"/>
+      <c r="C23" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23" s="203" t="s">
         <v>224</v>
       </c>
-      <c r="E22" s="221"/>
-    </row>
-    <row r="23" spans="2:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="230"/>
-      <c r="C23" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="D23" s="222" t="s">
-        <v>226</v>
-      </c>
-      <c r="E23" s="223"/>
+      <c r="E23" s="204"/>
       <c r="F23" s="5"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="230"/>
+      <c r="B24" s="211"/>
       <c r="C24" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D24" s="74" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E24" s="75"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B25" s="68"/>
       <c r="C25" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E25" s="67"/>
       <c r="F25" s="5"/>
@@ -3695,10 +3695,10 @@
     <row r="26" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="69"/>
       <c r="C26" s="73" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D26" s="70" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E26" s="71"/>
     </row>
@@ -3742,29 +3742,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="B2" s="188" t="s">
+      <c r="B2" s="229" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="192" t="s">
+      <c r="C2" s="233" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="200" t="s">
+      <c r="D2" s="239" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="201"/>
-      <c r="F2" s="202" t="s">
+      <c r="E2" s="240"/>
+      <c r="F2" s="241" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="202"/>
-      <c r="H2" s="202"/>
-      <c r="I2" s="201"/>
-      <c r="J2" s="190" t="s">
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="240"/>
+      <c r="J2" s="231" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="189"/>
-      <c r="C3" s="193"/>
+      <c r="B3" s="230"/>
+      <c r="C3" s="234"/>
       <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
@@ -3783,11 +3783,11 @@
       <c r="I3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="191"/>
+      <c r="J3" s="232"/>
     </row>
     <row r="4" spans="1:10" s="83" customFormat="1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="204" t="s">
-        <v>93</v>
+      <c r="A4" s="224" t="s">
+        <v>91</v>
       </c>
       <c r="B4" s="78" t="s">
         <v>16</v>
@@ -3799,7 +3799,7 @@
         <v>200000</v>
       </c>
       <c r="E4" s="78" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F4" s="81"/>
       <c r="G4" s="82"/>
@@ -3810,7 +3810,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" s="83" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A5" s="204"/>
+      <c r="A5" s="224"/>
       <c r="B5" s="84" t="s">
         <v>18</v>
       </c>
@@ -3828,11 +3828,11 @@
       <c r="H5" s="87"/>
       <c r="I5" s="84"/>
       <c r="J5" s="86" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="83" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A6" s="204"/>
+      <c r="A6" s="224"/>
       <c r="B6" s="84" t="s">
         <v>22</v>
       </c>
@@ -3852,18 +3852,18 @@
       <c r="J6" s="86"/>
     </row>
     <row r="7" spans="1:10" s="83" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="204"/>
+      <c r="A7" s="224"/>
       <c r="B7" s="84" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7" s="85" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D7" s="86">
         <v>20</v>
       </c>
       <c r="E7" s="84" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F7" s="86"/>
       <c r="G7" s="87"/>
@@ -3872,7 +3872,7 @@
       <c r="J7" s="86"/>
     </row>
     <row r="8" spans="1:10" s="83" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A8" s="204"/>
+      <c r="A8" s="224"/>
       <c r="B8" s="84" t="s">
         <v>23</v>
       </c>
@@ -3893,7 +3893,7 @@
     </row>
     <row r="9" spans="1:10" s="98" customFormat="1" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="92" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B9" s="93" t="s">
         <v>29</v>
@@ -3916,66 +3916,66 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="104" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A10" s="205" t="s">
-        <v>95</v>
+      <c r="A10" s="225" t="s">
+        <v>93</v>
       </c>
       <c r="B10" s="99" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="100" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="101" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="99" t="s">
         <v>39</v>
-      </c>
-      <c r="D10" s="101" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="99" t="s">
-        <v>40</v>
       </c>
       <c r="F10" s="102"/>
       <c r="G10" s="103"/>
       <c r="H10" s="103"/>
       <c r="I10" s="99"/>
       <c r="J10" s="102" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="104" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="205"/>
-      <c r="B11" s="196" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="194" t="s">
-        <v>43</v>
+      <c r="A11" s="225"/>
+      <c r="B11" s="227" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="235" t="s">
+        <v>42</v>
       </c>
       <c r="D11" s="102" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="E11" s="196" t="s">
-        <v>244</v>
+      <c r="E11" s="227" t="s">
+        <v>242</v>
       </c>
       <c r="F11" s="102"/>
       <c r="G11" s="103"/>
       <c r="H11" s="103"/>
       <c r="I11" s="99"/>
-      <c r="J11" s="198"/>
+      <c r="J11" s="237"/>
     </row>
     <row r="12" spans="1:10" s="104" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="205"/>
-      <c r="B12" s="197"/>
-      <c r="C12" s="195"/>
+      <c r="A12" s="225"/>
+      <c r="B12" s="228"/>
+      <c r="C12" s="236"/>
       <c r="D12" s="102" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="E12" s="197"/>
+      <c r="E12" s="228"/>
       <c r="F12" s="102"/>
       <c r="G12" s="103"/>
       <c r="H12" s="103"/>
       <c r="I12" s="99"/>
-      <c r="J12" s="199"/>
-    </row>
-    <row r="13" spans="1:10" s="109" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A13" s="206" t="s">
-        <v>96</v>
+      <c r="J12" s="238"/>
+    </row>
+    <row r="13" spans="1:10" s="109" customFormat="1" ht="105" x14ac:dyDescent="0.2">
+      <c r="A13" s="226" t="s">
+        <v>94</v>
       </c>
       <c r="B13" s="105" t="s">
         <v>34</v>
@@ -3984,10 +3984,10 @@
         <v>35</v>
       </c>
       <c r="D13" s="107" t="s">
-        <v>36</v>
+        <v>325</v>
       </c>
       <c r="E13" s="105" t="s">
-        <v>59</v>
+        <v>326</v>
       </c>
       <c r="F13" s="107"/>
       <c r="G13" s="108"/>
@@ -3996,40 +3996,40 @@
       <c r="J13" s="107"/>
     </row>
     <row r="14" spans="1:10" s="109" customFormat="1" ht="188" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="206"/>
+      <c r="A14" s="226"/>
       <c r="B14" s="105" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="106" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="105" t="s">
         <v>45</v>
-      </c>
-      <c r="D14" s="107" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="105" t="s">
-        <v>46</v>
       </c>
       <c r="F14" s="107"/>
       <c r="G14" s="108"/>
       <c r="H14" s="108"/>
       <c r="I14" s="105"/>
       <c r="J14" s="107" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="109" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A15" s="226"/>
+      <c r="B15" s="105" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" s="109" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="206"/>
-      <c r="B15" s="105" t="s">
+      <c r="C15" s="106" t="s">
         <v>48</v>
-      </c>
-      <c r="C15" s="106" t="s">
-        <v>49</v>
       </c>
       <c r="D15" s="107">
         <v>0.5</v>
       </c>
       <c r="E15" s="105" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F15" s="107"/>
       <c r="G15" s="108"/>
@@ -4038,40 +4038,40 @@
       <c r="J15" s="107"/>
     </row>
     <row r="16" spans="1:10" s="109" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A16" s="206"/>
+      <c r="A16" s="226"/>
       <c r="B16" s="105" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="106" t="s">
         <v>51</v>
-      </c>
-      <c r="C16" s="106" t="s">
-        <v>52</v>
       </c>
       <c r="D16" s="107">
         <v>1</v>
       </c>
       <c r="E16" s="105" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F16" s="107"/>
       <c r="G16" s="108"/>
       <c r="H16" s="108"/>
       <c r="I16" s="105"/>
       <c r="J16" s="107" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="109" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A17" s="226"/>
+      <c r="B17" s="105" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" s="109" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="206"/>
-      <c r="B17" s="105" t="s">
+      <c r="C17" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="106" t="s">
+      <c r="D17" s="107" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="107" t="s">
+      <c r="E17" s="105" t="s">
         <v>57</v>
-      </c>
-      <c r="E17" s="105" t="s">
-        <v>58</v>
       </c>
       <c r="F17" s="107"/>
       <c r="G17" s="108"/>
@@ -4080,17 +4080,17 @@
       <c r="J17" s="107"/>
     </row>
     <row r="18" spans="1:10" s="109" customFormat="1" ht="120" x14ac:dyDescent="0.2">
-      <c r="A18" s="206"/>
+      <c r="A18" s="226"/>
       <c r="B18" s="105" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C18" s="106" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D18" s="107"/>
       <c r="E18" s="105"/>
       <c r="F18" s="107" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G18" s="108">
         <v>0</v>
@@ -4099,17 +4099,17 @@
         <v>1</v>
       </c>
       <c r="I18" s="105" t="s">
+        <v>61</v>
+      </c>
+      <c r="J18" s="107"/>
+    </row>
+    <row r="19" spans="1:10" s="109" customFormat="1" ht="105" x14ac:dyDescent="0.2">
+      <c r="A19" s="226"/>
+      <c r="B19" s="105" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="106" t="s">
         <v>63</v>
-      </c>
-      <c r="J18" s="107"/>
-    </row>
-    <row r="19" spans="1:10" s="109" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A19" s="206"/>
-      <c r="B19" s="105" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="106" t="s">
-        <v>65</v>
       </c>
       <c r="D19" s="107"/>
       <c r="E19" s="105"/>
@@ -4123,23 +4123,23 @@
         <v>0.5</v>
       </c>
       <c r="I19" s="105" t="s">
+        <v>64</v>
+      </c>
+      <c r="J19" s="107"/>
+    </row>
+    <row r="20" spans="1:10" s="109" customFormat="1" ht="115" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="226"/>
+      <c r="B20" s="105" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="110" t="s">
         <v>66</v>
       </c>
-      <c r="J19" s="107"/>
-    </row>
-    <row r="20" spans="1:10" s="109" customFormat="1" ht="115" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="206"/>
-      <c r="B20" s="105" t="s">
+      <c r="D20" s="107" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="107" t="s">
-        <v>69</v>
-      </c>
       <c r="E20" s="105" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F20" s="107"/>
       <c r="G20" s="108"/>
@@ -4148,100 +4148,100 @@
       <c r="J20" s="111"/>
     </row>
     <row r="21" spans="1:10" s="109" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="206"/>
+      <c r="A21" s="226"/>
       <c r="B21" s="112" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" s="210" t="s">
-        <v>106</v>
+        <v>101</v>
+      </c>
+      <c r="C21" s="215" t="s">
+        <v>104</v>
       </c>
       <c r="D21" s="111" t="s">
-        <v>173</v>
-      </c>
-      <c r="E21" s="207" t="s">
-        <v>107</v>
+        <v>171</v>
+      </c>
+      <c r="E21" s="212" t="s">
+        <v>105</v>
       </c>
       <c r="F21" s="113"/>
       <c r="G21" s="114"/>
       <c r="H21" s="114"/>
-      <c r="I21" s="207" t="s">
-        <v>175</v>
-      </c>
-      <c r="J21" s="213" t="s">
-        <v>245</v>
+      <c r="I21" s="212" t="s">
+        <v>173</v>
+      </c>
+      <c r="J21" s="218" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="109" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="206"/>
+      <c r="A22" s="226"/>
       <c r="B22" s="115" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22" s="211"/>
+        <v>103</v>
+      </c>
+      <c r="C22" s="216"/>
       <c r="D22" s="114" t="s">
-        <v>174</v>
-      </c>
-      <c r="E22" s="208"/>
+        <v>172</v>
+      </c>
+      <c r="E22" s="213"/>
       <c r="F22" s="111"/>
       <c r="G22" s="107"/>
       <c r="H22" s="107"/>
-      <c r="I22" s="208"/>
-      <c r="J22" s="214"/>
+      <c r="I22" s="213"/>
+      <c r="J22" s="219"/>
     </row>
     <row r="23" spans="1:10" s="109" customFormat="1" ht="180" x14ac:dyDescent="0.2">
-      <c r="A23" s="206"/>
+      <c r="A23" s="226"/>
       <c r="B23" s="105" t="s">
-        <v>104</v>
-      </c>
-      <c r="C23" s="212"/>
+        <v>102</v>
+      </c>
+      <c r="C23" s="217"/>
       <c r="D23" s="111" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E23" s="112" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F23" s="187"/>
       <c r="G23" s="107"/>
       <c r="H23" s="107"/>
-      <c r="I23" s="209"/>
-      <c r="J23" s="215"/>
+      <c r="I23" s="214"/>
+      <c r="J23" s="220"/>
     </row>
     <row r="24" spans="1:10" s="109" customFormat="1" ht="255" x14ac:dyDescent="0.2">
       <c r="A24" s="185"/>
       <c r="B24" s="105" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C24" s="106" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="107" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="107" t="s">
-        <v>101</v>
-      </c>
       <c r="E24" s="105" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F24" s="107"/>
       <c r="G24" s="108"/>
       <c r="H24" s="108"/>
       <c r="I24" s="105"/>
       <c r="J24" s="107" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="91" customFormat="1" ht="73" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="126" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B25" s="88" t="s">
+        <v>237</v>
+      </c>
+      <c r="C25" s="127" t="s">
         <v>239</v>
       </c>
-      <c r="C25" s="127" t="s">
-        <v>241</v>
-      </c>
       <c r="D25" s="90">
         <v>0</v>
       </c>
       <c r="E25" s="89" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F25" s="90"/>
       <c r="G25" s="90"/>
@@ -4251,16 +4251,16 @@
     </row>
     <row r="26" spans="1:10" s="119" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="186" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B26" s="116" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="121" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="117" t="s">
         <v>70</v>
-      </c>
-      <c r="C26" s="121" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" s="117" t="s">
-        <v>72</v>
       </c>
       <c r="E26" s="116"/>
       <c r="F26" s="117"/>
@@ -4268,16 +4268,16 @@
       <c r="H26" s="122"/>
       <c r="I26" s="116"/>
       <c r="J26" s="123" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="119" customFormat="1" ht="45" x14ac:dyDescent="0.2">
       <c r="A27" s="186"/>
       <c r="B27" s="116" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C27" s="124" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D27" s="117"/>
       <c r="E27" s="116"/>
@@ -4291,25 +4291,25 @@
         <v>1</v>
       </c>
       <c r="I27" s="116" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J27" s="123" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="119" customFormat="1" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="186"/>
       <c r="B28" s="116" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="125" t="s">
         <v>89</v>
-      </c>
-      <c r="C28" s="125" t="s">
-        <v>91</v>
       </c>
       <c r="D28" s="117">
         <v>50</v>
       </c>
       <c r="E28" s="116" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F28" s="117"/>
       <c r="G28" s="122"/>
@@ -4320,16 +4320,16 @@
     <row r="29" spans="1:10" s="119" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="186"/>
       <c r="B29" s="116" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="125" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="117">
+        <v>0</v>
+      </c>
+      <c r="E29" s="116" t="s">
         <v>90</v>
-      </c>
-      <c r="C29" s="125" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="117">
-        <v>0</v>
-      </c>
-      <c r="E29" s="116" t="s">
-        <v>92</v>
       </c>
       <c r="F29" s="117"/>
       <c r="G29" s="122"/>
@@ -4340,10 +4340,10 @@
     <row r="30" spans="1:10" s="119" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="186"/>
       <c r="B30" s="116" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C30" s="125" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D30" s="117"/>
       <c r="E30" s="116"/>
@@ -4357,25 +4357,25 @@
         <v>12</v>
       </c>
       <c r="I30" s="116" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J30" s="117" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="119" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="186"/>
       <c r="B31" s="116" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C31" s="125" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D31" s="117">
         <v>20</v>
       </c>
       <c r="E31" s="116" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F31" s="117"/>
       <c r="G31" s="122"/>
@@ -4386,19 +4386,19 @@
     <row r="32" spans="1:10" s="119" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A32" s="186"/>
       <c r="B32" s="116" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="118" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="117" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="118" t="s">
+      <c r="E32" s="116" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="117" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" s="116" t="s">
+      <c r="F32" s="117" t="s">
         <v>78</v>
-      </c>
-      <c r="F32" s="117" t="s">
-        <v>80</v>
       </c>
       <c r="G32" s="122">
         <v>0</v>
@@ -4407,66 +4407,56 @@
         <v>1</v>
       </c>
       <c r="I32" s="116" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J32" s="117"/>
     </row>
     <row r="33" spans="1:10" s="134" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="203" t="s">
-        <v>249</v>
+      <c r="A33" s="223" t="s">
+        <v>247</v>
       </c>
       <c r="B33" s="130" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C33" s="131" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D33" s="132" t="b">
         <v>0</v>
       </c>
       <c r="E33" s="130" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F33" s="132"/>
       <c r="G33" s="133"/>
       <c r="H33" s="133"/>
       <c r="I33" s="130"/>
-      <c r="J33" s="216" t="s">
-        <v>248</v>
+      <c r="J33" s="221" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="134" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A34" s="203"/>
+      <c r="A34" s="223"/>
       <c r="B34" s="130" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" s="131" t="s">
         <v>114</v>
       </c>
-      <c r="C34" s="131" t="s">
-        <v>116</v>
-      </c>
       <c r="D34" s="132" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E34" s="130" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F34" s="132"/>
       <c r="G34" s="133"/>
       <c r="H34" s="133"/>
       <c r="I34" s="130"/>
-      <c r="J34" s="217"/>
+      <c r="J34" s="222"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="J21:J23"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B11:B12"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="C2:C3"/>
@@ -4475,6 +4465,16 @@
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="J21:J23"/>
+    <mergeCell ref="J33:J34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -4491,2553 +4491,2553 @@
   <sheetData>
     <row r="1" spans="1:8" s="12" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="32" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E2" s="38">
         <v>0.12</v>
       </c>
-      <c r="H2" s="231" t="s">
-        <v>322</v>
+      <c r="H2" s="242" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E3" s="41">
         <v>0.88</v>
       </c>
-      <c r="H3" s="231"/>
+      <c r="H3" s="242"/>
     </row>
     <row r="4" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E4" s="41">
         <v>0</v>
       </c>
-      <c r="H4" s="231"/>
+      <c r="H4" s="242"/>
     </row>
     <row r="5" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C5" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="35" t="s">
         <v>131</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>133</v>
       </c>
       <c r="E5" s="38">
         <v>0.12</v>
       </c>
-      <c r="H5" s="231"/>
+      <c r="H5" s="242"/>
     </row>
     <row r="6" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E6" s="41">
         <v>0.88</v>
       </c>
-      <c r="H6" s="231"/>
+      <c r="H6" s="242"/>
     </row>
     <row r="7" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E7" s="41">
         <v>0</v>
       </c>
-      <c r="H7" s="231"/>
+      <c r="H7" s="242"/>
     </row>
     <row r="8" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E8" s="38">
         <v>0.12</v>
       </c>
-      <c r="H8" s="231"/>
+      <c r="H8" s="242"/>
     </row>
     <row r="9" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E9" s="41">
         <v>0.88</v>
       </c>
-      <c r="H9" s="231"/>
+      <c r="H9" s="242"/>
     </row>
     <row r="10" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E10" s="41">
         <v>0</v>
       </c>
-      <c r="H10" s="231"/>
+      <c r="H10" s="242"/>
     </row>
     <row r="11" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E11" s="38">
         <v>0.12</v>
       </c>
-      <c r="H11" s="231"/>
+      <c r="H11" s="242"/>
     </row>
     <row r="12" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E12" s="41">
         <v>0.88</v>
       </c>
-      <c r="H12" s="231"/>
+      <c r="H12" s="242"/>
     </row>
     <row r="13" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E13" s="41">
         <v>0</v>
       </c>
-      <c r="H13" s="231"/>
+      <c r="H13" s="242"/>
     </row>
     <row r="14" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E14" s="38">
         <v>0.12</v>
       </c>
-      <c r="H14" s="231"/>
+      <c r="H14" s="242"/>
     </row>
     <row r="15" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E15" s="41">
         <v>0.88</v>
       </c>
-      <c r="H15" s="231"/>
+      <c r="H15" s="242"/>
     </row>
     <row r="16" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E16" s="41">
         <v>0</v>
       </c>
-      <c r="H16" s="231"/>
+      <c r="H16" s="242"/>
     </row>
     <row r="17" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B17" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="40" t="s">
-        <v>126</v>
-      </c>
       <c r="D17" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E17" s="38">
         <v>0.12</v>
       </c>
-      <c r="H17" s="231"/>
+      <c r="H17" s="242"/>
     </row>
     <row r="18" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B18" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="40" t="s">
-        <v>126</v>
-      </c>
       <c r="D18" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E18" s="41">
         <v>0.88</v>
       </c>
-      <c r="H18" s="231"/>
+      <c r="H18" s="242"/>
     </row>
     <row r="19" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B19" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="C19" s="40" t="s">
-        <v>126</v>
-      </c>
       <c r="D19" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E19" s="41">
         <v>0</v>
       </c>
-      <c r="H19" s="231"/>
+      <c r="H19" s="242"/>
     </row>
     <row r="20" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E20" s="38">
         <v>0.12</v>
       </c>
-      <c r="H20" s="231"/>
+      <c r="H20" s="242"/>
     </row>
     <row r="21" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D21" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E21" s="41">
         <v>0.88</v>
       </c>
-      <c r="H21" s="231"/>
+      <c r="H21" s="242"/>
     </row>
     <row r="22" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B22" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="C22" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="D22" s="35" t="s">
-        <v>125</v>
-      </c>
       <c r="E22" s="41">
         <v>0</v>
       </c>
-      <c r="H22" s="231"/>
+      <c r="H22" s="242"/>
     </row>
     <row r="23" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C23" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" s="35" t="s">
         <v>131</v>
-      </c>
-      <c r="D23" s="35" t="s">
-        <v>133</v>
       </c>
       <c r="E23" s="38">
         <v>0.12</v>
       </c>
-      <c r="H23" s="231"/>
+      <c r="H23" s="242"/>
     </row>
     <row r="24" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D24" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E24" s="41">
         <v>0.88</v>
       </c>
-      <c r="H24" s="231"/>
+      <c r="H24" s="242"/>
     </row>
     <row r="25" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B25" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="D25" s="35" t="s">
-        <v>125</v>
-      </c>
       <c r="E25" s="41">
         <v>0</v>
       </c>
-      <c r="H25" s="231"/>
+      <c r="H25" s="242"/>
     </row>
     <row r="26" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E26" s="38">
         <v>0.12</v>
       </c>
-      <c r="H26" s="231"/>
+      <c r="H26" s="242"/>
     </row>
     <row r="27" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D27" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E27" s="41">
         <v>0.88</v>
       </c>
-      <c r="H27" s="231"/>
+      <c r="H27" s="242"/>
     </row>
     <row r="28" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B28" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="C28" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="D28" s="35" t="s">
-        <v>125</v>
-      </c>
       <c r="E28" s="41">
         <v>0</v>
       </c>
-      <c r="H28" s="231"/>
+      <c r="H28" s="242"/>
     </row>
     <row r="29" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D29" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E29" s="38">
         <v>0.12</v>
       </c>
-      <c r="H29" s="231"/>
+      <c r="H29" s="242"/>
     </row>
     <row r="30" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D30" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E30" s="41">
         <v>0.88</v>
       </c>
-      <c r="H30" s="231"/>
+      <c r="H30" s="242"/>
     </row>
     <row r="31" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B31" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="D31" s="35" t="s">
-        <v>125</v>
-      </c>
       <c r="E31" s="41">
         <v>0</v>
       </c>
-      <c r="H31" s="231"/>
+      <c r="H31" s="242"/>
     </row>
     <row r="32" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D32" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E32" s="38">
         <v>0.12</v>
       </c>
-      <c r="H32" s="231"/>
+      <c r="H32" s="242"/>
     </row>
     <row r="33" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D33" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E33" s="41">
         <v>0.88</v>
       </c>
-      <c r="H33" s="231"/>
+      <c r="H33" s="242"/>
     </row>
     <row r="34" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B34" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="C34" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="D34" s="35" t="s">
-        <v>125</v>
-      </c>
       <c r="E34" s="41">
         <v>0</v>
       </c>
-      <c r="H34" s="231"/>
+      <c r="H34" s="242"/>
     </row>
     <row r="35" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C35" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D35" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E35" s="38">
         <v>0.12</v>
       </c>
-      <c r="H35" s="231"/>
+      <c r="H35" s="242"/>
     </row>
     <row r="36" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D36" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E36" s="41">
         <v>0.88</v>
       </c>
-      <c r="H36" s="231"/>
+      <c r="H36" s="242"/>
     </row>
     <row r="37" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B37" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C37" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="C37" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="D37" s="35" t="s">
-        <v>125</v>
-      </c>
       <c r="E37" s="41">
         <v>0</v>
       </c>
-      <c r="H37" s="231"/>
+      <c r="H37" s="242"/>
     </row>
     <row r="38" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C38" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D38" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E38" s="41">
         <v>0.94</v>
       </c>
-      <c r="H38" s="231"/>
+      <c r="H38" s="242"/>
     </row>
     <row r="39" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C39" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D39" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E39" s="41">
         <v>0.06</v>
       </c>
-      <c r="H39" s="231"/>
+      <c r="H39" s="242"/>
     </row>
     <row r="40" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C40" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D40" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E40" s="41">
         <v>0</v>
       </c>
-      <c r="H40" s="231"/>
+      <c r="H40" s="242"/>
     </row>
     <row r="41" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C41" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D41" s="35" t="s">
         <v>131</v>
-      </c>
-      <c r="D41" s="35" t="s">
-        <v>133</v>
       </c>
       <c r="E41" s="41">
         <v>0.94</v>
       </c>
-      <c r="H41" s="231"/>
+      <c r="H41" s="242"/>
     </row>
     <row r="42" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C42" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E42" s="41">
         <v>0.06</v>
       </c>
-      <c r="H42" s="231"/>
+      <c r="H42" s="242"/>
     </row>
     <row r="43" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C43" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D43" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E43" s="41">
         <v>0</v>
       </c>
-      <c r="H43" s="231"/>
+      <c r="H43" s="242"/>
     </row>
     <row r="44" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C44" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D44" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E44" s="41">
         <v>0.94</v>
       </c>
-      <c r="H44" s="231"/>
+      <c r="H44" s="242"/>
     </row>
     <row r="45" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B45" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C45" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D45" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E45" s="41">
         <v>0.06</v>
       </c>
-      <c r="H45" s="231"/>
+      <c r="H45" s="242"/>
     </row>
     <row r="46" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B46" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C46" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D46" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E46" s="41">
         <v>0</v>
       </c>
-      <c r="H46" s="231"/>
+      <c r="H46" s="242"/>
     </row>
     <row r="47" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B47" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C47" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D47" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E47" s="41">
         <v>0.94</v>
       </c>
-      <c r="H47" s="231"/>
+      <c r="H47" s="242"/>
     </row>
     <row r="48" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B48" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C48" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D48" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E48" s="41">
         <v>0.06</v>
       </c>
-      <c r="H48" s="231"/>
+      <c r="H48" s="242"/>
     </row>
     <row r="49" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B49" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C49" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D49" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E49" s="41">
         <v>0</v>
       </c>
-      <c r="H49" s="231"/>
+      <c r="H49" s="242"/>
     </row>
     <row r="50" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C50" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D50" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E50" s="41">
         <v>0.94</v>
       </c>
-      <c r="H50" s="231"/>
+      <c r="H50" s="242"/>
     </row>
     <row r="51" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C51" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D51" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E51" s="41">
         <v>0.06</v>
       </c>
-      <c r="H51" s="231"/>
+      <c r="H51" s="242"/>
     </row>
     <row r="52" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B52" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C52" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D52" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E52" s="41">
         <v>0</v>
       </c>
-      <c r="H52" s="231"/>
+      <c r="H52" s="242"/>
     </row>
     <row r="53" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B53" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C53" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D53" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E53" s="41">
         <v>0.94</v>
       </c>
-      <c r="H53" s="231"/>
+      <c r="H53" s="242"/>
     </row>
     <row r="54" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B54" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C54" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D54" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E54" s="41">
         <v>0.06</v>
       </c>
-      <c r="H54" s="231"/>
+      <c r="H54" s="242"/>
     </row>
     <row r="55" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B55" s="39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C55" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D55" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E55" s="41">
         <v>0</v>
       </c>
-      <c r="H55" s="231"/>
+      <c r="H55" s="242"/>
     </row>
     <row r="56" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B56" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C56" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D56" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E56" s="41">
         <v>0.94</v>
       </c>
-      <c r="H56" s="231"/>
+      <c r="H56" s="242"/>
     </row>
     <row r="57" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B57" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C57" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D57" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E57" s="41">
         <v>0.06</v>
       </c>
-      <c r="H57" s="231"/>
+      <c r="H57" s="242"/>
     </row>
     <row r="58" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B58" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C58" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D58" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E58" s="41">
         <v>0</v>
       </c>
-      <c r="H58" s="231"/>
+      <c r="H58" s="242"/>
     </row>
     <row r="59" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B59" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C59" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D59" s="35" t="s">
         <v>131</v>
-      </c>
-      <c r="D59" s="35" t="s">
-        <v>133</v>
       </c>
       <c r="E59" s="41">
         <v>0.94</v>
       </c>
-      <c r="H59" s="231"/>
+      <c r="H59" s="242"/>
     </row>
     <row r="60" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B60" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C60" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D60" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E60" s="41">
         <v>0.06</v>
       </c>
-      <c r="H60" s="231"/>
+      <c r="H60" s="242"/>
     </row>
     <row r="61" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B61" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C61" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D61" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E61" s="41">
         <v>0</v>
       </c>
-      <c r="H61" s="231"/>
+      <c r="H61" s="242"/>
     </row>
     <row r="62" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B62" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C62" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D62" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E62" s="41">
         <v>0.94</v>
       </c>
-      <c r="H62" s="231"/>
+      <c r="H62" s="242"/>
     </row>
     <row r="63" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B63" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C63" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D63" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E63" s="41">
         <v>0.06</v>
       </c>
-      <c r="H63" s="231"/>
+      <c r="H63" s="242"/>
     </row>
     <row r="64" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B64" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C64" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D64" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E64" s="41">
         <v>0</v>
       </c>
-      <c r="H64" s="231"/>
+      <c r="H64" s="242"/>
     </row>
     <row r="65" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B65" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C65" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D65" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E65" s="41">
         <v>0.94</v>
       </c>
-      <c r="H65" s="231"/>
+      <c r="H65" s="242"/>
     </row>
     <row r="66" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B66" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C66" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D66" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E66" s="41">
         <v>0.06</v>
       </c>
-      <c r="H66" s="231"/>
+      <c r="H66" s="242"/>
     </row>
     <row r="67" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B67" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C67" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D67" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E67" s="41">
         <v>0</v>
       </c>
-      <c r="H67" s="231"/>
+      <c r="H67" s="242"/>
     </row>
     <row r="68" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B68" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C68" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D68" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E68" s="41">
         <v>0.94</v>
       </c>
-      <c r="H68" s="231"/>
+      <c r="H68" s="242"/>
     </row>
     <row r="69" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B69" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C69" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D69" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E69" s="41">
         <v>0.06</v>
       </c>
-      <c r="H69" s="231"/>
+      <c r="H69" s="242"/>
     </row>
     <row r="70" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B70" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C70" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D70" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E70" s="41">
         <v>0</v>
       </c>
-      <c r="H70" s="231"/>
+      <c r="H70" s="242"/>
     </row>
     <row r="71" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B71" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C71" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D71" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E71" s="41">
         <v>0.94</v>
       </c>
-      <c r="H71" s="231"/>
+      <c r="H71" s="242"/>
     </row>
     <row r="72" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B72" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C72" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D72" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E72" s="41">
         <v>0.06</v>
       </c>
-      <c r="H72" s="231"/>
+      <c r="H72" s="242"/>
     </row>
     <row r="73" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B73" s="39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C73" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D73" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E73" s="41">
         <v>0</v>
       </c>
-      <c r="H73" s="231"/>
+      <c r="H73" s="242"/>
     </row>
     <row r="74" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B74" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C74" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D74" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E74" s="41">
         <v>0.94</v>
       </c>
-      <c r="H74" s="231"/>
+      <c r="H74" s="242"/>
     </row>
     <row r="75" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B75" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C75" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D75" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E75" s="41">
         <v>0.06</v>
       </c>
-      <c r="H75" s="231"/>
+      <c r="H75" s="242"/>
     </row>
     <row r="76" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B76" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C76" s="40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D76" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E76" s="41">
         <v>0</v>
       </c>
-      <c r="H76" s="231"/>
+      <c r="H76" s="242"/>
     </row>
     <row r="77" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B77" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C77" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D77" s="35" t="s">
         <v>131</v>
-      </c>
-      <c r="D77" s="35" t="s">
-        <v>133</v>
       </c>
       <c r="E77" s="41">
         <v>0.94</v>
       </c>
-      <c r="H77" s="231"/>
+      <c r="H77" s="242"/>
     </row>
     <row r="78" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B78" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C78" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D78" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E78" s="41">
         <v>0.06</v>
       </c>
-      <c r="H78" s="231"/>
+      <c r="H78" s="242"/>
     </row>
     <row r="79" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B79" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C79" s="40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D79" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E79" s="41">
         <v>0</v>
       </c>
-      <c r="H79" s="231"/>
+      <c r="H79" s="242"/>
     </row>
     <row r="80" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B80" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C80" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D80" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E80" s="41">
         <v>0.94</v>
       </c>
-      <c r="H80" s="231"/>
+      <c r="H80" s="242"/>
     </row>
     <row r="81" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B81" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C81" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D81" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E81" s="41">
         <v>0.06</v>
       </c>
-      <c r="H81" s="231"/>
+      <c r="H81" s="242"/>
     </row>
     <row r="82" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B82" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C82" s="40" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D82" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E82" s="41">
         <v>0</v>
       </c>
-      <c r="H82" s="231"/>
+      <c r="H82" s="242"/>
     </row>
     <row r="83" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B83" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C83" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D83" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E83" s="41">
         <v>0.94</v>
       </c>
-      <c r="H83" s="231"/>
+      <c r="H83" s="242"/>
     </row>
     <row r="84" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B84" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C84" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D84" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E84" s="41">
         <v>0.06</v>
       </c>
-      <c r="H84" s="231"/>
+      <c r="H84" s="242"/>
     </row>
     <row r="85" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B85" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C85" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D85" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E85" s="41">
         <v>0</v>
       </c>
-      <c r="H85" s="231"/>
+      <c r="H85" s="242"/>
     </row>
     <row r="86" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B86" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C86" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D86" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E86" s="41">
         <v>0.94</v>
       </c>
-      <c r="H86" s="231"/>
+      <c r="H86" s="242"/>
     </row>
     <row r="87" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B87" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C87" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D87" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E87" s="41">
         <v>0.06</v>
       </c>
-      <c r="H87" s="231"/>
+      <c r="H87" s="242"/>
     </row>
     <row r="88" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B88" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C88" s="40" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D88" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E88" s="41">
         <v>0</v>
       </c>
-      <c r="H88" s="231"/>
+      <c r="H88" s="242"/>
     </row>
     <row r="89" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B89" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C89" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D89" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E89" s="41">
         <v>0.94</v>
       </c>
-      <c r="H89" s="231"/>
+      <c r="H89" s="242"/>
     </row>
     <row r="90" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B90" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C90" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D90" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E90" s="41">
         <v>0.06</v>
       </c>
-      <c r="H90" s="231"/>
+      <c r="H90" s="242"/>
     </row>
     <row r="91" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B91" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C91" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D91" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E91" s="41">
         <v>0</v>
       </c>
-      <c r="H91" s="231"/>
+      <c r="H91" s="242"/>
     </row>
     <row r="92" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B92" s="24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D92" s="22" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E92" s="26">
         <v>0.9</v>
       </c>
-      <c r="H92" s="232" t="s">
-        <v>286</v>
+      <c r="H92" s="243" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="93" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A93" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B93" s="24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C93" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D93" s="22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E93" s="26">
         <v>0</v>
       </c>
-      <c r="H93" s="232"/>
+      <c r="H93" s="243"/>
     </row>
     <row r="94" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B94" s="24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D94" s="22" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E94" s="26">
         <v>0.1</v>
       </c>
-      <c r="H94" s="232"/>
+      <c r="H94" s="243"/>
     </row>
     <row r="95" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B95" s="24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D95" s="22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E95" s="26">
         <v>0</v>
       </c>
-      <c r="H95" s="232"/>
+      <c r="H95" s="243"/>
     </row>
     <row r="96" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B96" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C96" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D96" s="22" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E96" s="26">
         <v>0.9</v>
       </c>
-      <c r="H96" s="232"/>
+      <c r="H96" s="243"/>
     </row>
     <row r="97" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B97" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C97" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D97" s="22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E97" s="26">
         <v>0</v>
       </c>
-      <c r="H97" s="232"/>
+      <c r="H97" s="243"/>
     </row>
     <row r="98" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B98" s="24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D98" s="22" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E98" s="26">
         <v>0.1</v>
       </c>
-      <c r="H98" s="232"/>
+      <c r="H98" s="243"/>
     </row>
     <row r="99" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A99" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B99" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="C99" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D99" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="C99" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="D99" s="22" t="s">
-        <v>125</v>
-      </c>
       <c r="E99" s="26">
         <v>0</v>
       </c>
-      <c r="H99" s="232"/>
+      <c r="H99" s="243"/>
     </row>
     <row r="100" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B100" s="24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C100" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D100" s="22" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E100" s="26">
         <v>0.9</v>
       </c>
-      <c r="H100" s="232"/>
+      <c r="H100" s="243"/>
     </row>
     <row r="101" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B101" s="24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C101" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D101" s="22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E101" s="26">
         <v>0</v>
       </c>
-      <c r="H101" s="232"/>
+      <c r="H101" s="243"/>
     </row>
     <row r="102" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A102" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B102" s="24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C102" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D102" s="22" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E102" s="26">
         <v>0.1</v>
       </c>
-      <c r="H102" s="232"/>
+      <c r="H102" s="243"/>
     </row>
     <row r="103" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B103" s="24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C103" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D103" s="22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E103" s="26">
         <v>0</v>
       </c>
-      <c r="H103" s="232"/>
+      <c r="H103" s="243"/>
     </row>
     <row r="104" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B104" s="24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C104" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D104" s="22" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E104" s="26">
         <v>0.15</v>
       </c>
-      <c r="H104" s="232"/>
+      <c r="H104" s="243"/>
     </row>
     <row r="105" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A105" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B105" s="24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C105" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D105" s="22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E105" s="26">
         <v>0</v>
       </c>
-      <c r="H105" s="232"/>
+      <c r="H105" s="243"/>
     </row>
     <row r="106" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B106" s="24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C106" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D106" s="22" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E106" s="26">
         <v>0.85</v>
       </c>
-      <c r="H106" s="232"/>
+      <c r="H106" s="243"/>
     </row>
     <row r="107" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B107" s="24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C107" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D107" s="22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E107" s="26">
         <v>0</v>
       </c>
-      <c r="H107" s="232"/>
+      <c r="H107" s="243"/>
     </row>
     <row r="108" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B108" s="24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C108" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D108" s="22" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E108" s="26">
         <v>0</v>
       </c>
-      <c r="H108" s="232"/>
+      <c r="H108" s="243"/>
     </row>
     <row r="109" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B109" s="24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C109" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D109" s="22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E109" s="26">
         <v>0</v>
       </c>
-      <c r="H109" s="232"/>
+      <c r="H109" s="243"/>
     </row>
     <row r="110" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A110" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B110" s="24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C110" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D110" s="22" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E110" s="26">
         <v>1</v>
       </c>
-      <c r="H110" s="232"/>
+      <c r="H110" s="243"/>
     </row>
     <row r="111" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B111" s="24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C111" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D111" s="22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E111" s="26">
         <v>0</v>
       </c>
-      <c r="H111" s="232"/>
+      <c r="H111" s="243"/>
     </row>
     <row r="112" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C112" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E112" s="15">
         <v>0.7</v>
       </c>
-      <c r="H112" s="233" t="s">
-        <v>324</v>
+      <c r="H112" s="244" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="113" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A113" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C113" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E113" s="15">
         <v>0</v>
       </c>
-      <c r="H113" s="233"/>
+      <c r="H113" s="244"/>
     </row>
     <row r="114" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C114" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E114" s="15">
         <v>0</v>
       </c>
-      <c r="H114" s="233"/>
+      <c r="H114" s="244"/>
     </row>
     <row r="115" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A115" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="C115" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D115" s="16" t="s">
         <v>135</v>
-      </c>
-      <c r="B115" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="C115" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="D115" s="16" t="s">
-        <v>137</v>
       </c>
       <c r="E115" s="15">
         <v>0.3</v>
       </c>
-      <c r="H115" s="233"/>
+      <c r="H115" s="244"/>
     </row>
     <row r="116" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C116" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D116" s="16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E116" s="15">
         <v>0</v>
       </c>
-      <c r="H116" s="233"/>
+      <c r="H116" s="244"/>
     </row>
     <row r="117" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B117" s="19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C117" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D117" s="16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E117" s="15">
         <v>0</v>
       </c>
-      <c r="H117" s="233"/>
+      <c r="H117" s="244"/>
     </row>
     <row r="118" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A118" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C118" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D118" s="16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E118" s="15">
         <v>0.6</v>
       </c>
-      <c r="H118" s="233"/>
+      <c r="H118" s="244"/>
     </row>
     <row r="119" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C119" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D119" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E119" s="15">
         <v>0</v>
       </c>
-      <c r="H119" s="233"/>
+      <c r="H119" s="244"/>
     </row>
     <row r="120" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C120" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E120" s="15">
         <v>0</v>
       </c>
-      <c r="H120" s="233"/>
+      <c r="H120" s="244"/>
     </row>
     <row r="121" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A121" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C121" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D121" s="16" t="s">
         <v>135</v>
-      </c>
-      <c r="B121" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="C121" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="D121" s="16" t="s">
-        <v>137</v>
       </c>
       <c r="E121" s="15">
         <v>0.4</v>
       </c>
-      <c r="H121" s="233"/>
+      <c r="H121" s="244"/>
     </row>
     <row r="122" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C122" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E122" s="15">
         <v>0</v>
       </c>
-      <c r="H122" s="233"/>
+      <c r="H122" s="244"/>
     </row>
     <row r="123" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B123" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C123" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D123" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="C123" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="D123" s="16" t="s">
-        <v>125</v>
-      </c>
       <c r="E123" s="15">
         <v>0</v>
       </c>
-      <c r="H123" s="233"/>
+      <c r="H123" s="244"/>
     </row>
     <row r="124" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B124" s="19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C124" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D124" s="16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E124" s="15">
         <v>0.42</v>
       </c>
-      <c r="H124" s="233"/>
+      <c r="H124" s="244"/>
     </row>
     <row r="125" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B125" s="19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C125" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E125" s="15">
         <v>0</v>
       </c>
-      <c r="H125" s="233"/>
+      <c r="H125" s="244"/>
     </row>
     <row r="126" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B126" s="19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C126" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D126" s="16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E126" s="15">
         <v>0</v>
       </c>
-      <c r="H126" s="233"/>
+      <c r="H126" s="244"/>
     </row>
     <row r="127" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C127" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D127" s="16" t="s">
         <v>135</v>
-      </c>
-      <c r="B127" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="C127" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="D127" s="16" t="s">
-        <v>137</v>
       </c>
       <c r="E127" s="15">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H127" s="233"/>
+      <c r="H127" s="244"/>
     </row>
     <row r="128" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B128" s="19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C128" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E128" s="15">
         <v>0</v>
       </c>
-      <c r="H128" s="233"/>
+      <c r="H128" s="244"/>
     </row>
     <row r="129" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A129" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B129" s="19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C129" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D129" s="16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E129" s="15">
         <v>0</v>
       </c>
-      <c r="H129" s="233"/>
+      <c r="H129" s="244"/>
     </row>
     <row r="130" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B130" s="19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C130" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D130" s="16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E130" s="15">
         <v>0.05</v>
       </c>
-      <c r="H130" s="233"/>
+      <c r="H130" s="244"/>
     </row>
     <row r="131" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A131" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B131" s="19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C131" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E131" s="15">
         <v>0</v>
       </c>
-      <c r="H131" s="233"/>
+      <c r="H131" s="244"/>
     </row>
     <row r="132" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B132" s="19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C132" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E132" s="15">
         <v>0</v>
       </c>
-      <c r="H132" s="233"/>
+      <c r="H132" s="244"/>
     </row>
     <row r="133" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B133" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C133" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D133" s="16" t="s">
         <v>135</v>
-      </c>
-      <c r="B133" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="C133" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="D133" s="16" t="s">
-        <v>137</v>
       </c>
       <c r="E133" s="15">
         <v>0.95</v>
       </c>
-      <c r="H133" s="233"/>
+      <c r="H133" s="244"/>
     </row>
     <row r="134" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A134" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C134" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E134" s="15">
         <v>0</v>
       </c>
-      <c r="H134" s="233"/>
+      <c r="H134" s="244"/>
     </row>
     <row r="135" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B135" s="19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C135" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E135" s="15">
         <v>0</v>
       </c>
-      <c r="H135" s="233"/>
+      <c r="H135" s="244"/>
     </row>
     <row r="136" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A136" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B136" s="19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C136" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D136" s="16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E136" s="15">
         <v>0</v>
       </c>
-      <c r="H136" s="233"/>
+      <c r="H136" s="244"/>
     </row>
     <row r="137" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A137" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B137" s="19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C137" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E137" s="15">
         <v>0</v>
       </c>
-      <c r="H137" s="233"/>
+      <c r="H137" s="244"/>
     </row>
     <row r="138" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A138" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B138" s="19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C138" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D138" s="16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E138" s="15">
         <v>0</v>
       </c>
-      <c r="H138" s="233"/>
+      <c r="H138" s="244"/>
     </row>
     <row r="139" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A139" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B139" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C139" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D139" s="16" t="s">
         <v>135</v>
-      </c>
-      <c r="B139" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="C139" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="D139" s="16" t="s">
-        <v>137</v>
       </c>
       <c r="E139" s="15">
         <v>0.05</v>
       </c>
-      <c r="H139" s="233"/>
+      <c r="H139" s="244"/>
     </row>
     <row r="140" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A140" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B140" s="19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C140" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E140" s="15">
         <v>0.95</v>
       </c>
-      <c r="H140" s="233"/>
+      <c r="H140" s="244"/>
     </row>
     <row r="141" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A141" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B141" s="19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C141" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E141" s="15">
         <v>0</v>
       </c>
-      <c r="H141" s="233"/>
+      <c r="H141" s="244"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D144" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -7060,13 +7060,13 @@
   <sheetData>
     <row r="1" spans="1:5" s="12" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E1" s="73" t="s">
         <v>10</v>
@@ -7074,153 +7074,153 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="32" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C2" s="33">
         <v>0.96499999999999997</v>
       </c>
-      <c r="E2" s="234" t="s">
-        <v>287</v>
+      <c r="E2" s="194" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="34" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C3" s="35">
         <v>0.96499999999999997</v>
       </c>
-      <c r="E3" s="234"/>
+      <c r="E3" s="194"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="34" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C4" s="35">
         <v>0.5</v>
       </c>
-      <c r="E4" s="234"/>
+      <c r="E4" s="194"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="34" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C5" s="35">
         <v>0.1</v>
       </c>
-      <c r="E5" s="234"/>
+      <c r="E5" s="194"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C6" s="22">
         <v>0.96499999999999997</v>
       </c>
-      <c r="E6" s="234"/>
+      <c r="E6" s="194"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="21" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C7" s="22">
         <v>0.96499999999999997</v>
       </c>
-      <c r="E7" s="234"/>
+      <c r="E7" s="194"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="21" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" s="22">
         <v>0.5</v>
       </c>
-      <c r="E8" s="234"/>
+      <c r="E8" s="194"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="21" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C9" s="22">
         <v>0.1</v>
       </c>
-      <c r="E9" s="234"/>
+      <c r="E9" s="194"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" s="16">
         <v>0.96499999999999997</v>
       </c>
-      <c r="E10" s="234"/>
+      <c r="E10" s="194"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C11" s="16">
         <v>0.96499999999999997</v>
       </c>
-      <c r="E11" s="234"/>
+      <c r="E11" s="194"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C12" s="16">
         <v>0.96499999999999997</v>
       </c>
-      <c r="E12" s="234"/>
+      <c r="E12" s="194"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C13" s="16">
         <v>0.1</v>
       </c>
-      <c r="E13" s="234"/>
+      <c r="E13" s="194"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -7242,87 +7242,87 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="B2" s="33" t="s">
-        <v>122</v>
-      </c>
       <c r="C2" s="43" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D2" s="33">
         <v>0</v>
       </c>
       <c r="F2" s="135" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D3" s="35">
         <v>0.95</v>
       </c>
       <c r="F3" s="136" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D4" s="35">
         <v>0</v>
       </c>
       <c r="F4" s="136" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="23" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>119</v>
-      </c>
       <c r="C5" s="45" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D5" s="22">
         <v>0.8</v>
       </c>
       <c r="F5" s="46" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -7352,84 +7352,84 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="252" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" s="238" t="s">
+      <c r="B2" s="263" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="265" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="239"/>
-      <c r="E2" s="239"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="250" t="s">
+      <c r="D2" s="266"/>
+      <c r="E2" s="266"/>
+      <c r="F2" s="267"/>
+      <c r="G2" s="280" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="252" t="s">
-        <v>273</v>
-      </c>
-      <c r="I2" s="238" t="s">
+      <c r="H2" s="263" t="s">
+        <v>271</v>
+      </c>
+      <c r="I2" s="265" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="239"/>
-      <c r="K2" s="240"/>
+      <c r="J2" s="266"/>
+      <c r="K2" s="275"/>
     </row>
     <row r="3" spans="1:21" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="253"/>
-      <c r="C3" s="241"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="255"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="253"/>
-      <c r="I3" s="241"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="243"/>
+      <c r="B3" s="264"/>
+      <c r="C3" s="268"/>
+      <c r="D3" s="269"/>
+      <c r="E3" s="269"/>
+      <c r="F3" s="270"/>
+      <c r="G3" s="281"/>
+      <c r="H3" s="264"/>
+      <c r="I3" s="268"/>
+      <c r="J3" s="269"/>
+      <c r="K3" s="276"/>
     </row>
     <row r="4" spans="1:21" s="120" customFormat="1" ht="270" x14ac:dyDescent="0.2">
       <c r="A4" s="138"/>
       <c r="B4" s="140" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" s="256" t="s">
-        <v>314</v>
-      </c>
-      <c r="D4" s="257"/>
-      <c r="E4" s="257"/>
-      <c r="F4" s="258"/>
+        <v>159</v>
+      </c>
+      <c r="C4" s="271" t="s">
+        <v>312</v>
+      </c>
+      <c r="D4" s="272"/>
+      <c r="E4" s="272"/>
+      <c r="F4" s="273"/>
       <c r="G4" s="141" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H4" s="142" t="s">
-        <v>281</v>
-      </c>
-      <c r="I4" s="247" t="s">
-        <v>309</v>
-      </c>
-      <c r="J4" s="248"/>
-      <c r="K4" s="249"/>
+        <v>279</v>
+      </c>
+      <c r="I4" s="277" t="s">
+        <v>307</v>
+      </c>
+      <c r="J4" s="278"/>
+      <c r="K4" s="279"/>
     </row>
     <row r="5" spans="1:21" s="120" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="138"/>
       <c r="B5" s="93" t="s">
-        <v>162</v>
-      </c>
-      <c r="C5" s="244" t="s">
-        <v>315</v>
-      </c>
-      <c r="D5" s="245"/>
-      <c r="E5" s="245"/>
-      <c r="F5" s="246"/>
+        <v>160</v>
+      </c>
+      <c r="C5" s="245" t="s">
+        <v>313</v>
+      </c>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="274"/>
       <c r="G5" s="143">
         <v>0.8</v>
       </c>
       <c r="H5" s="144" t="s">
-        <v>325</v>
-      </c>
-      <c r="I5" s="235" t="s">
-        <v>279</v>
-      </c>
-      <c r="J5" s="236"/>
-      <c r="K5" s="237"/>
+        <v>323</v>
+      </c>
+      <c r="I5" s="248" t="s">
+        <v>277</v>
+      </c>
+      <c r="J5" s="249"/>
+      <c r="K5" s="250"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
@@ -7437,25 +7437,25 @@
     <row r="6" spans="1:21" s="120" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="138"/>
       <c r="B6" s="93" t="s">
-        <v>163</v>
-      </c>
-      <c r="C6" s="244" t="s">
-        <v>316</v>
-      </c>
-      <c r="D6" s="245"/>
-      <c r="E6" s="245"/>
-      <c r="F6" s="246"/>
+        <v>161</v>
+      </c>
+      <c r="C6" s="245" t="s">
+        <v>314</v>
+      </c>
+      <c r="D6" s="246"/>
+      <c r="E6" s="246"/>
+      <c r="F6" s="274"/>
       <c r="G6" s="143">
         <v>0.8</v>
       </c>
       <c r="H6" s="145" t="s">
-        <v>325</v>
-      </c>
-      <c r="I6" s="235" t="s">
-        <v>278</v>
-      </c>
-      <c r="J6" s="236"/>
-      <c r="K6" s="237"/>
+        <v>323</v>
+      </c>
+      <c r="I6" s="248" t="s">
+        <v>276</v>
+      </c>
+      <c r="J6" s="249"/>
+      <c r="K6" s="250"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
@@ -7463,23 +7463,23 @@
     <row r="7" spans="1:21" s="120" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="138"/>
       <c r="B7" s="93" t="s">
-        <v>311</v>
-      </c>
-      <c r="C7" s="244" t="s">
-        <v>312</v>
-      </c>
-      <c r="D7" s="245"/>
-      <c r="E7" s="245"/>
-      <c r="F7" s="246"/>
+        <v>309</v>
+      </c>
+      <c r="C7" s="245" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" s="246"/>
+      <c r="E7" s="246"/>
+      <c r="F7" s="274"/>
       <c r="G7" s="143">
         <v>1</v>
       </c>
       <c r="H7" s="145"/>
-      <c r="I7" s="235" t="s">
-        <v>313</v>
-      </c>
-      <c r="J7" s="236"/>
-      <c r="K7" s="237"/>
+      <c r="I7" s="248" t="s">
+        <v>311</v>
+      </c>
+      <c r="J7" s="249"/>
+      <c r="K7" s="250"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
@@ -7487,23 +7487,23 @@
     <row r="8" spans="1:21" s="120" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A8" s="138"/>
       <c r="B8" s="93" t="s">
-        <v>164</v>
-      </c>
-      <c r="C8" s="244" t="s">
-        <v>275</v>
-      </c>
-      <c r="D8" s="245"/>
-      <c r="E8" s="245"/>
-      <c r="F8" s="246"/>
+        <v>162</v>
+      </c>
+      <c r="C8" s="245" t="s">
+        <v>273</v>
+      </c>
+      <c r="D8" s="246"/>
+      <c r="E8" s="246"/>
+      <c r="F8" s="274"/>
       <c r="G8" s="143">
         <v>1</v>
       </c>
       <c r="H8" s="144" t="s">
-        <v>276</v>
-      </c>
-      <c r="I8" s="235"/>
-      <c r="J8" s="236"/>
-      <c r="K8" s="237"/>
+        <v>274</v>
+      </c>
+      <c r="I8" s="248"/>
+      <c r="J8" s="249"/>
+      <c r="K8" s="250"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
@@ -7511,25 +7511,25 @@
     <row r="9" spans="1:21" s="120" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="138"/>
       <c r="B9" s="93" t="s">
-        <v>165</v>
-      </c>
-      <c r="C9" s="244" t="s">
-        <v>166</v>
-      </c>
-      <c r="D9" s="245"/>
-      <c r="E9" s="245"/>
-      <c r="F9" s="246"/>
+        <v>163</v>
+      </c>
+      <c r="C9" s="245" t="s">
+        <v>164</v>
+      </c>
+      <c r="D9" s="246"/>
+      <c r="E9" s="246"/>
+      <c r="F9" s="274"/>
       <c r="G9" s="143">
         <v>0.95</v>
       </c>
       <c r="H9" s="144" t="s">
-        <v>325</v>
-      </c>
-      <c r="I9" s="244" t="s">
-        <v>274</v>
-      </c>
-      <c r="J9" s="245"/>
-      <c r="K9" s="261"/>
+        <v>323</v>
+      </c>
+      <c r="I9" s="245" t="s">
+        <v>272</v>
+      </c>
+      <c r="J9" s="246"/>
+      <c r="K9" s="247"/>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -7537,23 +7537,23 @@
     <row r="10" spans="1:21" s="120" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="139"/>
       <c r="B10" s="93" t="s">
-        <v>167</v>
-      </c>
-      <c r="C10" s="244" t="s">
-        <v>170</v>
-      </c>
-      <c r="D10" s="245"/>
-      <c r="E10" s="245"/>
-      <c r="F10" s="246"/>
+        <v>165</v>
+      </c>
+      <c r="C10" s="245" t="s">
+        <v>168</v>
+      </c>
+      <c r="D10" s="246"/>
+      <c r="E10" s="246"/>
+      <c r="F10" s="274"/>
       <c r="G10" s="146">
         <v>0.9</v>
       </c>
       <c r="H10" s="144"/>
-      <c r="I10" s="235" t="s">
-        <v>277</v>
-      </c>
-      <c r="J10" s="236"/>
-      <c r="K10" s="237"/>
+      <c r="I10" s="248" t="s">
+        <v>275</v>
+      </c>
+      <c r="J10" s="249"/>
+      <c r="K10" s="250"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -7561,23 +7561,23 @@
     <row r="11" spans="1:21" s="120" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="138"/>
       <c r="B11" s="93" t="s">
-        <v>168</v>
-      </c>
-      <c r="C11" s="244" t="s">
-        <v>169</v>
-      </c>
-      <c r="D11" s="245"/>
-      <c r="E11" s="245"/>
-      <c r="F11" s="246"/>
+        <v>166</v>
+      </c>
+      <c r="C11" s="245" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="274"/>
       <c r="G11" s="146">
         <v>0.9</v>
       </c>
       <c r="H11" s="145"/>
-      <c r="I11" s="235" t="s">
-        <v>277</v>
-      </c>
-      <c r="J11" s="236"/>
-      <c r="K11" s="237"/>
+      <c r="I11" s="248" t="s">
+        <v>275</v>
+      </c>
+      <c r="J11" s="249"/>
+      <c r="K11" s="250"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -7585,7 +7585,7 @@
     <row r="12" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B13" s="147" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C13" s="148"/>
       <c r="D13" s="148"/>
@@ -7608,28 +7608,28 @@
       <c r="U13" s="150"/>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="266" t="s">
-        <v>268</v>
-      </c>
-      <c r="C14" s="267"/>
-      <c r="D14" s="267"/>
-      <c r="E14" s="267"/>
-      <c r="F14" s="267"/>
-      <c r="G14" s="267"/>
-      <c r="H14" s="267"/>
-      <c r="I14" s="267"/>
-      <c r="J14" s="267"/>
-      <c r="K14" s="267"/>
-      <c r="L14" s="267"/>
-      <c r="M14" s="267"/>
-      <c r="N14" s="267"/>
-      <c r="O14" s="267"/>
-      <c r="P14" s="267"/>
-      <c r="Q14" s="267"/>
-      <c r="R14" s="267"/>
-      <c r="S14" s="267"/>
-      <c r="T14" s="267"/>
-      <c r="U14" s="268"/>
+      <c r="B14" s="255" t="s">
+        <v>266</v>
+      </c>
+      <c r="C14" s="256"/>
+      <c r="D14" s="256"/>
+      <c r="E14" s="256"/>
+      <c r="F14" s="256"/>
+      <c r="G14" s="256"/>
+      <c r="H14" s="256"/>
+      <c r="I14" s="256"/>
+      <c r="J14" s="256"/>
+      <c r="K14" s="256"/>
+      <c r="L14" s="256"/>
+      <c r="M14" s="256"/>
+      <c r="N14" s="256"/>
+      <c r="O14" s="256"/>
+      <c r="P14" s="256"/>
+      <c r="Q14" s="256"/>
+      <c r="R14" s="256"/>
+      <c r="S14" s="256"/>
+      <c r="T14" s="256"/>
+      <c r="U14" s="257"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B15" s="151"/>
@@ -7654,34 +7654,34 @@
       <c r="U15" s="154"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B16" s="264" t="s">
-        <v>264</v>
-      </c>
-      <c r="C16" s="265"/>
-      <c r="D16" s="265"/>
-      <c r="E16" s="265"/>
-      <c r="F16" s="265"/>
-      <c r="G16" s="265"/>
-      <c r="H16" s="265"/>
-      <c r="I16" s="265"/>
-      <c r="J16" s="265"/>
-      <c r="K16" s="265"/>
-      <c r="L16" s="265"/>
-      <c r="M16" s="265"/>
-      <c r="N16" s="265"/>
-      <c r="O16" s="265"/>
-      <c r="P16" s="265"/>
-      <c r="Q16" s="265"/>
-      <c r="R16" s="265"/>
-      <c r="S16" s="265"/>
-      <c r="T16" s="265"/>
-      <c r="U16" s="271"/>
+      <c r="B16" s="253" t="s">
+        <v>262</v>
+      </c>
+      <c r="C16" s="254"/>
+      <c r="D16" s="254"/>
+      <c r="E16" s="254"/>
+      <c r="F16" s="254"/>
+      <c r="G16" s="254"/>
+      <c r="H16" s="254"/>
+      <c r="I16" s="254"/>
+      <c r="J16" s="254"/>
+      <c r="K16" s="254"/>
+      <c r="L16" s="254"/>
+      <c r="M16" s="254"/>
+      <c r="N16" s="254"/>
+      <c r="O16" s="254"/>
+      <c r="P16" s="254"/>
+      <c r="Q16" s="254"/>
+      <c r="R16" s="254"/>
+      <c r="S16" s="254"/>
+      <c r="T16" s="254"/>
+      <c r="U16" s="262"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B17" s="259" t="s">
-        <v>260</v>
-      </c>
-      <c r="C17" s="260"/>
+      <c r="B17" s="258" t="s">
+        <v>258</v>
+      </c>
+      <c r="C17" s="259"/>
       <c r="D17" s="161">
         <v>2008</v>
       </c>
@@ -7734,14 +7734,14 @@
         <v>2024</v>
       </c>
       <c r="U17" s="165" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18" s="269" t="s">
-        <v>261</v>
-      </c>
-      <c r="C18" s="270"/>
+      <c r="B18" s="260" t="s">
+        <v>259</v>
+      </c>
+      <c r="C18" s="261"/>
       <c r="D18" s="162">
         <v>0.86</v>
       </c>
@@ -7798,10 +7798,10 @@
       </c>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B19" s="269" t="s">
-        <v>262</v>
-      </c>
-      <c r="C19" s="270"/>
+      <c r="B19" s="260" t="s">
+        <v>260</v>
+      </c>
+      <c r="C19" s="261"/>
       <c r="D19" s="162">
         <f>78/86</f>
         <v>0.90697674418604646</v>
@@ -7873,10 +7873,10 @@
       </c>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B20" s="269" t="s">
-        <v>263</v>
-      </c>
-      <c r="C20" s="270"/>
+      <c r="B20" s="260" t="s">
+        <v>261</v>
+      </c>
+      <c r="C20" s="261"/>
       <c r="D20" s="162">
         <v>1</v>
       </c>
@@ -7955,17 +7955,17 @@
       <c r="U21" s="154"/>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B22" s="264" t="s">
-        <v>267</v>
-      </c>
-      <c r="C22" s="265"/>
-      <c r="D22" s="265"/>
-      <c r="E22" s="265"/>
-      <c r="F22" s="265"/>
-      <c r="G22" s="265"/>
-      <c r="H22" s="265"/>
-      <c r="I22" s="265"/>
-      <c r="J22" s="265"/>
+      <c r="B22" s="253" t="s">
+        <v>265</v>
+      </c>
+      <c r="C22" s="254"/>
+      <c r="D22" s="254"/>
+      <c r="E22" s="254"/>
+      <c r="F22" s="254"/>
+      <c r="G22" s="254"/>
+      <c r="H22" s="254"/>
+      <c r="I22" s="254"/>
+      <c r="J22" s="254"/>
       <c r="K22" s="156"/>
       <c r="L22" s="156"/>
       <c r="M22" s="156"/>
@@ -7979,10 +7979,10 @@
       <c r="U22" s="157"/>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B23" s="259" t="s">
-        <v>260</v>
-      </c>
-      <c r="C23" s="260"/>
+      <c r="B23" s="258" t="s">
+        <v>258</v>
+      </c>
+      <c r="C23" s="259"/>
       <c r="D23" s="161">
         <v>2019</v>
       </c>
@@ -8002,7 +8002,7 @@
         <v>2024</v>
       </c>
       <c r="J23" s="160" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K23" s="152"/>
       <c r="L23" s="152"/>
@@ -8017,10 +8017,10 @@
       <c r="U23" s="154"/>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B24" s="259" t="s">
-        <v>261</v>
-      </c>
-      <c r="C24" s="260"/>
+      <c r="B24" s="258" t="s">
+        <v>259</v>
+      </c>
+      <c r="C24" s="259"/>
       <c r="D24" s="162">
         <f>E24</f>
         <v>0.53</v>
@@ -8047,7 +8047,7 @@
       <c r="L24" s="152"/>
       <c r="M24" s="152"/>
       <c r="N24" s="156" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="O24" s="152"/>
       <c r="P24" s="152"/>
@@ -8058,10 +8058,10 @@
       <c r="U24" s="154"/>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B25" s="259" t="s">
-        <v>262</v>
-      </c>
-      <c r="C25" s="260"/>
+      <c r="B25" s="258" t="s">
+        <v>260</v>
+      </c>
+      <c r="C25" s="259"/>
       <c r="D25" s="162">
         <f>E25</f>
         <v>0.35830985915492958</v>
@@ -8099,10 +8099,10 @@
       <c r="U25" s="154"/>
     </row>
     <row r="26" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="262" t="s">
-        <v>263</v>
-      </c>
-      <c r="C26" s="263"/>
+      <c r="B26" s="251" t="s">
+        <v>261</v>
+      </c>
+      <c r="C26" s="252"/>
       <c r="D26" s="168">
         <v>0</v>
       </c>
@@ -8138,7 +8138,7 @@
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.2">
       <c r="M28" s="7" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.2">
@@ -8167,6 +8167,26 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="I10:K10"/>
     <mergeCell ref="B26:C26"/>
@@ -8179,26 +8199,6 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B16:U16"/>
     <mergeCell ref="I11:K11"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8222,44 +8222,44 @@
     <row r="1" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="175" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C2" s="176" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="176" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="176" t="s">
         <v>254</v>
-      </c>
-      <c r="D2" s="176" t="s">
-        <v>255</v>
-      </c>
-      <c r="E2" s="176" t="s">
-        <v>256</v>
       </c>
       <c r="F2" s="177" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="176" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H2" s="178" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="272" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="273"/>
-      <c r="D3" s="273"/>
-      <c r="E3" s="273"/>
-      <c r="F3" s="274"/>
+      <c r="B3" s="195" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="197"/>
       <c r="G3" s="171"/>
       <c r="H3" s="67"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4" s="68" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D4">
         <v>0.8</v>
@@ -8277,31 +8277,31 @@
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="272" t="s">
-        <v>270</v>
-      </c>
-      <c r="C5" s="273"/>
-      <c r="D5" s="273"/>
-      <c r="E5" s="273"/>
-      <c r="F5" s="274"/>
+      <c r="B5" s="195" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" s="196"/>
+      <c r="D5" s="196"/>
+      <c r="E5" s="196"/>
+      <c r="F5" s="197"/>
       <c r="G5" s="171"/>
       <c r="H5" s="67"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B6" s="68" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D6">
         <v>0.8</v>
       </c>
       <c r="E6" s="172" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F6" s="174" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G6" s="179">
         <v>3</v>
@@ -8312,142 +8312,142 @@
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="272" t="s">
-        <v>283</v>
-      </c>
-      <c r="C7" s="273"/>
-      <c r="D7" s="273"/>
-      <c r="E7" s="273"/>
-      <c r="F7" s="274"/>
+      <c r="B7" s="195" t="s">
+        <v>281</v>
+      </c>
+      <c r="C7" s="196"/>
+      <c r="D7" s="196"/>
+      <c r="E7" s="196"/>
+      <c r="F7" s="197"/>
       <c r="G7" s="171"/>
       <c r="H7" s="67"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="181" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C8" s="183" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D8" s="182">
         <v>0.68</v>
       </c>
       <c r="E8" s="182" t="s">
+        <v>304</v>
+      </c>
+      <c r="F8" s="193" t="s">
         <v>306</v>
-      </c>
-      <c r="F8" s="275" t="s">
-        <v>308</v>
       </c>
       <c r="G8" s="171"/>
       <c r="H8" s="67"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B9" s="181" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C9" s="183" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D9" s="182">
         <v>0.76</v>
       </c>
       <c r="E9" s="182" t="s">
-        <v>307</v>
-      </c>
-      <c r="F9" s="275"/>
+        <v>305</v>
+      </c>
+      <c r="F9" s="193"/>
       <c r="G9" s="171"/>
       <c r="H9" s="67"/>
     </row>
     <row r="10" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="68" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C10" s="74" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D10">
         <v>0.8</v>
       </c>
       <c r="E10" s="172" t="s">
-        <v>284</v>
-      </c>
-      <c r="F10" s="275"/>
-      <c r="G10" s="280">
+        <v>282</v>
+      </c>
+      <c r="F10" s="193"/>
+      <c r="G10" s="191">
         <v>3</v>
       </c>
-      <c r="H10" s="278">
+      <c r="H10" s="189">
         <f>H6*G10</f>
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B11" s="68" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D11">
         <v>0.8</v>
       </c>
       <c r="E11" s="172" t="s">
-        <v>284</v>
-      </c>
-      <c r="F11" s="275"/>
-      <c r="G11" s="280"/>
-      <c r="H11" s="278"/>
+        <v>282</v>
+      </c>
+      <c r="F11" s="193"/>
+      <c r="G11" s="191"/>
+      <c r="H11" s="189"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" s="68" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D12">
         <v>0.9</v>
       </c>
       <c r="E12" s="172" t="s">
-        <v>292</v>
-      </c>
-      <c r="F12" s="275"/>
-      <c r="G12" s="280"/>
-      <c r="H12" s="278"/>
+        <v>290</v>
+      </c>
+      <c r="F12" s="193"/>
+      <c r="G12" s="191"/>
+      <c r="H12" s="189"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B13" s="68" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D13">
         <v>0.9</v>
       </c>
       <c r="E13" s="172" t="s">
-        <v>285</v>
-      </c>
-      <c r="F13" s="275"/>
-      <c r="G13" s="280"/>
-      <c r="H13" s="278"/>
+        <v>283</v>
+      </c>
+      <c r="F13" s="193"/>
+      <c r="G13" s="191"/>
+      <c r="H13" s="189"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="272" t="s">
-        <v>323</v>
-      </c>
-      <c r="C14" s="273"/>
-      <c r="D14" s="273"/>
-      <c r="E14" s="273"/>
-      <c r="F14" s="274"/>
+      <c r="B14" s="195" t="s">
+        <v>321</v>
+      </c>
+      <c r="C14" s="196"/>
+      <c r="D14" s="196"/>
+      <c r="E14" s="196"/>
+      <c r="F14" s="197"/>
       <c r="G14" s="180"/>
       <c r="H14" s="67"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B15" s="68" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C15" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D15">
         <v>0.1</v>
@@ -8455,23 +8455,23 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="275" t="s">
-        <v>291</v>
-      </c>
-      <c r="G15" s="280">
+      <c r="F15" s="193" t="s">
+        <v>289</v>
+      </c>
+      <c r="G15" s="191">
         <v>2</v>
       </c>
-      <c r="H15" s="278">
+      <c r="H15" s="189">
         <f>H10*G15</f>
         <v>36</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B16" s="68" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C16" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D16">
         <v>0.1</v>
@@ -8479,16 +8479,16 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="275"/>
-      <c r="G16" s="280"/>
-      <c r="H16" s="278"/>
+      <c r="F16" s="193"/>
+      <c r="G16" s="191"/>
+      <c r="H16" s="189"/>
     </row>
     <row r="17" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="69" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C17" s="70" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D17" s="70">
         <v>0.1</v>
@@ -8496,14 +8496,14 @@
       <c r="E17" s="70">
         <v>0</v>
       </c>
-      <c r="F17" s="276"/>
-      <c r="G17" s="281"/>
-      <c r="H17" s="279"/>
+      <c r="F17" s="198"/>
+      <c r="G17" s="192"/>
+      <c r="H17" s="190"/>
     </row>
     <row r="18" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F19" s="169" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G19" s="170">
         <f>G4+G6+G10+G15</f>
@@ -8512,7 +8512,7 @@
     </row>
     <row r="20" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="F20" s="69" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G20" s="71">
         <f>H15</f>
@@ -8520,56 +8520,61 @@
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C22" s="234" t="s">
-        <v>310</v>
-      </c>
-      <c r="D22" s="234"/>
-      <c r="E22" s="234"/>
-      <c r="F22" s="234"/>
-      <c r="G22" s="234"/>
+      <c r="C22" s="194" t="s">
+        <v>308</v>
+      </c>
+      <c r="D22" s="194"/>
+      <c r="E22" s="194"/>
+      <c r="F22" s="194"/>
+      <c r="G22" s="194"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C23" s="234"/>
-      <c r="D23" s="234"/>
-      <c r="E23" s="234"/>
-      <c r="F23" s="234"/>
-      <c r="G23" s="234"/>
+      <c r="C23" s="194"/>
+      <c r="D23" s="194"/>
+      <c r="E23" s="194"/>
+      <c r="F23" s="194"/>
+      <c r="G23" s="194"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C24" s="234"/>
-      <c r="D24" s="234"/>
-      <c r="E24" s="234"/>
-      <c r="F24" s="234"/>
-      <c r="G24" s="234"/>
+      <c r="C24" s="194"/>
+      <c r="D24" s="194"/>
+      <c r="E24" s="194"/>
+      <c r="F24" s="194"/>
+      <c r="G24" s="194"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C27" s="277" t="s">
-        <v>320</v>
-      </c>
-      <c r="D27" s="277"/>
-      <c r="E27" s="277"/>
-      <c r="F27" s="277"/>
-      <c r="G27" s="277"/>
-      <c r="H27" s="277"/>
+      <c r="C27" s="188" t="s">
+        <v>318</v>
+      </c>
+      <c r="D27" s="188"/>
+      <c r="E27" s="188"/>
+      <c r="F27" s="188"/>
+      <c r="G27" s="188"/>
+      <c r="H27" s="188"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C28" s="277"/>
-      <c r="D28" s="277"/>
-      <c r="E28" s="277"/>
-      <c r="F28" s="277"/>
-      <c r="G28" s="277"/>
-      <c r="H28" s="277"/>
+      <c r="C28" s="188"/>
+      <c r="D28" s="188"/>
+      <c r="E28" s="188"/>
+      <c r="F28" s="188"/>
+      <c r="G28" s="188"/>
+      <c r="H28" s="188"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C29" s="277"/>
-      <c r="D29" s="277"/>
-      <c r="E29" s="277"/>
-      <c r="F29" s="277"/>
-      <c r="G29" s="277"/>
-      <c r="H29" s="277"/>
+      <c r="C29" s="188"/>
+      <c r="D29" s="188"/>
+      <c r="E29" s="188"/>
+      <c r="F29" s="188"/>
+      <c r="G29" s="188"/>
+      <c r="H29" s="188"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="C27:H29"/>
     <mergeCell ref="H10:H13"/>
     <mergeCell ref="H15:H17"/>
@@ -8577,11 +8582,6 @@
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="F8:F13"/>
     <mergeCell ref="C22:G24"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="B14:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/project_documents/parameterDirectory.xlsx
+++ b/project_documents/parameterDirectory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabian/Documents/DPhil Work/Academic Work/EnglandCervicalScreeningProject/project_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C17E0E3-BD92-0049-87E0-71E2F7BF48FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B22C2A2-9886-0D4E-8563-56A6A848F273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="15760" windowHeight="17100" firstSheet="4" activeTab="7" xr2:uid="{9CDCC384-B02C-4946-8A51-C0AA91FF93D1}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17180" activeTab="7" xr2:uid="{9CDCC384-B02C-4946-8A51-C0AA91FF93D1}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -753,9 +753,6 @@
     <t>An agent has latent infection with genotype g if they do have infection with this genotype, but their infection has undetectably low viral load - and this low viral load is not a result of cancer's development but rather because the virus itself is 'asleep'. So if an agent has an active infection with genotype g (high viral load) but this or a different genotype develops into cancer (which sets all genotypes to 'inactive'), that is not incorrectly classed as latent infection.</t>
   </si>
   <si>
-    <t>As with sexual debut, it is difficult to find information on this. These mixing matrices agree with studies on sexual mixing in their overall trends, and are validated with the fits achieved when HPVsim is parameterised with them</t>
-  </si>
-  <si>
     <t>We note that we assume no initial prevalence of HPV in the ages 0-16 years old, and note that any note that burnin is set to 20 years. We further ensure that our model keeps prevalance of HPV at the approximately right levels by calibrating to the right number of cancers (including validating to unseen data). Note that out model has almost no agents in the latent state at any one point (with 100k agents, at most 1 agent at latent state at any one point with median number 0 over all the timepoints) - because the only agents in the latent state are those who have cleared cancer and had other genotypes made latent by the now-cleared cancer. Therefore, we can equate the inital HPV prevalence to the observable HPV prevalence - in short because in our modelling, most HPV cases are active</t>
   </si>
   <si>
@@ -1114,6 +1111,9 @@
   </si>
   <si>
     <t>P(normal|susceptible, latent, pre-cin), for lbc</t>
+  </si>
+  <si>
+    <t>Married matrix: our own analysis of NATSAL-3 data. Casual matrix: https://doi.org/10.1016/j.epidem.2018.03.004</t>
   </si>
 </sst>
 </file>
@@ -2152,7 +2152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="307">
+  <cellXfs count="303">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2301,63 +2301,6 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2378,15 +2321,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2534,15 +2468,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2558,14 +2483,8 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2579,39 +2498,13 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2631,9 +2524,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2642,9 +2532,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2655,113 +2542,26 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="9" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="9" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="9" fillId="2" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2770,23 +2570,124 @@
     <xf numFmtId="43" fontId="9" fillId="7" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="43" fontId="9" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2796,109 +2697,200 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2928,22 +2920,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>57244</xdr:colOff>
+      <xdr:colOff>65853</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>42236</xdr:rowOff>
+      <xdr:rowOff>37630</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>752803</xdr:colOff>
+      <xdr:colOff>783013</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>723605</xdr:rowOff>
+      <xdr:rowOff>743185</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDD2053E-1713-46C0-72D0-BAFD09B2B2BE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A068B30E-9264-1EED-A974-1F04B4F5590E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2959,8 +2951,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6013446" y="7750841"/>
-          <a:ext cx="695559" cy="681369"/>
+          <a:off x="6020742" y="7770519"/>
+          <a:ext cx="717160" cy="705555"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2972,22 +2964,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>34925</xdr:colOff>
+      <xdr:colOff>84667</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>28576</xdr:rowOff>
+      <xdr:rowOff>47037</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>759714</xdr:colOff>
+      <xdr:colOff>769064</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>739776</xdr:rowOff>
+      <xdr:rowOff>733778</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="6" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{960FAAE3-772B-0998-80AC-BEE1CE56E681}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62129F7E-1349-8513-49E3-6EFA9F509787}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3003,8 +2995,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5991225" y="8499476"/>
-          <a:ext cx="724789" cy="711200"/>
+          <a:off x="6039556" y="8541926"/>
+          <a:ext cx="684397" cy="686741"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3348,11 +3340,11 @@
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="238" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
+      <c r="C4" s="238"/>
+      <c r="D4" s="238"/>
     </row>
     <row r="5" spans="2:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -3393,7 +3385,7 @@
         <v>142</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="34" x14ac:dyDescent="0.2">
@@ -3404,7 +3396,7 @@
         <v>150</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="68" x14ac:dyDescent="0.2">
@@ -3415,7 +3407,7 @@
         <v>163</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="34" x14ac:dyDescent="0.2">
@@ -3426,30 +3418,30 @@
         <v>5</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="73" t="s">
+      <c r="B13" s="239" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
+      <c r="C13" s="239"/>
+      <c r="D13" s="239"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
+      <c r="B14" s="239"/>
+      <c r="C14" s="239"/>
+      <c r="D14" s="239"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
+      <c r="B15" s="239"/>
+      <c r="C15" s="239"/>
+      <c r="D15" s="239"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="73"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
+      <c r="B16" s="239"/>
+      <c r="C16" s="239"/>
+      <c r="D16" s="239"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3480,13 +3472,13 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="242" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
     </row>
     <row r="5" spans="2:6" ht="35" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
@@ -3506,7 +3498,7 @@
       </c>
     </row>
     <row r="6" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="244" t="s">
         <v>177</v>
       </c>
       <c r="C6" s="27" t="s">
@@ -3521,7 +3513,7 @@
       <c r="F6" s="14"/>
     </row>
     <row r="7" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" s="79"/>
+      <c r="B7" s="245"/>
       <c r="C7" s="28" t="s">
         <v>179</v>
       </c>
@@ -3534,7 +3526,7 @@
       <c r="F7" s="15"/>
     </row>
     <row r="8" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B8" s="79"/>
+      <c r="B8" s="245"/>
       <c r="C8" s="28" t="s">
         <v>180</v>
       </c>
@@ -3547,7 +3539,7 @@
       <c r="F8" s="15"/>
     </row>
     <row r="9" spans="2:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="B9" s="79"/>
+      <c r="B9" s="245"/>
       <c r="C9" s="28" t="s">
         <v>181</v>
       </c>
@@ -3560,7 +3552,7 @@
       <c r="F9" s="15"/>
     </row>
     <row r="10" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B10" s="80" t="s">
+      <c r="B10" s="246" t="s">
         <v>173</v>
       </c>
       <c r="C10" s="29" t="s">
@@ -3577,7 +3569,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B11" s="80"/>
+      <c r="B11" s="246"/>
       <c r="C11" s="29" t="s">
         <v>187</v>
       </c>
@@ -3592,7 +3584,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B12" s="80"/>
+      <c r="B12" s="246"/>
       <c r="C12" s="29" t="s">
         <v>188</v>
       </c>
@@ -3607,7 +3599,7 @@
       </c>
     </row>
     <row r="13" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B13" s="81" t="s">
+      <c r="B13" s="247" t="s">
         <v>174</v>
       </c>
       <c r="C13" s="30" t="s">
@@ -3624,7 +3616,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B14" s="81"/>
+      <c r="B14" s="247"/>
       <c r="C14" s="30" t="s">
         <v>113</v>
       </c>
@@ -3639,7 +3631,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B15" s="81"/>
+      <c r="B15" s="247"/>
       <c r="C15" s="30" t="s">
         <v>111</v>
       </c>
@@ -3654,7 +3646,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B16" s="82" t="s">
+      <c r="B16" s="248" t="s">
         <v>175</v>
       </c>
       <c r="C16" s="31" t="s">
@@ -3669,7 +3661,7 @@
       <c r="F16" s="18"/>
     </row>
     <row r="17" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B17" s="82"/>
+      <c r="B17" s="248"/>
       <c r="C17" s="31" t="s">
         <v>133</v>
       </c>
@@ -3684,7 +3676,7 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="135" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="82"/>
+      <c r="B18" s="248"/>
       <c r="C18" s="31" t="s">
         <v>115</v>
       </c>
@@ -3706,7 +3698,7 @@
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B19" s="82"/>
+      <c r="B19" s="248"/>
       <c r="C19" s="31" t="s">
         <v>114</v>
       </c>
@@ -3725,30 +3717,30 @@
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="249" t="s">
         <v>132</v>
       </c>
       <c r="C22" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="74" t="s">
+      <c r="D22" s="240" t="s">
         <v>216</v>
       </c>
-      <c r="E22" s="75"/>
+      <c r="E22" s="241"/>
     </row>
     <row r="23" spans="2:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="84"/>
+      <c r="B23" s="250"/>
       <c r="C23" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="76" t="s">
+      <c r="D23" s="242" t="s">
         <v>218</v>
       </c>
-      <c r="E23" s="77"/>
+      <c r="E23" s="243"/>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="84"/>
+      <c r="B24" s="250"/>
       <c r="C24" s="8" t="s">
         <v>114</v>
       </c>
@@ -3805,7 +3797,7 @@
   <dimension ref="A2:J34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="265"/>
+    <col min="1" max="1" width="10.83203125" style="195"/>
     <col min="2" max="2" width="14.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53" style="5" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" style="5"/>
@@ -3818,35 +3810,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" s="70" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="265"/>
-      <c r="B2" s="266" t="s">
+      <c r="A2" s="195"/>
+      <c r="B2" s="225" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="267" t="s">
+      <c r="C2" s="229" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="268" t="s">
+      <c r="D2" s="235" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="269"/>
-      <c r="F2" s="270" t="s">
+      <c r="E2" s="236"/>
+      <c r="F2" s="237" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="270"/>
-      <c r="H2" s="270"/>
-      <c r="I2" s="269"/>
-      <c r="J2" s="271" t="s">
+      <c r="G2" s="237"/>
+      <c r="H2" s="237"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="227" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="70" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="265"/>
-      <c r="B3" s="272"/>
-      <c r="C3" s="273"/>
+      <c r="A3" s="195"/>
+      <c r="B3" s="226"/>
+      <c r="C3" s="230"/>
       <c r="D3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="274" t="s">
+      <c r="E3" s="196" t="s">
         <v>25</v>
       </c>
       <c r="F3" s="11" t="s">
@@ -3858,686 +3850,675 @@
       <c r="H3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="274" t="s">
+      <c r="I3" s="196" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="275"/>
-    </row>
-    <row r="4" spans="1:10" s="112" customFormat="1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="276" t="s">
+      <c r="J3" s="228"/>
+    </row>
+    <row r="4" spans="1:10" s="90" customFormat="1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="220" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="109">
+      <c r="D4" s="87">
         <v>200000</v>
       </c>
-      <c r="E4" s="107" t="s">
+      <c r="E4" s="85" t="s">
+        <v>300</v>
+      </c>
+      <c r="F4" s="88"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="88" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="90" customFormat="1" ht="105" x14ac:dyDescent="0.2">
+      <c r="A5" s="220"/>
+      <c r="B5" s="92" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="91" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="93">
+        <v>1980</v>
+      </c>
+      <c r="E5" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="93"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="93" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="90" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A6" s="220"/>
+      <c r="B6" s="92" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="91" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="93">
+        <v>2055</v>
+      </c>
+      <c r="E6" s="92" t="s">
+        <v>310</v>
+      </c>
+      <c r="F6" s="93"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="93"/>
+    </row>
+    <row r="7" spans="1:10" s="90" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A7" s="220"/>
+      <c r="B7" s="92" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="93">
+        <v>20</v>
+      </c>
+      <c r="E7" s="92" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="93"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="93"/>
+    </row>
+    <row r="8" spans="1:10" s="90" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A8" s="220"/>
+      <c r="B8" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="91" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="93">
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="92" t="s">
+        <v>311</v>
+      </c>
+      <c r="F8" s="93"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="93"/>
+    </row>
+    <row r="9" spans="1:10" s="101" customFormat="1" ht="139" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="95" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="96" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="97" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="98" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="96" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="99"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="99" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="107" customFormat="1" ht="90" x14ac:dyDescent="0.2">
+      <c r="A10" s="221" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="102" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="103" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="104" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="102" t="s">
+        <v>312</v>
+      </c>
+      <c r="F10" s="105"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="106"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="105" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="107" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="221"/>
+      <c r="B11" s="223" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="231" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="105"/>
+      <c r="E11" s="223" t="s">
+        <v>328</v>
+      </c>
+      <c r="F11" s="105"/>
+      <c r="G11" s="106"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="233"/>
+    </row>
+    <row r="12" spans="1:10" s="107" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="221"/>
+      <c r="B12" s="224"/>
+      <c r="C12" s="232"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="224"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="106"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="234"/>
+    </row>
+    <row r="13" spans="1:10" s="112" customFormat="1" ht="105" x14ac:dyDescent="0.2">
+      <c r="A13" s="222" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="108" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="109" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="110" t="s">
+        <v>309</v>
+      </c>
+      <c r="E13" s="108" t="s">
+        <v>313</v>
+      </c>
+      <c r="F13" s="110"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="108"/>
+      <c r="J13" s="110"/>
+    </row>
+    <row r="14" spans="1:10" s="112" customFormat="1" ht="188" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="222"/>
+      <c r="B14" s="108" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="109" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="110" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="108" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="110"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="108"/>
+      <c r="J14" s="110" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="112" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A15" s="222"/>
+      <c r="B15" s="108" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="109" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="110">
+        <v>0.5</v>
+      </c>
+      <c r="E15" s="108" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="110"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="108"/>
+      <c r="J15" s="110"/>
+    </row>
+    <row r="16" spans="1:10" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A16" s="222"/>
+      <c r="B16" s="108" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="109" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="110">
+        <v>1</v>
+      </c>
+      <c r="E16" s="108" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="110"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="108"/>
+      <c r="J16" s="110" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="112" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A17" s="222"/>
+      <c r="B17" s="108" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="109" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="110" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="108" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="110"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="110"/>
+    </row>
+    <row r="18" spans="1:10" s="112" customFormat="1" ht="135" x14ac:dyDescent="0.2">
+      <c r="A18" s="222"/>
+      <c r="B18" s="108" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="109" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="110"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="110" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" s="111">
+        <v>0</v>
+      </c>
+      <c r="H18" s="111">
+        <v>1</v>
+      </c>
+      <c r="I18" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="J18" s="110"/>
+    </row>
+    <row r="19" spans="1:10" s="112" customFormat="1" ht="105" x14ac:dyDescent="0.2">
+      <c r="A19" s="222"/>
+      <c r="B19" s="108" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="109" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="110"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="110">
+        <v>0.25</v>
+      </c>
+      <c r="G19" s="111">
+        <v>0</v>
+      </c>
+      <c r="H19" s="111">
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="108" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="110"/>
+    </row>
+    <row r="20" spans="1:10" s="112" customFormat="1" ht="115" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="222"/>
+      <c r="B20" s="108" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="113" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="110" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="108" t="s">
         <v>301</v>
       </c>
-      <c r="F4" s="110"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="110" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="112" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A5" s="276"/>
-      <c r="B5" s="114" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="115">
-        <v>1980</v>
-      </c>
-      <c r="E5" s="114" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="115"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="115" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A6" s="276"/>
-      <c r="B6" s="114" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="113" t="s">
+      <c r="F20" s="110"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="111"/>
+      <c r="I20" s="108"/>
+      <c r="J20" s="114"/>
+    </row>
+    <row r="21" spans="1:10" s="43" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="222"/>
+      <c r="B21" s="200" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="208" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="114" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" s="205" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" s="76"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="205" t="s">
+        <v>167</v>
+      </c>
+      <c r="J21" s="211" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="43" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="222"/>
+      <c r="B22" s="201" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="209"/>
+      <c r="D22" s="202" t="s">
+        <v>166</v>
+      </c>
+      <c r="E22" s="206"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="206"/>
+      <c r="J22" s="212"/>
+    </row>
+    <row r="23" spans="1:10" s="43" customFormat="1" ht="180" x14ac:dyDescent="0.2">
+      <c r="A23" s="222"/>
+      <c r="B23" s="108" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="210"/>
+      <c r="D23" s="114" t="s">
+        <v>308</v>
+      </c>
+      <c r="E23" s="200" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="78"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="207"/>
+      <c r="J23" s="213"/>
+    </row>
+    <row r="24" spans="1:10" s="43" customFormat="1" ht="255" x14ac:dyDescent="0.2">
+      <c r="A24" s="197"/>
+      <c r="B24" s="108" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="109" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="110" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="108" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="73"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="110" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="122" customFormat="1" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="115" t="s">
+        <v>232</v>
+      </c>
+      <c r="B25" s="116" t="s">
+        <v>231</v>
+      </c>
+      <c r="C25" s="117" t="s">
+        <v>233</v>
+      </c>
+      <c r="D25" s="118">
+        <v>0</v>
+      </c>
+      <c r="E25" s="119" t="s">
+        <v>219</v>
+      </c>
+      <c r="F25" s="118"/>
+      <c r="G25" s="118"/>
+      <c r="H25" s="118"/>
+      <c r="I25" s="120"/>
+      <c r="J25" s="121"/>
+    </row>
+    <row r="26" spans="1:10" s="129" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="123" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="124" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="125" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="126" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="124"/>
+      <c r="F26" s="126"/>
+      <c r="G26" s="127"/>
+      <c r="H26" s="127"/>
+      <c r="I26" s="124"/>
+      <c r="J26" s="128" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" s="129" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A27" s="123"/>
+      <c r="B27" s="124" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="216" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="126"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="126">
+        <v>0.25</v>
+      </c>
+      <c r="G27" s="127">
+        <v>0</v>
+      </c>
+      <c r="H27" s="127">
+        <v>1</v>
+      </c>
+      <c r="I27" s="124" t="s">
+        <v>81</v>
+      </c>
+      <c r="J27" s="128" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" s="129" customFormat="1" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="123"/>
+      <c r="B28" s="124" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="217"/>
+      <c r="D28" s="126">
+        <v>50</v>
+      </c>
+      <c r="E28" s="124" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="126"/>
+      <c r="G28" s="127"/>
+      <c r="H28" s="127"/>
+      <c r="I28" s="124"/>
+      <c r="J28" s="126"/>
+    </row>
+    <row r="29" spans="1:10" s="129" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="123"/>
+      <c r="B29" s="124" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="218"/>
+      <c r="D29" s="126">
+        <v>0</v>
+      </c>
+      <c r="E29" s="124" t="s">
+        <v>84</v>
+      </c>
+      <c r="F29" s="126"/>
+      <c r="G29" s="127"/>
+      <c r="H29" s="127"/>
+      <c r="I29" s="124"/>
+      <c r="J29" s="126"/>
+    </row>
+    <row r="30" spans="1:10" s="129" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="123"/>
+      <c r="B30" s="124" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="130" t="s">
+        <v>302</v>
+      </c>
+      <c r="D30" s="126"/>
+      <c r="E30" s="124"/>
+      <c r="F30" s="126">
+        <v>5</v>
+      </c>
+      <c r="G30" s="127">
+        <v>1</v>
+      </c>
+      <c r="H30" s="127">
+        <v>12</v>
+      </c>
+      <c r="I30" s="124" t="s">
+        <v>315</v>
+      </c>
+      <c r="J30" s="126" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" s="129" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="123"/>
+      <c r="B31" s="124" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="130" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="126">
         <v>20</v>
       </c>
-      <c r="D6" s="115">
-        <v>2055</v>
-      </c>
-      <c r="E6" s="114" t="s">
-        <v>311</v>
-      </c>
-      <c r="F6" s="115"/>
-      <c r="G6" s="116"/>
-      <c r="H6" s="116"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="115"/>
-    </row>
-    <row r="7" spans="1:10" s="112" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="276"/>
-      <c r="B7" s="114" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="113" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="115">
-        <v>20</v>
-      </c>
-      <c r="E7" s="114" t="s">
-        <v>103</v>
-      </c>
-      <c r="F7" s="115"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="114"/>
-      <c r="J7" s="115"/>
-    </row>
-    <row r="8" spans="1:10" s="112" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A8" s="276"/>
-      <c r="B8" s="114" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="113" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="115">
-        <v>0.25</v>
-      </c>
-      <c r="E8" s="114" t="s">
-        <v>312</v>
-      </c>
-      <c r="F8" s="115"/>
-      <c r="G8" s="116"/>
-      <c r="H8" s="116"/>
-      <c r="I8" s="114"/>
-      <c r="J8" s="115"/>
-    </row>
-    <row r="9" spans="1:10" s="123" customFormat="1" ht="139" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="117" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="119" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="120" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="118" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="121"/>
-      <c r="G9" s="122"/>
-      <c r="H9" s="122"/>
-      <c r="I9" s="118"/>
-      <c r="J9" s="121" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="129" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A10" s="277" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="124" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="125" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="126" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="124" t="s">
-        <v>313</v>
-      </c>
-      <c r="F10" s="127"/>
-      <c r="G10" s="128"/>
-      <c r="H10" s="128"/>
-      <c r="I10" s="124"/>
-      <c r="J10" s="127" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="129" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="277"/>
-      <c r="B11" s="295" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="296" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="127"/>
-      <c r="E11" s="295" t="s">
-        <v>236</v>
-      </c>
-      <c r="F11" s="127"/>
-      <c r="G11" s="128"/>
-      <c r="H11" s="128"/>
-      <c r="I11" s="124"/>
-      <c r="J11" s="297"/>
-    </row>
-    <row r="12" spans="1:10" s="129" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="277"/>
-      <c r="B12" s="298"/>
-      <c r="C12" s="299"/>
-      <c r="D12" s="127"/>
-      <c r="E12" s="298"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="128"/>
-      <c r="H12" s="128"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="300"/>
-    </row>
-    <row r="13" spans="1:10" s="134" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A13" s="278" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="130" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="131" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="132" t="s">
-        <v>310</v>
-      </c>
-      <c r="E13" s="130" t="s">
-        <v>314</v>
-      </c>
-      <c r="F13" s="132"/>
-      <c r="G13" s="133"/>
-      <c r="H13" s="133"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="132"/>
-    </row>
-    <row r="14" spans="1:10" s="134" customFormat="1" ht="188" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="278"/>
-      <c r="B14" s="130" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="131" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="132" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="130" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="132"/>
-      <c r="G14" s="133"/>
-      <c r="H14" s="133"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="132" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="134" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="278"/>
-      <c r="B15" s="130" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="131" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="132">
-        <v>0.5</v>
-      </c>
-      <c r="E15" s="130" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="132"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="133"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="132"/>
-    </row>
-    <row r="16" spans="1:10" s="134" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A16" s="278"/>
-      <c r="B16" s="130" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="131" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="132">
+      <c r="E31" s="124" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="126"/>
+      <c r="G31" s="127"/>
+      <c r="H31" s="127"/>
+      <c r="I31" s="124"/>
+      <c r="J31" s="126"/>
+    </row>
+    <row r="32" spans="1:10" s="129" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A32" s="123"/>
+      <c r="B32" s="124" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="131" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="126" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" s="124" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="126" t="s">
+        <v>74</v>
+      </c>
+      <c r="G32" s="127">
+        <v>0</v>
+      </c>
+      <c r="H32" s="127">
         <v>1</v>
       </c>
-      <c r="E16" s="130" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="132"/>
-      <c r="G16" s="133"/>
-      <c r="H16" s="133"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="132" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" s="134" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="278"/>
-      <c r="B17" s="130" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="131" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="132" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="130" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="132"/>
-      <c r="G17" s="133"/>
-      <c r="H17" s="133"/>
-      <c r="I17" s="130"/>
-      <c r="J17" s="132"/>
-    </row>
-    <row r="18" spans="1:10" s="134" customFormat="1" ht="135" x14ac:dyDescent="0.2">
-      <c r="A18" s="278"/>
-      <c r="B18" s="130" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="131" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="132"/>
-      <c r="E18" s="130"/>
-      <c r="F18" s="132" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18" s="133">
-        <v>0</v>
-      </c>
-      <c r="H18" s="133">
-        <v>1</v>
-      </c>
-      <c r="I18" s="130" t="s">
-        <v>315</v>
-      </c>
-      <c r="J18" s="132"/>
-    </row>
-    <row r="19" spans="1:10" s="134" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A19" s="278"/>
-      <c r="B19" s="130" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="131" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="132"/>
-      <c r="E19" s="130"/>
-      <c r="F19" s="132">
-        <v>0.25</v>
-      </c>
-      <c r="G19" s="133">
-        <v>0</v>
-      </c>
-      <c r="H19" s="133">
-        <v>0.5</v>
-      </c>
-      <c r="I19" s="130" t="s">
-        <v>60</v>
-      </c>
-      <c r="J19" s="132"/>
-    </row>
-    <row r="20" spans="1:10" s="134" customFormat="1" ht="115" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="278"/>
-      <c r="B20" s="130" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="135" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="132" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="130" t="s">
-        <v>302</v>
-      </c>
-      <c r="F20" s="132"/>
-      <c r="G20" s="133"/>
-      <c r="H20" s="133"/>
-      <c r="I20" s="130"/>
-      <c r="J20" s="136"/>
-    </row>
-    <row r="21" spans="1:10" s="43" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="278"/>
-      <c r="B21" s="283" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="284" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="136" t="s">
-        <v>165</v>
-      </c>
-      <c r="E21" s="285" t="s">
-        <v>99</v>
-      </c>
-      <c r="F21" s="95"/>
-      <c r="G21" s="96"/>
-      <c r="H21" s="96"/>
-      <c r="I21" s="285" t="s">
-        <v>167</v>
-      </c>
-      <c r="J21" s="291" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" s="43" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="278"/>
-      <c r="B22" s="286" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="287"/>
-      <c r="D22" s="288" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22" s="289"/>
-      <c r="F22" s="94"/>
-      <c r="G22" s="92"/>
-      <c r="H22" s="92"/>
-      <c r="I22" s="289"/>
-      <c r="J22" s="292"/>
-    </row>
-    <row r="23" spans="1:10" s="43" customFormat="1" ht="180" x14ac:dyDescent="0.2">
-      <c r="A23" s="278"/>
-      <c r="B23" s="130" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="290"/>
-      <c r="D23" s="136" t="s">
-        <v>309</v>
-      </c>
-      <c r="E23" s="283" t="s">
-        <v>100</v>
-      </c>
-      <c r="F23" s="97"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="92"/>
-      <c r="I23" s="293"/>
-      <c r="J23" s="294"/>
-    </row>
-    <row r="24" spans="1:10" s="43" customFormat="1" ht="255" x14ac:dyDescent="0.2">
-      <c r="A24" s="279"/>
-      <c r="B24" s="130" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="131" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" s="132" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="130" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24" s="92"/>
-      <c r="G24" s="93"/>
-      <c r="H24" s="93"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="132" t="s">
+      <c r="I32" s="124" t="s">
+        <v>73</v>
+      </c>
+      <c r="J32" s="126"/>
+    </row>
+    <row r="33" spans="1:10" s="136" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="219" t="s">
+        <v>239</v>
+      </c>
+      <c r="B33" s="132" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="133" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" s="134" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="132" t="s">
+        <v>219</v>
+      </c>
+      <c r="F33" s="134"/>
+      <c r="G33" s="135"/>
+      <c r="H33" s="135"/>
+      <c r="I33" s="132"/>
+      <c r="J33" s="214" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="144" customFormat="1" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="137" t="s">
-        <v>232</v>
-      </c>
-      <c r="B25" s="138" t="s">
-        <v>231</v>
-      </c>
-      <c r="C25" s="139" t="s">
-        <v>233</v>
-      </c>
-      <c r="D25" s="140">
-        <v>0</v>
-      </c>
-      <c r="E25" s="141" t="s">
-        <v>219</v>
-      </c>
-      <c r="F25" s="140"/>
-      <c r="G25" s="140"/>
-      <c r="H25" s="140"/>
-      <c r="I25" s="142"/>
-      <c r="J25" s="143"/>
-    </row>
-    <row r="26" spans="1:10" s="151" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="145" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" s="146" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="147" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="148" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="146"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="149"/>
-      <c r="H26" s="149"/>
-      <c r="I26" s="146"/>
-      <c r="J26" s="150" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" s="151" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A27" s="145"/>
-      <c r="B27" s="146" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="153" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="148"/>
-      <c r="E27" s="146"/>
-      <c r="F27" s="148">
-        <v>0.25</v>
-      </c>
-      <c r="G27" s="149">
-        <v>0</v>
-      </c>
-      <c r="H27" s="149">
-        <v>1</v>
-      </c>
-      <c r="I27" s="146" t="s">
-        <v>81</v>
-      </c>
-      <c r="J27" s="150" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" s="151" customFormat="1" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="145"/>
-      <c r="B28" s="146" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="154"/>
-      <c r="D28" s="148">
-        <v>50</v>
-      </c>
-      <c r="E28" s="146" t="s">
-        <v>84</v>
-      </c>
-      <c r="F28" s="148"/>
-      <c r="G28" s="149"/>
-      <c r="H28" s="149"/>
-      <c r="I28" s="146"/>
-      <c r="J28" s="148"/>
-    </row>
-    <row r="29" spans="1:10" s="151" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="145"/>
-      <c r="B29" s="146" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="155"/>
-      <c r="D29" s="148">
-        <v>0</v>
-      </c>
-      <c r="E29" s="146" t="s">
-        <v>84</v>
-      </c>
-      <c r="F29" s="148"/>
-      <c r="G29" s="149"/>
-      <c r="H29" s="149"/>
-      <c r="I29" s="146"/>
-      <c r="J29" s="148"/>
-    </row>
-    <row r="30" spans="1:10" s="151" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="145"/>
-      <c r="B30" s="146" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="152" t="s">
-        <v>303</v>
-      </c>
-      <c r="D30" s="148"/>
-      <c r="E30" s="146"/>
-      <c r="F30" s="148">
-        <v>5</v>
-      </c>
-      <c r="G30" s="149">
-        <v>1</v>
-      </c>
-      <c r="H30" s="149">
-        <v>12</v>
-      </c>
-      <c r="I30" s="146" t="s">
+    <row r="34" spans="1:10" s="136" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A34" s="219"/>
+      <c r="B34" s="132" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="133" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="134" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="132" t="s">
         <v>316</v>
       </c>
-      <c r="J30" s="148" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" s="151" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="145"/>
-      <c r="B31" s="146" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" s="152" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" s="148">
-        <v>20</v>
-      </c>
-      <c r="E31" s="146" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31" s="148"/>
-      <c r="G31" s="149"/>
-      <c r="H31" s="149"/>
-      <c r="I31" s="146"/>
-      <c r="J31" s="148"/>
-    </row>
-    <row r="32" spans="1:10" s="151" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A32" s="145"/>
-      <c r="B32" s="146" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" s="156" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" s="148" t="s">
-        <v>71</v>
-      </c>
-      <c r="E32" s="146" t="s">
-        <v>72</v>
-      </c>
-      <c r="F32" s="148" t="s">
-        <v>74</v>
-      </c>
-      <c r="G32" s="149">
-        <v>0</v>
-      </c>
-      <c r="H32" s="149">
-        <v>1</v>
-      </c>
-      <c r="I32" s="146" t="s">
-        <v>73</v>
-      </c>
-      <c r="J32" s="148"/>
-    </row>
-    <row r="33" spans="1:10" s="162" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="280" t="s">
-        <v>240</v>
-      </c>
-      <c r="B33" s="157" t="s">
-        <v>104</v>
-      </c>
-      <c r="C33" s="158" t="s">
-        <v>105</v>
-      </c>
-      <c r="D33" s="159" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" s="157" t="s">
-        <v>219</v>
-      </c>
-      <c r="F33" s="159"/>
-      <c r="G33" s="160"/>
-      <c r="H33" s="160"/>
-      <c r="I33" s="157"/>
-      <c r="J33" s="161" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" s="162" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A34" s="280"/>
-      <c r="B34" s="157" t="s">
-        <v>106</v>
-      </c>
-      <c r="C34" s="158" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" s="159" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" s="157" t="s">
-        <v>317</v>
-      </c>
-      <c r="F34" s="159"/>
-      <c r="G34" s="160"/>
-      <c r="H34" s="160"/>
-      <c r="I34" s="157"/>
-      <c r="J34" s="163"/>
+      <c r="F34" s="134"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="135"/>
+      <c r="I34" s="132"/>
+      <c r="J34" s="215"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="J21:J23"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B11:B12"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="C2:C3"/>
@@ -4546,6 +4527,17 @@
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="J21:J23"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="C27:C29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -4564,2571 +4556,2571 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="194" t="s">
+      <c r="A1" s="157" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="195" t="s">
+      <c r="B1" s="158" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="196" t="s">
+      <c r="C1" s="159" t="s">
         <v>137</v>
       </c>
-      <c r="D1" s="197" t="s">
+      <c r="D1" s="160" t="s">
         <v>136</v>
       </c>
-      <c r="E1" s="198" t="s">
+      <c r="E1" s="161" t="s">
         <v>135</v>
       </c>
-      <c r="H1" s="199" t="s">
+      <c r="H1" s="162" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="200" t="s">
+    <row r="2" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="137" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="163" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="201" t="s">
+      <c r="C2" s="164" t="s">
         <v>124</v>
       </c>
-      <c r="D2" s="165" t="s">
+      <c r="D2" s="138" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="202">
+      <c r="E2" s="165">
         <v>0.12</v>
       </c>
-      <c r="H2" s="204" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B3" s="205" t="s">
+      <c r="H2" s="251" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="206" t="s">
+      <c r="C3" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="D3" s="168" t="s">
+      <c r="D3" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="207">
+      <c r="E3" s="169">
         <v>0.88</v>
       </c>
-      <c r="H3" s="204"/>
-    </row>
-    <row r="4" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="205" t="s">
+      <c r="H3" s="251"/>
+    </row>
+    <row r="4" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="168" t="s">
+      <c r="D4" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E4" s="207">
-        <v>0</v>
-      </c>
-      <c r="H4" s="204"/>
-    </row>
-    <row r="5" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" s="205" t="s">
+      <c r="E4" s="169">
+        <v>0</v>
+      </c>
+      <c r="H4" s="251"/>
+    </row>
+    <row r="5" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="206" t="s">
+      <c r="C5" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="168" t="s">
+      <c r="D5" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="202">
+      <c r="E5" s="165">
         <v>0.12</v>
       </c>
-      <c r="H5" s="204"/>
-    </row>
-    <row r="6" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" s="205" t="s">
+      <c r="H5" s="251"/>
+    </row>
+    <row r="6" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="206" t="s">
+      <c r="C6" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="168" t="s">
+      <c r="D6" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="207">
+      <c r="E6" s="169">
         <v>0.88</v>
       </c>
-      <c r="H6" s="204"/>
-    </row>
-    <row r="7" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B7" s="205" t="s">
+      <c r="H6" s="251"/>
+    </row>
+    <row r="7" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="206" t="s">
+      <c r="C7" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D7" s="168" t="s">
+      <c r="D7" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E7" s="207">
-        <v>0</v>
-      </c>
-      <c r="H7" s="204"/>
-    </row>
-    <row r="8" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B8" s="205" t="s">
+      <c r="E7" s="169">
+        <v>0</v>
+      </c>
+      <c r="H7" s="251"/>
+    </row>
+    <row r="8" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="206" t="s">
+      <c r="C8" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D8" s="168" t="s">
+      <c r="D8" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E8" s="202">
+      <c r="E8" s="165">
         <v>0.12</v>
       </c>
-      <c r="H8" s="204"/>
-    </row>
-    <row r="9" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" s="205" t="s">
+      <c r="H8" s="251"/>
+    </row>
+    <row r="9" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="206" t="s">
+      <c r="C9" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="168" t="s">
+      <c r="D9" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="207">
+      <c r="E9" s="169">
         <v>0.88</v>
       </c>
-      <c r="H9" s="204"/>
-    </row>
-    <row r="10" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B10" s="205" t="s">
+      <c r="H9" s="251"/>
+    </row>
+    <row r="10" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="206" t="s">
+      <c r="C10" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="168" t="s">
+      <c r="D10" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E10" s="207">
-        <v>0</v>
-      </c>
-      <c r="H10" s="204"/>
-    </row>
-    <row r="11" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" s="205" t="s">
+      <c r="E10" s="169">
+        <v>0</v>
+      </c>
+      <c r="H10" s="251"/>
+    </row>
+    <row r="11" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C11" s="206" t="s">
+      <c r="C11" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="168" t="s">
+      <c r="D11" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E11" s="202">
+      <c r="E11" s="165">
         <v>0.12</v>
       </c>
-      <c r="H11" s="204"/>
-    </row>
-    <row r="12" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" s="205" t="s">
+      <c r="H11" s="251"/>
+    </row>
+    <row r="12" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C12" s="206" t="s">
+      <c r="C12" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D12" s="168" t="s">
+      <c r="D12" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E12" s="207">
+      <c r="E12" s="169">
         <v>0.88</v>
       </c>
-      <c r="H12" s="204"/>
-    </row>
-    <row r="13" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="205" t="s">
+      <c r="H12" s="251"/>
+    </row>
+    <row r="13" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C13" s="206" t="s">
+      <c r="C13" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D13" s="168" t="s">
+      <c r="D13" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="207">
-        <v>0</v>
-      </c>
-      <c r="H13" s="204"/>
-    </row>
-    <row r="14" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B14" s="205" t="s">
+      <c r="E13" s="169">
+        <v>0</v>
+      </c>
+      <c r="H13" s="251"/>
+    </row>
+    <row r="14" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="206" t="s">
+      <c r="C14" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="168" t="s">
+      <c r="D14" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E14" s="202">
+      <c r="E14" s="165">
         <v>0.12</v>
       </c>
-      <c r="H14" s="204"/>
-    </row>
-    <row r="15" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B15" s="205" t="s">
+      <c r="H14" s="251"/>
+    </row>
+    <row r="15" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="206" t="s">
+      <c r="C15" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D15" s="168" t="s">
+      <c r="D15" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="207">
+      <c r="E15" s="169">
         <v>0.88</v>
       </c>
-      <c r="H15" s="204"/>
-    </row>
-    <row r="16" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" s="205" t="s">
+      <c r="H15" s="251"/>
+    </row>
+    <row r="16" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="206" t="s">
+      <c r="C16" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D16" s="168" t="s">
+      <c r="D16" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E16" s="207">
-        <v>0</v>
-      </c>
-      <c r="H16" s="204"/>
-    </row>
-    <row r="17" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B17" s="205" t="s">
+      <c r="E16" s="169">
+        <v>0</v>
+      </c>
+      <c r="H16" s="251"/>
+    </row>
+    <row r="17" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="206" t="s">
+      <c r="C17" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="168" t="s">
+      <c r="D17" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="202">
+      <c r="E17" s="165">
         <v>0.12</v>
       </c>
-      <c r="H17" s="204"/>
-    </row>
-    <row r="18" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B18" s="205" t="s">
+      <c r="H17" s="251"/>
+    </row>
+    <row r="18" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="206" t="s">
+      <c r="C18" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D18" s="168" t="s">
+      <c r="D18" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E18" s="207">
+      <c r="E18" s="169">
         <v>0.88</v>
       </c>
-      <c r="H18" s="204"/>
-    </row>
-    <row r="19" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B19" s="205" t="s">
+      <c r="H18" s="251"/>
+    </row>
+    <row r="19" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="C19" s="206" t="s">
+      <c r="C19" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D19" s="168" t="s">
+      <c r="D19" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E19" s="207">
-        <v>0</v>
-      </c>
-      <c r="H19" s="204"/>
-    </row>
-    <row r="20" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B20" s="205" t="s">
+      <c r="E19" s="169">
+        <v>0</v>
+      </c>
+      <c r="H19" s="251"/>
+    </row>
+    <row r="20" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="206" t="s">
+      <c r="C20" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="168" t="s">
+      <c r="D20" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E20" s="202">
+      <c r="E20" s="165">
         <v>0.12</v>
       </c>
-      <c r="H20" s="204"/>
-    </row>
-    <row r="21" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B21" s="205" t="s">
+      <c r="H20" s="251"/>
+    </row>
+    <row r="21" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="206" t="s">
+      <c r="C21" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="D21" s="168" t="s">
+      <c r="D21" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="207">
+      <c r="E21" s="169">
         <v>0.88</v>
       </c>
-      <c r="H21" s="204"/>
-    </row>
-    <row r="22" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B22" s="205" t="s">
+      <c r="H21" s="251"/>
+    </row>
+    <row r="22" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="206" t="s">
+      <c r="C22" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="168" t="s">
+      <c r="D22" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E22" s="207">
-        <v>0</v>
-      </c>
-      <c r="H22" s="204"/>
-    </row>
-    <row r="23" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B23" s="205" t="s">
+      <c r="E22" s="169">
+        <v>0</v>
+      </c>
+      <c r="H22" s="251"/>
+    </row>
+    <row r="23" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="206" t="s">
+      <c r="C23" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D23" s="168" t="s">
+      <c r="D23" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="202">
+      <c r="E23" s="165">
         <v>0.12</v>
       </c>
-      <c r="H23" s="204"/>
-    </row>
-    <row r="24" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B24" s="205" t="s">
+      <c r="H23" s="251"/>
+    </row>
+    <row r="24" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C24" s="206" t="s">
+      <c r="C24" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D24" s="168" t="s">
+      <c r="D24" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E24" s="207">
+      <c r="E24" s="169">
         <v>0.88</v>
       </c>
-      <c r="H24" s="204"/>
-    </row>
-    <row r="25" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B25" s="205" t="s">
+      <c r="H24" s="251"/>
+    </row>
+    <row r="25" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C25" s="206" t="s">
+      <c r="C25" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D25" s="168" t="s">
+      <c r="D25" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="207">
-        <v>0</v>
-      </c>
-      <c r="H25" s="204"/>
-    </row>
-    <row r="26" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B26" s="205" t="s">
+      <c r="E25" s="169">
+        <v>0</v>
+      </c>
+      <c r="H25" s="251"/>
+    </row>
+    <row r="26" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="206" t="s">
+      <c r="C26" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="168" t="s">
+      <c r="D26" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E26" s="202">
+      <c r="E26" s="165">
         <v>0.12</v>
       </c>
-      <c r="H26" s="204"/>
-    </row>
-    <row r="27" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B27" s="205" t="s">
+      <c r="H26" s="251"/>
+    </row>
+    <row r="27" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C27" s="206" t="s">
+      <c r="C27" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D27" s="168" t="s">
+      <c r="D27" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="207">
+      <c r="E27" s="169">
         <v>0.88</v>
       </c>
-      <c r="H27" s="204"/>
-    </row>
-    <row r="28" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B28" s="205" t="s">
+      <c r="H27" s="251"/>
+    </row>
+    <row r="28" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C28" s="206" t="s">
+      <c r="C28" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="168" t="s">
+      <c r="D28" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E28" s="207">
-        <v>0</v>
-      </c>
-      <c r="H28" s="204"/>
-    </row>
-    <row r="29" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B29" s="205" t="s">
+      <c r="E28" s="169">
+        <v>0</v>
+      </c>
+      <c r="H28" s="251"/>
+    </row>
+    <row r="29" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C29" s="206" t="s">
+      <c r="C29" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="168" t="s">
+      <c r="D29" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E29" s="202">
+      <c r="E29" s="165">
         <v>0.12</v>
       </c>
-      <c r="H29" s="204"/>
-    </row>
-    <row r="30" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B30" s="205" t="s">
+      <c r="H29" s="251"/>
+    </row>
+    <row r="30" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C30" s="206" t="s">
+      <c r="C30" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D30" s="168" t="s">
+      <c r="D30" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="207">
+      <c r="E30" s="169">
         <v>0.88</v>
       </c>
-      <c r="H30" s="204"/>
-    </row>
-    <row r="31" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B31" s="205" t="s">
+      <c r="H30" s="251"/>
+    </row>
+    <row r="31" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C31" s="206" t="s">
+      <c r="C31" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D31" s="168" t="s">
+      <c r="D31" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E31" s="207">
-        <v>0</v>
-      </c>
-      <c r="H31" s="204"/>
-    </row>
-    <row r="32" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B32" s="205" t="s">
+      <c r="E31" s="169">
+        <v>0</v>
+      </c>
+      <c r="H31" s="251"/>
+    </row>
+    <row r="32" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="206" t="s">
+      <c r="C32" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D32" s="168" t="s">
+      <c r="D32" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E32" s="202">
+      <c r="E32" s="165">
         <v>0.12</v>
       </c>
-      <c r="H32" s="204"/>
-    </row>
-    <row r="33" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B33" s="205" t="s">
+      <c r="H32" s="251"/>
+    </row>
+    <row r="33" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C33" s="206" t="s">
+      <c r="C33" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D33" s="168" t="s">
+      <c r="D33" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E33" s="207">
+      <c r="E33" s="169">
         <v>0.88</v>
       </c>
-      <c r="H33" s="204"/>
-    </row>
-    <row r="34" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B34" s="205" t="s">
+      <c r="H33" s="251"/>
+    </row>
+    <row r="34" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C34" s="206" t="s">
+      <c r="C34" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D34" s="168" t="s">
+      <c r="D34" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="207">
-        <v>0</v>
-      </c>
-      <c r="H34" s="204"/>
-    </row>
-    <row r="35" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B35" s="205" t="s">
+      <c r="E34" s="169">
+        <v>0</v>
+      </c>
+      <c r="H34" s="251"/>
+    </row>
+    <row r="35" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C35" s="206" t="s">
+      <c r="C35" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="168" t="s">
+      <c r="D35" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="202">
+      <c r="E35" s="165">
         <v>0.12</v>
       </c>
-      <c r="H35" s="204"/>
-    </row>
-    <row r="36" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B36" s="205" t="s">
+      <c r="H35" s="251"/>
+    </row>
+    <row r="36" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C36" s="206" t="s">
+      <c r="C36" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D36" s="168" t="s">
+      <c r="D36" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E36" s="207">
+      <c r="E36" s="169">
         <v>0.88</v>
       </c>
-      <c r="H36" s="204"/>
-    </row>
-    <row r="37" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B37" s="205" t="s">
+      <c r="H36" s="251"/>
+    </row>
+    <row r="37" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="C37" s="206" t="s">
+      <c r="C37" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D37" s="168" t="s">
+      <c r="D37" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E37" s="207">
-        <v>0</v>
-      </c>
-      <c r="H37" s="204"/>
-    </row>
-    <row r="38" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B38" s="205" t="s">
+      <c r="E37" s="169">
+        <v>0</v>
+      </c>
+      <c r="H37" s="251"/>
+    </row>
+    <row r="38" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C38" s="206" t="s">
+      <c r="C38" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="D38" s="168" t="s">
+      <c r="D38" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E38" s="207">
+      <c r="E38" s="169">
         <v>0.94</v>
       </c>
-      <c r="H38" s="204"/>
-    </row>
-    <row r="39" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B39" s="205" t="s">
+      <c r="H38" s="251"/>
+    </row>
+    <row r="39" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="206" t="s">
+      <c r="C39" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="D39" s="168" t="s">
+      <c r="D39" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E39" s="207">
+      <c r="E39" s="169">
         <v>0.06</v>
       </c>
-      <c r="H39" s="204"/>
-    </row>
-    <row r="40" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B40" s="205" t="s">
+      <c r="H39" s="251"/>
+    </row>
+    <row r="40" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="206" t="s">
+      <c r="C40" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="D40" s="168" t="s">
+      <c r="D40" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E40" s="207">
-        <v>0</v>
-      </c>
-      <c r="H40" s="204"/>
-    </row>
-    <row r="41" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B41" s="205" t="s">
+      <c r="E40" s="169">
+        <v>0</v>
+      </c>
+      <c r="H40" s="251"/>
+    </row>
+    <row r="41" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B41" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C41" s="206" t="s">
+      <c r="C41" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D41" s="168" t="s">
+      <c r="D41" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E41" s="207">
+      <c r="E41" s="169">
         <v>0.94</v>
       </c>
-      <c r="H41" s="204"/>
-    </row>
-    <row r="42" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B42" s="205" t="s">
+      <c r="H41" s="251"/>
+    </row>
+    <row r="42" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C42" s="206" t="s">
+      <c r="C42" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D42" s="168" t="s">
+      <c r="D42" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E42" s="207">
+      <c r="E42" s="169">
         <v>0.06</v>
       </c>
-      <c r="H42" s="204"/>
-    </row>
-    <row r="43" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B43" s="205" t="s">
+      <c r="H42" s="251"/>
+    </row>
+    <row r="43" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C43" s="206" t="s">
+      <c r="C43" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D43" s="168" t="s">
+      <c r="D43" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E43" s="207">
-        <v>0</v>
-      </c>
-      <c r="H43" s="204"/>
-    </row>
-    <row r="44" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B44" s="205" t="s">
+      <c r="E43" s="169">
+        <v>0</v>
+      </c>
+      <c r="H43" s="251"/>
+    </row>
+    <row r="44" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="206" t="s">
+      <c r="C44" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D44" s="168" t="s">
+      <c r="D44" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E44" s="207">
+      <c r="E44" s="169">
         <v>0.94</v>
       </c>
-      <c r="H44" s="204"/>
-    </row>
-    <row r="45" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B45" s="205" t="s">
+      <c r="H44" s="251"/>
+    </row>
+    <row r="45" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="206" t="s">
+      <c r="C45" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D45" s="168" t="s">
+      <c r="D45" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E45" s="207">
+      <c r="E45" s="169">
         <v>0.06</v>
       </c>
-      <c r="H45" s="204"/>
-    </row>
-    <row r="46" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B46" s="205" t="s">
+      <c r="H45" s="251"/>
+    </row>
+    <row r="46" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C46" s="206" t="s">
+      <c r="C46" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D46" s="168" t="s">
+      <c r="D46" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E46" s="207">
-        <v>0</v>
-      </c>
-      <c r="H46" s="204"/>
-    </row>
-    <row r="47" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B47" s="205" t="s">
+      <c r="E46" s="169">
+        <v>0</v>
+      </c>
+      <c r="H46" s="251"/>
+    </row>
+    <row r="47" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C47" s="206" t="s">
+      <c r="C47" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D47" s="168" t="s">
+      <c r="D47" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E47" s="207">
+      <c r="E47" s="169">
         <v>0.94</v>
       </c>
-      <c r="H47" s="204"/>
-    </row>
-    <row r="48" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B48" s="205" t="s">
+      <c r="H47" s="251"/>
+    </row>
+    <row r="48" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C48" s="206" t="s">
+      <c r="C48" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D48" s="168" t="s">
+      <c r="D48" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E48" s="207">
+      <c r="E48" s="169">
         <v>0.06</v>
       </c>
-      <c r="H48" s="204"/>
-    </row>
-    <row r="49" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B49" s="205" t="s">
+      <c r="H48" s="251"/>
+    </row>
+    <row r="49" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C49" s="206" t="s">
+      <c r="C49" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="168" t="s">
+      <c r="D49" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E49" s="207">
-        <v>0</v>
-      </c>
-      <c r="H49" s="204"/>
-    </row>
-    <row r="50" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50" s="205" t="s">
+      <c r="E49" s="169">
+        <v>0</v>
+      </c>
+      <c r="H49" s="251"/>
+    </row>
+    <row r="50" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C50" s="206" t="s">
+      <c r="C50" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D50" s="168" t="s">
+      <c r="D50" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E50" s="207">
+      <c r="E50" s="169">
         <v>0.94</v>
       </c>
-      <c r="H50" s="204"/>
-    </row>
-    <row r="51" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B51" s="205" t="s">
+      <c r="H50" s="251"/>
+    </row>
+    <row r="51" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C51" s="206" t="s">
+      <c r="C51" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D51" s="168" t="s">
+      <c r="D51" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E51" s="207">
+      <c r="E51" s="169">
         <v>0.06</v>
       </c>
-      <c r="H51" s="204"/>
-    </row>
-    <row r="52" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B52" s="205" t="s">
+      <c r="H51" s="251"/>
+    </row>
+    <row r="52" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C52" s="206" t="s">
+      <c r="C52" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D52" s="168" t="s">
+      <c r="D52" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E52" s="207">
-        <v>0</v>
-      </c>
-      <c r="H52" s="204"/>
-    </row>
-    <row r="53" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B53" s="205" t="s">
+      <c r="E52" s="169">
+        <v>0</v>
+      </c>
+      <c r="H52" s="251"/>
+    </row>
+    <row r="53" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C53" s="206" t="s">
+      <c r="C53" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D53" s="168" t="s">
+      <c r="D53" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E53" s="207">
+      <c r="E53" s="169">
         <v>0.94</v>
       </c>
-      <c r="H53" s="204"/>
-    </row>
-    <row r="54" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B54" s="205" t="s">
+      <c r="H53" s="251"/>
+    </row>
+    <row r="54" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B54" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C54" s="206" t="s">
+      <c r="C54" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D54" s="168" t="s">
+      <c r="D54" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E54" s="207">
+      <c r="E54" s="169">
         <v>0.06</v>
       </c>
-      <c r="H54" s="204"/>
-    </row>
-    <row r="55" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B55" s="205" t="s">
+      <c r="H54" s="251"/>
+    </row>
+    <row r="55" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="C55" s="206" t="s">
+      <c r="C55" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D55" s="168" t="s">
+      <c r="D55" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E55" s="207">
-        <v>0</v>
-      </c>
-      <c r="H55" s="204"/>
-    </row>
-    <row r="56" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B56" s="205" t="s">
+      <c r="E55" s="169">
+        <v>0</v>
+      </c>
+      <c r="H55" s="251"/>
+    </row>
+    <row r="56" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C56" s="206" t="s">
+      <c r="C56" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="D56" s="168" t="s">
+      <c r="D56" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E56" s="207">
+      <c r="E56" s="169">
         <v>0.94</v>
       </c>
-      <c r="H56" s="204"/>
-    </row>
-    <row r="57" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B57" s="205" t="s">
+      <c r="H56" s="251"/>
+    </row>
+    <row r="57" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="206" t="s">
+      <c r="C57" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="D57" s="168" t="s">
+      <c r="D57" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E57" s="207">
+      <c r="E57" s="169">
         <v>0.06</v>
       </c>
-      <c r="H57" s="204"/>
-    </row>
-    <row r="58" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B58" s="205" t="s">
+      <c r="H57" s="251"/>
+    </row>
+    <row r="58" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C58" s="206" t="s">
+      <c r="C58" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="D58" s="168" t="s">
+      <c r="D58" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E58" s="207">
-        <v>0</v>
-      </c>
-      <c r="H58" s="204"/>
-    </row>
-    <row r="59" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" s="205" t="s">
+      <c r="E58" s="169">
+        <v>0</v>
+      </c>
+      <c r="H58" s="251"/>
+    </row>
+    <row r="59" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C59" s="206" t="s">
+      <c r="C59" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D59" s="168" t="s">
+      <c r="D59" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E59" s="207">
+      <c r="E59" s="169">
         <v>0.94</v>
       </c>
-      <c r="H59" s="204"/>
-    </row>
-    <row r="60" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B60" s="205" t="s">
+      <c r="H59" s="251"/>
+    </row>
+    <row r="60" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C60" s="206" t="s">
+      <c r="C60" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D60" s="168" t="s">
+      <c r="D60" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E60" s="207">
+      <c r="E60" s="169">
         <v>0.06</v>
       </c>
-      <c r="H60" s="204"/>
-    </row>
-    <row r="61" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B61" s="205" t="s">
+      <c r="H60" s="251"/>
+    </row>
+    <row r="61" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B61" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C61" s="206" t="s">
+      <c r="C61" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D61" s="168" t="s">
+      <c r="D61" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E61" s="207">
-        <v>0</v>
-      </c>
-      <c r="H61" s="204"/>
-    </row>
-    <row r="62" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B62" s="205" t="s">
+      <c r="E61" s="169">
+        <v>0</v>
+      </c>
+      <c r="H61" s="251"/>
+    </row>
+    <row r="62" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B62" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C62" s="206" t="s">
+      <c r="C62" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D62" s="168" t="s">
+      <c r="D62" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E62" s="207">
+      <c r="E62" s="169">
         <v>0.94</v>
       </c>
-      <c r="H62" s="204"/>
-    </row>
-    <row r="63" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B63" s="205" t="s">
+      <c r="H62" s="251"/>
+    </row>
+    <row r="63" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C63" s="206" t="s">
+      <c r="C63" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D63" s="168" t="s">
+      <c r="D63" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E63" s="207">
+      <c r="E63" s="169">
         <v>0.06</v>
       </c>
-      <c r="H63" s="204"/>
-    </row>
-    <row r="64" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B64" s="205" t="s">
+      <c r="H63" s="251"/>
+    </row>
+    <row r="64" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C64" s="206" t="s">
+      <c r="C64" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D64" s="168" t="s">
+      <c r="D64" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E64" s="207">
-        <v>0</v>
-      </c>
-      <c r="H64" s="204"/>
-    </row>
-    <row r="65" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B65" s="205" t="s">
+      <c r="E64" s="169">
+        <v>0</v>
+      </c>
+      <c r="H64" s="251"/>
+    </row>
+    <row r="65" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C65" s="206" t="s">
+      <c r="C65" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D65" s="168" t="s">
+      <c r="D65" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E65" s="207">
+      <c r="E65" s="169">
         <v>0.94</v>
       </c>
-      <c r="H65" s="204"/>
-    </row>
-    <row r="66" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B66" s="205" t="s">
+      <c r="H65" s="251"/>
+    </row>
+    <row r="66" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C66" s="206" t="s">
+      <c r="C66" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D66" s="168" t="s">
+      <c r="D66" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E66" s="207">
+      <c r="E66" s="169">
         <v>0.06</v>
       </c>
-      <c r="H66" s="204"/>
-    </row>
-    <row r="67" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B67" s="205" t="s">
+      <c r="H66" s="251"/>
+    </row>
+    <row r="67" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B67" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C67" s="206" t="s">
+      <c r="C67" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D67" s="168" t="s">
+      <c r="D67" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E67" s="207">
-        <v>0</v>
-      </c>
-      <c r="H67" s="204"/>
-    </row>
-    <row r="68" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B68" s="205" t="s">
+      <c r="E67" s="169">
+        <v>0</v>
+      </c>
+      <c r="H67" s="251"/>
+    </row>
+    <row r="68" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B68" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C68" s="206" t="s">
+      <c r="C68" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D68" s="168" t="s">
+      <c r="D68" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E68" s="207">
+      <c r="E68" s="169">
         <v>0.94</v>
       </c>
-      <c r="H68" s="204"/>
-    </row>
-    <row r="69" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B69" s="205" t="s">
+      <c r="H68" s="251"/>
+    </row>
+    <row r="69" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B69" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C69" s="206" t="s">
+      <c r="C69" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D69" s="168" t="s">
+      <c r="D69" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E69" s="207">
+      <c r="E69" s="169">
         <v>0.06</v>
       </c>
-      <c r="H69" s="204"/>
-    </row>
-    <row r="70" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B70" s="205" t="s">
+      <c r="H69" s="251"/>
+    </row>
+    <row r="70" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B70" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C70" s="206" t="s">
+      <c r="C70" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D70" s="168" t="s">
+      <c r="D70" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E70" s="207">
-        <v>0</v>
-      </c>
-      <c r="H70" s="204"/>
-    </row>
-    <row r="71" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B71" s="205" t="s">
+      <c r="E70" s="169">
+        <v>0</v>
+      </c>
+      <c r="H70" s="251"/>
+    </row>
+    <row r="71" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B71" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C71" s="206" t="s">
+      <c r="C71" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D71" s="168" t="s">
+      <c r="D71" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E71" s="207">
+      <c r="E71" s="169">
         <v>0.94</v>
       </c>
-      <c r="H71" s="204"/>
-    </row>
-    <row r="72" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B72" s="205" t="s">
+      <c r="H71" s="251"/>
+    </row>
+    <row r="72" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B72" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C72" s="206" t="s">
+      <c r="C72" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D72" s="168" t="s">
+      <c r="D72" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E72" s="207">
+      <c r="E72" s="169">
         <v>0.06</v>
       </c>
-      <c r="H72" s="204"/>
-    </row>
-    <row r="73" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B73" s="205" t="s">
+      <c r="H72" s="251"/>
+    </row>
+    <row r="73" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B73" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="C73" s="206" t="s">
+      <c r="C73" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D73" s="168" t="s">
+      <c r="D73" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E73" s="207">
-        <v>0</v>
-      </c>
-      <c r="H73" s="204"/>
-    </row>
-    <row r="74" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B74" s="205" t="s">
+      <c r="E73" s="169">
+        <v>0</v>
+      </c>
+      <c r="H73" s="251"/>
+    </row>
+    <row r="74" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B74" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C74" s="206" t="s">
+      <c r="C74" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="D74" s="168" t="s">
+      <c r="D74" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E74" s="207">
+      <c r="E74" s="169">
         <v>0.94</v>
       </c>
-      <c r="H74" s="204"/>
-    </row>
-    <row r="75" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B75" s="205" t="s">
+      <c r="H74" s="251"/>
+    </row>
+    <row r="75" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B75" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C75" s="206" t="s">
+      <c r="C75" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="D75" s="168" t="s">
+      <c r="D75" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E75" s="207">
+      <c r="E75" s="169">
         <v>0.06</v>
       </c>
-      <c r="H75" s="204"/>
-    </row>
-    <row r="76" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B76" s="205" t="s">
+      <c r="H75" s="251"/>
+    </row>
+    <row r="76" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B76" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C76" s="206" t="s">
+      <c r="C76" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="D76" s="168" t="s">
+      <c r="D76" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E76" s="207">
-        <v>0</v>
-      </c>
-      <c r="H76" s="204"/>
-    </row>
-    <row r="77" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B77" s="205" t="s">
+      <c r="E76" s="169">
+        <v>0</v>
+      </c>
+      <c r="H76" s="251"/>
+    </row>
+    <row r="77" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B77" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C77" s="206" t="s">
+      <c r="C77" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D77" s="168" t="s">
+      <c r="D77" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E77" s="207">
+      <c r="E77" s="169">
         <v>0.94</v>
       </c>
-      <c r="H77" s="204"/>
-    </row>
-    <row r="78" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B78" s="205" t="s">
+      <c r="H77" s="251"/>
+    </row>
+    <row r="78" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B78" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C78" s="206" t="s">
+      <c r="C78" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D78" s="168" t="s">
+      <c r="D78" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E78" s="207">
+      <c r="E78" s="169">
         <v>0.06</v>
       </c>
-      <c r="H78" s="204"/>
-    </row>
-    <row r="79" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B79" s="205" t="s">
+      <c r="H78" s="251"/>
+    </row>
+    <row r="79" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B79" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C79" s="206" t="s">
+      <c r="C79" s="168" t="s">
         <v>123</v>
       </c>
-      <c r="D79" s="168" t="s">
+      <c r="D79" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E79" s="207">
-        <v>0</v>
-      </c>
-      <c r="H79" s="204"/>
-    </row>
-    <row r="80" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B80" s="205" t="s">
+      <c r="E79" s="169">
+        <v>0</v>
+      </c>
+      <c r="H79" s="251"/>
+    </row>
+    <row r="80" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B80" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C80" s="206" t="s">
+      <c r="C80" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D80" s="168" t="s">
+      <c r="D80" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E80" s="207">
+      <c r="E80" s="169">
         <v>0.94</v>
       </c>
-      <c r="H80" s="204"/>
-    </row>
-    <row r="81" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B81" s="205" t="s">
+      <c r="H80" s="251"/>
+    </row>
+    <row r="81" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B81" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C81" s="206" t="s">
+      <c r="C81" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D81" s="168" t="s">
+      <c r="D81" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E81" s="207">
+      <c r="E81" s="169">
         <v>0.06</v>
       </c>
-      <c r="H81" s="204"/>
-    </row>
-    <row r="82" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B82" s="205" t="s">
+      <c r="H81" s="251"/>
+    </row>
+    <row r="82" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B82" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C82" s="206" t="s">
+      <c r="C82" s="168" t="s">
         <v>122</v>
       </c>
-      <c r="D82" s="168" t="s">
+      <c r="D82" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E82" s="207">
-        <v>0</v>
-      </c>
-      <c r="H82" s="204"/>
-    </row>
-    <row r="83" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B83" s="205" t="s">
+      <c r="E82" s="169">
+        <v>0</v>
+      </c>
+      <c r="H82" s="251"/>
+    </row>
+    <row r="83" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B83" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C83" s="206" t="s">
+      <c r="C83" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D83" s="168" t="s">
+      <c r="D83" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E83" s="207">
+      <c r="E83" s="169">
         <v>0.94</v>
       </c>
-      <c r="H83" s="204"/>
-    </row>
-    <row r="84" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B84" s="205" t="s">
+      <c r="H83" s="251"/>
+    </row>
+    <row r="84" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B84" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C84" s="206" t="s">
+      <c r="C84" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D84" s="168" t="s">
+      <c r="D84" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E84" s="207">
+      <c r="E84" s="169">
         <v>0.06</v>
       </c>
-      <c r="H84" s="204"/>
-    </row>
-    <row r="85" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B85" s="205" t="s">
+      <c r="H84" s="251"/>
+    </row>
+    <row r="85" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B85" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C85" s="206" t="s">
+      <c r="C85" s="168" t="s">
         <v>121</v>
       </c>
-      <c r="D85" s="168" t="s">
+      <c r="D85" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E85" s="207">
-        <v>0</v>
-      </c>
-      <c r="H85" s="204"/>
-    </row>
-    <row r="86" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B86" s="205" t="s">
+      <c r="E85" s="169">
+        <v>0</v>
+      </c>
+      <c r="H85" s="251"/>
+    </row>
+    <row r="86" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B86" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C86" s="206" t="s">
+      <c r="C86" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D86" s="168" t="s">
+      <c r="D86" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E86" s="207">
+      <c r="E86" s="169">
         <v>0.94</v>
       </c>
-      <c r="H86" s="204"/>
-    </row>
-    <row r="87" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B87" s="205" t="s">
+      <c r="H86" s="251"/>
+    </row>
+    <row r="87" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B87" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C87" s="206" t="s">
+      <c r="C87" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D87" s="168" t="s">
+      <c r="D87" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E87" s="207">
+      <c r="E87" s="169">
         <v>0.06</v>
       </c>
-      <c r="H87" s="204"/>
-    </row>
-    <row r="88" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B88" s="205" t="s">
+      <c r="H87" s="251"/>
+    </row>
+    <row r="88" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B88" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C88" s="206" t="s">
+      <c r="C88" s="168" t="s">
         <v>120</v>
       </c>
-      <c r="D88" s="168" t="s">
+      <c r="D88" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E88" s="207">
-        <v>0</v>
-      </c>
-      <c r="H88" s="204"/>
-    </row>
-    <row r="89" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B89" s="205" t="s">
+      <c r="E88" s="169">
+        <v>0</v>
+      </c>
+      <c r="H88" s="251"/>
+    </row>
+    <row r="89" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B89" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C89" s="206" t="s">
+      <c r="C89" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D89" s="168" t="s">
+      <c r="D89" s="141" t="s">
         <v>125</v>
       </c>
-      <c r="E89" s="207">
+      <c r="E89" s="169">
         <v>0.94</v>
       </c>
-      <c r="H89" s="204"/>
-    </row>
-    <row r="90" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B90" s="205" t="s">
+      <c r="H89" s="251"/>
+    </row>
+    <row r="90" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B90" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C90" s="206" t="s">
+      <c r="C90" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D90" s="168" t="s">
+      <c r="D90" s="141" t="s">
         <v>119</v>
       </c>
-      <c r="E90" s="207">
+      <c r="E90" s="169">
         <v>0.06</v>
       </c>
-      <c r="H90" s="204"/>
-    </row>
-    <row r="91" spans="1:8" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="167" t="s">
-        <v>126</v>
-      </c>
-      <c r="B91" s="205" t="s">
+      <c r="H90" s="251"/>
+    </row>
+    <row r="91" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="140" t="s">
+        <v>126</v>
+      </c>
+      <c r="B91" s="167" t="s">
         <v>111</v>
       </c>
-      <c r="C91" s="206" t="s">
+      <c r="C91" s="168" t="s">
         <v>118</v>
       </c>
-      <c r="D91" s="168" t="s">
+      <c r="D91" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E91" s="207">
-        <v>0</v>
-      </c>
-      <c r="F91" s="208"/>
-      <c r="H91" s="204"/>
-    </row>
-    <row r="92" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="169" t="s">
+      <c r="E91" s="169">
+        <v>0</v>
+      </c>
+      <c r="F91" s="170"/>
+      <c r="H91" s="251"/>
+    </row>
+    <row r="92" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B92" s="188" t="s">
+      <c r="B92" s="151" t="s">
         <v>116</v>
       </c>
-      <c r="C92" s="189" t="s">
+      <c r="C92" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D92" s="170" t="s">
+      <c r="D92" s="143" t="s">
         <v>132</v>
       </c>
-      <c r="E92" s="190">
+      <c r="E92" s="153">
         <v>0.96</v>
       </c>
-      <c r="F92" s="191"/>
-      <c r="H92" s="193" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="169" t="s">
+      <c r="F92" s="154"/>
+      <c r="H92" s="252" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B93" s="188" t="s">
+      <c r="B93" s="151" t="s">
         <v>116</v>
       </c>
-      <c r="C93" s="189" t="s">
+      <c r="C93" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D93" s="170" t="s">
+      <c r="D93" s="143" t="s">
         <v>131</v>
       </c>
-      <c r="E93" s="190">
-        <v>0</v>
-      </c>
-      <c r="F93" s="191"/>
-      <c r="H93" s="193"/>
-    </row>
-    <row r="94" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="169" t="s">
+      <c r="E93" s="153">
+        <v>0</v>
+      </c>
+      <c r="F93" s="154"/>
+      <c r="H93" s="252"/>
+    </row>
+    <row r="94" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B94" s="188" t="s">
+      <c r="B94" s="151" t="s">
         <v>116</v>
       </c>
-      <c r="C94" s="189" t="s">
+      <c r="C94" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D94" s="170" t="s">
+      <c r="D94" s="143" t="s">
         <v>133</v>
       </c>
-      <c r="E94" s="190">
+      <c r="E94" s="153">
         <v>0.04</v>
       </c>
-      <c r="F94" s="191"/>
-      <c r="H94" s="193"/>
-    </row>
-    <row r="95" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="169" t="s">
+      <c r="F94" s="154"/>
+      <c r="H94" s="252"/>
+    </row>
+    <row r="95" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B95" s="188" t="s">
+      <c r="B95" s="151" t="s">
         <v>116</v>
       </c>
-      <c r="C95" s="189" t="s">
+      <c r="C95" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D95" s="170" t="s">
+      <c r="D95" s="143" t="s">
         <v>117</v>
       </c>
-      <c r="E95" s="190">
-        <v>0</v>
-      </c>
-      <c r="F95" s="191"/>
-      <c r="H95" s="193"/>
-    </row>
-    <row r="96" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="169" t="s">
+      <c r="E95" s="153">
+        <v>0</v>
+      </c>
+      <c r="F95" s="154"/>
+      <c r="H95" s="252"/>
+    </row>
+    <row r="96" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B96" s="188" t="s">
+      <c r="B96" s="151" t="s">
         <v>115</v>
       </c>
-      <c r="C96" s="189" t="s">
+      <c r="C96" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D96" s="170" t="s">
+      <c r="D96" s="143" t="s">
         <v>132</v>
       </c>
-      <c r="E96" s="190">
+      <c r="E96" s="153">
         <v>0.96</v>
       </c>
-      <c r="F96" s="191"/>
-      <c r="H96" s="193"/>
-    </row>
-    <row r="97" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="169" t="s">
+      <c r="F96" s="154"/>
+      <c r="H96" s="252"/>
+    </row>
+    <row r="97" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B97" s="188" t="s">
+      <c r="B97" s="151" t="s">
         <v>115</v>
       </c>
-      <c r="C97" s="189" t="s">
+      <c r="C97" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D97" s="170" t="s">
+      <c r="D97" s="143" t="s">
         <v>131</v>
       </c>
-      <c r="E97" s="190">
-        <v>0</v>
-      </c>
-      <c r="F97" s="191"/>
-      <c r="H97" s="193"/>
-    </row>
-    <row r="98" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="169" t="s">
+      <c r="E97" s="153">
+        <v>0</v>
+      </c>
+      <c r="F97" s="154"/>
+      <c r="H97" s="252"/>
+    </row>
+    <row r="98" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B98" s="188" t="s">
+      <c r="B98" s="151" t="s">
         <v>115</v>
       </c>
-      <c r="C98" s="189" t="s">
+      <c r="C98" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D98" s="170" t="s">
+      <c r="D98" s="143" t="s">
         <v>133</v>
       </c>
-      <c r="E98" s="190">
+      <c r="E98" s="153">
         <v>0.04</v>
       </c>
-      <c r="F98" s="191"/>
-      <c r="H98" s="193"/>
-    </row>
-    <row r="99" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="169" t="s">
+      <c r="F98" s="154"/>
+      <c r="H98" s="252"/>
+    </row>
+    <row r="99" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B99" s="188" t="s">
+      <c r="B99" s="151" t="s">
         <v>115</v>
       </c>
-      <c r="C99" s="189" t="s">
+      <c r="C99" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D99" s="170" t="s">
+      <c r="D99" s="143" t="s">
         <v>117</v>
       </c>
-      <c r="E99" s="190">
-        <v>0</v>
-      </c>
-      <c r="F99" s="191"/>
-      <c r="H99" s="193"/>
-    </row>
-    <row r="100" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="169" t="s">
+      <c r="E99" s="153">
+        <v>0</v>
+      </c>
+      <c r="F99" s="154"/>
+      <c r="H99" s="252"/>
+    </row>
+    <row r="100" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B100" s="188" t="s">
+      <c r="B100" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="C100" s="189" t="s">
+      <c r="C100" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D100" s="170" t="s">
+      <c r="D100" s="143" t="s">
         <v>132</v>
       </c>
-      <c r="E100" s="190">
+      <c r="E100" s="153">
         <v>0.96</v>
       </c>
-      <c r="F100" s="191"/>
-      <c r="H100" s="193"/>
-    </row>
-    <row r="101" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="169" t="s">
+      <c r="F100" s="154"/>
+      <c r="H100" s="252"/>
+    </row>
+    <row r="101" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B101" s="188" t="s">
+      <c r="B101" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="C101" s="189" t="s">
+      <c r="C101" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="170" t="s">
+      <c r="D101" s="143" t="s">
         <v>131</v>
       </c>
-      <c r="E101" s="190">
-        <v>0</v>
-      </c>
-      <c r="F101" s="191"/>
-      <c r="H101" s="193"/>
-    </row>
-    <row r="102" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="169" t="s">
+      <c r="E101" s="153">
+        <v>0</v>
+      </c>
+      <c r="F101" s="154"/>
+      <c r="H101" s="252"/>
+    </row>
+    <row r="102" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B102" s="188" t="s">
+      <c r="B102" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="C102" s="189" t="s">
+      <c r="C102" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D102" s="170" t="s">
+      <c r="D102" s="143" t="s">
         <v>133</v>
       </c>
-      <c r="E102" s="190">
+      <c r="E102" s="153">
         <v>0.04</v>
       </c>
-      <c r="F102" s="191"/>
-      <c r="H102" s="193"/>
-    </row>
-    <row r="103" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="169" t="s">
+      <c r="F102" s="154"/>
+      <c r="H102" s="252"/>
+    </row>
+    <row r="103" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B103" s="188" t="s">
+      <c r="B103" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="C103" s="189" t="s">
+      <c r="C103" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D103" s="170" t="s">
+      <c r="D103" s="143" t="s">
         <v>117</v>
       </c>
-      <c r="E103" s="190">
-        <v>0</v>
-      </c>
-      <c r="F103" s="191"/>
-      <c r="H103" s="193"/>
-    </row>
-    <row r="104" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="169" t="s">
+      <c r="E103" s="153">
+        <v>0</v>
+      </c>
+      <c r="F103" s="154"/>
+      <c r="H103" s="252"/>
+    </row>
+    <row r="104" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B104" s="188" t="s">
+      <c r="B104" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="C104" s="189" t="s">
+      <c r="C104" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D104" s="170" t="s">
+      <c r="D104" s="143" t="s">
         <v>132</v>
       </c>
-      <c r="E104" s="190">
+      <c r="E104" s="153">
         <v>0.3</v>
       </c>
-      <c r="F104" s="191"/>
-      <c r="H104" s="193"/>
-    </row>
-    <row r="105" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="169" t="s">
+      <c r="F104" s="154"/>
+      <c r="H104" s="252"/>
+    </row>
+    <row r="105" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B105" s="188" t="s">
+      <c r="B105" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="C105" s="189" t="s">
+      <c r="C105" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D105" s="170" t="s">
+      <c r="D105" s="143" t="s">
         <v>131</v>
       </c>
-      <c r="E105" s="190">
-        <v>0</v>
-      </c>
-      <c r="F105" s="191"/>
-      <c r="H105" s="193"/>
-    </row>
-    <row r="106" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="169" t="s">
+      <c r="E105" s="153">
+        <v>0</v>
+      </c>
+      <c r="F105" s="154"/>
+      <c r="H105" s="252"/>
+    </row>
+    <row r="106" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B106" s="188" t="s">
+      <c r="B106" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="C106" s="189" t="s">
+      <c r="C106" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D106" s="170" t="s">
+      <c r="D106" s="143" t="s">
         <v>133</v>
       </c>
-      <c r="E106" s="190">
+      <c r="E106" s="153">
         <v>0.7</v>
       </c>
-      <c r="F106" s="191"/>
-      <c r="H106" s="193"/>
-    </row>
-    <row r="107" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="169" t="s">
+      <c r="F106" s="154"/>
+      <c r="H106" s="252"/>
+    </row>
+    <row r="107" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B107" s="188" t="s">
+      <c r="B107" s="151" t="s">
         <v>113</v>
       </c>
-      <c r="C107" s="189" t="s">
+      <c r="C107" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D107" s="170" t="s">
+      <c r="D107" s="143" t="s">
         <v>117</v>
       </c>
-      <c r="E107" s="190">
-        <v>0</v>
-      </c>
-      <c r="F107" s="191"/>
-      <c r="H107" s="193"/>
-    </row>
-    <row r="108" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="169" t="s">
+      <c r="E107" s="153">
+        <v>0</v>
+      </c>
+      <c r="F107" s="154"/>
+      <c r="H107" s="252"/>
+    </row>
+    <row r="108" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B108" s="188" t="s">
+      <c r="B108" s="151" t="s">
         <v>111</v>
       </c>
-      <c r="C108" s="189" t="s">
+      <c r="C108" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D108" s="170" t="s">
+      <c r="D108" s="143" t="s">
         <v>132</v>
       </c>
-      <c r="E108" s="190">
-        <v>0</v>
-      </c>
-      <c r="F108" s="191"/>
-      <c r="H108" s="193"/>
-    </row>
-    <row r="109" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="169" t="s">
+      <c r="E108" s="153">
+        <v>0</v>
+      </c>
+      <c r="F108" s="154"/>
+      <c r="H108" s="252"/>
+    </row>
+    <row r="109" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B109" s="188" t="s">
+      <c r="B109" s="151" t="s">
         <v>111</v>
       </c>
-      <c r="C109" s="189" t="s">
+      <c r="C109" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D109" s="170" t="s">
+      <c r="D109" s="143" t="s">
         <v>131</v>
       </c>
-      <c r="E109" s="190">
-        <v>0</v>
-      </c>
-      <c r="F109" s="191"/>
-      <c r="H109" s="193"/>
-    </row>
-    <row r="110" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="169" t="s">
+      <c r="E109" s="153">
+        <v>0</v>
+      </c>
+      <c r="F109" s="154"/>
+      <c r="H109" s="252"/>
+    </row>
+    <row r="110" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B110" s="188" t="s">
+      <c r="B110" s="151" t="s">
         <v>111</v>
       </c>
-      <c r="C110" s="189" t="s">
+      <c r="C110" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D110" s="170" t="s">
+      <c r="D110" s="143" t="s">
         <v>133</v>
       </c>
-      <c r="E110" s="190">
+      <c r="E110" s="153">
         <v>1</v>
       </c>
-      <c r="F110" s="191"/>
-      <c r="H110" s="193"/>
-    </row>
-    <row r="111" spans="1:8" s="192" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="169" t="s">
+      <c r="F110" s="154"/>
+      <c r="H110" s="252"/>
+    </row>
+    <row r="111" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="B111" s="188" t="s">
+      <c r="B111" s="151" t="s">
         <v>111</v>
       </c>
-      <c r="C111" s="189" t="s">
+      <c r="C111" s="152" t="s">
         <v>110</v>
       </c>
-      <c r="D111" s="170" t="s">
+      <c r="D111" s="143" t="s">
         <v>117</v>
       </c>
-      <c r="E111" s="190">
-        <v>0</v>
-      </c>
-      <c r="F111" s="191"/>
-      <c r="H111" s="193"/>
-    </row>
-    <row r="112" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="171" t="s">
+      <c r="E111" s="153">
+        <v>0</v>
+      </c>
+      <c r="F111" s="154"/>
+      <c r="H111" s="252"/>
+    </row>
+    <row r="112" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B112" s="209" t="s">
+      <c r="B112" s="171" t="s">
         <v>116</v>
       </c>
-      <c r="C112" s="210" t="s">
+      <c r="C112" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D112" s="172" t="s">
+      <c r="D112" s="145" t="s">
         <v>132</v>
       </c>
-      <c r="E112" s="211">
+      <c r="E112" s="173">
         <v>0.7</v>
       </c>
-      <c r="H112" s="213" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="171" t="s">
+      <c r="H112" s="253" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B113" s="209" t="s">
+      <c r="B113" s="171" t="s">
         <v>116</v>
       </c>
-      <c r="C113" s="210" t="s">
+      <c r="C113" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D113" s="172" t="s">
+      <c r="D113" s="145" t="s">
         <v>131</v>
       </c>
-      <c r="E113" s="211">
-        <v>0</v>
-      </c>
-      <c r="H113" s="213"/>
-    </row>
-    <row r="114" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="171" t="s">
+      <c r="E113" s="173">
+        <v>0</v>
+      </c>
+      <c r="H113" s="253"/>
+    </row>
+    <row r="114" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B114" s="209" t="s">
+      <c r="B114" s="171" t="s">
         <v>116</v>
       </c>
-      <c r="C114" s="210" t="s">
+      <c r="C114" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D114" s="172" t="s">
+      <c r="D114" s="145" t="s">
         <v>130</v>
       </c>
-      <c r="E114" s="211">
-        <v>0</v>
-      </c>
-      <c r="H114" s="213"/>
-    </row>
-    <row r="115" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="171" t="s">
+      <c r="E114" s="173">
+        <v>0</v>
+      </c>
+      <c r="H114" s="253"/>
+    </row>
+    <row r="115" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B115" s="209" t="s">
+      <c r="B115" s="171" t="s">
         <v>116</v>
       </c>
-      <c r="C115" s="210" t="s">
+      <c r="C115" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D115" s="172" t="s">
+      <c r="D115" s="145" t="s">
         <v>129</v>
       </c>
-      <c r="E115" s="211">
+      <c r="E115" s="173">
         <v>0.3</v>
       </c>
-      <c r="H115" s="213"/>
-    </row>
-    <row r="116" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="171" t="s">
+      <c r="H115" s="253"/>
+    </row>
+    <row r="116" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B116" s="209" t="s">
+      <c r="B116" s="171" t="s">
         <v>116</v>
       </c>
-      <c r="C116" s="210" t="s">
+      <c r="C116" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D116" s="172" t="s">
+      <c r="D116" s="145" t="s">
         <v>128</v>
       </c>
-      <c r="E116" s="211">
-        <v>0</v>
-      </c>
-      <c r="H116" s="213"/>
-    </row>
-    <row r="117" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="171" t="s">
+      <c r="E116" s="173">
+        <v>0</v>
+      </c>
+      <c r="H116" s="253"/>
+    </row>
+    <row r="117" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B117" s="209" t="s">
+      <c r="B117" s="171" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="210" t="s">
+      <c r="C117" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D117" s="172" t="s">
+      <c r="D117" s="145" t="s">
         <v>117</v>
       </c>
-      <c r="E117" s="211">
-        <v>0</v>
-      </c>
-      <c r="H117" s="213"/>
-    </row>
-    <row r="118" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="171" t="s">
+      <c r="E117" s="173">
+        <v>0</v>
+      </c>
+      <c r="H117" s="253"/>
+    </row>
+    <row r="118" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B118" s="209" t="s">
+      <c r="B118" s="171" t="s">
         <v>115</v>
       </c>
-      <c r="C118" s="210" t="s">
+      <c r="C118" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D118" s="172" t="s">
+      <c r="D118" s="145" t="s">
         <v>132</v>
       </c>
-      <c r="E118" s="211">
+      <c r="E118" s="173">
         <v>0.6</v>
       </c>
-      <c r="H118" s="213"/>
-    </row>
-    <row r="119" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="171" t="s">
+      <c r="H118" s="253"/>
+    </row>
+    <row r="119" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B119" s="209" t="s">
+      <c r="B119" s="171" t="s">
         <v>115</v>
       </c>
-      <c r="C119" s="210" t="s">
+      <c r="C119" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D119" s="172" t="s">
+      <c r="D119" s="145" t="s">
         <v>131</v>
       </c>
-      <c r="E119" s="211">
-        <v>0</v>
-      </c>
-      <c r="H119" s="213"/>
-    </row>
-    <row r="120" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="171" t="s">
+      <c r="E119" s="173">
+        <v>0</v>
+      </c>
+      <c r="H119" s="253"/>
+    </row>
+    <row r="120" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B120" s="209" t="s">
+      <c r="B120" s="171" t="s">
         <v>115</v>
       </c>
-      <c r="C120" s="210" t="s">
+      <c r="C120" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D120" s="172" t="s">
+      <c r="D120" s="145" t="s">
         <v>130</v>
       </c>
-      <c r="E120" s="211">
-        <v>0</v>
-      </c>
-      <c r="H120" s="213"/>
-    </row>
-    <row r="121" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="171" t="s">
+      <c r="E120" s="173">
+        <v>0</v>
+      </c>
+      <c r="H120" s="253"/>
+    </row>
+    <row r="121" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B121" s="209" t="s">
+      <c r="B121" s="171" t="s">
         <v>115</v>
       </c>
-      <c r="C121" s="210" t="s">
+      <c r="C121" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D121" s="172" t="s">
+      <c r="D121" s="145" t="s">
         <v>129</v>
       </c>
-      <c r="E121" s="211">
+      <c r="E121" s="173">
         <v>0.4</v>
       </c>
-      <c r="H121" s="213"/>
-    </row>
-    <row r="122" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="171" t="s">
+      <c r="H121" s="253"/>
+    </row>
+    <row r="122" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B122" s="209" t="s">
+      <c r="B122" s="171" t="s">
         <v>115</v>
       </c>
-      <c r="C122" s="210" t="s">
+      <c r="C122" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D122" s="172" t="s">
+      <c r="D122" s="145" t="s">
         <v>128</v>
       </c>
-      <c r="E122" s="211">
-        <v>0</v>
-      </c>
-      <c r="H122" s="213"/>
-    </row>
-    <row r="123" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="171" t="s">
+      <c r="E122" s="173">
+        <v>0</v>
+      </c>
+      <c r="H122" s="253"/>
+    </row>
+    <row r="123" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B123" s="209" t="s">
+      <c r="B123" s="171" t="s">
         <v>115</v>
       </c>
-      <c r="C123" s="210" t="s">
+      <c r="C123" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D123" s="172" t="s">
+      <c r="D123" s="145" t="s">
         <v>117</v>
       </c>
-      <c r="E123" s="211">
-        <v>0</v>
-      </c>
-      <c r="H123" s="213"/>
-    </row>
-    <row r="124" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="171" t="s">
+      <c r="E123" s="173">
+        <v>0</v>
+      </c>
+      <c r="H123" s="253"/>
+    </row>
+    <row r="124" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B124" s="209" t="s">
+      <c r="B124" s="171" t="s">
         <v>114</v>
       </c>
-      <c r="C124" s="210" t="s">
+      <c r="C124" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D124" s="172" t="s">
+      <c r="D124" s="145" t="s">
         <v>132</v>
       </c>
-      <c r="E124" s="211">
+      <c r="E124" s="173">
         <v>0.42</v>
       </c>
-      <c r="H124" s="213"/>
-    </row>
-    <row r="125" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="171" t="s">
+      <c r="H124" s="253"/>
+    </row>
+    <row r="125" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B125" s="209" t="s">
+      <c r="B125" s="171" t="s">
         <v>114</v>
       </c>
-      <c r="C125" s="210" t="s">
+      <c r="C125" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D125" s="172" t="s">
+      <c r="D125" s="145" t="s">
         <v>131</v>
       </c>
-      <c r="E125" s="211">
-        <v>0</v>
-      </c>
-      <c r="H125" s="213"/>
-    </row>
-    <row r="126" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="171" t="s">
+      <c r="E125" s="173">
+        <v>0</v>
+      </c>
+      <c r="H125" s="253"/>
+    </row>
+    <row r="126" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B126" s="209" t="s">
+      <c r="B126" s="171" t="s">
         <v>114</v>
       </c>
-      <c r="C126" s="210" t="s">
+      <c r="C126" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D126" s="172" t="s">
+      <c r="D126" s="145" t="s">
         <v>130</v>
       </c>
-      <c r="E126" s="211">
-        <v>0</v>
-      </c>
-      <c r="H126" s="213"/>
-    </row>
-    <row r="127" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="171" t="s">
+      <c r="E126" s="173">
+        <v>0</v>
+      </c>
+      <c r="H126" s="253"/>
+    </row>
+    <row r="127" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B127" s="209" t="s">
+      <c r="B127" s="171" t="s">
         <v>114</v>
       </c>
-      <c r="C127" s="210" t="s">
+      <c r="C127" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D127" s="172" t="s">
+      <c r="D127" s="145" t="s">
         <v>129</v>
       </c>
-      <c r="E127" s="211">
+      <c r="E127" s="173">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H127" s="213"/>
-    </row>
-    <row r="128" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="171" t="s">
+      <c r="H127" s="253"/>
+    </row>
+    <row r="128" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B128" s="209" t="s">
+      <c r="B128" s="171" t="s">
         <v>114</v>
       </c>
-      <c r="C128" s="210" t="s">
+      <c r="C128" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D128" s="172" t="s">
+      <c r="D128" s="145" t="s">
         <v>128</v>
       </c>
-      <c r="E128" s="211">
-        <v>0</v>
-      </c>
-      <c r="H128" s="213"/>
-    </row>
-    <row r="129" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="171" t="s">
+      <c r="E128" s="173">
+        <v>0</v>
+      </c>
+      <c r="H128" s="253"/>
+    </row>
+    <row r="129" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B129" s="209" t="s">
+      <c r="B129" s="171" t="s">
         <v>114</v>
       </c>
-      <c r="C129" s="210" t="s">
+      <c r="C129" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D129" s="172" t="s">
+      <c r="D129" s="145" t="s">
         <v>117</v>
       </c>
-      <c r="E129" s="211">
-        <v>0</v>
-      </c>
-      <c r="H129" s="213"/>
-    </row>
-    <row r="130" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="171" t="s">
+      <c r="E129" s="173">
+        <v>0</v>
+      </c>
+      <c r="H129" s="253"/>
+    </row>
+    <row r="130" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B130" s="209" t="s">
+      <c r="B130" s="171" t="s">
         <v>113</v>
       </c>
-      <c r="C130" s="210" t="s">
+      <c r="C130" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D130" s="172" t="s">
+      <c r="D130" s="145" t="s">
         <v>132</v>
       </c>
-      <c r="E130" s="211">
+      <c r="E130" s="173">
         <v>0.05</v>
       </c>
-      <c r="H130" s="213"/>
-    </row>
-    <row r="131" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="171" t="s">
+      <c r="H130" s="253"/>
+    </row>
+    <row r="131" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B131" s="209" t="s">
+      <c r="B131" s="171" t="s">
         <v>113</v>
       </c>
-      <c r="C131" s="210" t="s">
+      <c r="C131" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D131" s="172" t="s">
+      <c r="D131" s="145" t="s">
         <v>131</v>
       </c>
-      <c r="E131" s="211">
-        <v>0</v>
-      </c>
-      <c r="H131" s="213"/>
-    </row>
-    <row r="132" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="171" t="s">
+      <c r="E131" s="173">
+        <v>0</v>
+      </c>
+      <c r="H131" s="253"/>
+    </row>
+    <row r="132" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B132" s="209" t="s">
+      <c r="B132" s="171" t="s">
         <v>113</v>
       </c>
-      <c r="C132" s="210" t="s">
+      <c r="C132" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D132" s="172" t="s">
+      <c r="D132" s="145" t="s">
         <v>130</v>
       </c>
-      <c r="E132" s="211">
-        <v>0</v>
-      </c>
-      <c r="H132" s="213"/>
-    </row>
-    <row r="133" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="171" t="s">
+      <c r="E132" s="173">
+        <v>0</v>
+      </c>
+      <c r="H132" s="253"/>
+    </row>
+    <row r="133" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B133" s="209" t="s">
+      <c r="B133" s="171" t="s">
         <v>113</v>
       </c>
-      <c r="C133" s="210" t="s">
+      <c r="C133" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D133" s="172" t="s">
+      <c r="D133" s="145" t="s">
         <v>129</v>
       </c>
-      <c r="E133" s="211">
+      <c r="E133" s="173">
         <v>0.95</v>
       </c>
-      <c r="H133" s="213"/>
-    </row>
-    <row r="134" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="171" t="s">
+      <c r="H133" s="253"/>
+    </row>
+    <row r="134" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B134" s="209" t="s">
+      <c r="B134" s="171" t="s">
         <v>113</v>
       </c>
-      <c r="C134" s="210" t="s">
+      <c r="C134" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D134" s="172" t="s">
+      <c r="D134" s="145" t="s">
         <v>128</v>
       </c>
-      <c r="E134" s="211">
-        <v>0</v>
-      </c>
-      <c r="H134" s="213"/>
-    </row>
-    <row r="135" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="171" t="s">
+      <c r="E134" s="173">
+        <v>0</v>
+      </c>
+      <c r="H134" s="253"/>
+    </row>
+    <row r="135" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B135" s="209" t="s">
+      <c r="B135" s="171" t="s">
         <v>113</v>
       </c>
-      <c r="C135" s="210" t="s">
+      <c r="C135" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D135" s="172" t="s">
+      <c r="D135" s="145" t="s">
         <v>117</v>
       </c>
-      <c r="E135" s="211">
-        <v>0</v>
-      </c>
-      <c r="H135" s="213"/>
-    </row>
-    <row r="136" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="171" t="s">
+      <c r="E135" s="173">
+        <v>0</v>
+      </c>
+      <c r="H135" s="253"/>
+    </row>
+    <row r="136" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B136" s="209" t="s">
+      <c r="B136" s="171" t="s">
         <v>111</v>
       </c>
-      <c r="C136" s="210" t="s">
+      <c r="C136" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D136" s="172" t="s">
+      <c r="D136" s="145" t="s">
         <v>132</v>
       </c>
-      <c r="E136" s="211">
-        <v>0</v>
-      </c>
-      <c r="H136" s="213"/>
-    </row>
-    <row r="137" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="171" t="s">
+      <c r="E136" s="173">
+        <v>0</v>
+      </c>
+      <c r="H136" s="253"/>
+    </row>
+    <row r="137" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B137" s="209" t="s">
+      <c r="B137" s="171" t="s">
         <v>111</v>
       </c>
-      <c r="C137" s="210" t="s">
+      <c r="C137" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D137" s="172" t="s">
+      <c r="D137" s="145" t="s">
         <v>131</v>
       </c>
-      <c r="E137" s="211">
-        <v>0</v>
-      </c>
-      <c r="H137" s="213"/>
-    </row>
-    <row r="138" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="171" t="s">
+      <c r="E137" s="173">
+        <v>0</v>
+      </c>
+      <c r="H137" s="253"/>
+    </row>
+    <row r="138" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B138" s="209" t="s">
+      <c r="B138" s="171" t="s">
         <v>111</v>
       </c>
-      <c r="C138" s="210" t="s">
+      <c r="C138" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D138" s="172" t="s">
+      <c r="D138" s="145" t="s">
         <v>130</v>
       </c>
-      <c r="E138" s="211">
-        <v>0</v>
-      </c>
-      <c r="H138" s="213"/>
-    </row>
-    <row r="139" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="171" t="s">
+      <c r="E138" s="173">
+        <v>0</v>
+      </c>
+      <c r="H138" s="253"/>
+    </row>
+    <row r="139" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B139" s="209" t="s">
+      <c r="B139" s="171" t="s">
         <v>111</v>
       </c>
-      <c r="C139" s="210" t="s">
+      <c r="C139" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D139" s="172" t="s">
+      <c r="D139" s="145" t="s">
         <v>129</v>
       </c>
-      <c r="E139" s="211">
+      <c r="E139" s="173">
         <v>0.05</v>
       </c>
-      <c r="H139" s="213"/>
-    </row>
-    <row r="140" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="171" t="s">
+      <c r="H139" s="253"/>
+    </row>
+    <row r="140" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B140" s="209" t="s">
+      <c r="B140" s="171" t="s">
         <v>111</v>
       </c>
-      <c r="C140" s="210" t="s">
+      <c r="C140" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D140" s="172" t="s">
+      <c r="D140" s="145" t="s">
         <v>128</v>
       </c>
-      <c r="E140" s="211">
+      <c r="E140" s="173">
         <v>0.95</v>
       </c>
-      <c r="H140" s="213"/>
-    </row>
-    <row r="141" spans="1:8" s="212" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="171" t="s">
+      <c r="H140" s="253"/>
+    </row>
+    <row r="141" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B141" s="209" t="s">
+      <c r="B141" s="171" t="s">
         <v>111</v>
       </c>
-      <c r="C141" s="210" t="s">
+      <c r="C141" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="D141" s="172" t="s">
+      <c r="D141" s="145" t="s">
         <v>117</v>
       </c>
-      <c r="E141" s="211">
-        <v>0</v>
-      </c>
-      <c r="H141" s="213"/>
+      <c r="E141" s="173">
+        <v>0</v>
+      </c>
+      <c r="H141" s="253"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7164,162 +7156,162 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="137" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="164" t="s">
+      <c r="B2" s="137" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="165">
+      <c r="C2" s="138">
         <v>0.96499999999999997</v>
       </c>
       <c r="D2" s="65"/>
-      <c r="E2" s="166" t="s">
-        <v>318</v>
+      <c r="E2" s="254" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="167" t="s">
+      <c r="A3" s="140" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="167" t="s">
+      <c r="B3" s="140" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="168">
+      <c r="C3" s="141">
         <v>0.96499999999999997</v>
       </c>
       <c r="D3" s="65"/>
-      <c r="E3" s="166"/>
+      <c r="E3" s="254"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="167" t="s">
+      <c r="A4" s="140" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="140" t="s">
         <v>122</v>
       </c>
-      <c r="C4" s="168">
+      <c r="C4" s="141">
         <v>0.5</v>
       </c>
       <c r="D4" s="65"/>
-      <c r="E4" s="166"/>
+      <c r="E4" s="254"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="140" t="s">
         <v>147</v>
       </c>
-      <c r="B5" s="167" t="s">
+      <c r="B5" s="140" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="168">
+      <c r="C5" s="141">
         <v>0</v>
       </c>
       <c r="D5" s="65"/>
-      <c r="E5" s="166"/>
+      <c r="E5" s="254"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="169" t="s">
+      <c r="A6" s="142" t="s">
         <v>146</v>
       </c>
-      <c r="B6" s="169" t="s">
+      <c r="B6" s="142" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="170">
+      <c r="C6" s="143">
         <v>0.96499999999999997</v>
       </c>
       <c r="D6" s="65"/>
-      <c r="E6" s="166"/>
+      <c r="E6" s="254"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="169" t="s">
+      <c r="A7" s="142" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="169" t="s">
+      <c r="B7" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="170">
+      <c r="C7" s="143">
         <v>0.96499999999999997</v>
       </c>
       <c r="D7" s="65"/>
-      <c r="E7" s="166"/>
+      <c r="E7" s="254"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="169" t="s">
+      <c r="A8" s="142" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="169" t="s">
+      <c r="B8" s="142" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="170">
+      <c r="C8" s="143">
         <v>0.5</v>
       </c>
       <c r="D8" s="65"/>
-      <c r="E8" s="166"/>
+      <c r="E8" s="254"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="169" t="s">
+      <c r="A9" s="142" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="169" t="s">
+      <c r="B9" s="142" t="s">
         <v>121</v>
       </c>
-      <c r="C9" s="170">
+      <c r="C9" s="143">
         <v>0</v>
       </c>
       <c r="D9" s="65"/>
-      <c r="E9" s="166"/>
+      <c r="E9" s="254"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="171" t="s">
+      <c r="A10" s="144" t="s">
         <v>145</v>
       </c>
-      <c r="B10" s="171" t="s">
+      <c r="B10" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="C10" s="172">
+      <c r="C10" s="145">
         <v>0.96499999999999997</v>
       </c>
       <c r="D10" s="65"/>
-      <c r="E10" s="166"/>
+      <c r="E10" s="254"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="171" t="s">
+      <c r="A11" s="144" t="s">
         <v>145</v>
       </c>
-      <c r="B11" s="171" t="s">
+      <c r="B11" s="144" t="s">
         <v>123</v>
       </c>
-      <c r="C11" s="172">
+      <c r="C11" s="145">
         <v>0.96499999999999997</v>
       </c>
       <c r="D11" s="65"/>
-      <c r="E11" s="166"/>
+      <c r="E11" s="254"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="171" t="s">
+      <c r="A12" s="144" t="s">
         <v>145</v>
       </c>
-      <c r="B12" s="171" t="s">
+      <c r="B12" s="144" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="172">
+      <c r="C12" s="145">
         <v>0.96499999999999997</v>
       </c>
       <c r="D12" s="65"/>
-      <c r="E12" s="166"/>
+      <c r="E12" s="254"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="171" t="s">
+      <c r="A13" s="144" t="s">
         <v>145</v>
       </c>
-      <c r="B13" s="171" t="s">
+      <c r="B13" s="144" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="172">
+      <c r="C13" s="145">
         <v>0</v>
       </c>
       <c r="D13" s="65"/>
-      <c r="E13" s="166"/>
+      <c r="E13" s="254"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" s="65"/>
@@ -7344,92 +7336,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="194" t="s">
+      <c r="A1" s="157" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="197" t="s">
+      <c r="B1" s="160" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="214" t="s">
+      <c r="C1" s="175" t="s">
         <v>137</v>
       </c>
-      <c r="D1" s="197" t="s">
+      <c r="D1" s="160" t="s">
         <v>144</v>
       </c>
-      <c r="F1" s="199" t="s">
+      <c r="F1" s="162" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+    <row r="2" spans="1:6" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="137" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="138" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="215" t="s">
+      <c r="C2" s="176" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="165">
-        <v>0</v>
-      </c>
-      <c r="F2" s="216" t="s">
+      <c r="D2" s="138">
+        <v>0</v>
+      </c>
+      <c r="F2" s="177" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="140" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="141" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="178" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="141">
+        <v>0.95</v>
+      </c>
+      <c r="F3" s="179" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="167" t="s">
+    <row r="4" spans="1:6" s="166" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="140" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="168" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="217" t="s">
+      <c r="B4" s="141" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="178" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="168">
-        <v>0.95</v>
-      </c>
-      <c r="F3" s="218" t="s">
+      <c r="D4" s="141">
+        <v>0</v>
+      </c>
+      <c r="F4" s="179" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="203" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="167" t="s">
-        <v>112</v>
-      </c>
-      <c r="B4" s="168" t="s">
+    <row r="5" spans="1:6" s="155" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="142" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="143" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="217" t="s">
+      <c r="C5" s="180" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="168">
-        <v>0</v>
-      </c>
-      <c r="F4" s="218" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="192" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" s="170" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" s="219" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="170">
+      <c r="D5" s="143">
         <v>0.8</v>
       </c>
-      <c r="F5" s="220" t="s">
-        <v>250</v>
+      <c r="F5" s="156" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F6" s="178"/>
+      <c r="F6" s="149"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7452,232 +7444,232 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="221" t="s">
+      <c r="B2" s="271" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="222" t="s">
+      <c r="C2" s="273" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="224"/>
-      <c r="G2" s="225" t="s">
+      <c r="D2" s="274"/>
+      <c r="E2" s="274"/>
+      <c r="F2" s="275"/>
+      <c r="G2" s="288" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="221" t="s">
-        <v>264</v>
-      </c>
-      <c r="I2" s="222" t="s">
+      <c r="H2" s="271" t="s">
+        <v>263</v>
+      </c>
+      <c r="I2" s="273" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="223"/>
-      <c r="K2" s="226"/>
+      <c r="J2" s="274"/>
+      <c r="K2" s="283"/>
     </row>
     <row r="3" spans="1:21" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="227"/>
-      <c r="C3" s="228"/>
-      <c r="D3" s="229"/>
-      <c r="E3" s="229"/>
-      <c r="F3" s="230"/>
-      <c r="G3" s="231"/>
-      <c r="H3" s="227"/>
-      <c r="I3" s="228"/>
-      <c r="J3" s="229"/>
-      <c r="K3" s="232"/>
+      <c r="B3" s="272"/>
+      <c r="C3" s="276"/>
+      <c r="D3" s="277"/>
+      <c r="E3" s="277"/>
+      <c r="F3" s="278"/>
+      <c r="G3" s="289"/>
+      <c r="H3" s="272"/>
+      <c r="I3" s="276"/>
+      <c r="J3" s="277"/>
+      <c r="K3" s="284"/>
     </row>
     <row r="4" spans="1:21" s="44" customFormat="1" ht="270" x14ac:dyDescent="0.2">
       <c r="A4" s="46"/>
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="181" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="234" t="s">
-        <v>323</v>
-      </c>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="237" t="s">
+      <c r="C4" s="279" t="s">
+        <v>322</v>
+      </c>
+      <c r="D4" s="280"/>
+      <c r="E4" s="280"/>
+      <c r="F4" s="281"/>
+      <c r="G4" s="182" t="s">
+        <v>270</v>
+      </c>
+      <c r="H4" s="183" t="s">
         <v>271</v>
       </c>
-      <c r="H4" s="238" t="s">
-        <v>272</v>
-      </c>
-      <c r="I4" s="239" t="s">
-        <v>296</v>
-      </c>
-      <c r="J4" s="240"/>
-      <c r="K4" s="241"/>
+      <c r="I4" s="285" t="s">
+        <v>295</v>
+      </c>
+      <c r="J4" s="286"/>
+      <c r="K4" s="287"/>
     </row>
     <row r="5" spans="1:21" s="44" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="46"/>
-      <c r="B5" s="118" t="s">
+      <c r="B5" s="96" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="242" t="s">
-        <v>324</v>
-      </c>
-      <c r="D5" s="243"/>
-      <c r="E5" s="243"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="245">
+      <c r="C5" s="255" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5" s="256"/>
+      <c r="E5" s="256"/>
+      <c r="F5" s="282"/>
+      <c r="G5" s="184">
         <v>0.8</v>
       </c>
-      <c r="H5" s="246" t="s">
-        <v>308</v>
-      </c>
-      <c r="I5" s="247" t="s">
-        <v>270</v>
-      </c>
-      <c r="J5" s="248"/>
-      <c r="K5" s="249"/>
+      <c r="H5" s="185" t="s">
+        <v>307</v>
+      </c>
+      <c r="I5" s="258" t="s">
+        <v>269</v>
+      </c>
+      <c r="J5" s="259"/>
+      <c r="K5" s="260"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
     </row>
     <row r="6" spans="1:21" s="44" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="46"/>
-      <c r="B6" s="118" t="s">
+      <c r="B6" s="96" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="242" t="s">
-        <v>325</v>
-      </c>
-      <c r="D6" s="243"/>
-      <c r="E6" s="243"/>
-      <c r="F6" s="244"/>
-      <c r="G6" s="245">
+      <c r="C6" s="255" t="s">
+        <v>324</v>
+      </c>
+      <c r="D6" s="256"/>
+      <c r="E6" s="256"/>
+      <c r="F6" s="282"/>
+      <c r="G6" s="184">
         <v>0.8</v>
       </c>
-      <c r="H6" s="250" t="s">
-        <v>308</v>
-      </c>
-      <c r="I6" s="247" t="s">
-        <v>269</v>
-      </c>
-      <c r="J6" s="248"/>
-      <c r="K6" s="249"/>
+      <c r="H6" s="186" t="s">
+        <v>307</v>
+      </c>
+      <c r="I6" s="258" t="s">
+        <v>268</v>
+      </c>
+      <c r="J6" s="259"/>
+      <c r="K6" s="260"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
     </row>
     <row r="7" spans="1:21" s="44" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="46"/>
-      <c r="B7" s="118" t="s">
+      <c r="B7" s="96" t="s">
+        <v>297</v>
+      </c>
+      <c r="C7" s="255" t="s">
         <v>298</v>
       </c>
-      <c r="C7" s="242" t="s">
+      <c r="D7" s="256"/>
+      <c r="E7" s="256"/>
+      <c r="F7" s="282"/>
+      <c r="G7" s="184">
+        <v>1</v>
+      </c>
+      <c r="H7" s="186"/>
+      <c r="I7" s="258" t="s">
         <v>299</v>
       </c>
-      <c r="D7" s="243"/>
-      <c r="E7" s="243"/>
-      <c r="F7" s="244"/>
-      <c r="G7" s="245">
-        <v>1</v>
-      </c>
-      <c r="H7" s="250"/>
-      <c r="I7" s="247" t="s">
-        <v>300</v>
-      </c>
-      <c r="J7" s="248"/>
-      <c r="K7" s="249"/>
+      <c r="J7" s="259"/>
+      <c r="K7" s="260"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:21" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A8" s="46"/>
-      <c r="B8" s="118" t="s">
+      <c r="B8" s="96" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="242" t="s">
+      <c r="C8" s="255" t="s">
+        <v>265</v>
+      </c>
+      <c r="D8" s="256"/>
+      <c r="E8" s="256"/>
+      <c r="F8" s="282"/>
+      <c r="G8" s="184">
+        <v>1</v>
+      </c>
+      <c r="H8" s="185" t="s">
         <v>266</v>
       </c>
-      <c r="D8" s="243"/>
-      <c r="E8" s="243"/>
-      <c r="F8" s="244"/>
-      <c r="G8" s="245">
-        <v>1</v>
-      </c>
-      <c r="H8" s="246" t="s">
-        <v>267</v>
-      </c>
-      <c r="I8" s="247"/>
-      <c r="J8" s="248"/>
-      <c r="K8" s="249"/>
+      <c r="I8" s="258"/>
+      <c r="J8" s="259"/>
+      <c r="K8" s="260"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="1:21" s="44" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="46"/>
-      <c r="B9" s="118" t="s">
+      <c r="B9" s="96" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="242" t="s">
+      <c r="C9" s="255" t="s">
         <v>158</v>
       </c>
-      <c r="D9" s="243"/>
-      <c r="E9" s="243"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="245">
+      <c r="D9" s="256"/>
+      <c r="E9" s="256"/>
+      <c r="F9" s="282"/>
+      <c r="G9" s="184">
         <v>0.95</v>
       </c>
-      <c r="H9" s="246" t="s">
-        <v>308</v>
-      </c>
-      <c r="I9" s="242" t="s">
-        <v>265</v>
-      </c>
-      <c r="J9" s="243"/>
-      <c r="K9" s="251"/>
+      <c r="H9" s="185" t="s">
+        <v>307</v>
+      </c>
+      <c r="I9" s="255" t="s">
+        <v>264</v>
+      </c>
+      <c r="J9" s="256"/>
+      <c r="K9" s="257"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:21" s="44" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="47"/>
-      <c r="B10" s="118" t="s">
+      <c r="B10" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="C10" s="242" t="s">
+      <c r="C10" s="255" t="s">
         <v>162</v>
       </c>
-      <c r="D10" s="243"/>
-      <c r="E10" s="243"/>
-      <c r="F10" s="244"/>
-      <c r="G10" s="252">
+      <c r="D10" s="256"/>
+      <c r="E10" s="256"/>
+      <c r="F10" s="282"/>
+      <c r="G10" s="187">
         <v>0.9</v>
       </c>
-      <c r="H10" s="246"/>
-      <c r="I10" s="247" t="s">
-        <v>268</v>
-      </c>
-      <c r="J10" s="248"/>
-      <c r="K10" s="249"/>
+      <c r="H10" s="185"/>
+      <c r="I10" s="258" t="s">
+        <v>267</v>
+      </c>
+      <c r="J10" s="259"/>
+      <c r="K10" s="260"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
     </row>
     <row r="11" spans="1:21" s="44" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="46"/>
-      <c r="B11" s="118" t="s">
+      <c r="B11" s="96" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="242" t="s">
+      <c r="C11" s="255" t="s">
         <v>161</v>
       </c>
-      <c r="D11" s="243"/>
-      <c r="E11" s="243"/>
-      <c r="F11" s="244"/>
-      <c r="G11" s="252">
+      <c r="D11" s="256"/>
+      <c r="E11" s="256"/>
+      <c r="F11" s="282"/>
+      <c r="G11" s="187">
         <v>0.9</v>
       </c>
-      <c r="H11" s="250"/>
-      <c r="I11" s="247" t="s">
-        <v>268</v>
-      </c>
-      <c r="J11" s="248"/>
-      <c r="K11" s="249"/>
+      <c r="H11" s="186"/>
+      <c r="I11" s="258" t="s">
+        <v>267</v>
+      </c>
+      <c r="J11" s="259"/>
+      <c r="K11" s="260"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -7685,7 +7677,7 @@
     <row r="12" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B13" s="48" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C13" s="49"/>
       <c r="D13" s="49"/>
@@ -7708,28 +7700,28 @@
       <c r="U13" s="51"/>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="86" t="s">
-        <v>259</v>
-      </c>
-      <c r="C14" s="87"/>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="87"/>
-      <c r="G14" s="87"/>
-      <c r="H14" s="87"/>
-      <c r="I14" s="87"/>
-      <c r="J14" s="87"/>
-      <c r="K14" s="87"/>
-      <c r="L14" s="87"/>
-      <c r="M14" s="87"/>
-      <c r="N14" s="87"/>
-      <c r="O14" s="87"/>
-      <c r="P14" s="87"/>
-      <c r="Q14" s="87"/>
-      <c r="R14" s="87"/>
-      <c r="S14" s="87"/>
-      <c r="T14" s="87"/>
-      <c r="U14" s="88"/>
+      <c r="B14" s="265" t="s">
+        <v>258</v>
+      </c>
+      <c r="C14" s="266"/>
+      <c r="D14" s="266"/>
+      <c r="E14" s="266"/>
+      <c r="F14" s="266"/>
+      <c r="G14" s="266"/>
+      <c r="H14" s="266"/>
+      <c r="I14" s="266"/>
+      <c r="J14" s="266"/>
+      <c r="K14" s="266"/>
+      <c r="L14" s="266"/>
+      <c r="M14" s="266"/>
+      <c r="N14" s="266"/>
+      <c r="O14" s="266"/>
+      <c r="P14" s="266"/>
+      <c r="Q14" s="266"/>
+      <c r="R14" s="266"/>
+      <c r="S14" s="266"/>
+      <c r="T14" s="266"/>
+      <c r="U14" s="267"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B15" s="52"/>
@@ -7754,94 +7746,94 @@
       <c r="U15" s="55"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B16" s="253" t="s">
-        <v>255</v>
-      </c>
-      <c r="C16" s="254"/>
-      <c r="D16" s="254"/>
-      <c r="E16" s="254"/>
-      <c r="F16" s="254"/>
-      <c r="G16" s="254"/>
-      <c r="H16" s="254"/>
-      <c r="I16" s="254"/>
-      <c r="J16" s="254"/>
-      <c r="K16" s="254"/>
-      <c r="L16" s="254"/>
-      <c r="M16" s="254"/>
-      <c r="N16" s="254"/>
-      <c r="O16" s="254"/>
-      <c r="P16" s="254"/>
-      <c r="Q16" s="254"/>
-      <c r="R16" s="254"/>
-      <c r="S16" s="254"/>
-      <c r="T16" s="254"/>
-      <c r="U16" s="255"/>
+      <c r="B16" s="263" t="s">
+        <v>254</v>
+      </c>
+      <c r="C16" s="264"/>
+      <c r="D16" s="264"/>
+      <c r="E16" s="264"/>
+      <c r="F16" s="264"/>
+      <c r="G16" s="264"/>
+      <c r="H16" s="264"/>
+      <c r="I16" s="264"/>
+      <c r="J16" s="264"/>
+      <c r="K16" s="264"/>
+      <c r="L16" s="264"/>
+      <c r="M16" s="264"/>
+      <c r="N16" s="264"/>
+      <c r="O16" s="264"/>
+      <c r="P16" s="264"/>
+      <c r="Q16" s="264"/>
+      <c r="R16" s="264"/>
+      <c r="S16" s="264"/>
+      <c r="T16" s="264"/>
+      <c r="U16" s="270"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B17" s="89" t="s">
+      <c r="B17" s="268" t="s">
+        <v>250</v>
+      </c>
+      <c r="C17" s="269"/>
+      <c r="D17" s="188">
+        <v>2008</v>
+      </c>
+      <c r="E17" s="188">
+        <v>2009</v>
+      </c>
+      <c r="F17" s="188">
+        <v>2010</v>
+      </c>
+      <c r="G17" s="188">
+        <v>2011</v>
+      </c>
+      <c r="H17" s="188">
+        <v>2012</v>
+      </c>
+      <c r="I17" s="188">
+        <v>2013</v>
+      </c>
+      <c r="J17" s="188">
+        <v>2014</v>
+      </c>
+      <c r="K17" s="188">
+        <v>2015</v>
+      </c>
+      <c r="L17" s="188">
+        <v>2016</v>
+      </c>
+      <c r="M17" s="188">
+        <v>2017</v>
+      </c>
+      <c r="N17" s="188">
+        <v>2018</v>
+      </c>
+      <c r="O17" s="188">
+        <v>2019</v>
+      </c>
+      <c r="P17" s="188">
+        <v>2020</v>
+      </c>
+      <c r="Q17" s="188">
+        <v>2021</v>
+      </c>
+      <c r="R17" s="188">
+        <v>2022</v>
+      </c>
+      <c r="S17" s="188">
+        <v>2023</v>
+      </c>
+      <c r="T17" s="188">
+        <v>2024</v>
+      </c>
+      <c r="U17" s="189" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B18" s="268" t="s">
         <v>251</v>
       </c>
-      <c r="C17" s="90"/>
-      <c r="D17" s="256">
-        <v>2008</v>
-      </c>
-      <c r="E17" s="256">
-        <v>2009</v>
-      </c>
-      <c r="F17" s="256">
-        <v>2010</v>
-      </c>
-      <c r="G17" s="256">
-        <v>2011</v>
-      </c>
-      <c r="H17" s="256">
-        <v>2012</v>
-      </c>
-      <c r="I17" s="256">
-        <v>2013</v>
-      </c>
-      <c r="J17" s="256">
-        <v>2014</v>
-      </c>
-      <c r="K17" s="256">
-        <v>2015</v>
-      </c>
-      <c r="L17" s="256">
-        <v>2016</v>
-      </c>
-      <c r="M17" s="256">
-        <v>2017</v>
-      </c>
-      <c r="N17" s="256">
-        <v>2018</v>
-      </c>
-      <c r="O17" s="256">
-        <v>2019</v>
-      </c>
-      <c r="P17" s="256">
-        <v>2020</v>
-      </c>
-      <c r="Q17" s="256">
-        <v>2021</v>
-      </c>
-      <c r="R17" s="256">
-        <v>2022</v>
-      </c>
-      <c r="S17" s="256">
-        <v>2023</v>
-      </c>
-      <c r="T17" s="256">
-        <v>2024</v>
-      </c>
-      <c r="U17" s="257" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18" s="89" t="s">
-        <v>252</v>
-      </c>
-      <c r="C18" s="90"/>
+      <c r="C18" s="269"/>
       <c r="D18" s="59">
         <v>0.86</v>
       </c>
@@ -7893,15 +7885,15 @@
       <c r="T18" s="59">
         <v>0.8</v>
       </c>
-      <c r="U18" s="258">
+      <c r="U18" s="190">
         <v>0.8</v>
       </c>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B19" s="89" t="s">
-        <v>253</v>
-      </c>
-      <c r="C19" s="90"/>
+      <c r="B19" s="268" t="s">
+        <v>252</v>
+      </c>
+      <c r="C19" s="269"/>
       <c r="D19" s="59">
         <f>78/86</f>
         <v>0.90697674418604646</v>
@@ -7968,15 +7960,15 @@
       <c r="T19" s="59">
         <v>0</v>
       </c>
-      <c r="U19" s="258">
+      <c r="U19" s="190">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B20" s="89" t="s">
-        <v>254</v>
-      </c>
-      <c r="C20" s="90"/>
+      <c r="B20" s="268" t="s">
+        <v>253</v>
+      </c>
+      <c r="C20" s="269"/>
       <c r="D20" s="59">
         <v>1</v>
       </c>
@@ -8028,7 +8020,7 @@
       <c r="T20" s="59">
         <v>0</v>
       </c>
-      <c r="U20" s="258">
+      <c r="U20" s="190">
         <v>0</v>
       </c>
     </row>
@@ -8055,54 +8047,54 @@
       <c r="U21" s="55"/>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B22" s="253" t="s">
-        <v>258</v>
-      </c>
-      <c r="C22" s="254"/>
-      <c r="D22" s="254"/>
-      <c r="E22" s="254"/>
-      <c r="F22" s="254"/>
-      <c r="G22" s="254"/>
-      <c r="H22" s="254"/>
-      <c r="I22" s="254"/>
-      <c r="J22" s="254"/>
-      <c r="K22" s="259"/>
-      <c r="L22" s="259"/>
-      <c r="M22" s="259"/>
-      <c r="N22" s="259"/>
-      <c r="O22" s="259"/>
-      <c r="P22" s="259"/>
-      <c r="Q22" s="259"/>
-      <c r="R22" s="259"/>
-      <c r="S22" s="259"/>
-      <c r="T22" s="259"/>
-      <c r="U22" s="260"/>
+      <c r="B22" s="263" t="s">
+        <v>257</v>
+      </c>
+      <c r="C22" s="264"/>
+      <c r="D22" s="264"/>
+      <c r="E22" s="264"/>
+      <c r="F22" s="264"/>
+      <c r="G22" s="264"/>
+      <c r="H22" s="264"/>
+      <c r="I22" s="264"/>
+      <c r="J22" s="264"/>
+      <c r="K22" s="191"/>
+      <c r="L22" s="191"/>
+      <c r="M22" s="191"/>
+      <c r="N22" s="191"/>
+      <c r="O22" s="191"/>
+      <c r="P22" s="191"/>
+      <c r="Q22" s="191"/>
+      <c r="R22" s="191"/>
+      <c r="S22" s="191"/>
+      <c r="T22" s="191"/>
+      <c r="U22" s="192"/>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B23" s="89" t="s">
-        <v>251</v>
-      </c>
-      <c r="C23" s="90"/>
-      <c r="D23" s="256">
+      <c r="B23" s="268" t="s">
+        <v>250</v>
+      </c>
+      <c r="C23" s="269"/>
+      <c r="D23" s="188">
         <v>2019</v>
       </c>
-      <c r="E23" s="256">
+      <c r="E23" s="188">
         <v>2020</v>
       </c>
-      <c r="F23" s="256">
+      <c r="F23" s="188">
         <v>2021</v>
       </c>
-      <c r="G23" s="256">
+      <c r="G23" s="188">
         <v>2022</v>
       </c>
-      <c r="H23" s="256">
+      <c r="H23" s="188">
         <v>2023</v>
       </c>
-      <c r="I23" s="256">
+      <c r="I23" s="188">
         <v>2024</v>
       </c>
       <c r="J23" s="71" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K23" s="53"/>
       <c r="L23" s="53"/>
@@ -8117,10 +8109,10 @@
       <c r="U23" s="55"/>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B24" s="89" t="s">
-        <v>252</v>
-      </c>
-      <c r="C24" s="90"/>
+      <c r="B24" s="268" t="s">
+        <v>251</v>
+      </c>
+      <c r="C24" s="269"/>
       <c r="D24" s="59">
         <f>E24</f>
         <v>0.53</v>
@@ -8146,8 +8138,8 @@
       <c r="K24" s="53"/>
       <c r="L24" s="53"/>
       <c r="M24" s="53"/>
-      <c r="N24" s="259" t="s">
-        <v>260</v>
+      <c r="N24" s="191" t="s">
+        <v>259</v>
       </c>
       <c r="O24" s="53"/>
       <c r="P24" s="53"/>
@@ -8158,10 +8150,10 @@
       <c r="U24" s="55"/>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B25" s="89" t="s">
-        <v>253</v>
-      </c>
-      <c r="C25" s="90"/>
+      <c r="B25" s="268" t="s">
+        <v>252</v>
+      </c>
+      <c r="C25" s="269"/>
       <c r="D25" s="59">
         <f>E25</f>
         <v>0.35830985915492958</v>
@@ -8200,28 +8192,28 @@
     </row>
     <row r="26" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="261" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" s="262"/>
-      <c r="D26" s="263">
-        <v>0</v>
-      </c>
-      <c r="E26" s="263">
-        <v>0</v>
-      </c>
-      <c r="F26" s="263">
-        <v>0</v>
-      </c>
-      <c r="G26" s="263">
-        <v>0</v>
-      </c>
-      <c r="H26" s="263">
-        <v>0</v>
-      </c>
-      <c r="I26" s="263">
-        <v>0</v>
-      </c>
-      <c r="J26" s="263">
+      <c r="D26" s="193">
+        <v>0</v>
+      </c>
+      <c r="E26" s="193">
+        <v>0</v>
+      </c>
+      <c r="F26" s="193">
+        <v>0</v>
+      </c>
+      <c r="G26" s="193">
+        <v>0</v>
+      </c>
+      <c r="H26" s="193">
+        <v>0</v>
+      </c>
+      <c r="I26" s="193">
+        <v>0</v>
+      </c>
+      <c r="J26" s="193">
         <v>0</v>
       </c>
       <c r="K26" s="57"/>
@@ -8238,35 +8230,55 @@
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.2">
       <c r="M28" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="E29" s="264"/>
-      <c r="F29" s="264"/>
-      <c r="G29" s="264"/>
-      <c r="H29" s="264"/>
-      <c r="I29" s="264"/>
-      <c r="J29" s="264"/>
+      <c r="E29" s="194"/>
+      <c r="F29" s="194"/>
+      <c r="G29" s="194"/>
+      <c r="H29" s="194"/>
+      <c r="I29" s="194"/>
+      <c r="J29" s="194"/>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="E30" s="264"/>
-      <c r="F30" s="264"/>
-      <c r="G30" s="264"/>
-      <c r="H30" s="264"/>
-      <c r="I30" s="264"/>
-      <c r="J30" s="264"/>
+      <c r="E30" s="194"/>
+      <c r="F30" s="194"/>
+      <c r="G30" s="194"/>
+      <c r="H30" s="194"/>
+      <c r="I30" s="194"/>
+      <c r="J30" s="194"/>
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="E31" s="264"/>
-      <c r="F31" s="264"/>
-      <c r="G31" s="264"/>
-      <c r="H31" s="264"/>
-      <c r="I31" s="264"/>
-      <c r="J31" s="264"/>
+      <c r="E31" s="194"/>
+      <c r="F31" s="194"/>
+      <c r="G31" s="194"/>
+      <c r="H31" s="194"/>
+      <c r="I31" s="194"/>
+      <c r="J31" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="I10:K10"/>
     <mergeCell ref="B26:C26"/>
@@ -8279,26 +8291,6 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B16:U16"/>
     <mergeCell ref="I11:K11"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8322,44 +8314,44 @@
     <row r="1" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="61" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C2" s="62" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" s="62" t="s">
         <v>245</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="E2" s="62" t="s">
         <v>246</v>
-      </c>
-      <c r="E2" s="62" t="s">
-        <v>247</v>
       </c>
       <c r="F2" s="63" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="62" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H2" s="64" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="98" t="s">
-        <v>244</v>
-      </c>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="102"/>
+      <c r="B3" s="290" t="s">
+        <v>243</v>
+      </c>
+      <c r="C3" s="291"/>
+      <c r="D3" s="291"/>
+      <c r="E3" s="291"/>
+      <c r="F3" s="292"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="2:8" s="65" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="173" t="s">
+      <c r="B4" s="146" t="s">
         <v>141</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D4" s="65">
         <v>0.8</v>
@@ -8371,95 +8363,100 @@
       <c r="G4" s="68">
         <v>2</v>
       </c>
-      <c r="H4" s="301">
+      <c r="H4" s="203">
         <f>G4</f>
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="98" t="s">
+      <c r="B5" s="290" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" s="291"/>
+      <c r="D5" s="291"/>
+      <c r="E5" s="291"/>
+      <c r="F5" s="292"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="203"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B6" s="146" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="65" t="s">
         <v>261</v>
-      </c>
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="301"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B6" s="173" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" s="65" t="s">
-        <v>262</v>
       </c>
       <c r="D6" s="65">
         <v>0.8</v>
       </c>
       <c r="E6" s="68" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F6" s="60" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G6" s="68">
         <v>3</v>
       </c>
-      <c r="H6" s="301">
+      <c r="H6" s="203">
         <f>H4*G6</f>
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="98" t="s">
-        <v>274</v>
-      </c>
-      <c r="C7" s="99"/>
-      <c r="D7" s="99"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="100"/>
+      <c r="B7" s="290" t="s">
+        <v>273</v>
+      </c>
+      <c r="C7" s="291"/>
+      <c r="D7" s="291"/>
+      <c r="E7" s="291"/>
+      <c r="F7" s="292"/>
       <c r="G7" s="66"/>
-      <c r="H7" s="301"/>
+      <c r="H7" s="203"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="67" t="s">
         <v>164</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D8" s="68">
         <v>0.68</v>
       </c>
       <c r="E8" s="68" t="s">
-        <v>293</v>
-      </c>
-      <c r="F8" s="174" t="s">
-        <v>295</v>
-      </c>
-      <c r="G8" s="66"/>
-      <c r="H8" s="301"/>
+        <v>292</v>
+      </c>
+      <c r="F8" s="293" t="s">
+        <v>294</v>
+      </c>
+      <c r="G8" s="298">
+        <v>3</v>
+      </c>
+      <c r="H8" s="296">
+        <f>H6*G8</f>
+        <v>18</v>
+      </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B9" s="67" t="s">
         <v>164</v>
       </c>
       <c r="C9" s="69" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D9" s="68">
         <v>0.76</v>
       </c>
       <c r="E9" s="68" t="s">
-        <v>294</v>
-      </c>
-      <c r="F9" s="174"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="301"/>
+        <v>293</v>
+      </c>
+      <c r="F9" s="293"/>
+      <c r="G9" s="298"/>
+      <c r="H9" s="296"/>
     </row>
     <row r="10" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="173" t="s">
+      <c r="B10" s="146" t="s">
         <v>164</v>
       </c>
       <c r="C10" s="69" t="s">
@@ -8469,19 +8466,14 @@
         <v>0.8</v>
       </c>
       <c r="E10" s="68" t="s">
-        <v>275</v>
-      </c>
-      <c r="F10" s="174"/>
-      <c r="G10" s="175">
-        <v>3</v>
-      </c>
-      <c r="H10" s="302">
-        <f>H6*G10</f>
-        <v>18</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="F10" s="293"/>
+      <c r="G10" s="298"/>
+      <c r="H10" s="296"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="173" t="s">
+      <c r="B11" s="146" t="s">
         <v>164</v>
       </c>
       <c r="C11" s="65" t="s">
@@ -8491,14 +8483,14 @@
         <v>0.8</v>
       </c>
       <c r="E11" s="68" t="s">
-        <v>275</v>
-      </c>
-      <c r="F11" s="174"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="302"/>
+        <v>274</v>
+      </c>
+      <c r="F11" s="293"/>
+      <c r="G11" s="298"/>
+      <c r="H11" s="296"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B12" s="173" t="s">
+      <c r="B12" s="146" t="s">
         <v>164</v>
       </c>
       <c r="C12" s="65" t="s">
@@ -8508,14 +8500,14 @@
         <v>0.9</v>
       </c>
       <c r="E12" s="68" t="s">
-        <v>281</v>
-      </c>
-      <c r="F12" s="174"/>
-      <c r="G12" s="175"/>
-      <c r="H12" s="302"/>
+        <v>280</v>
+      </c>
+      <c r="F12" s="293"/>
+      <c r="G12" s="298"/>
+      <c r="H12" s="296"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="173" t="s">
+      <c r="B13" s="146" t="s">
         <v>164</v>
       </c>
       <c r="C13" s="65" t="s">
@@ -8525,29 +8517,29 @@
         <v>0.9</v>
       </c>
       <c r="E13" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="F13" s="293"/>
+      <c r="G13" s="298"/>
+      <c r="H13" s="296"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B14" s="290" t="s">
+        <v>305</v>
+      </c>
+      <c r="C14" s="291"/>
+      <c r="D14" s="291"/>
+      <c r="E14" s="291"/>
+      <c r="F14" s="292"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="203"/>
+    </row>
+    <row r="15" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="146" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="65" t="s">
         <v>276</v>
-      </c>
-      <c r="F13" s="174"/>
-      <c r="G13" s="175"/>
-      <c r="H13" s="302"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="98" t="s">
-        <v>306</v>
-      </c>
-      <c r="C14" s="99"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="99"/>
-      <c r="F14" s="100"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="301"/>
-    </row>
-    <row r="15" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="173" t="s">
-        <v>149</v>
-      </c>
-      <c r="C15" s="65" t="s">
-        <v>277</v>
       </c>
       <c r="D15" s="65">
         <v>0</v>
@@ -8555,23 +8547,23 @@
       <c r="E15" s="65">
         <v>0.1</v>
       </c>
-      <c r="F15" s="174" t="s">
-        <v>280</v>
-      </c>
-      <c r="G15" s="303">
+      <c r="F15" s="293" t="s">
+        <v>279</v>
+      </c>
+      <c r="G15" s="294">
         <v>2</v>
       </c>
-      <c r="H15" s="302">
-        <f>H10*G15</f>
+      <c r="H15" s="295">
+        <f>H8*G15</f>
         <v>36</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B16" s="173" t="s">
+      <c r="B16" s="146" t="s">
         <v>149</v>
       </c>
       <c r="C16" s="65" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D16" s="65">
         <v>0</v>
@@ -8579,113 +8571,113 @@
       <c r="E16" s="65">
         <v>0.1</v>
       </c>
-      <c r="F16" s="174"/>
-      <c r="G16" s="303"/>
-      <c r="H16" s="302"/>
+      <c r="F16" s="293"/>
+      <c r="G16" s="294"/>
+      <c r="H16" s="295"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="173" t="s">
+      <c r="B17" s="146" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="182" t="s">
-        <v>279</v>
-      </c>
-      <c r="D17" s="182">
-        <v>0</v>
-      </c>
-      <c r="E17" s="182">
+      <c r="C17" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="D17" s="65">
+        <v>0</v>
+      </c>
+      <c r="E17" s="65">
         <v>0.1</v>
       </c>
-      <c r="F17" s="174"/>
-      <c r="G17" s="303"/>
-      <c r="H17" s="302"/>
+      <c r="F17" s="293"/>
+      <c r="G17" s="294"/>
+      <c r="H17" s="295"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" s="98" t="s">
+      <c r="B18" s="290" t="s">
+        <v>325</v>
+      </c>
+      <c r="C18" s="291"/>
+      <c r="D18" s="291"/>
+      <c r="E18" s="291"/>
+      <c r="F18" s="292"/>
+      <c r="G18" s="204"/>
+      <c r="H18" s="203"/>
+    </row>
+    <row r="19" spans="2:8" ht="49" x14ac:dyDescent="0.2">
+      <c r="B19" s="146" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="198" t="s">
+        <v>308</v>
+      </c>
+      <c r="E19" s="198" t="s">
+        <v>166</v>
+      </c>
+      <c r="F19" s="199" t="s">
         <v>326</v>
       </c>
-      <c r="C18" s="183"/>
-      <c r="D18" s="183"/>
-      <c r="E18" s="183"/>
-      <c r="F18" s="100"/>
-      <c r="G18" s="304"/>
-      <c r="H18" s="301"/>
-    </row>
-    <row r="19" spans="2:8" ht="49" x14ac:dyDescent="0.2">
-      <c r="B19" s="173" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="182" t="s">
-        <v>96</v>
-      </c>
-      <c r="D19" s="281" t="s">
-        <v>309</v>
-      </c>
-      <c r="E19" s="281" t="s">
-        <v>166</v>
-      </c>
-      <c r="F19" s="282" t="s">
+      <c r="G19" s="204">
+        <v>2</v>
+      </c>
+      <c r="H19" s="203">
+        <f>H15*G19</f>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20" s="290" t="s">
+        <v>319</v>
+      </c>
+      <c r="C20" s="291"/>
+      <c r="D20" s="291"/>
+      <c r="E20" s="291"/>
+      <c r="F20" s="292"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="150"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B21" s="146" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="65" t="s">
         <v>327</v>
       </c>
-      <c r="G19" s="304">
+      <c r="D21" s="65">
+        <v>0.96</v>
+      </c>
+      <c r="E21" s="65">
+        <v>0.9</v>
+      </c>
+      <c r="F21" s="301" t="s">
+        <v>321</v>
+      </c>
+      <c r="G21" s="298">
         <v>2</v>
       </c>
-      <c r="H19" s="301" t="e">
-        <f>#REF!*G19</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B20" s="98" t="s">
+      <c r="H21" s="296">
+        <f>H19*G21</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="147" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" s="148" t="s">
         <v>320</v>
       </c>
-      <c r="C20" s="183"/>
-      <c r="D20" s="183"/>
-      <c r="E20" s="183"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="181"/>
-      <c r="H20" s="180"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B21" s="173" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" s="184" t="s">
-        <v>328</v>
-      </c>
-      <c r="D21" s="184">
-        <v>0.96</v>
-      </c>
-      <c r="E21" s="184">
-        <v>0.9</v>
-      </c>
-      <c r="F21" s="186" t="s">
-        <v>322</v>
-      </c>
-      <c r="G21" s="179">
-        <v>2</v>
-      </c>
-      <c r="H21" s="305" t="e">
-        <f>H19*G21</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="176" t="s">
-        <v>140</v>
-      </c>
-      <c r="C22" s="177" t="s">
-        <v>321</v>
-      </c>
-      <c r="D22" s="177">
+      <c r="D22" s="148">
         <v>0.7</v>
       </c>
-      <c r="E22" s="177">
+      <c r="E22" s="148">
         <v>0.85</v>
       </c>
-      <c r="F22" s="187"/>
-      <c r="G22" s="185"/>
-      <c r="H22" s="306"/>
+      <c r="F22" s="302"/>
+      <c r="G22" s="299"/>
+      <c r="H22" s="300"/>
     </row>
     <row r="23" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B23" s="8"/>
@@ -8701,12 +8693,12 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="104" t="s">
-        <v>283</v>
-      </c>
-      <c r="G24" s="105" t="e">
-        <f>G4+G6+G10+G15+G21+G19+#REF!-COUNT(G3:G22)</f>
-        <v>#REF!</v>
+      <c r="F24" s="82" t="s">
+        <v>282</v>
+      </c>
+      <c r="G24" s="83">
+        <f>G4+G6+G8+G15+G19+G21-COUNT(G3:G22)</f>
+        <v>8</v>
       </c>
       <c r="H24" s="8"/>
     </row>
@@ -8715,56 +8707,56 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="103" t="s">
-        <v>284</v>
-      </c>
-      <c r="G25" s="106" t="e">
+      <c r="F25" s="81" t="s">
+        <v>283</v>
+      </c>
+      <c r="G25" s="84">
         <f>H21</f>
-        <v>#REF!</v>
+        <v>144</v>
       </c>
       <c r="H25" s="8"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C27" s="85" t="s">
-        <v>297</v>
-      </c>
-      <c r="D27" s="85"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
+      <c r="C27" s="297" t="s">
+        <v>296</v>
+      </c>
+      <c r="D27" s="297"/>
+      <c r="E27" s="297"/>
+      <c r="F27" s="297"/>
+      <c r="G27" s="297"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C28" s="85"/>
-      <c r="D28" s="85"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="85"/>
-      <c r="G28" s="85"/>
+      <c r="C28" s="297"/>
+      <c r="D28" s="297"/>
+      <c r="E28" s="297"/>
+      <c r="F28" s="297"/>
+      <c r="G28" s="297"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C29" s="85"/>
-      <c r="D29" s="85"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
+      <c r="C29" s="297"/>
+      <c r="D29" s="297"/>
+      <c r="E29" s="297"/>
+      <c r="F29" s="297"/>
+      <c r="G29" s="297"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="H10:H13"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="F8:F13"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="G8:G13"/>
     <mergeCell ref="C27:G29"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="H21:H22"/>
     <mergeCell ref="F21:F22"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="F8:F13"/>
+    <mergeCell ref="H8:H13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/project_documents/parameterDirectory.xlsx
+++ b/project_documents/parameterDirectory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabian/Documents/DPhil Work/Academic Work/EnglandCervicalScreeningProject/project_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B22C2A2-9886-0D4E-8563-56A6A848F273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5C8E38-CBBF-4947-8DFC-51B5B498F7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17180" activeTab="7" xr2:uid="{9CDCC384-B02C-4946-8A51-C0AA91FF93D1}"/>
   </bookViews>
@@ -1212,7 +1212,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1267,6 +1267,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="72">
     <border>
@@ -2152,7 +2158,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="303">
+  <cellXfs count="317">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2279,7 +2285,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="9" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2288,15 +2293,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2497,9 +2493,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2579,10 +2572,6 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2598,6 +2587,114 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2640,102 +2737,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2749,23 +2750,86 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2787,110 +2851,80 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3340,11 +3374,11 @@
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="200" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="238"/>
-      <c r="D4" s="238"/>
+      <c r="C4" s="200"/>
+      <c r="D4" s="200"/>
     </row>
     <row r="5" spans="2:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -3422,26 +3456,26 @@
       </c>
     </row>
     <row r="13" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="239" t="s">
+      <c r="B13" s="201" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="239"/>
-      <c r="D13" s="239"/>
+      <c r="C13" s="201"/>
+      <c r="D13" s="201"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="239"/>
-      <c r="C14" s="239"/>
-      <c r="D14" s="239"/>
+      <c r="B14" s="201"/>
+      <c r="C14" s="201"/>
+      <c r="D14" s="201"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="239"/>
-      <c r="C15" s="239"/>
-      <c r="D15" s="239"/>
+      <c r="B15" s="201"/>
+      <c r="C15" s="201"/>
+      <c r="D15" s="201"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="239"/>
-      <c r="C16" s="239"/>
-      <c r="D16" s="239"/>
+      <c r="B16" s="201"/>
+      <c r="C16" s="201"/>
+      <c r="D16" s="201"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3472,13 +3506,13 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="242" t="s">
+      <c r="B3" s="204" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="242"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
+      <c r="C3" s="204"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="204"/>
+      <c r="F3" s="204"/>
     </row>
     <row r="5" spans="2:6" ht="35" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
@@ -3498,7 +3532,7 @@
       </c>
     </row>
     <row r="6" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B6" s="244" t="s">
+      <c r="B6" s="206" t="s">
         <v>177</v>
       </c>
       <c r="C6" s="27" t="s">
@@ -3513,7 +3547,7 @@
       <c r="F6" s="14"/>
     </row>
     <row r="7" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" s="245"/>
+      <c r="B7" s="207"/>
       <c r="C7" s="28" t="s">
         <v>179</v>
       </c>
@@ -3526,7 +3560,7 @@
       <c r="F7" s="15"/>
     </row>
     <row r="8" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B8" s="245"/>
+      <c r="B8" s="207"/>
       <c r="C8" s="28" t="s">
         <v>180</v>
       </c>
@@ -3539,7 +3573,7 @@
       <c r="F8" s="15"/>
     </row>
     <row r="9" spans="2:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="B9" s="245"/>
+      <c r="B9" s="207"/>
       <c r="C9" s="28" t="s">
         <v>181</v>
       </c>
@@ -3552,7 +3586,7 @@
       <c r="F9" s="15"/>
     </row>
     <row r="10" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B10" s="246" t="s">
+      <c r="B10" s="208" t="s">
         <v>173</v>
       </c>
       <c r="C10" s="29" t="s">
@@ -3569,7 +3603,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B11" s="246"/>
+      <c r="B11" s="208"/>
       <c r="C11" s="29" t="s">
         <v>187</v>
       </c>
@@ -3584,7 +3618,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B12" s="246"/>
+      <c r="B12" s="208"/>
       <c r="C12" s="29" t="s">
         <v>188</v>
       </c>
@@ -3599,7 +3633,7 @@
       </c>
     </row>
     <row r="13" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B13" s="247" t="s">
+      <c r="B13" s="209" t="s">
         <v>174</v>
       </c>
       <c r="C13" s="30" t="s">
@@ -3616,7 +3650,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B14" s="247"/>
+      <c r="B14" s="209"/>
       <c r="C14" s="30" t="s">
         <v>113</v>
       </c>
@@ -3631,7 +3665,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B15" s="247"/>
+      <c r="B15" s="209"/>
       <c r="C15" s="30" t="s">
         <v>111</v>
       </c>
@@ -3646,7 +3680,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B16" s="248" t="s">
+      <c r="B16" s="210" t="s">
         <v>175</v>
       </c>
       <c r="C16" s="31" t="s">
@@ -3661,7 +3695,7 @@
       <c r="F16" s="18"/>
     </row>
     <row r="17" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B17" s="248"/>
+      <c r="B17" s="210"/>
       <c r="C17" s="31" t="s">
         <v>133</v>
       </c>
@@ -3676,7 +3710,7 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="135" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="248"/>
+      <c r="B18" s="210"/>
       <c r="C18" s="31" t="s">
         <v>115</v>
       </c>
@@ -3698,7 +3732,7 @@
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B19" s="248"/>
+      <c r="B19" s="210"/>
       <c r="C19" s="31" t="s">
         <v>114</v>
       </c>
@@ -3717,30 +3751,30 @@
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B22" s="249" t="s">
+      <c r="B22" s="211" t="s">
         <v>132</v>
       </c>
       <c r="C22" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="240" t="s">
+      <c r="D22" s="202" t="s">
         <v>216</v>
       </c>
-      <c r="E22" s="241"/>
+      <c r="E22" s="203"/>
     </row>
     <row r="23" spans="2:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="250"/>
+      <c r="B23" s="212"/>
       <c r="C23" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="242" t="s">
+      <c r="D23" s="204" t="s">
         <v>218</v>
       </c>
-      <c r="E23" s="243"/>
+      <c r="E23" s="205"/>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="250"/>
+      <c r="B24" s="212"/>
       <c r="C24" s="8" t="s">
         <v>114</v>
       </c>
@@ -3797,7 +3831,7 @@
   <dimension ref="A2:J34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="195"/>
+    <col min="1" max="1" width="10.83203125" style="188"/>
     <col min="2" max="2" width="14.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53" style="5" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" style="5"/>
@@ -3809,36 +3843,36 @@
     <col min="11" max="16384" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" s="70" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="195"/>
-      <c r="B2" s="225" t="s">
+    <row r="2" spans="1:10" s="66" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="188"/>
+      <c r="B2" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="229" t="s">
+      <c r="C2" s="217" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="235" t="s">
+      <c r="D2" s="225" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="236"/>
-      <c r="F2" s="237" t="s">
+      <c r="E2" s="226"/>
+      <c r="F2" s="227" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="237"/>
-      <c r="H2" s="237"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="227" t="s">
+      <c r="G2" s="227"/>
+      <c r="H2" s="227"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="215" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="70" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="195"/>
-      <c r="B3" s="226"/>
-      <c r="C3" s="230"/>
+    <row r="3" spans="1:10" s="66" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="188"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="218"/>
       <c r="D3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="196" t="s">
+      <c r="E3" s="189" t="s">
         <v>25</v>
       </c>
       <c r="F3" s="11" t="s">
@@ -3850,675 +3884,686 @@
       <c r="H3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="196" t="s">
+      <c r="I3" s="189" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="228"/>
-    </row>
-    <row r="4" spans="1:10" s="90" customFormat="1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="220" t="s">
+      <c r="J3" s="216"/>
+    </row>
+    <row r="4" spans="1:10" s="86" customFormat="1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="229" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="87">
+      <c r="D4" s="83">
         <v>200000</v>
       </c>
-      <c r="E4" s="85" t="s">
+      <c r="E4" s="81" t="s">
         <v>300</v>
       </c>
-      <c r="F4" s="88"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="88" t="s">
+      <c r="F4" s="84"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="84" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="90" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A5" s="220"/>
-      <c r="B5" s="92" t="s">
+    <row r="5" spans="1:10" s="86" customFormat="1" ht="105" x14ac:dyDescent="0.2">
+      <c r="A5" s="229"/>
+      <c r="B5" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="91" t="s">
+      <c r="C5" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="93">
+      <c r="D5" s="89">
         <v>1980</v>
       </c>
-      <c r="E5" s="92" t="s">
+      <c r="E5" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="93"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="92"/>
-      <c r="J5" s="93" t="s">
+      <c r="F5" s="89"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="89" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="90" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A6" s="220"/>
-      <c r="B6" s="92" t="s">
+    <row r="6" spans="1:10" s="86" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A6" s="229"/>
+      <c r="B6" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="91" t="s">
+      <c r="C6" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="93">
+      <c r="D6" s="89">
         <v>2055</v>
       </c>
-      <c r="E6" s="92" t="s">
+      <c r="E6" s="88" t="s">
         <v>310</v>
       </c>
-      <c r="F6" s="93"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="93"/>
-    </row>
-    <row r="7" spans="1:10" s="90" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="220"/>
-      <c r="B7" s="92" t="s">
+      <c r="F6" s="89"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="89"/>
+    </row>
+    <row r="7" spans="1:10" s="86" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A7" s="229"/>
+      <c r="B7" s="88" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="91" t="s">
+      <c r="C7" s="87" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="93">
+      <c r="D7" s="89">
         <v>20</v>
       </c>
-      <c r="E7" s="92" t="s">
+      <c r="E7" s="88" t="s">
         <v>103</v>
       </c>
-      <c r="F7" s="93"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
-    </row>
-    <row r="8" spans="1:10" s="90" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A8" s="220"/>
-      <c r="B8" s="92" t="s">
+      <c r="F7" s="89"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="88"/>
+      <c r="J7" s="89"/>
+    </row>
+    <row r="8" spans="1:10" s="86" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A8" s="229"/>
+      <c r="B8" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="91" t="s">
+      <c r="C8" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="93">
+      <c r="D8" s="89">
         <v>0.25</v>
       </c>
-      <c r="E8" s="92" t="s">
+      <c r="E8" s="88" t="s">
         <v>311</v>
       </c>
-      <c r="F8" s="93"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="92"/>
-      <c r="J8" s="93"/>
-    </row>
-    <row r="9" spans="1:10" s="101" customFormat="1" ht="139" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="95" t="s">
+      <c r="F8" s="89"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="89"/>
+    </row>
+    <row r="9" spans="1:10" s="97" customFormat="1" ht="139" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="96" t="s">
+      <c r="B9" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="97" t="s">
+      <c r="C9" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="98" t="s">
+      <c r="D9" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="96" t="s">
+      <c r="E9" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="99"/>
-      <c r="G9" s="100"/>
-      <c r="H9" s="100"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="99" t="s">
+      <c r="F9" s="95"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="95" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="107" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A10" s="221" t="s">
+    <row r="10" spans="1:10" s="103" customFormat="1" ht="90" x14ac:dyDescent="0.2">
+      <c r="A10" s="230" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="103" t="s">
+      <c r="C10" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="104" t="s">
+      <c r="D10" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="102" t="s">
+      <c r="E10" s="98" t="s">
         <v>312</v>
       </c>
-      <c r="F10" s="105"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="105" t="s">
+      <c r="F10" s="101"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="101" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="107" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="221"/>
-      <c r="B11" s="223" t="s">
+    <row r="11" spans="1:10" s="103" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="230"/>
+      <c r="B11" s="221" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="231" t="s">
+      <c r="C11" s="219" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="105"/>
-      <c r="E11" s="223" t="s">
+      <c r="D11" s="101"/>
+      <c r="E11" s="221" t="s">
         <v>328</v>
       </c>
-      <c r="F11" s="105"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="106"/>
-      <c r="I11" s="102"/>
-      <c r="J11" s="233"/>
-    </row>
-    <row r="12" spans="1:10" s="107" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="221"/>
-      <c r="B12" s="224"/>
-      <c r="C12" s="232"/>
-      <c r="D12" s="105"/>
-      <c r="E12" s="224"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="106"/>
-      <c r="I12" s="102"/>
-      <c r="J12" s="234"/>
-    </row>
-    <row r="13" spans="1:10" s="112" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A13" s="222" t="s">
+      <c r="F11" s="101"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="98"/>
+      <c r="J11" s="223"/>
+    </row>
+    <row r="12" spans="1:10" s="103" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="230"/>
+      <c r="B12" s="222"/>
+      <c r="C12" s="220"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="222"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="224"/>
+    </row>
+    <row r="13" spans="1:10" s="108" customFormat="1" ht="105" x14ac:dyDescent="0.2">
+      <c r="A13" s="231" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="108" t="s">
+      <c r="B13" s="104" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="109" t="s">
+      <c r="C13" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="110" t="s">
+      <c r="D13" s="106" t="s">
         <v>309</v>
       </c>
-      <c r="E13" s="108" t="s">
+      <c r="E13" s="104" t="s">
         <v>313</v>
       </c>
-      <c r="F13" s="110"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="110"/>
-    </row>
-    <row r="14" spans="1:10" s="112" customFormat="1" ht="188" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="222"/>
-      <c r="B14" s="108" t="s">
+      <c r="F13" s="106"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="106"/>
+    </row>
+    <row r="14" spans="1:10" s="108" customFormat="1" ht="188" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="231"/>
+      <c r="B14" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="109" t="s">
+      <c r="C14" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="110" t="s">
+      <c r="D14" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="108" t="s">
+      <c r="E14" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="110"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="108"/>
-      <c r="J14" s="110" t="s">
+      <c r="F14" s="106"/>
+      <c r="G14" s="107"/>
+      <c r="H14" s="107"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="106" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="112" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="222"/>
-      <c r="B15" s="108" t="s">
+    <row r="15" spans="1:10" s="108" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A15" s="231"/>
+      <c r="B15" s="104" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="109" t="s">
+      <c r="C15" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="110">
+      <c r="D15" s="106">
         <v>0.5</v>
       </c>
-      <c r="E15" s="108" t="s">
+      <c r="E15" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="110"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="110"/>
-    </row>
-    <row r="16" spans="1:10" s="112" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A16" s="222"/>
-      <c r="B16" s="108" t="s">
+      <c r="F15" s="106"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="106"/>
+    </row>
+    <row r="16" spans="1:10" s="108" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A16" s="231"/>
+      <c r="B16" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="109" t="s">
+      <c r="C16" s="105" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="110">
+      <c r="D16" s="106">
         <v>1</v>
       </c>
-      <c r="E16" s="108" t="s">
+      <c r="E16" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="110"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="108"/>
-      <c r="J16" s="110" t="s">
+      <c r="F16" s="106"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="107"/>
+      <c r="I16" s="104"/>
+      <c r="J16" s="106" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="112" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="222"/>
-      <c r="B17" s="108" t="s">
+    <row r="17" spans="1:10" s="108" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A17" s="231"/>
+      <c r="B17" s="104" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="109" t="s">
+      <c r="C17" s="105" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="110" t="s">
+      <c r="D17" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="108" t="s">
+      <c r="E17" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="110"/>
-      <c r="G17" s="111"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="110"/>
-    </row>
-    <row r="18" spans="1:10" s="112" customFormat="1" ht="135" x14ac:dyDescent="0.2">
-      <c r="A18" s="222"/>
-      <c r="B18" s="108" t="s">
+      <c r="F17" s="106"/>
+      <c r="G17" s="107"/>
+      <c r="H17" s="107"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="106"/>
+    </row>
+    <row r="18" spans="1:10" s="108" customFormat="1" ht="135" x14ac:dyDescent="0.2">
+      <c r="A18" s="231"/>
+      <c r="B18" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="109" t="s">
+      <c r="C18" s="105" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="110"/>
-      <c r="E18" s="108"/>
-      <c r="F18" s="110" t="s">
+      <c r="D18" s="106"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="106" t="s">
         <v>57</v>
       </c>
-      <c r="G18" s="111">
-        <v>0</v>
-      </c>
-      <c r="H18" s="111">
+      <c r="G18" s="107">
+        <v>0</v>
+      </c>
+      <c r="H18" s="107">
         <v>1</v>
       </c>
-      <c r="I18" s="108" t="s">
+      <c r="I18" s="104" t="s">
         <v>314</v>
       </c>
-      <c r="J18" s="110"/>
-    </row>
-    <row r="19" spans="1:10" s="112" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A19" s="222"/>
-      <c r="B19" s="108" t="s">
+      <c r="J18" s="106"/>
+    </row>
+    <row r="19" spans="1:10" s="108" customFormat="1" ht="105" x14ac:dyDescent="0.2">
+      <c r="A19" s="231"/>
+      <c r="B19" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="109" t="s">
+      <c r="C19" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="110"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="110">
+      <c r="D19" s="106"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="106">
         <v>0.25</v>
       </c>
-      <c r="G19" s="111">
-        <v>0</v>
-      </c>
-      <c r="H19" s="111">
+      <c r="G19" s="107">
+        <v>0</v>
+      </c>
+      <c r="H19" s="107">
         <v>0.5</v>
       </c>
-      <c r="I19" s="108" t="s">
+      <c r="I19" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="J19" s="110"/>
-    </row>
-    <row r="20" spans="1:10" s="112" customFormat="1" ht="115" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="222"/>
-      <c r="B20" s="108" t="s">
+      <c r="J19" s="106"/>
+    </row>
+    <row r="20" spans="1:10" s="108" customFormat="1" ht="115" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="231"/>
+      <c r="B20" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="113" t="s">
+      <c r="C20" s="109" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="110" t="s">
+      <c r="D20" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="108" t="s">
+      <c r="E20" s="104" t="s">
         <v>301</v>
       </c>
-      <c r="F20" s="110"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="108"/>
-      <c r="J20" s="114"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="104"/>
+      <c r="J20" s="110"/>
     </row>
     <row r="21" spans="1:10" s="43" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="222"/>
-      <c r="B21" s="200" t="s">
+      <c r="A21" s="231"/>
+      <c r="B21" s="191" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="208" t="s">
+      <c r="C21" s="235" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="114" t="s">
+      <c r="D21" s="110" t="s">
         <v>165</v>
       </c>
-      <c r="E21" s="205" t="s">
+      <c r="E21" s="232" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="76"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="205" t="s">
+      <c r="F21" s="72"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="232" t="s">
         <v>167</v>
       </c>
-      <c r="J21" s="211" t="s">
+      <c r="J21" s="238" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="43" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="222"/>
-      <c r="B22" s="201" t="s">
+      <c r="A22" s="231"/>
+      <c r="B22" s="192" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="209"/>
-      <c r="D22" s="202" t="s">
+      <c r="C22" s="236"/>
+      <c r="D22" s="193" t="s">
         <v>166</v>
       </c>
-      <c r="E22" s="206"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="206"/>
-      <c r="J22" s="212"/>
+      <c r="E22" s="233"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="233"/>
+      <c r="J22" s="239"/>
     </row>
     <row r="23" spans="1:10" s="43" customFormat="1" ht="180" x14ac:dyDescent="0.2">
-      <c r="A23" s="222"/>
-      <c r="B23" s="108" t="s">
+      <c r="A23" s="231"/>
+      <c r="B23" s="104" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="210"/>
-      <c r="D23" s="114" t="s">
+      <c r="C23" s="237"/>
+      <c r="D23" s="110" t="s">
         <v>308</v>
       </c>
-      <c r="E23" s="200" t="s">
+      <c r="E23" s="191" t="s">
         <v>100</v>
       </c>
-      <c r="F23" s="78"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="207"/>
-      <c r="J23" s="213"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="234"/>
+      <c r="J23" s="240"/>
     </row>
     <row r="24" spans="1:10" s="43" customFormat="1" ht="255" x14ac:dyDescent="0.2">
-      <c r="A24" s="197"/>
-      <c r="B24" s="108" t="s">
+      <c r="A24" s="190"/>
+      <c r="B24" s="104" t="s">
         <v>90</v>
       </c>
-      <c r="C24" s="109" t="s">
+      <c r="C24" s="105" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="110" t="s">
+      <c r="D24" s="106" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="108" t="s">
+      <c r="E24" s="104" t="s">
         <v>94</v>
       </c>
-      <c r="F24" s="73"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="110" t="s">
+      <c r="F24" s="69"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="106" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="122" customFormat="1" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="115" t="s">
+    <row r="25" spans="1:10" s="118" customFormat="1" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="111" t="s">
         <v>232</v>
       </c>
-      <c r="B25" s="116" t="s">
+      <c r="B25" s="112" t="s">
         <v>231</v>
       </c>
-      <c r="C25" s="117" t="s">
+      <c r="C25" s="113" t="s">
         <v>233</v>
       </c>
-      <c r="D25" s="118">
-        <v>0</v>
-      </c>
-      <c r="E25" s="119" t="s">
+      <c r="D25" s="114">
+        <v>0</v>
+      </c>
+      <c r="E25" s="115" t="s">
         <v>219</v>
       </c>
-      <c r="F25" s="118"/>
-      <c r="G25" s="118"/>
-      <c r="H25" s="118"/>
-      <c r="I25" s="120"/>
-      <c r="J25" s="121"/>
-    </row>
-    <row r="26" spans="1:10" s="129" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="123" t="s">
+      <c r="F25" s="114"/>
+      <c r="G25" s="114"/>
+      <c r="H25" s="114"/>
+      <c r="I25" s="116"/>
+      <c r="J25" s="117"/>
+    </row>
+    <row r="26" spans="1:10" s="125" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="119" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="124" t="s">
+      <c r="B26" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="125" t="s">
+      <c r="C26" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="126" t="s">
+      <c r="D26" s="122" t="s">
         <v>66</v>
       </c>
-      <c r="E26" s="124"/>
-      <c r="F26" s="126"/>
-      <c r="G26" s="127"/>
-      <c r="H26" s="127"/>
-      <c r="I26" s="124"/>
-      <c r="J26" s="128" t="s">
+      <c r="E26" s="120"/>
+      <c r="F26" s="122"/>
+      <c r="G26" s="123"/>
+      <c r="H26" s="123"/>
+      <c r="I26" s="120"/>
+      <c r="J26" s="124" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="129" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A27" s="123"/>
-      <c r="B27" s="124" t="s">
+    <row r="27" spans="1:10" s="125" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A27" s="119"/>
+      <c r="B27" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="216" t="s">
+      <c r="C27" s="243" t="s">
         <v>79</v>
       </c>
-      <c r="D27" s="126"/>
-      <c r="E27" s="124"/>
-      <c r="F27" s="126">
+      <c r="D27" s="122"/>
+      <c r="E27" s="120"/>
+      <c r="F27" s="122">
         <v>0.25</v>
       </c>
-      <c r="G27" s="127">
-        <v>0</v>
-      </c>
-      <c r="H27" s="127">
+      <c r="G27" s="123">
+        <v>0</v>
+      </c>
+      <c r="H27" s="123">
         <v>1</v>
       </c>
-      <c r="I27" s="124" t="s">
+      <c r="I27" s="120" t="s">
         <v>81</v>
       </c>
-      <c r="J27" s="128" t="s">
+      <c r="J27" s="124" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="129" customFormat="1" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="123"/>
-      <c r="B28" s="124" t="s">
+    <row r="28" spans="1:10" s="125" customFormat="1" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="119"/>
+      <c r="B28" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="217"/>
-      <c r="D28" s="126">
+      <c r="C28" s="244"/>
+      <c r="D28" s="122">
         <v>50</v>
       </c>
-      <c r="E28" s="124" t="s">
+      <c r="E28" s="120" t="s">
         <v>84</v>
       </c>
-      <c r="F28" s="126"/>
-      <c r="G28" s="127"/>
-      <c r="H28" s="127"/>
-      <c r="I28" s="124"/>
-      <c r="J28" s="126"/>
-    </row>
-    <row r="29" spans="1:10" s="129" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="123"/>
-      <c r="B29" s="124" t="s">
+      <c r="F28" s="122"/>
+      <c r="G28" s="123"/>
+      <c r="H28" s="123"/>
+      <c r="I28" s="120"/>
+      <c r="J28" s="122"/>
+    </row>
+    <row r="29" spans="1:10" s="125" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="119"/>
+      <c r="B29" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="218"/>
-      <c r="D29" s="126">
-        <v>0</v>
-      </c>
-      <c r="E29" s="124" t="s">
+      <c r="C29" s="245"/>
+      <c r="D29" s="122">
+        <v>0</v>
+      </c>
+      <c r="E29" s="120" t="s">
         <v>84</v>
       </c>
-      <c r="F29" s="126"/>
-      <c r="G29" s="127"/>
-      <c r="H29" s="127"/>
-      <c r="I29" s="124"/>
-      <c r="J29" s="126"/>
-    </row>
-    <row r="30" spans="1:10" s="129" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="123"/>
-      <c r="B30" s="124" t="s">
+      <c r="F29" s="122"/>
+      <c r="G29" s="123"/>
+      <c r="H29" s="123"/>
+      <c r="I29" s="120"/>
+      <c r="J29" s="122"/>
+    </row>
+    <row r="30" spans="1:10" s="125" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="119"/>
+      <c r="B30" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="130" t="s">
+      <c r="C30" s="126" t="s">
         <v>302</v>
       </c>
-      <c r="D30" s="126"/>
-      <c r="E30" s="124"/>
-      <c r="F30" s="126">
+      <c r="D30" s="122"/>
+      <c r="E30" s="120"/>
+      <c r="F30" s="122">
         <v>5</v>
       </c>
-      <c r="G30" s="127">
+      <c r="G30" s="123">
         <v>1</v>
       </c>
-      <c r="H30" s="127">
+      <c r="H30" s="123">
         <v>12</v>
       </c>
-      <c r="I30" s="124" t="s">
+      <c r="I30" s="120" t="s">
         <v>315</v>
       </c>
-      <c r="J30" s="126" t="s">
+      <c r="J30" s="122" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:10" s="129" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="123"/>
-      <c r="B31" s="124" t="s">
+    <row r="31" spans="1:10" s="125" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="119"/>
+      <c r="B31" s="120" t="s">
         <v>76</v>
       </c>
-      <c r="C31" s="130" t="s">
+      <c r="C31" s="126" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="126">
+      <c r="D31" s="122">
         <v>20</v>
       </c>
-      <c r="E31" s="124" t="s">
+      <c r="E31" s="120" t="s">
         <v>78</v>
       </c>
-      <c r="F31" s="126"/>
-      <c r="G31" s="127"/>
-      <c r="H31" s="127"/>
-      <c r="I31" s="124"/>
-      <c r="J31" s="126"/>
-    </row>
-    <row r="32" spans="1:10" s="129" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A32" s="123"/>
-      <c r="B32" s="124" t="s">
+      <c r="F31" s="122"/>
+      <c r="G31" s="123"/>
+      <c r="H31" s="123"/>
+      <c r="I31" s="120"/>
+      <c r="J31" s="122"/>
+    </row>
+    <row r="32" spans="1:10" s="125" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A32" s="119"/>
+      <c r="B32" s="120" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="131" t="s">
+      <c r="C32" s="127" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="126" t="s">
+      <c r="D32" s="122" t="s">
         <v>71</v>
       </c>
-      <c r="E32" s="124" t="s">
+      <c r="E32" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="F32" s="126" t="s">
+      <c r="F32" s="122" t="s">
         <v>74</v>
       </c>
-      <c r="G32" s="127">
-        <v>0</v>
-      </c>
-      <c r="H32" s="127">
+      <c r="G32" s="123">
+        <v>0</v>
+      </c>
+      <c r="H32" s="123">
         <v>1</v>
       </c>
-      <c r="I32" s="124" t="s">
+      <c r="I32" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="J32" s="126"/>
-    </row>
-    <row r="33" spans="1:10" s="136" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="219" t="s">
+      <c r="J32" s="122"/>
+    </row>
+    <row r="33" spans="1:10" s="132" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="228" t="s">
         <v>239</v>
       </c>
-      <c r="B33" s="132" t="s">
+      <c r="B33" s="128" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="133" t="s">
+      <c r="C33" s="129" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="134" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" s="132" t="s">
+      <c r="D33" s="130" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="128" t="s">
         <v>219</v>
       </c>
-      <c r="F33" s="134"/>
-      <c r="G33" s="135"/>
-      <c r="H33" s="135"/>
-      <c r="I33" s="132"/>
-      <c r="J33" s="214" t="s">
+      <c r="F33" s="130"/>
+      <c r="G33" s="131"/>
+      <c r="H33" s="131"/>
+      <c r="I33" s="128"/>
+      <c r="J33" s="241" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="136" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A34" s="219"/>
-      <c r="B34" s="132" t="s">
+    <row r="34" spans="1:10" s="132" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A34" s="228"/>
+      <c r="B34" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="133" t="s">
+      <c r="C34" s="129" t="s">
         <v>108</v>
       </c>
-      <c r="D34" s="134" t="s">
+      <c r="D34" s="130" t="s">
         <v>107</v>
       </c>
-      <c r="E34" s="132" t="s">
+      <c r="E34" s="128" t="s">
         <v>316</v>
       </c>
-      <c r="F34" s="134"/>
-      <c r="G34" s="135"/>
-      <c r="H34" s="135"/>
-      <c r="I34" s="132"/>
-      <c r="J34" s="215"/>
+      <c r="F34" s="130"/>
+      <c r="G34" s="131"/>
+      <c r="H34" s="131"/>
+      <c r="I34" s="128"/>
+      <c r="J34" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="J21:J23"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B11:B12"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="C2:C3"/>
@@ -4527,17 +4572,6 @@
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="J21:J23"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="C27:C29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -4550,2577 +4584,2577 @@
   <dimension ref="A1:H141"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="7" width="10.83203125" style="65"/>
-    <col min="8" max="8" width="61.83203125" style="65" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="65"/>
+    <col min="1" max="7" width="10.83203125" style="64"/>
+    <col min="8" max="8" width="61.83203125" style="64" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="64"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="150" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="158" t="s">
+      <c r="B1" s="151" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="159" t="s">
+      <c r="C1" s="152" t="s">
         <v>137</v>
       </c>
-      <c r="D1" s="160" t="s">
+      <c r="D1" s="153" t="s">
         <v>136</v>
       </c>
-      <c r="E1" s="161" t="s">
+      <c r="E1" s="154" t="s">
         <v>135</v>
       </c>
-      <c r="H1" s="162" t="s">
+      <c r="H1" s="155" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="137" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="163" t="s">
+    <row r="2" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="133" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="164" t="s">
+      <c r="C2" s="157" t="s">
         <v>124</v>
       </c>
-      <c r="D2" s="138" t="s">
+      <c r="D2" s="134" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="165">
+      <c r="E2" s="158">
         <v>0.12</v>
       </c>
-      <c r="H2" s="251" t="s">
+      <c r="H2" s="246" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B3" s="167" t="s">
+    <row r="3" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="D3" s="141" t="s">
+      <c r="D3" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="169">
+      <c r="E3" s="162">
         <v>0.88</v>
       </c>
-      <c r="H3" s="251"/>
-    </row>
-    <row r="4" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="167" t="s">
+      <c r="H3" s="246"/>
+    </row>
+    <row r="4" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="168" t="s">
+      <c r="C4" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="141" t="s">
+      <c r="D4" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E4" s="169">
-        <v>0</v>
-      </c>
-      <c r="H4" s="251"/>
-    </row>
-    <row r="5" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" s="167" t="s">
+      <c r="E4" s="162">
+        <v>0</v>
+      </c>
+      <c r="H4" s="246"/>
+    </row>
+    <row r="5" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="168" t="s">
+      <c r="C5" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="141" t="s">
+      <c r="D5" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="165">
+      <c r="E5" s="158">
         <v>0.12</v>
       </c>
-      <c r="H5" s="251"/>
-    </row>
-    <row r="6" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" s="167" t="s">
+      <c r="H5" s="246"/>
+    </row>
+    <row r="6" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="168" t="s">
+      <c r="C6" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="141" t="s">
+      <c r="D6" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="169">
+      <c r="E6" s="162">
         <v>0.88</v>
       </c>
-      <c r="H6" s="251"/>
-    </row>
-    <row r="7" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B7" s="167" t="s">
+      <c r="H6" s="246"/>
+    </row>
+    <row r="7" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="168" t="s">
+      <c r="C7" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D7" s="141" t="s">
+      <c r="D7" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E7" s="169">
-        <v>0</v>
-      </c>
-      <c r="H7" s="251"/>
-    </row>
-    <row r="8" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B8" s="167" t="s">
+      <c r="E7" s="162">
+        <v>0</v>
+      </c>
+      <c r="H7" s="246"/>
+    </row>
+    <row r="8" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="168" t="s">
+      <c r="C8" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D8" s="141" t="s">
+      <c r="D8" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E8" s="165">
+      <c r="E8" s="158">
         <v>0.12</v>
       </c>
-      <c r="H8" s="251"/>
-    </row>
-    <row r="9" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" s="167" t="s">
+      <c r="H8" s="246"/>
+    </row>
+    <row r="9" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="168" t="s">
+      <c r="C9" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="141" t="s">
+      <c r="D9" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="169">
+      <c r="E9" s="162">
         <v>0.88</v>
       </c>
-      <c r="H9" s="251"/>
-    </row>
-    <row r="10" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B10" s="167" t="s">
+      <c r="H9" s="246"/>
+    </row>
+    <row r="10" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="168" t="s">
+      <c r="C10" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="141" t="s">
+      <c r="D10" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E10" s="169">
-        <v>0</v>
-      </c>
-      <c r="H10" s="251"/>
-    </row>
-    <row r="11" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" s="167" t="s">
+      <c r="E10" s="162">
+        <v>0</v>
+      </c>
+      <c r="H10" s="246"/>
+    </row>
+    <row r="11" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C11" s="168" t="s">
+      <c r="C11" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="141" t="s">
+      <c r="D11" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E11" s="165">
+      <c r="E11" s="158">
         <v>0.12</v>
       </c>
-      <c r="H11" s="251"/>
-    </row>
-    <row r="12" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" s="167" t="s">
+      <c r="H11" s="246"/>
+    </row>
+    <row r="12" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C12" s="168" t="s">
+      <c r="C12" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D12" s="141" t="s">
+      <c r="D12" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E12" s="169">
+      <c r="E12" s="162">
         <v>0.88</v>
       </c>
-      <c r="H12" s="251"/>
-    </row>
-    <row r="13" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="167" t="s">
+      <c r="H12" s="246"/>
+    </row>
+    <row r="13" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C13" s="168" t="s">
+      <c r="C13" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D13" s="141" t="s">
+      <c r="D13" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="169">
-        <v>0</v>
-      </c>
-      <c r="H13" s="251"/>
-    </row>
-    <row r="14" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B14" s="167" t="s">
+      <c r="E13" s="162">
+        <v>0</v>
+      </c>
+      <c r="H13" s="246"/>
+    </row>
+    <row r="14" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="168" t="s">
+      <c r="C14" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="141" t="s">
+      <c r="D14" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E14" s="165">
+      <c r="E14" s="158">
         <v>0.12</v>
       </c>
-      <c r="H14" s="251"/>
-    </row>
-    <row r="15" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B15" s="167" t="s">
+      <c r="H14" s="246"/>
+    </row>
+    <row r="15" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="168" t="s">
+      <c r="C15" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D15" s="141" t="s">
+      <c r="D15" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="169">
+      <c r="E15" s="162">
         <v>0.88</v>
       </c>
-      <c r="H15" s="251"/>
-    </row>
-    <row r="16" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" s="167" t="s">
+      <c r="H15" s="246"/>
+    </row>
+    <row r="16" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="168" t="s">
+      <c r="C16" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D16" s="141" t="s">
+      <c r="D16" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E16" s="169">
-        <v>0</v>
-      </c>
-      <c r="H16" s="251"/>
-    </row>
-    <row r="17" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B17" s="167" t="s">
+      <c r="E16" s="162">
+        <v>0</v>
+      </c>
+      <c r="H16" s="246"/>
+    </row>
+    <row r="17" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="168" t="s">
+      <c r="C17" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="141" t="s">
+      <c r="D17" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="165">
+      <c r="E17" s="158">
         <v>0.12</v>
       </c>
-      <c r="H17" s="251"/>
-    </row>
-    <row r="18" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B18" s="167" t="s">
+      <c r="H17" s="246"/>
+    </row>
+    <row r="18" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="168" t="s">
+      <c r="C18" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D18" s="141" t="s">
+      <c r="D18" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E18" s="169">
+      <c r="E18" s="162">
         <v>0.88</v>
       </c>
-      <c r="H18" s="251"/>
-    </row>
-    <row r="19" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B19" s="167" t="s">
+      <c r="H18" s="246"/>
+    </row>
+    <row r="19" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="C19" s="168" t="s">
+      <c r="C19" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D19" s="141" t="s">
+      <c r="D19" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E19" s="169">
-        <v>0</v>
-      </c>
-      <c r="H19" s="251"/>
-    </row>
-    <row r="20" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B20" s="167" t="s">
+      <c r="E19" s="162">
+        <v>0</v>
+      </c>
+      <c r="H19" s="246"/>
+    </row>
+    <row r="20" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="168" t="s">
+      <c r="C20" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="141" t="s">
+      <c r="D20" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E20" s="165">
+      <c r="E20" s="158">
         <v>0.12</v>
       </c>
-      <c r="H20" s="251"/>
-    </row>
-    <row r="21" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B21" s="167" t="s">
+      <c r="H20" s="246"/>
+    </row>
+    <row r="21" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="168" t="s">
+      <c r="C21" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="D21" s="141" t="s">
+      <c r="D21" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="169">
+      <c r="E21" s="162">
         <v>0.88</v>
       </c>
-      <c r="H21" s="251"/>
-    </row>
-    <row r="22" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B22" s="167" t="s">
+      <c r="H21" s="246"/>
+    </row>
+    <row r="22" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="168" t="s">
+      <c r="C22" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="141" t="s">
+      <c r="D22" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E22" s="169">
-        <v>0</v>
-      </c>
-      <c r="H22" s="251"/>
-    </row>
-    <row r="23" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B23" s="167" t="s">
+      <c r="E22" s="162">
+        <v>0</v>
+      </c>
+      <c r="H22" s="246"/>
+    </row>
+    <row r="23" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="168" t="s">
+      <c r="C23" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D23" s="141" t="s">
+      <c r="D23" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="165">
+      <c r="E23" s="158">
         <v>0.12</v>
       </c>
-      <c r="H23" s="251"/>
-    </row>
-    <row r="24" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B24" s="167" t="s">
+      <c r="H23" s="246"/>
+    </row>
+    <row r="24" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C24" s="168" t="s">
+      <c r="C24" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D24" s="141" t="s">
+      <c r="D24" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E24" s="169">
+      <c r="E24" s="162">
         <v>0.88</v>
       </c>
-      <c r="H24" s="251"/>
-    </row>
-    <row r="25" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B25" s="167" t="s">
+      <c r="H24" s="246"/>
+    </row>
+    <row r="25" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C25" s="168" t="s">
+      <c r="C25" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D25" s="141" t="s">
+      <c r="D25" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="169">
-        <v>0</v>
-      </c>
-      <c r="H25" s="251"/>
-    </row>
-    <row r="26" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B26" s="167" t="s">
+      <c r="E25" s="162">
+        <v>0</v>
+      </c>
+      <c r="H25" s="246"/>
+    </row>
+    <row r="26" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="168" t="s">
+      <c r="C26" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="141" t="s">
+      <c r="D26" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E26" s="165">
+      <c r="E26" s="158">
         <v>0.12</v>
       </c>
-      <c r="H26" s="251"/>
-    </row>
-    <row r="27" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B27" s="167" t="s">
+      <c r="H26" s="246"/>
+    </row>
+    <row r="27" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C27" s="168" t="s">
+      <c r="C27" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D27" s="141" t="s">
+      <c r="D27" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="169">
+      <c r="E27" s="162">
         <v>0.88</v>
       </c>
-      <c r="H27" s="251"/>
-    </row>
-    <row r="28" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B28" s="167" t="s">
+      <c r="H27" s="246"/>
+    </row>
+    <row r="28" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C28" s="168" t="s">
+      <c r="C28" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="141" t="s">
+      <c r="D28" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E28" s="169">
-        <v>0</v>
-      </c>
-      <c r="H28" s="251"/>
-    </row>
-    <row r="29" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B29" s="167" t="s">
+      <c r="E28" s="162">
+        <v>0</v>
+      </c>
+      <c r="H28" s="246"/>
+    </row>
+    <row r="29" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C29" s="168" t="s">
+      <c r="C29" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="141" t="s">
+      <c r="D29" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E29" s="165">
+      <c r="E29" s="158">
         <v>0.12</v>
       </c>
-      <c r="H29" s="251"/>
-    </row>
-    <row r="30" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B30" s="167" t="s">
+      <c r="H29" s="246"/>
+    </row>
+    <row r="30" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C30" s="168" t="s">
+      <c r="C30" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D30" s="141" t="s">
+      <c r="D30" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="169">
+      <c r="E30" s="162">
         <v>0.88</v>
       </c>
-      <c r="H30" s="251"/>
-    </row>
-    <row r="31" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B31" s="167" t="s">
+      <c r="H30" s="246"/>
+    </row>
+    <row r="31" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C31" s="168" t="s">
+      <c r="C31" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D31" s="141" t="s">
+      <c r="D31" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E31" s="169">
-        <v>0</v>
-      </c>
-      <c r="H31" s="251"/>
-    </row>
-    <row r="32" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B32" s="167" t="s">
+      <c r="E31" s="162">
+        <v>0</v>
+      </c>
+      <c r="H31" s="246"/>
+    </row>
+    <row r="32" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="168" t="s">
+      <c r="C32" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D32" s="141" t="s">
+      <c r="D32" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E32" s="165">
+      <c r="E32" s="158">
         <v>0.12</v>
       </c>
-      <c r="H32" s="251"/>
-    </row>
-    <row r="33" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B33" s="167" t="s">
+      <c r="H32" s="246"/>
+    </row>
+    <row r="33" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C33" s="168" t="s">
+      <c r="C33" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D33" s="141" t="s">
+      <c r="D33" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E33" s="169">
+      <c r="E33" s="162">
         <v>0.88</v>
       </c>
-      <c r="H33" s="251"/>
-    </row>
-    <row r="34" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B34" s="167" t="s">
+      <c r="H33" s="246"/>
+    </row>
+    <row r="34" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C34" s="168" t="s">
+      <c r="C34" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D34" s="141" t="s">
+      <c r="D34" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="169">
-        <v>0</v>
-      </c>
-      <c r="H34" s="251"/>
-    </row>
-    <row r="35" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B35" s="167" t="s">
+      <c r="E34" s="162">
+        <v>0</v>
+      </c>
+      <c r="H34" s="246"/>
+    </row>
+    <row r="35" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C35" s="168" t="s">
+      <c r="C35" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="141" t="s">
+      <c r="D35" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="165">
+      <c r="E35" s="158">
         <v>0.12</v>
       </c>
-      <c r="H35" s="251"/>
-    </row>
-    <row r="36" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B36" s="167" t="s">
+      <c r="H35" s="246"/>
+    </row>
+    <row r="36" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C36" s="168" t="s">
+      <c r="C36" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D36" s="141" t="s">
+      <c r="D36" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E36" s="169">
+      <c r="E36" s="162">
         <v>0.88</v>
       </c>
-      <c r="H36" s="251"/>
-    </row>
-    <row r="37" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B37" s="167" t="s">
+      <c r="H36" s="246"/>
+    </row>
+    <row r="37" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" s="160" t="s">
         <v>115</v>
       </c>
-      <c r="C37" s="168" t="s">
+      <c r="C37" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D37" s="141" t="s">
+      <c r="D37" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E37" s="169">
-        <v>0</v>
-      </c>
-      <c r="H37" s="251"/>
-    </row>
-    <row r="38" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B38" s="167" t="s">
+      <c r="E37" s="162">
+        <v>0</v>
+      </c>
+      <c r="H37" s="246"/>
+    </row>
+    <row r="38" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C38" s="168" t="s">
+      <c r="C38" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="D38" s="141" t="s">
+      <c r="D38" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E38" s="169">
+      <c r="E38" s="162">
         <v>0.94</v>
       </c>
-      <c r="H38" s="251"/>
-    </row>
-    <row r="39" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B39" s="167" t="s">
+      <c r="H38" s="246"/>
+    </row>
+    <row r="39" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="168" t="s">
+      <c r="C39" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="D39" s="141" t="s">
+      <c r="D39" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E39" s="169">
+      <c r="E39" s="162">
         <v>0.06</v>
       </c>
-      <c r="H39" s="251"/>
-    </row>
-    <row r="40" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B40" s="167" t="s">
+      <c r="H39" s="246"/>
+    </row>
+    <row r="40" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="168" t="s">
+      <c r="C40" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="D40" s="141" t="s">
+      <c r="D40" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E40" s="169">
-        <v>0</v>
-      </c>
-      <c r="H40" s="251"/>
-    </row>
-    <row r="41" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B41" s="167" t="s">
+      <c r="E40" s="162">
+        <v>0</v>
+      </c>
+      <c r="H40" s="246"/>
+    </row>
+    <row r="41" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B41" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C41" s="168" t="s">
+      <c r="C41" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D41" s="141" t="s">
+      <c r="D41" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E41" s="169">
+      <c r="E41" s="162">
         <v>0.94</v>
       </c>
-      <c r="H41" s="251"/>
-    </row>
-    <row r="42" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B42" s="167" t="s">
+      <c r="H41" s="246"/>
+    </row>
+    <row r="42" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C42" s="168" t="s">
+      <c r="C42" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D42" s="141" t="s">
+      <c r="D42" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E42" s="169">
+      <c r="E42" s="162">
         <v>0.06</v>
       </c>
-      <c r="H42" s="251"/>
-    </row>
-    <row r="43" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B43" s="167" t="s">
+      <c r="H42" s="246"/>
+    </row>
+    <row r="43" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C43" s="168" t="s">
+      <c r="C43" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D43" s="141" t="s">
+      <c r="D43" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E43" s="169">
-        <v>0</v>
-      </c>
-      <c r="H43" s="251"/>
-    </row>
-    <row r="44" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B44" s="167" t="s">
+      <c r="E43" s="162">
+        <v>0</v>
+      </c>
+      <c r="H43" s="246"/>
+    </row>
+    <row r="44" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="168" t="s">
+      <c r="C44" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D44" s="141" t="s">
+      <c r="D44" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E44" s="169">
+      <c r="E44" s="162">
         <v>0.94</v>
       </c>
-      <c r="H44" s="251"/>
-    </row>
-    <row r="45" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B45" s="167" t="s">
+      <c r="H44" s="246"/>
+    </row>
+    <row r="45" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="168" t="s">
+      <c r="C45" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D45" s="141" t="s">
+      <c r="D45" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E45" s="169">
+      <c r="E45" s="162">
         <v>0.06</v>
       </c>
-      <c r="H45" s="251"/>
-    </row>
-    <row r="46" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B46" s="167" t="s">
+      <c r="H45" s="246"/>
+    </row>
+    <row r="46" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C46" s="168" t="s">
+      <c r="C46" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D46" s="141" t="s">
+      <c r="D46" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E46" s="169">
-        <v>0</v>
-      </c>
-      <c r="H46" s="251"/>
-    </row>
-    <row r="47" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B47" s="167" t="s">
+      <c r="E46" s="162">
+        <v>0</v>
+      </c>
+      <c r="H46" s="246"/>
+    </row>
+    <row r="47" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C47" s="168" t="s">
+      <c r="C47" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D47" s="141" t="s">
+      <c r="D47" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E47" s="169">
+      <c r="E47" s="162">
         <v>0.94</v>
       </c>
-      <c r="H47" s="251"/>
-    </row>
-    <row r="48" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B48" s="167" t="s">
+      <c r="H47" s="246"/>
+    </row>
+    <row r="48" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C48" s="168" t="s">
+      <c r="C48" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D48" s="141" t="s">
+      <c r="D48" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E48" s="169">
+      <c r="E48" s="162">
         <v>0.06</v>
       </c>
-      <c r="H48" s="251"/>
-    </row>
-    <row r="49" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B49" s="167" t="s">
+      <c r="H48" s="246"/>
+    </row>
+    <row r="49" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C49" s="168" t="s">
+      <c r="C49" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="141" t="s">
+      <c r="D49" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E49" s="169">
-        <v>0</v>
-      </c>
-      <c r="H49" s="251"/>
-    </row>
-    <row r="50" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50" s="167" t="s">
+      <c r="E49" s="162">
+        <v>0</v>
+      </c>
+      <c r="H49" s="246"/>
+    </row>
+    <row r="50" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C50" s="168" t="s">
+      <c r="C50" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D50" s="141" t="s">
+      <c r="D50" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E50" s="169">
+      <c r="E50" s="162">
         <v>0.94</v>
       </c>
-      <c r="H50" s="251"/>
-    </row>
-    <row r="51" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B51" s="167" t="s">
+      <c r="H50" s="246"/>
+    </row>
+    <row r="51" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C51" s="168" t="s">
+      <c r="C51" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D51" s="141" t="s">
+      <c r="D51" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E51" s="169">
+      <c r="E51" s="162">
         <v>0.06</v>
       </c>
-      <c r="H51" s="251"/>
-    </row>
-    <row r="52" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B52" s="167" t="s">
+      <c r="H51" s="246"/>
+    </row>
+    <row r="52" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C52" s="168" t="s">
+      <c r="C52" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D52" s="141" t="s">
+      <c r="D52" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E52" s="169">
-        <v>0</v>
-      </c>
-      <c r="H52" s="251"/>
-    </row>
-    <row r="53" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B53" s="167" t="s">
+      <c r="E52" s="162">
+        <v>0</v>
+      </c>
+      <c r="H52" s="246"/>
+    </row>
+    <row r="53" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C53" s="168" t="s">
+      <c r="C53" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D53" s="141" t="s">
+      <c r="D53" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E53" s="169">
+      <c r="E53" s="162">
         <v>0.94</v>
       </c>
-      <c r="H53" s="251"/>
-    </row>
-    <row r="54" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B54" s="167" t="s">
+      <c r="H53" s="246"/>
+    </row>
+    <row r="54" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B54" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C54" s="168" t="s">
+      <c r="C54" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D54" s="141" t="s">
+      <c r="D54" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E54" s="169">
+      <c r="E54" s="162">
         <v>0.06</v>
       </c>
-      <c r="H54" s="251"/>
-    </row>
-    <row r="55" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B55" s="167" t="s">
+      <c r="H54" s="246"/>
+    </row>
+    <row r="55" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" s="160" t="s">
         <v>114</v>
       </c>
-      <c r="C55" s="168" t="s">
+      <c r="C55" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D55" s="141" t="s">
+      <c r="D55" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E55" s="169">
-        <v>0</v>
-      </c>
-      <c r="H55" s="251"/>
-    </row>
-    <row r="56" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B56" s="167" t="s">
+      <c r="E55" s="162">
+        <v>0</v>
+      </c>
+      <c r="H55" s="246"/>
+    </row>
+    <row r="56" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C56" s="168" t="s">
+      <c r="C56" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="D56" s="141" t="s">
+      <c r="D56" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E56" s="169">
+      <c r="E56" s="162">
         <v>0.94</v>
       </c>
-      <c r="H56" s="251"/>
-    </row>
-    <row r="57" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B57" s="167" t="s">
+      <c r="H56" s="246"/>
+    </row>
+    <row r="57" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="168" t="s">
+      <c r="C57" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="D57" s="141" t="s">
+      <c r="D57" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E57" s="169">
+      <c r="E57" s="162">
         <v>0.06</v>
       </c>
-      <c r="H57" s="251"/>
-    </row>
-    <row r="58" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B58" s="167" t="s">
+      <c r="H57" s="246"/>
+    </row>
+    <row r="58" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C58" s="168" t="s">
+      <c r="C58" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="D58" s="141" t="s">
+      <c r="D58" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E58" s="169">
-        <v>0</v>
-      </c>
-      <c r="H58" s="251"/>
-    </row>
-    <row r="59" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" s="167" t="s">
+      <c r="E58" s="162">
+        <v>0</v>
+      </c>
+      <c r="H58" s="246"/>
+    </row>
+    <row r="59" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C59" s="168" t="s">
+      <c r="C59" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D59" s="141" t="s">
+      <c r="D59" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E59" s="169">
+      <c r="E59" s="162">
         <v>0.94</v>
       </c>
-      <c r="H59" s="251"/>
-    </row>
-    <row r="60" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B60" s="167" t="s">
+      <c r="H59" s="246"/>
+    </row>
+    <row r="60" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C60" s="168" t="s">
+      <c r="C60" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D60" s="141" t="s">
+      <c r="D60" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E60" s="169">
+      <c r="E60" s="162">
         <v>0.06</v>
       </c>
-      <c r="H60" s="251"/>
-    </row>
-    <row r="61" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B61" s="167" t="s">
+      <c r="H60" s="246"/>
+    </row>
+    <row r="61" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B61" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C61" s="168" t="s">
+      <c r="C61" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D61" s="141" t="s">
+      <c r="D61" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E61" s="169">
-        <v>0</v>
-      </c>
-      <c r="H61" s="251"/>
-    </row>
-    <row r="62" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B62" s="167" t="s">
+      <c r="E61" s="162">
+        <v>0</v>
+      </c>
+      <c r="H61" s="246"/>
+    </row>
+    <row r="62" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B62" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C62" s="168" t="s">
+      <c r="C62" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D62" s="141" t="s">
+      <c r="D62" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E62" s="169">
+      <c r="E62" s="162">
         <v>0.94</v>
       </c>
-      <c r="H62" s="251"/>
-    </row>
-    <row r="63" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B63" s="167" t="s">
+      <c r="H62" s="246"/>
+    </row>
+    <row r="63" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C63" s="168" t="s">
+      <c r="C63" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D63" s="141" t="s">
+      <c r="D63" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E63" s="169">
+      <c r="E63" s="162">
         <v>0.06</v>
       </c>
-      <c r="H63" s="251"/>
-    </row>
-    <row r="64" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B64" s="167" t="s">
+      <c r="H63" s="246"/>
+    </row>
+    <row r="64" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C64" s="168" t="s">
+      <c r="C64" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D64" s="141" t="s">
+      <c r="D64" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E64" s="169">
-        <v>0</v>
-      </c>
-      <c r="H64" s="251"/>
-    </row>
-    <row r="65" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B65" s="167" t="s">
+      <c r="E64" s="162">
+        <v>0</v>
+      </c>
+      <c r="H64" s="246"/>
+    </row>
+    <row r="65" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C65" s="168" t="s">
+      <c r="C65" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D65" s="141" t="s">
+      <c r="D65" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E65" s="169">
+      <c r="E65" s="162">
         <v>0.94</v>
       </c>
-      <c r="H65" s="251"/>
-    </row>
-    <row r="66" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B66" s="167" t="s">
+      <c r="H65" s="246"/>
+    </row>
+    <row r="66" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C66" s="168" t="s">
+      <c r="C66" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D66" s="141" t="s">
+      <c r="D66" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E66" s="169">
+      <c r="E66" s="162">
         <v>0.06</v>
       </c>
-      <c r="H66" s="251"/>
-    </row>
-    <row r="67" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B67" s="167" t="s">
+      <c r="H66" s="246"/>
+    </row>
+    <row r="67" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B67" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C67" s="168" t="s">
+      <c r="C67" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D67" s="141" t="s">
+      <c r="D67" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E67" s="169">
-        <v>0</v>
-      </c>
-      <c r="H67" s="251"/>
-    </row>
-    <row r="68" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B68" s="167" t="s">
+      <c r="E67" s="162">
+        <v>0</v>
+      </c>
+      <c r="H67" s="246"/>
+    </row>
+    <row r="68" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B68" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C68" s="168" t="s">
+      <c r="C68" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D68" s="141" t="s">
+      <c r="D68" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E68" s="169">
+      <c r="E68" s="162">
         <v>0.94</v>
       </c>
-      <c r="H68" s="251"/>
-    </row>
-    <row r="69" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B69" s="167" t="s">
+      <c r="H68" s="246"/>
+    </row>
+    <row r="69" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B69" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C69" s="168" t="s">
+      <c r="C69" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D69" s="141" t="s">
+      <c r="D69" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E69" s="169">
+      <c r="E69" s="162">
         <v>0.06</v>
       </c>
-      <c r="H69" s="251"/>
-    </row>
-    <row r="70" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B70" s="167" t="s">
+      <c r="H69" s="246"/>
+    </row>
+    <row r="70" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B70" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C70" s="168" t="s">
+      <c r="C70" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D70" s="141" t="s">
+      <c r="D70" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E70" s="169">
-        <v>0</v>
-      </c>
-      <c r="H70" s="251"/>
-    </row>
-    <row r="71" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B71" s="167" t="s">
+      <c r="E70" s="162">
+        <v>0</v>
+      </c>
+      <c r="H70" s="246"/>
+    </row>
+    <row r="71" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B71" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C71" s="168" t="s">
+      <c r="C71" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D71" s="141" t="s">
+      <c r="D71" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E71" s="169">
+      <c r="E71" s="162">
         <v>0.94</v>
       </c>
-      <c r="H71" s="251"/>
-    </row>
-    <row r="72" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B72" s="167" t="s">
+      <c r="H71" s="246"/>
+    </row>
+    <row r="72" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B72" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C72" s="168" t="s">
+      <c r="C72" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D72" s="141" t="s">
+      <c r="D72" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E72" s="169">
+      <c r="E72" s="162">
         <v>0.06</v>
       </c>
-      <c r="H72" s="251"/>
-    </row>
-    <row r="73" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B73" s="167" t="s">
+      <c r="H72" s="246"/>
+    </row>
+    <row r="73" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B73" s="160" t="s">
         <v>113</v>
       </c>
-      <c r="C73" s="168" t="s">
+      <c r="C73" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D73" s="141" t="s">
+      <c r="D73" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E73" s="169">
-        <v>0</v>
-      </c>
-      <c r="H73" s="251"/>
-    </row>
-    <row r="74" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B74" s="167" t="s">
+      <c r="E73" s="162">
+        <v>0</v>
+      </c>
+      <c r="H73" s="246"/>
+    </row>
+    <row r="74" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B74" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C74" s="168" t="s">
+      <c r="C74" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="D74" s="141" t="s">
+      <c r="D74" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E74" s="169">
+      <c r="E74" s="162">
         <v>0.94</v>
       </c>
-      <c r="H74" s="251"/>
-    </row>
-    <row r="75" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B75" s="167" t="s">
+      <c r="H74" s="246"/>
+    </row>
+    <row r="75" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B75" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C75" s="168" t="s">
+      <c r="C75" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="D75" s="141" t="s">
+      <c r="D75" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E75" s="169">
+      <c r="E75" s="162">
         <v>0.06</v>
       </c>
-      <c r="H75" s="251"/>
-    </row>
-    <row r="76" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B76" s="167" t="s">
+      <c r="H75" s="246"/>
+    </row>
+    <row r="76" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B76" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C76" s="168" t="s">
+      <c r="C76" s="161" t="s">
         <v>124</v>
       </c>
-      <c r="D76" s="141" t="s">
+      <c r="D76" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E76" s="169">
-        <v>0</v>
-      </c>
-      <c r="H76" s="251"/>
-    </row>
-    <row r="77" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B77" s="167" t="s">
+      <c r="E76" s="162">
+        <v>0</v>
+      </c>
+      <c r="H76" s="246"/>
+    </row>
+    <row r="77" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B77" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C77" s="168" t="s">
+      <c r="C77" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D77" s="141" t="s">
+      <c r="D77" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E77" s="169">
+      <c r="E77" s="162">
         <v>0.94</v>
       </c>
-      <c r="H77" s="251"/>
-    </row>
-    <row r="78" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B78" s="167" t="s">
+      <c r="H77" s="246"/>
+    </row>
+    <row r="78" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B78" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C78" s="168" t="s">
+      <c r="C78" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D78" s="141" t="s">
+      <c r="D78" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E78" s="169">
+      <c r="E78" s="162">
         <v>0.06</v>
       </c>
-      <c r="H78" s="251"/>
-    </row>
-    <row r="79" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B79" s="167" t="s">
+      <c r="H78" s="246"/>
+    </row>
+    <row r="79" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B79" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C79" s="168" t="s">
+      <c r="C79" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="D79" s="141" t="s">
+      <c r="D79" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E79" s="169">
-        <v>0</v>
-      </c>
-      <c r="H79" s="251"/>
-    </row>
-    <row r="80" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B80" s="167" t="s">
+      <c r="E79" s="162">
+        <v>0</v>
+      </c>
+      <c r="H79" s="246"/>
+    </row>
+    <row r="80" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B80" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C80" s="168" t="s">
+      <c r="C80" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D80" s="141" t="s">
+      <c r="D80" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E80" s="169">
+      <c r="E80" s="162">
         <v>0.94</v>
       </c>
-      <c r="H80" s="251"/>
-    </row>
-    <row r="81" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B81" s="167" t="s">
+      <c r="H80" s="246"/>
+    </row>
+    <row r="81" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B81" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C81" s="168" t="s">
+      <c r="C81" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D81" s="141" t="s">
+      <c r="D81" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E81" s="169">
+      <c r="E81" s="162">
         <v>0.06</v>
       </c>
-      <c r="H81" s="251"/>
-    </row>
-    <row r="82" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B82" s="167" t="s">
+      <c r="H81" s="246"/>
+    </row>
+    <row r="82" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B82" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C82" s="168" t="s">
+      <c r="C82" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="D82" s="141" t="s">
+      <c r="D82" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E82" s="169">
-        <v>0</v>
-      </c>
-      <c r="H82" s="251"/>
-    </row>
-    <row r="83" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B83" s="167" t="s">
+      <c r="E82" s="162">
+        <v>0</v>
+      </c>
+      <c r="H82" s="246"/>
+    </row>
+    <row r="83" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B83" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C83" s="168" t="s">
+      <c r="C83" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D83" s="141" t="s">
+      <c r="D83" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E83" s="169">
+      <c r="E83" s="162">
         <v>0.94</v>
       </c>
-      <c r="H83" s="251"/>
-    </row>
-    <row r="84" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B84" s="167" t="s">
+      <c r="H83" s="246"/>
+    </row>
+    <row r="84" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B84" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C84" s="168" t="s">
+      <c r="C84" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D84" s="141" t="s">
+      <c r="D84" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E84" s="169">
+      <c r="E84" s="162">
         <v>0.06</v>
       </c>
-      <c r="H84" s="251"/>
-    </row>
-    <row r="85" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B85" s="167" t="s">
+      <c r="H84" s="246"/>
+    </row>
+    <row r="85" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B85" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C85" s="168" t="s">
+      <c r="C85" s="161" t="s">
         <v>121</v>
       </c>
-      <c r="D85" s="141" t="s">
+      <c r="D85" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E85" s="169">
-        <v>0</v>
-      </c>
-      <c r="H85" s="251"/>
-    </row>
-    <row r="86" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B86" s="167" t="s">
+      <c r="E85" s="162">
+        <v>0</v>
+      </c>
+      <c r="H85" s="246"/>
+    </row>
+    <row r="86" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B86" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C86" s="168" t="s">
+      <c r="C86" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D86" s="141" t="s">
+      <c r="D86" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E86" s="169">
+      <c r="E86" s="162">
         <v>0.94</v>
       </c>
-      <c r="H86" s="251"/>
-    </row>
-    <row r="87" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B87" s="167" t="s">
+      <c r="H86" s="246"/>
+    </row>
+    <row r="87" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B87" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C87" s="168" t="s">
+      <c r="C87" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D87" s="141" t="s">
+      <c r="D87" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E87" s="169">
+      <c r="E87" s="162">
         <v>0.06</v>
       </c>
-      <c r="H87" s="251"/>
-    </row>
-    <row r="88" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B88" s="167" t="s">
+      <c r="H87" s="246"/>
+    </row>
+    <row r="88" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B88" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C88" s="168" t="s">
+      <c r="C88" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D88" s="141" t="s">
+      <c r="D88" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E88" s="169">
-        <v>0</v>
-      </c>
-      <c r="H88" s="251"/>
-    </row>
-    <row r="89" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B89" s="167" t="s">
+      <c r="E88" s="162">
+        <v>0</v>
+      </c>
+      <c r="H88" s="246"/>
+    </row>
+    <row r="89" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B89" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C89" s="168" t="s">
+      <c r="C89" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D89" s="141" t="s">
+      <c r="D89" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="E89" s="169">
+      <c r="E89" s="162">
         <v>0.94</v>
       </c>
-      <c r="H89" s="251"/>
-    </row>
-    <row r="90" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B90" s="167" t="s">
+      <c r="H89" s="246"/>
+    </row>
+    <row r="90" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B90" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C90" s="168" t="s">
+      <c r="C90" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D90" s="141" t="s">
+      <c r="D90" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="E90" s="169">
+      <c r="E90" s="162">
         <v>0.06</v>
       </c>
-      <c r="H90" s="251"/>
-    </row>
-    <row r="91" spans="1:8" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="140" t="s">
-        <v>126</v>
-      </c>
-      <c r="B91" s="167" t="s">
+      <c r="H90" s="246"/>
+    </row>
+    <row r="91" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B91" s="160" t="s">
         <v>111</v>
       </c>
-      <c r="C91" s="168" t="s">
+      <c r="C91" s="161" t="s">
         <v>118</v>
       </c>
-      <c r="D91" s="141" t="s">
+      <c r="D91" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="E91" s="169">
-        <v>0</v>
-      </c>
-      <c r="F91" s="170"/>
-      <c r="H91" s="251"/>
-    </row>
-    <row r="92" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="142" t="s">
+      <c r="E91" s="162">
+        <v>0</v>
+      </c>
+      <c r="F91" s="163"/>
+      <c r="H91" s="246"/>
+    </row>
+    <row r="92" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B92" s="151" t="s">
+      <c r="B92" s="144" t="s">
         <v>116</v>
       </c>
-      <c r="C92" s="152" t="s">
+      <c r="C92" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D92" s="143" t="s">
+      <c r="D92" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="E92" s="153">
+      <c r="E92" s="146">
         <v>0.96</v>
       </c>
-      <c r="F92" s="154"/>
-      <c r="H92" s="252" t="s">
+      <c r="F92" s="147"/>
+      <c r="H92" s="247" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="93" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="142" t="s">
+    <row r="93" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B93" s="151" t="s">
+      <c r="B93" s="144" t="s">
         <v>116</v>
       </c>
-      <c r="C93" s="152" t="s">
+      <c r="C93" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D93" s="143" t="s">
+      <c r="D93" s="139" t="s">
         <v>131</v>
       </c>
-      <c r="E93" s="153">
-        <v>0</v>
-      </c>
-      <c r="F93" s="154"/>
-      <c r="H93" s="252"/>
-    </row>
-    <row r="94" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="142" t="s">
+      <c r="E93" s="146">
+        <v>0</v>
+      </c>
+      <c r="F93" s="147"/>
+      <c r="H93" s="247"/>
+    </row>
+    <row r="94" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B94" s="151" t="s">
+      <c r="B94" s="144" t="s">
         <v>116</v>
       </c>
-      <c r="C94" s="152" t="s">
+      <c r="C94" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D94" s="143" t="s">
+      <c r="D94" s="139" t="s">
         <v>133</v>
       </c>
-      <c r="E94" s="153">
+      <c r="E94" s="146">
         <v>0.04</v>
       </c>
-      <c r="F94" s="154"/>
-      <c r="H94" s="252"/>
-    </row>
-    <row r="95" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="142" t="s">
+      <c r="F94" s="147"/>
+      <c r="H94" s="247"/>
+    </row>
+    <row r="95" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B95" s="151" t="s">
+      <c r="B95" s="144" t="s">
         <v>116</v>
       </c>
-      <c r="C95" s="152" t="s">
+      <c r="C95" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D95" s="143" t="s">
+      <c r="D95" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="E95" s="153">
-        <v>0</v>
-      </c>
-      <c r="F95" s="154"/>
-      <c r="H95" s="252"/>
-    </row>
-    <row r="96" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="142" t="s">
+      <c r="E95" s="146">
+        <v>0</v>
+      </c>
+      <c r="F95" s="147"/>
+      <c r="H95" s="247"/>
+    </row>
+    <row r="96" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B96" s="151" t="s">
+      <c r="B96" s="144" t="s">
         <v>115</v>
       </c>
-      <c r="C96" s="152" t="s">
+      <c r="C96" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D96" s="143" t="s">
+      <c r="D96" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="E96" s="153">
+      <c r="E96" s="146">
         <v>0.96</v>
       </c>
-      <c r="F96" s="154"/>
-      <c r="H96" s="252"/>
-    </row>
-    <row r="97" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="142" t="s">
+      <c r="F96" s="147"/>
+      <c r="H96" s="247"/>
+    </row>
+    <row r="97" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B97" s="151" t="s">
+      <c r="B97" s="144" t="s">
         <v>115</v>
       </c>
-      <c r="C97" s="152" t="s">
+      <c r="C97" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D97" s="143" t="s">
+      <c r="D97" s="139" t="s">
         <v>131</v>
       </c>
-      <c r="E97" s="153">
-        <v>0</v>
-      </c>
-      <c r="F97" s="154"/>
-      <c r="H97" s="252"/>
-    </row>
-    <row r="98" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="142" t="s">
+      <c r="E97" s="146">
+        <v>0</v>
+      </c>
+      <c r="F97" s="147"/>
+      <c r="H97" s="247"/>
+    </row>
+    <row r="98" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B98" s="151" t="s">
+      <c r="B98" s="144" t="s">
         <v>115</v>
       </c>
-      <c r="C98" s="152" t="s">
+      <c r="C98" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D98" s="143" t="s">
+      <c r="D98" s="139" t="s">
         <v>133</v>
       </c>
-      <c r="E98" s="153">
+      <c r="E98" s="146">
         <v>0.04</v>
       </c>
-      <c r="F98" s="154"/>
-      <c r="H98" s="252"/>
-    </row>
-    <row r="99" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="142" t="s">
+      <c r="F98" s="147"/>
+      <c r="H98" s="247"/>
+    </row>
+    <row r="99" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B99" s="151" t="s">
+      <c r="B99" s="144" t="s">
         <v>115</v>
       </c>
-      <c r="C99" s="152" t="s">
+      <c r="C99" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D99" s="143" t="s">
+      <c r="D99" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="E99" s="153">
-        <v>0</v>
-      </c>
-      <c r="F99" s="154"/>
-      <c r="H99" s="252"/>
-    </row>
-    <row r="100" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="142" t="s">
+      <c r="E99" s="146">
+        <v>0</v>
+      </c>
+      <c r="F99" s="147"/>
+      <c r="H99" s="247"/>
+    </row>
+    <row r="100" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B100" s="151" t="s">
+      <c r="B100" s="144" t="s">
         <v>114</v>
       </c>
-      <c r="C100" s="152" t="s">
+      <c r="C100" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D100" s="143" t="s">
+      <c r="D100" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="E100" s="153">
+      <c r="E100" s="146">
         <v>0.96</v>
       </c>
-      <c r="F100" s="154"/>
-      <c r="H100" s="252"/>
-    </row>
-    <row r="101" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="142" t="s">
+      <c r="F100" s="147"/>
+      <c r="H100" s="247"/>
+    </row>
+    <row r="101" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B101" s="151" t="s">
+      <c r="B101" s="144" t="s">
         <v>114</v>
       </c>
-      <c r="C101" s="152" t="s">
+      <c r="C101" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="143" t="s">
+      <c r="D101" s="139" t="s">
         <v>131</v>
       </c>
-      <c r="E101" s="153">
-        <v>0</v>
-      </c>
-      <c r="F101" s="154"/>
-      <c r="H101" s="252"/>
-    </row>
-    <row r="102" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="142" t="s">
+      <c r="E101" s="146">
+        <v>0</v>
+      </c>
+      <c r="F101" s="147"/>
+      <c r="H101" s="247"/>
+    </row>
+    <row r="102" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B102" s="151" t="s">
+      <c r="B102" s="144" t="s">
         <v>114</v>
       </c>
-      <c r="C102" s="152" t="s">
+      <c r="C102" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D102" s="143" t="s">
+      <c r="D102" s="139" t="s">
         <v>133</v>
       </c>
-      <c r="E102" s="153">
+      <c r="E102" s="146">
         <v>0.04</v>
       </c>
-      <c r="F102" s="154"/>
-      <c r="H102" s="252"/>
-    </row>
-    <row r="103" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="142" t="s">
+      <c r="F102" s="147"/>
+      <c r="H102" s="247"/>
+    </row>
+    <row r="103" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B103" s="151" t="s">
+      <c r="B103" s="144" t="s">
         <v>114</v>
       </c>
-      <c r="C103" s="152" t="s">
+      <c r="C103" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D103" s="143" t="s">
+      <c r="D103" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="E103" s="153">
-        <v>0</v>
-      </c>
-      <c r="F103" s="154"/>
-      <c r="H103" s="252"/>
-    </row>
-    <row r="104" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="142" t="s">
+      <c r="E103" s="146">
+        <v>0</v>
+      </c>
+      <c r="F103" s="147"/>
+      <c r="H103" s="247"/>
+    </row>
+    <row r="104" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B104" s="151" t="s">
+      <c r="B104" s="144" t="s">
         <v>113</v>
       </c>
-      <c r="C104" s="152" t="s">
+      <c r="C104" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D104" s="143" t="s">
+      <c r="D104" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="E104" s="153">
+      <c r="E104" s="146">
         <v>0.3</v>
       </c>
-      <c r="F104" s="154"/>
-      <c r="H104" s="252"/>
-    </row>
-    <row r="105" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="142" t="s">
+      <c r="F104" s="147"/>
+      <c r="H104" s="247"/>
+    </row>
+    <row r="105" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B105" s="151" t="s">
+      <c r="B105" s="144" t="s">
         <v>113</v>
       </c>
-      <c r="C105" s="152" t="s">
+      <c r="C105" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D105" s="143" t="s">
+      <c r="D105" s="139" t="s">
         <v>131</v>
       </c>
-      <c r="E105" s="153">
-        <v>0</v>
-      </c>
-      <c r="F105" s="154"/>
-      <c r="H105" s="252"/>
-    </row>
-    <row r="106" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="142" t="s">
+      <c r="E105" s="146">
+        <v>0</v>
+      </c>
+      <c r="F105" s="147"/>
+      <c r="H105" s="247"/>
+    </row>
+    <row r="106" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B106" s="151" t="s">
+      <c r="B106" s="144" t="s">
         <v>113</v>
       </c>
-      <c r="C106" s="152" t="s">
+      <c r="C106" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D106" s="143" t="s">
+      <c r="D106" s="139" t="s">
         <v>133</v>
       </c>
-      <c r="E106" s="153">
+      <c r="E106" s="146">
         <v>0.7</v>
       </c>
-      <c r="F106" s="154"/>
-      <c r="H106" s="252"/>
-    </row>
-    <row r="107" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="142" t="s">
+      <c r="F106" s="147"/>
+      <c r="H106" s="247"/>
+    </row>
+    <row r="107" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B107" s="151" t="s">
+      <c r="B107" s="144" t="s">
         <v>113</v>
       </c>
-      <c r="C107" s="152" t="s">
+      <c r="C107" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D107" s="143" t="s">
+      <c r="D107" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="E107" s="153">
-        <v>0</v>
-      </c>
-      <c r="F107" s="154"/>
-      <c r="H107" s="252"/>
-    </row>
-    <row r="108" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="142" t="s">
+      <c r="E107" s="146">
+        <v>0</v>
+      </c>
+      <c r="F107" s="147"/>
+      <c r="H107" s="247"/>
+    </row>
+    <row r="108" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B108" s="151" t="s">
+      <c r="B108" s="144" t="s">
         <v>111</v>
       </c>
-      <c r="C108" s="152" t="s">
+      <c r="C108" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D108" s="143" t="s">
+      <c r="D108" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="E108" s="153">
-        <v>0</v>
-      </c>
-      <c r="F108" s="154"/>
-      <c r="H108" s="252"/>
-    </row>
-    <row r="109" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="142" t="s">
+      <c r="E108" s="146">
+        <v>0</v>
+      </c>
+      <c r="F108" s="147"/>
+      <c r="H108" s="247"/>
+    </row>
+    <row r="109" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B109" s="151" t="s">
+      <c r="B109" s="144" t="s">
         <v>111</v>
       </c>
-      <c r="C109" s="152" t="s">
+      <c r="C109" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D109" s="143" t="s">
+      <c r="D109" s="139" t="s">
         <v>131</v>
       </c>
-      <c r="E109" s="153">
-        <v>0</v>
-      </c>
-      <c r="F109" s="154"/>
-      <c r="H109" s="252"/>
-    </row>
-    <row r="110" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="142" t="s">
+      <c r="E109" s="146">
+        <v>0</v>
+      </c>
+      <c r="F109" s="147"/>
+      <c r="H109" s="247"/>
+    </row>
+    <row r="110" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B110" s="151" t="s">
+      <c r="B110" s="144" t="s">
         <v>111</v>
       </c>
-      <c r="C110" s="152" t="s">
+      <c r="C110" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D110" s="143" t="s">
+      <c r="D110" s="139" t="s">
         <v>133</v>
       </c>
-      <c r="E110" s="153">
+      <c r="E110" s="146">
         <v>1</v>
       </c>
-      <c r="F110" s="154"/>
-      <c r="H110" s="252"/>
-    </row>
-    <row r="111" spans="1:8" s="155" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="142" t="s">
+      <c r="F110" s="147"/>
+      <c r="H110" s="247"/>
+    </row>
+    <row r="111" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="138" t="s">
         <v>134</v>
       </c>
-      <c r="B111" s="151" t="s">
+      <c r="B111" s="144" t="s">
         <v>111</v>
       </c>
-      <c r="C111" s="152" t="s">
+      <c r="C111" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="D111" s="143" t="s">
+      <c r="D111" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="E111" s="153">
-        <v>0</v>
-      </c>
-      <c r="F111" s="154"/>
-      <c r="H111" s="252"/>
-    </row>
-    <row r="112" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="144" t="s">
+      <c r="E111" s="146">
+        <v>0</v>
+      </c>
+      <c r="F111" s="147"/>
+      <c r="H111" s="247"/>
+    </row>
+    <row r="112" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B112" s="171" t="s">
+      <c r="B112" s="164" t="s">
         <v>116</v>
       </c>
-      <c r="C112" s="172" t="s">
+      <c r="C112" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D112" s="145" t="s">
+      <c r="D112" s="141" t="s">
         <v>132</v>
       </c>
-      <c r="E112" s="173">
+      <c r="E112" s="166">
         <v>0.7</v>
       </c>
-      <c r="H112" s="253" t="s">
+      <c r="H112" s="248" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="113" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="144" t="s">
+    <row r="113" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B113" s="171" t="s">
+      <c r="B113" s="164" t="s">
         <v>116</v>
       </c>
-      <c r="C113" s="172" t="s">
+      <c r="C113" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D113" s="145" t="s">
+      <c r="D113" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="E113" s="173">
-        <v>0</v>
-      </c>
-      <c r="H113" s="253"/>
-    </row>
-    <row r="114" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="144" t="s">
+      <c r="E113" s="166">
+        <v>0</v>
+      </c>
+      <c r="H113" s="248"/>
+    </row>
+    <row r="114" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B114" s="171" t="s">
+      <c r="B114" s="164" t="s">
         <v>116</v>
       </c>
-      <c r="C114" s="172" t="s">
+      <c r="C114" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D114" s="145" t="s">
+      <c r="D114" s="141" t="s">
         <v>130</v>
       </c>
-      <c r="E114" s="173">
-        <v>0</v>
-      </c>
-      <c r="H114" s="253"/>
-    </row>
-    <row r="115" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="144" t="s">
+      <c r="E114" s="166">
+        <v>0</v>
+      </c>
+      <c r="H114" s="248"/>
+    </row>
+    <row r="115" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B115" s="171" t="s">
+      <c r="B115" s="164" t="s">
         <v>116</v>
       </c>
-      <c r="C115" s="172" t="s">
+      <c r="C115" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D115" s="145" t="s">
+      <c r="D115" s="141" t="s">
         <v>129</v>
       </c>
-      <c r="E115" s="173">
+      <c r="E115" s="166">
         <v>0.3</v>
       </c>
-      <c r="H115" s="253"/>
-    </row>
-    <row r="116" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="144" t="s">
+      <c r="H115" s="248"/>
+    </row>
+    <row r="116" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B116" s="171" t="s">
+      <c r="B116" s="164" t="s">
         <v>116</v>
       </c>
-      <c r="C116" s="172" t="s">
+      <c r="C116" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D116" s="145" t="s">
+      <c r="D116" s="141" t="s">
         <v>128</v>
       </c>
-      <c r="E116" s="173">
-        <v>0</v>
-      </c>
-      <c r="H116" s="253"/>
-    </row>
-    <row r="117" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="144" t="s">
+      <c r="E116" s="166">
+        <v>0</v>
+      </c>
+      <c r="H116" s="248"/>
+    </row>
+    <row r="117" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B117" s="171" t="s">
+      <c r="B117" s="164" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="172" t="s">
+      <c r="C117" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D117" s="145" t="s">
+      <c r="D117" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E117" s="173">
-        <v>0</v>
-      </c>
-      <c r="H117" s="253"/>
-    </row>
-    <row r="118" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="144" t="s">
+      <c r="E117" s="166">
+        <v>0</v>
+      </c>
+      <c r="H117" s="248"/>
+    </row>
+    <row r="118" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B118" s="171" t="s">
+      <c r="B118" s="164" t="s">
         <v>115</v>
       </c>
-      <c r="C118" s="172" t="s">
+      <c r="C118" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D118" s="145" t="s">
+      <c r="D118" s="141" t="s">
         <v>132</v>
       </c>
-      <c r="E118" s="173">
+      <c r="E118" s="166">
         <v>0.6</v>
       </c>
-      <c r="H118" s="253"/>
-    </row>
-    <row r="119" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="144" t="s">
+      <c r="H118" s="248"/>
+    </row>
+    <row r="119" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B119" s="171" t="s">
+      <c r="B119" s="164" t="s">
         <v>115</v>
       </c>
-      <c r="C119" s="172" t="s">
+      <c r="C119" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D119" s="145" t="s">
+      <c r="D119" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="E119" s="173">
-        <v>0</v>
-      </c>
-      <c r="H119" s="253"/>
-    </row>
-    <row r="120" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="144" t="s">
+      <c r="E119" s="166">
+        <v>0</v>
+      </c>
+      <c r="H119" s="248"/>
+    </row>
+    <row r="120" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B120" s="171" t="s">
+      <c r="B120" s="164" t="s">
         <v>115</v>
       </c>
-      <c r="C120" s="172" t="s">
+      <c r="C120" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D120" s="145" t="s">
+      <c r="D120" s="141" t="s">
         <v>130</v>
       </c>
-      <c r="E120" s="173">
-        <v>0</v>
-      </c>
-      <c r="H120" s="253"/>
-    </row>
-    <row r="121" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="144" t="s">
+      <c r="E120" s="166">
+        <v>0</v>
+      </c>
+      <c r="H120" s="248"/>
+    </row>
+    <row r="121" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B121" s="171" t="s">
+      <c r="B121" s="164" t="s">
         <v>115</v>
       </c>
-      <c r="C121" s="172" t="s">
+      <c r="C121" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D121" s="145" t="s">
+      <c r="D121" s="141" t="s">
         <v>129</v>
       </c>
-      <c r="E121" s="173">
+      <c r="E121" s="166">
         <v>0.4</v>
       </c>
-      <c r="H121" s="253"/>
-    </row>
-    <row r="122" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="144" t="s">
+      <c r="H121" s="248"/>
+    </row>
+    <row r="122" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B122" s="171" t="s">
+      <c r="B122" s="164" t="s">
         <v>115</v>
       </c>
-      <c r="C122" s="172" t="s">
+      <c r="C122" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D122" s="145" t="s">
+      <c r="D122" s="141" t="s">
         <v>128</v>
       </c>
-      <c r="E122" s="173">
-        <v>0</v>
-      </c>
-      <c r="H122" s="253"/>
-    </row>
-    <row r="123" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="144" t="s">
+      <c r="E122" s="166">
+        <v>0</v>
+      </c>
+      <c r="H122" s="248"/>
+    </row>
+    <row r="123" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B123" s="171" t="s">
+      <c r="B123" s="164" t="s">
         <v>115</v>
       </c>
-      <c r="C123" s="172" t="s">
+      <c r="C123" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D123" s="145" t="s">
+      <c r="D123" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E123" s="173">
-        <v>0</v>
-      </c>
-      <c r="H123" s="253"/>
-    </row>
-    <row r="124" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="144" t="s">
+      <c r="E123" s="166">
+        <v>0</v>
+      </c>
+      <c r="H123" s="248"/>
+    </row>
+    <row r="124" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B124" s="171" t="s">
+      <c r="B124" s="164" t="s">
         <v>114</v>
       </c>
-      <c r="C124" s="172" t="s">
+      <c r="C124" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D124" s="145" t="s">
+      <c r="D124" s="141" t="s">
         <v>132</v>
       </c>
-      <c r="E124" s="173">
+      <c r="E124" s="166">
         <v>0.42</v>
       </c>
-      <c r="H124" s="253"/>
-    </row>
-    <row r="125" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="144" t="s">
+      <c r="H124" s="248"/>
+    </row>
+    <row r="125" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B125" s="171" t="s">
+      <c r="B125" s="164" t="s">
         <v>114</v>
       </c>
-      <c r="C125" s="172" t="s">
+      <c r="C125" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D125" s="145" t="s">
+      <c r="D125" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="E125" s="173">
-        <v>0</v>
-      </c>
-      <c r="H125" s="253"/>
-    </row>
-    <row r="126" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="144" t="s">
+      <c r="E125" s="166">
+        <v>0</v>
+      </c>
+      <c r="H125" s="248"/>
+    </row>
+    <row r="126" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B126" s="171" t="s">
+      <c r="B126" s="164" t="s">
         <v>114</v>
       </c>
-      <c r="C126" s="172" t="s">
+      <c r="C126" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D126" s="145" t="s">
+      <c r="D126" s="141" t="s">
         <v>130</v>
       </c>
-      <c r="E126" s="173">
-        <v>0</v>
-      </c>
-      <c r="H126" s="253"/>
-    </row>
-    <row r="127" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="144" t="s">
+      <c r="E126" s="166">
+        <v>0</v>
+      </c>
+      <c r="H126" s="248"/>
+    </row>
+    <row r="127" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B127" s="171" t="s">
+      <c r="B127" s="164" t="s">
         <v>114</v>
       </c>
-      <c r="C127" s="172" t="s">
+      <c r="C127" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D127" s="145" t="s">
+      <c r="D127" s="141" t="s">
         <v>129</v>
       </c>
-      <c r="E127" s="173">
+      <c r="E127" s="166">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H127" s="253"/>
-    </row>
-    <row r="128" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="144" t="s">
+      <c r="H127" s="248"/>
+    </row>
+    <row r="128" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B128" s="171" t="s">
+      <c r="B128" s="164" t="s">
         <v>114</v>
       </c>
-      <c r="C128" s="172" t="s">
+      <c r="C128" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D128" s="145" t="s">
+      <c r="D128" s="141" t="s">
         <v>128</v>
       </c>
-      <c r="E128" s="173">
-        <v>0</v>
-      </c>
-      <c r="H128" s="253"/>
-    </row>
-    <row r="129" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="144" t="s">
+      <c r="E128" s="166">
+        <v>0</v>
+      </c>
+      <c r="H128" s="248"/>
+    </row>
+    <row r="129" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B129" s="171" t="s">
+      <c r="B129" s="164" t="s">
         <v>114</v>
       </c>
-      <c r="C129" s="172" t="s">
+      <c r="C129" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D129" s="145" t="s">
+      <c r="D129" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E129" s="173">
-        <v>0</v>
-      </c>
-      <c r="H129" s="253"/>
-    </row>
-    <row r="130" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="144" t="s">
+      <c r="E129" s="166">
+        <v>0</v>
+      </c>
+      <c r="H129" s="248"/>
+    </row>
+    <row r="130" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B130" s="171" t="s">
+      <c r="B130" s="164" t="s">
         <v>113</v>
       </c>
-      <c r="C130" s="172" t="s">
+      <c r="C130" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D130" s="145" t="s">
+      <c r="D130" s="141" t="s">
         <v>132</v>
       </c>
-      <c r="E130" s="173">
+      <c r="E130" s="166">
         <v>0.05</v>
       </c>
-      <c r="H130" s="253"/>
-    </row>
-    <row r="131" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="144" t="s">
+      <c r="H130" s="248"/>
+    </row>
+    <row r="131" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B131" s="171" t="s">
+      <c r="B131" s="164" t="s">
         <v>113</v>
       </c>
-      <c r="C131" s="172" t="s">
+      <c r="C131" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D131" s="145" t="s">
+      <c r="D131" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="E131" s="173">
-        <v>0</v>
-      </c>
-      <c r="H131" s="253"/>
-    </row>
-    <row r="132" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="144" t="s">
+      <c r="E131" s="166">
+        <v>0</v>
+      </c>
+      <c r="H131" s="248"/>
+    </row>
+    <row r="132" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B132" s="171" t="s">
+      <c r="B132" s="164" t="s">
         <v>113</v>
       </c>
-      <c r="C132" s="172" t="s">
+      <c r="C132" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D132" s="145" t="s">
+      <c r="D132" s="141" t="s">
         <v>130</v>
       </c>
-      <c r="E132" s="173">
-        <v>0</v>
-      </c>
-      <c r="H132" s="253"/>
-    </row>
-    <row r="133" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="144" t="s">
+      <c r="E132" s="166">
+        <v>0</v>
+      </c>
+      <c r="H132" s="248"/>
+    </row>
+    <row r="133" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B133" s="171" t="s">
+      <c r="B133" s="164" t="s">
         <v>113</v>
       </c>
-      <c r="C133" s="172" t="s">
+      <c r="C133" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D133" s="145" t="s">
+      <c r="D133" s="141" t="s">
         <v>129</v>
       </c>
-      <c r="E133" s="173">
+      <c r="E133" s="166">
         <v>0.95</v>
       </c>
-      <c r="H133" s="253"/>
-    </row>
-    <row r="134" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="144" t="s">
+      <c r="H133" s="248"/>
+    </row>
+    <row r="134" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B134" s="171" t="s">
+      <c r="B134" s="164" t="s">
         <v>113</v>
       </c>
-      <c r="C134" s="172" t="s">
+      <c r="C134" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D134" s="145" t="s">
+      <c r="D134" s="141" t="s">
         <v>128</v>
       </c>
-      <c r="E134" s="173">
-        <v>0</v>
-      </c>
-      <c r="H134" s="253"/>
-    </row>
-    <row r="135" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="144" t="s">
+      <c r="E134" s="166">
+        <v>0</v>
+      </c>
+      <c r="H134" s="248"/>
+    </row>
+    <row r="135" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B135" s="171" t="s">
+      <c r="B135" s="164" t="s">
         <v>113</v>
       </c>
-      <c r="C135" s="172" t="s">
+      <c r="C135" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D135" s="145" t="s">
+      <c r="D135" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E135" s="173">
-        <v>0</v>
-      </c>
-      <c r="H135" s="253"/>
-    </row>
-    <row r="136" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="144" t="s">
+      <c r="E135" s="166">
+        <v>0</v>
+      </c>
+      <c r="H135" s="248"/>
+    </row>
+    <row r="136" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B136" s="171" t="s">
+      <c r="B136" s="164" t="s">
         <v>111</v>
       </c>
-      <c r="C136" s="172" t="s">
+      <c r="C136" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D136" s="145" t="s">
+      <c r="D136" s="141" t="s">
         <v>132</v>
       </c>
-      <c r="E136" s="173">
-        <v>0</v>
-      </c>
-      <c r="H136" s="253"/>
-    </row>
-    <row r="137" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="144" t="s">
+      <c r="E136" s="166">
+        <v>0</v>
+      </c>
+      <c r="H136" s="248"/>
+    </row>
+    <row r="137" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B137" s="171" t="s">
+      <c r="B137" s="164" t="s">
         <v>111</v>
       </c>
-      <c r="C137" s="172" t="s">
+      <c r="C137" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D137" s="145" t="s">
+      <c r="D137" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="E137" s="173">
-        <v>0</v>
-      </c>
-      <c r="H137" s="253"/>
-    </row>
-    <row r="138" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="144" t="s">
+      <c r="E137" s="166">
+        <v>0</v>
+      </c>
+      <c r="H137" s="248"/>
+    </row>
+    <row r="138" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B138" s="171" t="s">
+      <c r="B138" s="164" t="s">
         <v>111</v>
       </c>
-      <c r="C138" s="172" t="s">
+      <c r="C138" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D138" s="145" t="s">
+      <c r="D138" s="141" t="s">
         <v>130</v>
       </c>
-      <c r="E138" s="173">
-        <v>0</v>
-      </c>
-      <c r="H138" s="253"/>
-    </row>
-    <row r="139" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="144" t="s">
+      <c r="E138" s="166">
+        <v>0</v>
+      </c>
+      <c r="H138" s="248"/>
+    </row>
+    <row r="139" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B139" s="171" t="s">
+      <c r="B139" s="164" t="s">
         <v>111</v>
       </c>
-      <c r="C139" s="172" t="s">
+      <c r="C139" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D139" s="145" t="s">
+      <c r="D139" s="141" t="s">
         <v>129</v>
       </c>
-      <c r="E139" s="173">
+      <c r="E139" s="166">
         <v>0.05</v>
       </c>
-      <c r="H139" s="253"/>
-    </row>
-    <row r="140" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="144" t="s">
+      <c r="H139" s="248"/>
+    </row>
+    <row r="140" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B140" s="171" t="s">
+      <c r="B140" s="164" t="s">
         <v>111</v>
       </c>
-      <c r="C140" s="172" t="s">
+      <c r="C140" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D140" s="145" t="s">
+      <c r="D140" s="141" t="s">
         <v>128</v>
       </c>
-      <c r="E140" s="173">
+      <c r="E140" s="166">
         <v>0.95</v>
       </c>
-      <c r="H140" s="253"/>
-    </row>
-    <row r="141" spans="1:8" s="174" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="144" t="s">
+      <c r="H140" s="248"/>
+    </row>
+    <row r="141" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B141" s="171" t="s">
+      <c r="B141" s="164" t="s">
         <v>111</v>
       </c>
-      <c r="C141" s="172" t="s">
+      <c r="C141" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="D141" s="145" t="s">
+      <c r="D141" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="E141" s="173">
-        <v>0</v>
-      </c>
-      <c r="H141" s="253"/>
+      <c r="E141" s="166">
+        <v>0</v>
+      </c>
+      <c r="H141" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7156,165 +7190,165 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="133" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="133" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="138">
+      <c r="C2" s="134">
         <v>0.96499999999999997</v>
       </c>
-      <c r="D2" s="65"/>
-      <c r="E2" s="254" t="s">
+      <c r="D2" s="64"/>
+      <c r="E2" s="249" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="140" t="s">
+      <c r="A3" s="136" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="140" t="s">
+      <c r="B3" s="136" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="141">
+      <c r="C3" s="137">
         <v>0.96499999999999997</v>
       </c>
-      <c r="D3" s="65"/>
-      <c r="E3" s="254"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="249"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="140" t="s">
+      <c r="A4" s="136" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="140" t="s">
+      <c r="B4" s="136" t="s">
         <v>122</v>
       </c>
-      <c r="C4" s="141">
+      <c r="C4" s="137">
         <v>0.5</v>
       </c>
-      <c r="D4" s="65"/>
-      <c r="E4" s="254"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="249"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="140" t="s">
+      <c r="A5" s="136" t="s">
         <v>147</v>
       </c>
-      <c r="B5" s="140" t="s">
+      <c r="B5" s="136" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="141">
-        <v>0</v>
-      </c>
-      <c r="D5" s="65"/>
-      <c r="E5" s="254"/>
+      <c r="C5" s="137">
+        <v>0</v>
+      </c>
+      <c r="D5" s="64"/>
+      <c r="E5" s="249"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="142" t="s">
+      <c r="A6" s="138" t="s">
         <v>146</v>
       </c>
-      <c r="B6" s="142" t="s">
+      <c r="B6" s="138" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="143">
+      <c r="C6" s="139">
         <v>0.96499999999999997</v>
       </c>
-      <c r="D6" s="65"/>
-      <c r="E6" s="254"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="249"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="142" t="s">
+      <c r="A7" s="138" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="142" t="s">
+      <c r="B7" s="138" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="143">
+      <c r="C7" s="139">
         <v>0.96499999999999997</v>
       </c>
-      <c r="D7" s="65"/>
-      <c r="E7" s="254"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="249"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="142" t="s">
+      <c r="A8" s="138" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="142" t="s">
+      <c r="B8" s="138" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="143">
+      <c r="C8" s="139">
         <v>0.5</v>
       </c>
-      <c r="D8" s="65"/>
-      <c r="E8" s="254"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="249"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="142" t="s">
+      <c r="A9" s="138" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="142" t="s">
+      <c r="B9" s="138" t="s">
         <v>121</v>
       </c>
-      <c r="C9" s="143">
-        <v>0</v>
-      </c>
-      <c r="D9" s="65"/>
-      <c r="E9" s="254"/>
+      <c r="C9" s="139">
+        <v>0</v>
+      </c>
+      <c r="D9" s="64"/>
+      <c r="E9" s="249"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="144" t="s">
+      <c r="A10" s="140" t="s">
         <v>145</v>
       </c>
-      <c r="B10" s="144" t="s">
+      <c r="B10" s="140" t="s">
         <v>124</v>
       </c>
-      <c r="C10" s="145">
+      <c r="C10" s="141">
         <v>0.96499999999999997</v>
       </c>
-      <c r="D10" s="65"/>
-      <c r="E10" s="254"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="249"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="144" t="s">
+      <c r="A11" s="140" t="s">
         <v>145</v>
       </c>
-      <c r="B11" s="144" t="s">
+      <c r="B11" s="140" t="s">
         <v>123</v>
       </c>
-      <c r="C11" s="145">
+      <c r="C11" s="141">
         <v>0.96499999999999997</v>
       </c>
-      <c r="D11" s="65"/>
-      <c r="E11" s="254"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="249"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="144" t="s">
+      <c r="A12" s="140" t="s">
         <v>145</v>
       </c>
-      <c r="B12" s="144" t="s">
+      <c r="B12" s="140" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="145">
+      <c r="C12" s="141">
         <v>0.96499999999999997</v>
       </c>
-      <c r="D12" s="65"/>
-      <c r="E12" s="254"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="249"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="144" t="s">
+      <c r="A13" s="140" t="s">
         <v>145</v>
       </c>
-      <c r="B13" s="144" t="s">
+      <c r="B13" s="140" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="145">
-        <v>0</v>
-      </c>
-      <c r="D13" s="65"/>
-      <c r="E13" s="254"/>
+      <c r="C13" s="141">
+        <v>0</v>
+      </c>
+      <c r="D13" s="64"/>
+      <c r="E13" s="249"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B18" s="65"/>
+      <c r="B18" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7329,99 +7363,99 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23" style="65" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="10.83203125" style="65"/>
-    <col min="6" max="6" width="112.6640625" style="65" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="65"/>
+    <col min="1" max="1" width="23" style="64" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="10.83203125" style="64"/>
+    <col min="6" max="6" width="112.6640625" style="64" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="64"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="150" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="160" t="s">
+      <c r="B1" s="153" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="175" t="s">
+      <c r="C1" s="168" t="s">
         <v>137</v>
       </c>
-      <c r="D1" s="160" t="s">
+      <c r="D1" s="153" t="s">
         <v>144</v>
       </c>
-      <c r="F1" s="162" t="s">
+      <c r="F1" s="155" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="137" t="s">
+    <row r="2" spans="1:6" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="133" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="138" t="s">
+      <c r="B2" s="134" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="169" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="138">
-        <v>0</v>
-      </c>
-      <c r="F2" s="177" t="s">
+      <c r="D2" s="134">
+        <v>0</v>
+      </c>
+      <c r="F2" s="170" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="140" t="s">
+    <row r="3" spans="1:6" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="136" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="141" t="s">
+      <c r="B3" s="137" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="178" t="s">
+      <c r="C3" s="171" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="141">
+      <c r="D3" s="137">
         <v>0.95</v>
       </c>
-      <c r="F3" s="179" t="s">
+      <c r="F3" s="172" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="166" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="140" t="s">
+    <row r="4" spans="1:6" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="136" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="141" t="s">
+      <c r="B4" s="137" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="178" t="s">
+      <c r="C4" s="171" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="141">
-        <v>0</v>
-      </c>
-      <c r="F4" s="179" t="s">
+      <c r="D4" s="137">
+        <v>0</v>
+      </c>
+      <c r="F4" s="172" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="155" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="142" t="s">
+    <row r="5" spans="1:6" s="148" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="138" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="143" t="s">
+      <c r="B5" s="139" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="180" t="s">
+      <c r="C5" s="173" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="143">
+      <c r="D5" s="139">
         <v>0.8</v>
       </c>
-      <c r="F5" s="156" t="s">
+      <c r="F5" s="149" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F6" s="149"/>
+      <c r="F6" s="142"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7444,232 +7478,232 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="271" t="s">
+      <c r="B2" s="267" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="273" t="s">
+      <c r="C2" s="253" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="274"/>
-      <c r="E2" s="274"/>
-      <c r="F2" s="275"/>
-      <c r="G2" s="288" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="269"/>
+      <c r="G2" s="265" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="271" t="s">
+      <c r="H2" s="267" t="s">
         <v>263</v>
       </c>
-      <c r="I2" s="273" t="s">
+      <c r="I2" s="253" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="274"/>
-      <c r="K2" s="283"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="255"/>
     </row>
     <row r="3" spans="1:21" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="272"/>
-      <c r="C3" s="276"/>
-      <c r="D3" s="277"/>
-      <c r="E3" s="277"/>
-      <c r="F3" s="278"/>
-      <c r="G3" s="289"/>
-      <c r="H3" s="272"/>
-      <c r="I3" s="276"/>
-      <c r="J3" s="277"/>
-      <c r="K3" s="284"/>
+      <c r="B3" s="268"/>
+      <c r="C3" s="256"/>
+      <c r="D3" s="257"/>
+      <c r="E3" s="257"/>
+      <c r="F3" s="270"/>
+      <c r="G3" s="266"/>
+      <c r="H3" s="268"/>
+      <c r="I3" s="256"/>
+      <c r="J3" s="257"/>
+      <c r="K3" s="258"/>
     </row>
     <row r="4" spans="1:21" s="44" customFormat="1" ht="270" x14ac:dyDescent="0.2">
       <c r="A4" s="46"/>
-      <c r="B4" s="181" t="s">
+      <c r="B4" s="174" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="279" t="s">
+      <c r="C4" s="271" t="s">
         <v>322</v>
       </c>
-      <c r="D4" s="280"/>
-      <c r="E4" s="280"/>
-      <c r="F4" s="281"/>
-      <c r="G4" s="182" t="s">
+      <c r="D4" s="272"/>
+      <c r="E4" s="272"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="175" t="s">
         <v>270</v>
       </c>
-      <c r="H4" s="183" t="s">
+      <c r="H4" s="176" t="s">
         <v>271</v>
       </c>
-      <c r="I4" s="285" t="s">
+      <c r="I4" s="262" t="s">
         <v>295</v>
       </c>
-      <c r="J4" s="286"/>
-      <c r="K4" s="287"/>
+      <c r="J4" s="263"/>
+      <c r="K4" s="264"/>
     </row>
     <row r="5" spans="1:21" s="44" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="46"/>
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="92" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="255" t="s">
+      <c r="C5" s="259" t="s">
         <v>323</v>
       </c>
-      <c r="D5" s="256"/>
-      <c r="E5" s="256"/>
-      <c r="F5" s="282"/>
-      <c r="G5" s="184">
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="261"/>
+      <c r="G5" s="177">
         <v>0.8</v>
       </c>
-      <c r="H5" s="185" t="s">
+      <c r="H5" s="178" t="s">
         <v>307</v>
       </c>
-      <c r="I5" s="258" t="s">
+      <c r="I5" s="250" t="s">
         <v>269</v>
       </c>
-      <c r="J5" s="259"/>
-      <c r="K5" s="260"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="252"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
     </row>
     <row r="6" spans="1:21" s="44" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="46"/>
-      <c r="B6" s="96" t="s">
+      <c r="B6" s="92" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="255" t="s">
+      <c r="C6" s="259" t="s">
         <v>324</v>
       </c>
-      <c r="D6" s="256"/>
-      <c r="E6" s="256"/>
-      <c r="F6" s="282"/>
-      <c r="G6" s="184">
+      <c r="D6" s="260"/>
+      <c r="E6" s="260"/>
+      <c r="F6" s="261"/>
+      <c r="G6" s="177">
         <v>0.8</v>
       </c>
-      <c r="H6" s="186" t="s">
+      <c r="H6" s="179" t="s">
         <v>307</v>
       </c>
-      <c r="I6" s="258" t="s">
+      <c r="I6" s="250" t="s">
         <v>268</v>
       </c>
-      <c r="J6" s="259"/>
-      <c r="K6" s="260"/>
+      <c r="J6" s="251"/>
+      <c r="K6" s="252"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
     </row>
     <row r="7" spans="1:21" s="44" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="46"/>
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="92" t="s">
         <v>297</v>
       </c>
-      <c r="C7" s="255" t="s">
+      <c r="C7" s="259" t="s">
         <v>298</v>
       </c>
-      <c r="D7" s="256"/>
-      <c r="E7" s="256"/>
-      <c r="F7" s="282"/>
-      <c r="G7" s="184">
+      <c r="D7" s="260"/>
+      <c r="E7" s="260"/>
+      <c r="F7" s="261"/>
+      <c r="G7" s="177">
         <v>1</v>
       </c>
-      <c r="H7" s="186"/>
-      <c r="I7" s="258" t="s">
+      <c r="H7" s="179"/>
+      <c r="I7" s="250" t="s">
         <v>299</v>
       </c>
-      <c r="J7" s="259"/>
-      <c r="K7" s="260"/>
+      <c r="J7" s="251"/>
+      <c r="K7" s="252"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:21" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A8" s="46"/>
-      <c r="B8" s="96" t="s">
+      <c r="B8" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="255" t="s">
+      <c r="C8" s="259" t="s">
         <v>265</v>
       </c>
-      <c r="D8" s="256"/>
-      <c r="E8" s="256"/>
-      <c r="F8" s="282"/>
-      <c r="G8" s="184">
+      <c r="D8" s="260"/>
+      <c r="E8" s="260"/>
+      <c r="F8" s="261"/>
+      <c r="G8" s="177">
         <v>1</v>
       </c>
-      <c r="H8" s="185" t="s">
+      <c r="H8" s="178" t="s">
         <v>266</v>
       </c>
-      <c r="I8" s="258"/>
-      <c r="J8" s="259"/>
-      <c r="K8" s="260"/>
+      <c r="I8" s="250"/>
+      <c r="J8" s="251"/>
+      <c r="K8" s="252"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="1:21" s="44" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="46"/>
-      <c r="B9" s="96" t="s">
+      <c r="B9" s="92" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="255" t="s">
+      <c r="C9" s="259" t="s">
         <v>158</v>
       </c>
-      <c r="D9" s="256"/>
-      <c r="E9" s="256"/>
-      <c r="F9" s="282"/>
-      <c r="G9" s="184">
+      <c r="D9" s="260"/>
+      <c r="E9" s="260"/>
+      <c r="F9" s="261"/>
+      <c r="G9" s="177">
         <v>0.95</v>
       </c>
-      <c r="H9" s="185" t="s">
+      <c r="H9" s="178" t="s">
         <v>307</v>
       </c>
-      <c r="I9" s="255" t="s">
+      <c r="I9" s="259" t="s">
         <v>264</v>
       </c>
-      <c r="J9" s="256"/>
-      <c r="K9" s="257"/>
+      <c r="J9" s="260"/>
+      <c r="K9" s="276"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:21" s="44" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="47"/>
-      <c r="B10" s="96" t="s">
+      <c r="B10" s="92" t="s">
         <v>159</v>
       </c>
-      <c r="C10" s="255" t="s">
+      <c r="C10" s="259" t="s">
         <v>162</v>
       </c>
-      <c r="D10" s="256"/>
-      <c r="E10" s="256"/>
-      <c r="F10" s="282"/>
-      <c r="G10" s="187">
+      <c r="D10" s="260"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="261"/>
+      <c r="G10" s="180">
         <v>0.9</v>
       </c>
-      <c r="H10" s="185"/>
-      <c r="I10" s="258" t="s">
+      <c r="H10" s="178"/>
+      <c r="I10" s="250" t="s">
         <v>267</v>
       </c>
-      <c r="J10" s="259"/>
-      <c r="K10" s="260"/>
+      <c r="J10" s="251"/>
+      <c r="K10" s="252"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
     </row>
     <row r="11" spans="1:21" s="44" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="46"/>
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="92" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="255" t="s">
+      <c r="C11" s="259" t="s">
         <v>161</v>
       </c>
-      <c r="D11" s="256"/>
-      <c r="E11" s="256"/>
-      <c r="F11" s="282"/>
-      <c r="G11" s="187">
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="261"/>
+      <c r="G11" s="180">
         <v>0.9</v>
       </c>
-      <c r="H11" s="186"/>
-      <c r="I11" s="258" t="s">
+      <c r="H11" s="179"/>
+      <c r="I11" s="250" t="s">
         <v>267</v>
       </c>
-      <c r="J11" s="259"/>
-      <c r="K11" s="260"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="252"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -7700,28 +7734,28 @@
       <c r="U13" s="51"/>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="265" t="s">
+      <c r="B14" s="281" t="s">
         <v>258</v>
       </c>
-      <c r="C14" s="266"/>
-      <c r="D14" s="266"/>
-      <c r="E14" s="266"/>
-      <c r="F14" s="266"/>
-      <c r="G14" s="266"/>
-      <c r="H14" s="266"/>
-      <c r="I14" s="266"/>
-      <c r="J14" s="266"/>
-      <c r="K14" s="266"/>
-      <c r="L14" s="266"/>
-      <c r="M14" s="266"/>
-      <c r="N14" s="266"/>
-      <c r="O14" s="266"/>
-      <c r="P14" s="266"/>
-      <c r="Q14" s="266"/>
-      <c r="R14" s="266"/>
-      <c r="S14" s="266"/>
-      <c r="T14" s="266"/>
-      <c r="U14" s="267"/>
+      <c r="C14" s="282"/>
+      <c r="D14" s="282"/>
+      <c r="E14" s="282"/>
+      <c r="F14" s="282"/>
+      <c r="G14" s="282"/>
+      <c r="H14" s="282"/>
+      <c r="I14" s="282"/>
+      <c r="J14" s="282"/>
+      <c r="K14" s="282"/>
+      <c r="L14" s="282"/>
+      <c r="M14" s="282"/>
+      <c r="N14" s="282"/>
+      <c r="O14" s="282"/>
+      <c r="P14" s="282"/>
+      <c r="Q14" s="282"/>
+      <c r="R14" s="282"/>
+      <c r="S14" s="282"/>
+      <c r="T14" s="282"/>
+      <c r="U14" s="283"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B15" s="52"/>
@@ -7746,94 +7780,94 @@
       <c r="U15" s="55"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B16" s="263" t="s">
+      <c r="B16" s="279" t="s">
         <v>254</v>
       </c>
-      <c r="C16" s="264"/>
-      <c r="D16" s="264"/>
-      <c r="E16" s="264"/>
-      <c r="F16" s="264"/>
-      <c r="G16" s="264"/>
-      <c r="H16" s="264"/>
-      <c r="I16" s="264"/>
-      <c r="J16" s="264"/>
-      <c r="K16" s="264"/>
-      <c r="L16" s="264"/>
-      <c r="M16" s="264"/>
-      <c r="N16" s="264"/>
-      <c r="O16" s="264"/>
-      <c r="P16" s="264"/>
-      <c r="Q16" s="264"/>
-      <c r="R16" s="264"/>
-      <c r="S16" s="264"/>
-      <c r="T16" s="264"/>
-      <c r="U16" s="270"/>
+      <c r="C16" s="280"/>
+      <c r="D16" s="280"/>
+      <c r="E16" s="280"/>
+      <c r="F16" s="280"/>
+      <c r="G16" s="280"/>
+      <c r="H16" s="280"/>
+      <c r="I16" s="280"/>
+      <c r="J16" s="280"/>
+      <c r="K16" s="280"/>
+      <c r="L16" s="280"/>
+      <c r="M16" s="280"/>
+      <c r="N16" s="280"/>
+      <c r="O16" s="280"/>
+      <c r="P16" s="280"/>
+      <c r="Q16" s="280"/>
+      <c r="R16" s="280"/>
+      <c r="S16" s="280"/>
+      <c r="T16" s="280"/>
+      <c r="U16" s="284"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B17" s="268" t="s">
+      <c r="B17" s="274" t="s">
         <v>250</v>
       </c>
-      <c r="C17" s="269"/>
-      <c r="D17" s="188">
+      <c r="C17" s="275"/>
+      <c r="D17" s="181">
         <v>2008</v>
       </c>
-      <c r="E17" s="188">
+      <c r="E17" s="181">
         <v>2009</v>
       </c>
-      <c r="F17" s="188">
+      <c r="F17" s="181">
         <v>2010</v>
       </c>
-      <c r="G17" s="188">
+      <c r="G17" s="181">
         <v>2011</v>
       </c>
-      <c r="H17" s="188">
+      <c r="H17" s="181">
         <v>2012</v>
       </c>
-      <c r="I17" s="188">
+      <c r="I17" s="181">
         <v>2013</v>
       </c>
-      <c r="J17" s="188">
+      <c r="J17" s="181">
         <v>2014</v>
       </c>
-      <c r="K17" s="188">
+      <c r="K17" s="181">
         <v>2015</v>
       </c>
-      <c r="L17" s="188">
+      <c r="L17" s="181">
         <v>2016</v>
       </c>
-      <c r="M17" s="188">
+      <c r="M17" s="181">
         <v>2017</v>
       </c>
-      <c r="N17" s="188">
+      <c r="N17" s="181">
         <v>2018</v>
       </c>
-      <c r="O17" s="188">
+      <c r="O17" s="181">
         <v>2019</v>
       </c>
-      <c r="P17" s="188">
+      <c r="P17" s="181">
         <v>2020</v>
       </c>
-      <c r="Q17" s="188">
+      <c r="Q17" s="181">
         <v>2021</v>
       </c>
-      <c r="R17" s="188">
+      <c r="R17" s="181">
         <v>2022</v>
       </c>
-      <c r="S17" s="188">
+      <c r="S17" s="181">
         <v>2023</v>
       </c>
-      <c r="T17" s="188">
+      <c r="T17" s="181">
         <v>2024</v>
       </c>
-      <c r="U17" s="189" t="s">
+      <c r="U17" s="182" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18" s="268" t="s">
+      <c r="B18" s="274" t="s">
         <v>251</v>
       </c>
-      <c r="C18" s="269"/>
+      <c r="C18" s="275"/>
       <c r="D18" s="59">
         <v>0.86</v>
       </c>
@@ -7885,15 +7919,15 @@
       <c r="T18" s="59">
         <v>0.8</v>
       </c>
-      <c r="U18" s="190">
+      <c r="U18" s="183">
         <v>0.8</v>
       </c>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B19" s="268" t="s">
+      <c r="B19" s="274" t="s">
         <v>252</v>
       </c>
-      <c r="C19" s="269"/>
+      <c r="C19" s="275"/>
       <c r="D19" s="59">
         <f>78/86</f>
         <v>0.90697674418604646</v>
@@ -7960,15 +7994,15 @@
       <c r="T19" s="59">
         <v>0</v>
       </c>
-      <c r="U19" s="190">
+      <c r="U19" s="183">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B20" s="268" t="s">
+      <c r="B20" s="274" t="s">
         <v>253</v>
       </c>
-      <c r="C20" s="269"/>
+      <c r="C20" s="275"/>
       <c r="D20" s="59">
         <v>1</v>
       </c>
@@ -8020,7 +8054,7 @@
       <c r="T20" s="59">
         <v>0</v>
       </c>
-      <c r="U20" s="190">
+      <c r="U20" s="183">
         <v>0</v>
       </c>
     </row>
@@ -8047,53 +8081,53 @@
       <c r="U21" s="55"/>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B22" s="263" t="s">
+      <c r="B22" s="279" t="s">
         <v>257</v>
       </c>
-      <c r="C22" s="264"/>
-      <c r="D22" s="264"/>
-      <c r="E22" s="264"/>
-      <c r="F22" s="264"/>
-      <c r="G22" s="264"/>
-      <c r="H22" s="264"/>
-      <c r="I22" s="264"/>
-      <c r="J22" s="264"/>
-      <c r="K22" s="191"/>
-      <c r="L22" s="191"/>
-      <c r="M22" s="191"/>
-      <c r="N22" s="191"/>
-      <c r="O22" s="191"/>
-      <c r="P22" s="191"/>
-      <c r="Q22" s="191"/>
-      <c r="R22" s="191"/>
-      <c r="S22" s="191"/>
-      <c r="T22" s="191"/>
-      <c r="U22" s="192"/>
+      <c r="C22" s="280"/>
+      <c r="D22" s="280"/>
+      <c r="E22" s="280"/>
+      <c r="F22" s="280"/>
+      <c r="G22" s="280"/>
+      <c r="H22" s="280"/>
+      <c r="I22" s="280"/>
+      <c r="J22" s="280"/>
+      <c r="K22" s="184"/>
+      <c r="L22" s="184"/>
+      <c r="M22" s="184"/>
+      <c r="N22" s="184"/>
+      <c r="O22" s="184"/>
+      <c r="P22" s="184"/>
+      <c r="Q22" s="184"/>
+      <c r="R22" s="184"/>
+      <c r="S22" s="184"/>
+      <c r="T22" s="184"/>
+      <c r="U22" s="185"/>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B23" s="268" t="s">
+      <c r="B23" s="274" t="s">
         <v>250</v>
       </c>
-      <c r="C23" s="269"/>
-      <c r="D23" s="188">
+      <c r="C23" s="275"/>
+      <c r="D23" s="181">
         <v>2019</v>
       </c>
-      <c r="E23" s="188">
+      <c r="E23" s="181">
         <v>2020</v>
       </c>
-      <c r="F23" s="188">
+      <c r="F23" s="181">
         <v>2021</v>
       </c>
-      <c r="G23" s="188">
+      <c r="G23" s="181">
         <v>2022</v>
       </c>
-      <c r="H23" s="188">
+      <c r="H23" s="181">
         <v>2023</v>
       </c>
-      <c r="I23" s="188">
+      <c r="I23" s="181">
         <v>2024</v>
       </c>
-      <c r="J23" s="71" t="s">
+      <c r="J23" s="67" t="s">
         <v>256</v>
       </c>
       <c r="K23" s="53"/>
@@ -8109,10 +8143,10 @@
       <c r="U23" s="55"/>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B24" s="268" t="s">
+      <c r="B24" s="274" t="s">
         <v>251</v>
       </c>
-      <c r="C24" s="269"/>
+      <c r="C24" s="275"/>
       <c r="D24" s="59">
         <f>E24</f>
         <v>0.53</v>
@@ -8138,7 +8172,7 @@
       <c r="K24" s="53"/>
       <c r="L24" s="53"/>
       <c r="M24" s="53"/>
-      <c r="N24" s="191" t="s">
+      <c r="N24" s="184" t="s">
         <v>259</v>
       </c>
       <c r="O24" s="53"/>
@@ -8150,10 +8184,10 @@
       <c r="U24" s="55"/>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B25" s="268" t="s">
+      <c r="B25" s="274" t="s">
         <v>252</v>
       </c>
-      <c r="C25" s="269"/>
+      <c r="C25" s="275"/>
       <c r="D25" s="59">
         <f>E25</f>
         <v>0.35830985915492958</v>
@@ -8191,29 +8225,29 @@
       <c r="U25" s="55"/>
     </row>
     <row r="26" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="261" t="s">
+      <c r="B26" s="277" t="s">
         <v>253</v>
       </c>
-      <c r="C26" s="262"/>
-      <c r="D26" s="193">
-        <v>0</v>
-      </c>
-      <c r="E26" s="193">
-        <v>0</v>
-      </c>
-      <c r="F26" s="193">
-        <v>0</v>
-      </c>
-      <c r="G26" s="193">
-        <v>0</v>
-      </c>
-      <c r="H26" s="193">
-        <v>0</v>
-      </c>
-      <c r="I26" s="193">
-        <v>0</v>
-      </c>
-      <c r="J26" s="193">
+      <c r="C26" s="278"/>
+      <c r="D26" s="186">
+        <v>0</v>
+      </c>
+      <c r="E26" s="186">
+        <v>0</v>
+      </c>
+      <c r="F26" s="186">
+        <v>0</v>
+      </c>
+      <c r="G26" s="186">
+        <v>0</v>
+      </c>
+      <c r="H26" s="186">
+        <v>0</v>
+      </c>
+      <c r="I26" s="186">
+        <v>0</v>
+      </c>
+      <c r="J26" s="186">
         <v>0</v>
       </c>
       <c r="K26" s="57"/>
@@ -8234,51 +8268,31 @@
       </c>
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="E29" s="194"/>
-      <c r="F29" s="194"/>
-      <c r="G29" s="194"/>
-      <c r="H29" s="194"/>
-      <c r="I29" s="194"/>
-      <c r="J29" s="194"/>
+      <c r="E29" s="187"/>
+      <c r="F29" s="187"/>
+      <c r="G29" s="187"/>
+      <c r="H29" s="187"/>
+      <c r="I29" s="187"/>
+      <c r="J29" s="187"/>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="E30" s="194"/>
-      <c r="F30" s="194"/>
-      <c r="G30" s="194"/>
-      <c r="H30" s="194"/>
-      <c r="I30" s="194"/>
-      <c r="J30" s="194"/>
+      <c r="E30" s="187"/>
+      <c r="F30" s="187"/>
+      <c r="G30" s="187"/>
+      <c r="H30" s="187"/>
+      <c r="I30" s="187"/>
+      <c r="J30" s="187"/>
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="E31" s="194"/>
-      <c r="F31" s="194"/>
-      <c r="G31" s="194"/>
-      <c r="H31" s="194"/>
-      <c r="I31" s="194"/>
-      <c r="J31" s="194"/>
+      <c r="E31" s="187"/>
+      <c r="F31" s="187"/>
+      <c r="G31" s="187"/>
+      <c r="H31" s="187"/>
+      <c r="I31" s="187"/>
+      <c r="J31" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="I10:K10"/>
     <mergeCell ref="B26:C26"/>
@@ -8291,6 +8305,26 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B16:U16"/>
     <mergeCell ref="I11:K11"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8313,124 +8347,124 @@
   <sheetData>
     <row r="1" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="60" t="s">
         <v>247</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="61" t="s">
         <v>244</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="61" t="s">
         <v>245</v>
       </c>
-      <c r="E2" s="62" t="s">
+      <c r="E2" s="61" t="s">
         <v>246</v>
       </c>
-      <c r="F2" s="63" t="s">
+      <c r="F2" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="61" t="s">
         <v>281</v>
       </c>
-      <c r="H2" s="64" t="s">
+      <c r="H2" s="63" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="290" t="s">
+      <c r="B3" s="196" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="291"/>
-      <c r="D3" s="291"/>
-      <c r="E3" s="291"/>
-      <c r="F3" s="292"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="80"/>
-    </row>
-    <row r="4" spans="2:8" s="65" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="146" t="s">
+      <c r="C3" s="197"/>
+      <c r="D3" s="197"/>
+      <c r="E3" s="197"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="76"/>
+    </row>
+    <row r="4" spans="2:8" s="286" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="285" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="65" t="s">
+      <c r="C4" s="286" t="s">
         <v>248</v>
       </c>
-      <c r="D4" s="65">
+      <c r="D4" s="286">
         <v>0.8</v>
       </c>
-      <c r="E4" s="68">
+      <c r="E4" s="287">
         <v>0.65</v>
       </c>
-      <c r="F4" s="60"/>
-      <c r="G4" s="68">
+      <c r="F4" s="288"/>
+      <c r="G4" s="287">
         <v>2</v>
       </c>
-      <c r="H4" s="203">
+      <c r="H4" s="289">
         <f>G4</f>
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="290" t="s">
+      <c r="B5" s="196" t="s">
         <v>260</v>
       </c>
-      <c r="C5" s="291"/>
-      <c r="D5" s="291"/>
-      <c r="E5" s="291"/>
-      <c r="F5" s="292"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="203"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B6" s="146" t="s">
+      <c r="C5" s="197"/>
+      <c r="D5" s="197"/>
+      <c r="E5" s="197"/>
+      <c r="F5" s="198"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="194"/>
+    </row>
+    <row r="6" spans="2:8" s="290" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="285" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="286" t="s">
         <v>261</v>
       </c>
-      <c r="D6" s="65">
+      <c r="D6" s="286">
         <v>0.8</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="287" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="60" t="s">
+      <c r="F6" s="288" t="s">
         <v>272</v>
       </c>
-      <c r="G6" s="68">
+      <c r="G6" s="287">
         <v>3</v>
       </c>
-      <c r="H6" s="203">
+      <c r="H6" s="289">
         <f>H4*G6</f>
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="290" t="s">
+      <c r="B7" s="196" t="s">
         <v>273</v>
       </c>
-      <c r="C7" s="291"/>
-      <c r="D7" s="291"/>
-      <c r="E7" s="291"/>
-      <c r="F7" s="292"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="203"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B8" s="67" t="s">
+      <c r="C7" s="197"/>
+      <c r="D7" s="197"/>
+      <c r="E7" s="197"/>
+      <c r="F7" s="198"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="194"/>
+    </row>
+    <row r="8" spans="2:8" s="297" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="291" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="69" t="s">
+      <c r="C8" s="292" t="s">
         <v>290</v>
       </c>
-      <c r="D8" s="68">
+      <c r="D8" s="293">
         <v>0.68</v>
       </c>
-      <c r="E8" s="68" t="s">
+      <c r="E8" s="293" t="s">
         <v>292</v>
       </c>
-      <c r="F8" s="293" t="s">
+      <c r="F8" s="294" t="s">
         <v>294</v>
       </c>
-      <c r="G8" s="298">
+      <c r="G8" s="295">
         <v>3</v>
       </c>
       <c r="H8" s="296">
@@ -8438,246 +8472,246 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="67" t="s">
+    <row r="9" spans="2:8" s="297" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="291" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="292" t="s">
         <v>291</v>
       </c>
-      <c r="D9" s="68">
+      <c r="D9" s="293">
         <v>0.76</v>
       </c>
-      <c r="E9" s="68" t="s">
+      <c r="E9" s="293" t="s">
         <v>293</v>
       </c>
-      <c r="F9" s="293"/>
-      <c r="G9" s="298"/>
+      <c r="F9" s="294"/>
+      <c r="G9" s="295"/>
       <c r="H9" s="296"/>
     </row>
-    <row r="10" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="146" t="s">
+    <row r="10" spans="2:8" s="297" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="298" t="s">
         <v>164</v>
       </c>
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="292" t="s">
         <v>154</v>
       </c>
-      <c r="D10" s="65">
+      <c r="D10" s="167">
         <v>0.8</v>
       </c>
-      <c r="E10" s="68" t="s">
+      <c r="E10" s="293" t="s">
         <v>274</v>
       </c>
-      <c r="F10" s="293"/>
-      <c r="G10" s="298"/>
+      <c r="F10" s="294"/>
+      <c r="G10" s="295"/>
       <c r="H10" s="296"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="146" t="s">
+    <row r="11" spans="2:8" s="297" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="298" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="65" t="s">
+      <c r="C11" s="167" t="s">
         <v>155</v>
       </c>
-      <c r="D11" s="65">
+      <c r="D11" s="167">
         <v>0.8</v>
       </c>
-      <c r="E11" s="68" t="s">
+      <c r="E11" s="293" t="s">
         <v>274</v>
       </c>
-      <c r="F11" s="293"/>
-      <c r="G11" s="298"/>
+      <c r="F11" s="294"/>
+      <c r="G11" s="295"/>
       <c r="H11" s="296"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B12" s="146" t="s">
+    <row r="12" spans="2:8" s="297" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="298" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="65" t="s">
+      <c r="C12" s="167" t="s">
         <v>159</v>
       </c>
-      <c r="D12" s="65">
+      <c r="D12" s="167">
         <v>0.9</v>
       </c>
-      <c r="E12" s="68" t="s">
+      <c r="E12" s="293" t="s">
         <v>280</v>
       </c>
-      <c r="F12" s="293"/>
-      <c r="G12" s="298"/>
+      <c r="F12" s="294"/>
+      <c r="G12" s="295"/>
       <c r="H12" s="296"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="146" t="s">
+    <row r="13" spans="2:8" s="297" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="298" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="167" t="s">
         <v>160</v>
       </c>
-      <c r="D13" s="65">
+      <c r="D13" s="167">
         <v>0.9</v>
       </c>
-      <c r="E13" s="68" t="s">
+      <c r="E13" s="293" t="s">
         <v>275</v>
       </c>
-      <c r="F13" s="293"/>
-      <c r="G13" s="298"/>
+      <c r="F13" s="294"/>
+      <c r="G13" s="295"/>
       <c r="H13" s="296"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="290" t="s">
+      <c r="B14" s="196" t="s">
         <v>305</v>
       </c>
-      <c r="C14" s="291"/>
-      <c r="D14" s="291"/>
-      <c r="E14" s="291"/>
-      <c r="F14" s="292"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="203"/>
-    </row>
-    <row r="15" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="146" t="s">
+      <c r="C14" s="197"/>
+      <c r="D14" s="197"/>
+      <c r="E14" s="197"/>
+      <c r="F14" s="198"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="194"/>
+    </row>
+    <row r="15" spans="2:8" s="304" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="299" t="s">
         <v>149</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="300" t="s">
         <v>276</v>
       </c>
-      <c r="D15" s="65">
-        <v>0</v>
-      </c>
-      <c r="E15" s="65">
+      <c r="D15" s="300">
+        <v>0</v>
+      </c>
+      <c r="E15" s="300">
         <v>0.1</v>
       </c>
-      <c r="F15" s="293" t="s">
+      <c r="F15" s="301" t="s">
         <v>279</v>
       </c>
-      <c r="G15" s="294">
+      <c r="G15" s="302">
         <v>2</v>
       </c>
-      <c r="H15" s="295">
+      <c r="H15" s="303">
         <f>H8*G15</f>
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B16" s="146" t="s">
+    <row r="16" spans="2:8" s="304" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="299" t="s">
         <v>149</v>
       </c>
-      <c r="C16" s="65" t="s">
+      <c r="C16" s="300" t="s">
         <v>277</v>
       </c>
-      <c r="D16" s="65">
-        <v>0</v>
-      </c>
-      <c r="E16" s="65">
+      <c r="D16" s="300">
+        <v>0</v>
+      </c>
+      <c r="E16" s="300">
         <v>0.1</v>
       </c>
-      <c r="F16" s="293"/>
-      <c r="G16" s="294"/>
-      <c r="H16" s="295"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="146" t="s">
+      <c r="F16" s="301"/>
+      <c r="G16" s="302"/>
+      <c r="H16" s="303"/>
+    </row>
+    <row r="17" spans="2:8" s="304" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="299" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="65" t="s">
+      <c r="C17" s="300" t="s">
         <v>278</v>
       </c>
-      <c r="D17" s="65">
-        <v>0</v>
-      </c>
-      <c r="E17" s="65">
+      <c r="D17" s="300">
+        <v>0</v>
+      </c>
+      <c r="E17" s="300">
         <v>0.1</v>
       </c>
-      <c r="F17" s="293"/>
-      <c r="G17" s="294"/>
-      <c r="H17" s="295"/>
+      <c r="F17" s="301"/>
+      <c r="G17" s="302"/>
+      <c r="H17" s="303"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" s="290" t="s">
+      <c r="B18" s="196" t="s">
         <v>325</v>
       </c>
-      <c r="C18" s="291"/>
-      <c r="D18" s="291"/>
-      <c r="E18" s="291"/>
-      <c r="F18" s="292"/>
-      <c r="G18" s="204"/>
-      <c r="H18" s="203"/>
-    </row>
-    <row r="19" spans="2:8" ht="49" x14ac:dyDescent="0.2">
-      <c r="B19" s="146" t="s">
+      <c r="C18" s="197"/>
+      <c r="D18" s="197"/>
+      <c r="E18" s="197"/>
+      <c r="F18" s="198"/>
+      <c r="G18" s="195"/>
+      <c r="H18" s="194"/>
+    </row>
+    <row r="19" spans="2:8" s="297" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+      <c r="B19" s="298" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="65" t="s">
+      <c r="C19" s="167" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="198" t="s">
+      <c r="D19" s="305" t="s">
         <v>308</v>
       </c>
-      <c r="E19" s="198" t="s">
+      <c r="E19" s="305" t="s">
         <v>166</v>
       </c>
-      <c r="F19" s="199" t="s">
+      <c r="F19" s="306" t="s">
         <v>326</v>
       </c>
-      <c r="G19" s="204">
+      <c r="G19" s="307">
         <v>2</v>
       </c>
-      <c r="H19" s="203">
+      <c r="H19" s="308">
         <f>H15*G19</f>
         <v>72</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B20" s="290" t="s">
+      <c r="B20" s="196" t="s">
         <v>319</v>
       </c>
-      <c r="C20" s="291"/>
-      <c r="D20" s="291"/>
-      <c r="E20" s="291"/>
-      <c r="F20" s="292"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="150"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B21" s="146" t="s">
+      <c r="C20" s="197"/>
+      <c r="D20" s="197"/>
+      <c r="E20" s="197"/>
+      <c r="F20" s="198"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="143"/>
+    </row>
+    <row r="21" spans="2:8" s="304" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="299" t="s">
         <v>140</v>
       </c>
-      <c r="C21" s="65" t="s">
+      <c r="C21" s="300" t="s">
         <v>327</v>
       </c>
-      <c r="D21" s="65">
+      <c r="D21" s="300">
         <v>0.96</v>
       </c>
-      <c r="E21" s="65">
+      <c r="E21" s="300">
         <v>0.9</v>
       </c>
-      <c r="F21" s="301" t="s">
+      <c r="F21" s="309" t="s">
         <v>321</v>
       </c>
-      <c r="G21" s="298">
+      <c r="G21" s="310">
         <v>2</v>
       </c>
-      <c r="H21" s="296">
+      <c r="H21" s="311">
         <f>H19*G21</f>
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="147" t="s">
+    <row r="22" spans="2:8" s="304" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="312" t="s">
         <v>140</v>
       </c>
-      <c r="C22" s="148" t="s">
+      <c r="C22" s="313" t="s">
         <v>320</v>
       </c>
-      <c r="D22" s="148">
+      <c r="D22" s="313">
         <v>0.7</v>
       </c>
-      <c r="E22" s="148">
+      <c r="E22" s="313">
         <v>0.85</v>
       </c>
-      <c r="F22" s="302"/>
-      <c r="G22" s="299"/>
-      <c r="H22" s="300"/>
+      <c r="F22" s="314"/>
+      <c r="G22" s="315"/>
+      <c r="H22" s="316"/>
     </row>
     <row r="23" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B23" s="8"/>
@@ -8693,10 +8727,10 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="82" t="s">
+      <c r="F24" s="78" t="s">
         <v>282</v>
       </c>
-      <c r="G24" s="83">
+      <c r="G24" s="79">
         <f>G4+G6+G8+G15+G19+G21-COUNT(G3:G22)</f>
         <v>8</v>
       </c>
@@ -8707,56 +8741,56 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="81" t="s">
+      <c r="F25" s="77" t="s">
         <v>283</v>
       </c>
-      <c r="G25" s="84">
+      <c r="G25" s="80">
         <f>H21</f>
         <v>144</v>
       </c>
       <c r="H25" s="8"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C27" s="297" t="s">
+      <c r="C27" s="199" t="s">
         <v>296</v>
       </c>
-      <c r="D27" s="297"/>
-      <c r="E27" s="297"/>
-      <c r="F27" s="297"/>
-      <c r="G27" s="297"/>
+      <c r="D27" s="199"/>
+      <c r="E27" s="199"/>
+      <c r="F27" s="199"/>
+      <c r="G27" s="199"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C28" s="297"/>
-      <c r="D28" s="297"/>
-      <c r="E28" s="297"/>
-      <c r="F28" s="297"/>
-      <c r="G28" s="297"/>
+      <c r="C28" s="199"/>
+      <c r="D28" s="199"/>
+      <c r="E28" s="199"/>
+      <c r="F28" s="199"/>
+      <c r="G28" s="199"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C29" s="297"/>
-      <c r="D29" s="297"/>
-      <c r="E29" s="297"/>
-      <c r="F29" s="297"/>
-      <c r="G29" s="297"/>
+      <c r="C29" s="199"/>
+      <c r="D29" s="199"/>
+      <c r="E29" s="199"/>
+      <c r="F29" s="199"/>
+      <c r="G29" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="G8:G13"/>
-    <mergeCell ref="C27:G29"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="F21:F22"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="F15:F17"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="H15:H17"/>
     <mergeCell ref="F8:F13"/>
     <mergeCell ref="H8:H13"/>
+    <mergeCell ref="C27:G29"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="G8:G13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/project_documents/parameterDirectory.xlsx
+++ b/project_documents/parameterDirectory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabian/Documents/DPhil Work/Academic Work/EnglandCervicalScreeningProject/project_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5C8E38-CBBF-4947-8DFC-51B5B498F7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49999327-44F8-EB4B-A3A4-71A100E49CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17180" activeTab="7" xr2:uid="{9CDCC384-B02C-4946-8A51-C0AA91FF93D1}"/>
   </bookViews>
@@ -1029,9 +1029,6 @@
     <t>P(abnormal|cin), for lbc</t>
   </si>
   <si>
-    <t>These parameters are to be varied as two cases, as they are two different ways cytology have been modelled in literature</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Probability that a given screening -eligible person will take up screening </t>
     </r>
@@ -1115,6 +1112,9 @@
   <si>
     <t>Married matrix: our own analysis of NATSAL-3 data. Casual matrix: https://doi.org/10.1016/j.epidem.2018.03.004</t>
   </si>
+  <si>
+    <t>These parameters are to be varied together to form two cases, as they are two different ways cytology have been modelled in literature</t>
+  </si>
 </sst>
 </file>
 
@@ -1123,7 +1123,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1200,19 +1200,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1267,12 +1261,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="72">
     <border>
@@ -2158,7 +2146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="317">
+  <cellXfs count="318">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2587,273 +2575,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2864,68 +2585,336 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3374,11 +3363,11 @@
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="200" t="s">
+      <c r="B4" s="227" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="200"/>
-      <c r="D4" s="200"/>
+      <c r="C4" s="227"/>
+      <c r="D4" s="227"/>
     </row>
     <row r="5" spans="2:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -3456,26 +3445,26 @@
       </c>
     </row>
     <row r="13" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="201" t="s">
+      <c r="B13" s="228" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="201"/>
-      <c r="D13" s="201"/>
+      <c r="C13" s="228"/>
+      <c r="D13" s="228"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="201"/>
-      <c r="C14" s="201"/>
-      <c r="D14" s="201"/>
+      <c r="B14" s="228"/>
+      <c r="C14" s="228"/>
+      <c r="D14" s="228"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="201"/>
-      <c r="C15" s="201"/>
-      <c r="D15" s="201"/>
+      <c r="B15" s="228"/>
+      <c r="C15" s="228"/>
+      <c r="D15" s="228"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="201"/>
-      <c r="C16" s="201"/>
-      <c r="D16" s="201"/>
+      <c r="B16" s="228"/>
+      <c r="C16" s="228"/>
+      <c r="D16" s="228"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3506,13 +3495,13 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="204" t="s">
+      <c r="B3" s="231" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="204"/>
-      <c r="D3" s="204"/>
-      <c r="E3" s="204"/>
-      <c r="F3" s="204"/>
+      <c r="C3" s="231"/>
+      <c r="D3" s="231"/>
+      <c r="E3" s="231"/>
+      <c r="F3" s="231"/>
     </row>
     <row r="5" spans="2:6" ht="35" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
@@ -3532,7 +3521,7 @@
       </c>
     </row>
     <row r="6" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B6" s="206" t="s">
+      <c r="B6" s="233" t="s">
         <v>177</v>
       </c>
       <c r="C6" s="27" t="s">
@@ -3547,7 +3536,7 @@
       <c r="F6" s="14"/>
     </row>
     <row r="7" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" s="207"/>
+      <c r="B7" s="234"/>
       <c r="C7" s="28" t="s">
         <v>179</v>
       </c>
@@ -3560,7 +3549,7 @@
       <c r="F7" s="15"/>
     </row>
     <row r="8" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B8" s="207"/>
+      <c r="B8" s="234"/>
       <c r="C8" s="28" t="s">
         <v>180</v>
       </c>
@@ -3573,7 +3562,7 @@
       <c r="F8" s="15"/>
     </row>
     <row r="9" spans="2:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="B9" s="207"/>
+      <c r="B9" s="234"/>
       <c r="C9" s="28" t="s">
         <v>181</v>
       </c>
@@ -3586,7 +3575,7 @@
       <c r="F9" s="15"/>
     </row>
     <row r="10" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B10" s="208" t="s">
+      <c r="B10" s="235" t="s">
         <v>173</v>
       </c>
       <c r="C10" s="29" t="s">
@@ -3603,7 +3592,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B11" s="208"/>
+      <c r="B11" s="235"/>
       <c r="C11" s="29" t="s">
         <v>187</v>
       </c>
@@ -3618,7 +3607,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B12" s="208"/>
+      <c r="B12" s="235"/>
       <c r="C12" s="29" t="s">
         <v>188</v>
       </c>
@@ -3633,7 +3622,7 @@
       </c>
     </row>
     <row r="13" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B13" s="209" t="s">
+      <c r="B13" s="236" t="s">
         <v>174</v>
       </c>
       <c r="C13" s="30" t="s">
@@ -3650,7 +3639,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B14" s="209"/>
+      <c r="B14" s="236"/>
       <c r="C14" s="30" t="s">
         <v>113</v>
       </c>
@@ -3665,7 +3654,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B15" s="209"/>
+      <c r="B15" s="236"/>
       <c r="C15" s="30" t="s">
         <v>111</v>
       </c>
@@ -3680,7 +3669,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B16" s="210" t="s">
+      <c r="B16" s="237" t="s">
         <v>175</v>
       </c>
       <c r="C16" s="31" t="s">
@@ -3695,7 +3684,7 @@
       <c r="F16" s="18"/>
     </row>
     <row r="17" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B17" s="210"/>
+      <c r="B17" s="237"/>
       <c r="C17" s="31" t="s">
         <v>133</v>
       </c>
@@ -3710,7 +3699,7 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="135" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="210"/>
+      <c r="B18" s="237"/>
       <c r="C18" s="31" t="s">
         <v>115</v>
       </c>
@@ -3732,7 +3721,7 @@
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B19" s="210"/>
+      <c r="B19" s="237"/>
       <c r="C19" s="31" t="s">
         <v>114</v>
       </c>
@@ -3751,30 +3740,30 @@
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B22" s="211" t="s">
+      <c r="B22" s="238" t="s">
         <v>132</v>
       </c>
       <c r="C22" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="202" t="s">
+      <c r="D22" s="229" t="s">
         <v>216</v>
       </c>
-      <c r="E22" s="203"/>
+      <c r="E22" s="230"/>
     </row>
     <row r="23" spans="2:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="212"/>
+      <c r="B23" s="239"/>
       <c r="C23" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="204" t="s">
+      <c r="D23" s="231" t="s">
         <v>218</v>
       </c>
-      <c r="E23" s="205"/>
+      <c r="E23" s="232"/>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="212"/>
+      <c r="B24" s="239"/>
       <c r="C24" s="8" t="s">
         <v>114</v>
       </c>
@@ -3845,30 +3834,30 @@
   <sheetData>
     <row r="2" spans="1:10" s="66" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="188"/>
-      <c r="B2" s="213" t="s">
+      <c r="B2" s="260" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="217" t="s">
+      <c r="C2" s="264" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="225" t="s">
+      <c r="D2" s="270" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="226"/>
-      <c r="F2" s="227" t="s">
+      <c r="E2" s="271"/>
+      <c r="F2" s="272" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="227"/>
-      <c r="H2" s="227"/>
-      <c r="I2" s="226"/>
-      <c r="J2" s="215" t="s">
+      <c r="G2" s="272"/>
+      <c r="H2" s="272"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="262" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="66" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="188"/>
-      <c r="B3" s="214"/>
-      <c r="C3" s="218"/>
+      <c r="B3" s="261"/>
+      <c r="C3" s="265"/>
       <c r="D3" s="11" t="s">
         <v>9</v>
       </c>
@@ -3887,10 +3876,10 @@
       <c r="I3" s="189" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="216"/>
+      <c r="J3" s="263"/>
     </row>
     <row r="4" spans="1:10" s="86" customFormat="1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="229" t="s">
+      <c r="A4" s="255" t="s">
         <v>85</v>
       </c>
       <c r="B4" s="81" t="s">
@@ -3914,7 +3903,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" s="86" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A5" s="229"/>
+      <c r="A5" s="255"/>
       <c r="B5" s="88" t="s">
         <v>18</v>
       </c>
@@ -3936,7 +3925,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" s="86" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A6" s="229"/>
+      <c r="A6" s="255"/>
       <c r="B6" s="88" t="s">
         <v>22</v>
       </c>
@@ -3956,7 +3945,7 @@
       <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" s="86" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="229"/>
+      <c r="A7" s="255"/>
       <c r="B7" s="88" t="s">
         <v>101</v>
       </c>
@@ -3976,7 +3965,7 @@
       <c r="J7" s="89"/>
     </row>
     <row r="8" spans="1:10" s="86" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A8" s="229"/>
+      <c r="A8" s="255"/>
       <c r="B8" s="88" t="s">
         <v>23</v>
       </c>
@@ -4020,7 +4009,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="103" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A10" s="230" t="s">
+      <c r="A10" s="256" t="s">
         <v>87</v>
       </c>
       <c r="B10" s="98" t="s">
@@ -4044,37 +4033,37 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="103" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="230"/>
-      <c r="B11" s="221" t="s">
+      <c r="A11" s="256"/>
+      <c r="B11" s="258" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="219" t="s">
+      <c r="C11" s="266" t="s">
         <v>39</v>
       </c>
       <c r="D11" s="101"/>
-      <c r="E11" s="221" t="s">
-        <v>328</v>
+      <c r="E11" s="258" t="s">
+        <v>327</v>
       </c>
       <c r="F11" s="101"/>
       <c r="G11" s="102"/>
       <c r="H11" s="102"/>
       <c r="I11" s="98"/>
-      <c r="J11" s="223"/>
+      <c r="J11" s="268"/>
     </row>
     <row r="12" spans="1:10" s="103" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="230"/>
-      <c r="B12" s="222"/>
-      <c r="C12" s="220"/>
+      <c r="A12" s="256"/>
+      <c r="B12" s="259"/>
+      <c r="C12" s="267"/>
       <c r="D12" s="101"/>
-      <c r="E12" s="222"/>
+      <c r="E12" s="259"/>
       <c r="F12" s="101"/>
       <c r="G12" s="102"/>
       <c r="H12" s="102"/>
       <c r="I12" s="98"/>
-      <c r="J12" s="224"/>
+      <c r="J12" s="269"/>
     </row>
     <row r="13" spans="1:10" s="108" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A13" s="231" t="s">
+      <c r="A13" s="257" t="s">
         <v>88</v>
       </c>
       <c r="B13" s="104" t="s">
@@ -4096,7 +4085,7 @@
       <c r="J13" s="106"/>
     </row>
     <row r="14" spans="1:10" s="108" customFormat="1" ht="188" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="231"/>
+      <c r="A14" s="257"/>
       <c r="B14" s="104" t="s">
         <v>35</v>
       </c>
@@ -4118,7 +4107,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" s="108" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="231"/>
+      <c r="A15" s="257"/>
       <c r="B15" s="104" t="s">
         <v>44</v>
       </c>
@@ -4138,7 +4127,7 @@
       <c r="J15" s="106"/>
     </row>
     <row r="16" spans="1:10" s="108" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A16" s="231"/>
+      <c r="A16" s="257"/>
       <c r="B16" s="104" t="s">
         <v>47</v>
       </c>
@@ -4160,7 +4149,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" s="108" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="231"/>
+      <c r="A17" s="257"/>
       <c r="B17" s="104" t="s">
         <v>51</v>
       </c>
@@ -4180,7 +4169,7 @@
       <c r="J17" s="106"/>
     </row>
     <row r="18" spans="1:10" s="108" customFormat="1" ht="135" x14ac:dyDescent="0.2">
-      <c r="A18" s="231"/>
+      <c r="A18" s="257"/>
       <c r="B18" s="104" t="s">
         <v>55</v>
       </c>
@@ -4204,7 +4193,7 @@
       <c r="J18" s="106"/>
     </row>
     <row r="19" spans="1:10" s="108" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A19" s="231"/>
+      <c r="A19" s="257"/>
       <c r="B19" s="104" t="s">
         <v>58</v>
       </c>
@@ -4228,7 +4217,7 @@
       <c r="J19" s="106"/>
     </row>
     <row r="20" spans="1:10" s="108" customFormat="1" ht="115" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="231"/>
+      <c r="A20" s="257"/>
       <c r="B20" s="104" t="s">
         <v>61</v>
       </c>
@@ -4248,51 +4237,51 @@
       <c r="J20" s="110"/>
     </row>
     <row r="21" spans="1:10" s="43" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="231"/>
+      <c r="A21" s="257"/>
       <c r="B21" s="191" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="235" t="s">
+      <c r="C21" s="243" t="s">
         <v>98</v>
       </c>
       <c r="D21" s="110" t="s">
         <v>165</v>
       </c>
-      <c r="E21" s="232" t="s">
+      <c r="E21" s="240" t="s">
         <v>99</v>
       </c>
       <c r="F21" s="72"/>
       <c r="G21" s="73"/>
       <c r="H21" s="73"/>
-      <c r="I21" s="232" t="s">
+      <c r="I21" s="240" t="s">
         <v>167</v>
       </c>
-      <c r="J21" s="238" t="s">
+      <c r="J21" s="246" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="43" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="231"/>
+      <c r="A22" s="257"/>
       <c r="B22" s="192" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="236"/>
+      <c r="C22" s="244"/>
       <c r="D22" s="193" t="s">
         <v>166</v>
       </c>
-      <c r="E22" s="233"/>
+      <c r="E22" s="241"/>
       <c r="F22" s="71"/>
       <c r="G22" s="69"/>
       <c r="H22" s="69"/>
-      <c r="I22" s="233"/>
-      <c r="J22" s="239"/>
+      <c r="I22" s="241"/>
+      <c r="J22" s="247"/>
     </row>
     <row r="23" spans="1:10" s="43" customFormat="1" ht="180" x14ac:dyDescent="0.2">
-      <c r="A23" s="231"/>
+      <c r="A23" s="257"/>
       <c r="B23" s="104" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="237"/>
+      <c r="C23" s="245"/>
       <c r="D23" s="110" t="s">
         <v>308</v>
       </c>
@@ -4302,8 +4291,8 @@
       <c r="F23" s="74"/>
       <c r="G23" s="69"/>
       <c r="H23" s="69"/>
-      <c r="I23" s="234"/>
-      <c r="J23" s="240"/>
+      <c r="I23" s="242"/>
+      <c r="J23" s="248"/>
     </row>
     <row r="24" spans="1:10" s="43" customFormat="1" ht="255" x14ac:dyDescent="0.2">
       <c r="A24" s="190"/>
@@ -4376,7 +4365,7 @@
       <c r="B27" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="243" t="s">
+      <c r="C27" s="251" t="s">
         <v>79</v>
       </c>
       <c r="D27" s="122"/>
@@ -4402,7 +4391,7 @@
       <c r="B28" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="244"/>
+      <c r="C28" s="252"/>
       <c r="D28" s="122">
         <v>50</v>
       </c>
@@ -4420,7 +4409,7 @@
       <c r="B29" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="245"/>
+      <c r="C29" s="253"/>
       <c r="D29" s="122">
         <v>0</v>
       </c>
@@ -4508,7 +4497,7 @@
       <c r="J32" s="122"/>
     </row>
     <row r="33" spans="1:10" s="132" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="228" t="s">
+      <c r="A33" s="254" t="s">
         <v>239</v>
       </c>
       <c r="B33" s="128" t="s">
@@ -4527,12 +4516,12 @@
       <c r="G33" s="131"/>
       <c r="H33" s="131"/>
       <c r="I33" s="128"/>
-      <c r="J33" s="241" t="s">
+      <c r="J33" s="249" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="132" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A34" s="228"/>
+      <c r="A34" s="254"/>
       <c r="B34" s="128" t="s">
         <v>106</v>
       </c>
@@ -4549,21 +4538,10 @@
       <c r="G34" s="131"/>
       <c r="H34" s="131"/>
       <c r="I34" s="128"/>
-      <c r="J34" s="242"/>
+      <c r="J34" s="250"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="J21:J23"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B11:B12"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="C2:C3"/>
@@ -4572,6 +4550,17 @@
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="J21:J23"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="C27:C29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -4625,7 +4614,7 @@
       <c r="E2" s="158">
         <v>0.12</v>
       </c>
-      <c r="H2" s="246" t="s">
+      <c r="H2" s="273" t="s">
         <v>304</v>
       </c>
     </row>
@@ -4645,7 +4634,7 @@
       <c r="E3" s="162">
         <v>0.88</v>
       </c>
-      <c r="H3" s="246"/>
+      <c r="H3" s="273"/>
     </row>
     <row r="4" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="136" t="s">
@@ -4663,7 +4652,7 @@
       <c r="E4" s="162">
         <v>0</v>
       </c>
-      <c r="H4" s="246"/>
+      <c r="H4" s="273"/>
     </row>
     <row r="5" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="136" t="s">
@@ -4681,7 +4670,7 @@
       <c r="E5" s="158">
         <v>0.12</v>
       </c>
-      <c r="H5" s="246"/>
+      <c r="H5" s="273"/>
     </row>
     <row r="6" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="136" t="s">
@@ -4699,7 +4688,7 @@
       <c r="E6" s="162">
         <v>0.88</v>
       </c>
-      <c r="H6" s="246"/>
+      <c r="H6" s="273"/>
     </row>
     <row r="7" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="136" t="s">
@@ -4717,7 +4706,7 @@
       <c r="E7" s="162">
         <v>0</v>
       </c>
-      <c r="H7" s="246"/>
+      <c r="H7" s="273"/>
     </row>
     <row r="8" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="136" t="s">
@@ -4735,7 +4724,7 @@
       <c r="E8" s="158">
         <v>0.12</v>
       </c>
-      <c r="H8" s="246"/>
+      <c r="H8" s="273"/>
     </row>
     <row r="9" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="136" t="s">
@@ -4753,7 +4742,7 @@
       <c r="E9" s="162">
         <v>0.88</v>
       </c>
-      <c r="H9" s="246"/>
+      <c r="H9" s="273"/>
     </row>
     <row r="10" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="136" t="s">
@@ -4771,7 +4760,7 @@
       <c r="E10" s="162">
         <v>0</v>
       </c>
-      <c r="H10" s="246"/>
+      <c r="H10" s="273"/>
     </row>
     <row r="11" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="136" t="s">
@@ -4789,7 +4778,7 @@
       <c r="E11" s="158">
         <v>0.12</v>
       </c>
-      <c r="H11" s="246"/>
+      <c r="H11" s="273"/>
     </row>
     <row r="12" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="136" t="s">
@@ -4807,7 +4796,7 @@
       <c r="E12" s="162">
         <v>0.88</v>
       </c>
-      <c r="H12" s="246"/>
+      <c r="H12" s="273"/>
     </row>
     <row r="13" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="136" t="s">
@@ -4825,7 +4814,7 @@
       <c r="E13" s="162">
         <v>0</v>
       </c>
-      <c r="H13" s="246"/>
+      <c r="H13" s="273"/>
     </row>
     <row r="14" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="136" t="s">
@@ -4843,7 +4832,7 @@
       <c r="E14" s="158">
         <v>0.12</v>
       </c>
-      <c r="H14" s="246"/>
+      <c r="H14" s="273"/>
     </row>
     <row r="15" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="136" t="s">
@@ -4861,7 +4850,7 @@
       <c r="E15" s="162">
         <v>0.88</v>
       </c>
-      <c r="H15" s="246"/>
+      <c r="H15" s="273"/>
     </row>
     <row r="16" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="136" t="s">
@@ -4879,7 +4868,7 @@
       <c r="E16" s="162">
         <v>0</v>
       </c>
-      <c r="H16" s="246"/>
+      <c r="H16" s="273"/>
     </row>
     <row r="17" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="136" t="s">
@@ -4897,7 +4886,7 @@
       <c r="E17" s="158">
         <v>0.12</v>
       </c>
-      <c r="H17" s="246"/>
+      <c r="H17" s="273"/>
     </row>
     <row r="18" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="136" t="s">
@@ -4915,7 +4904,7 @@
       <c r="E18" s="162">
         <v>0.88</v>
       </c>
-      <c r="H18" s="246"/>
+      <c r="H18" s="273"/>
     </row>
     <row r="19" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="136" t="s">
@@ -4933,7 +4922,7 @@
       <c r="E19" s="162">
         <v>0</v>
       </c>
-      <c r="H19" s="246"/>
+      <c r="H19" s="273"/>
     </row>
     <row r="20" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="136" t="s">
@@ -4951,7 +4940,7 @@
       <c r="E20" s="158">
         <v>0.12</v>
       </c>
-      <c r="H20" s="246"/>
+      <c r="H20" s="273"/>
     </row>
     <row r="21" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="136" t="s">
@@ -4969,7 +4958,7 @@
       <c r="E21" s="162">
         <v>0.88</v>
       </c>
-      <c r="H21" s="246"/>
+      <c r="H21" s="273"/>
     </row>
     <row r="22" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="136" t="s">
@@ -4987,7 +4976,7 @@
       <c r="E22" s="162">
         <v>0</v>
       </c>
-      <c r="H22" s="246"/>
+      <c r="H22" s="273"/>
     </row>
     <row r="23" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="136" t="s">
@@ -5005,7 +4994,7 @@
       <c r="E23" s="158">
         <v>0.12</v>
       </c>
-      <c r="H23" s="246"/>
+      <c r="H23" s="273"/>
     </row>
     <row r="24" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="136" t="s">
@@ -5023,7 +5012,7 @@
       <c r="E24" s="162">
         <v>0.88</v>
       </c>
-      <c r="H24" s="246"/>
+      <c r="H24" s="273"/>
     </row>
     <row r="25" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="136" t="s">
@@ -5041,7 +5030,7 @@
       <c r="E25" s="162">
         <v>0</v>
       </c>
-      <c r="H25" s="246"/>
+      <c r="H25" s="273"/>
     </row>
     <row r="26" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="136" t="s">
@@ -5059,7 +5048,7 @@
       <c r="E26" s="158">
         <v>0.12</v>
       </c>
-      <c r="H26" s="246"/>
+      <c r="H26" s="273"/>
     </row>
     <row r="27" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="136" t="s">
@@ -5077,7 +5066,7 @@
       <c r="E27" s="162">
         <v>0.88</v>
       </c>
-      <c r="H27" s="246"/>
+      <c r="H27" s="273"/>
     </row>
     <row r="28" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="136" t="s">
@@ -5095,7 +5084,7 @@
       <c r="E28" s="162">
         <v>0</v>
       </c>
-      <c r="H28" s="246"/>
+      <c r="H28" s="273"/>
     </row>
     <row r="29" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="136" t="s">
@@ -5113,7 +5102,7 @@
       <c r="E29" s="158">
         <v>0.12</v>
       </c>
-      <c r="H29" s="246"/>
+      <c r="H29" s="273"/>
     </row>
     <row r="30" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="136" t="s">
@@ -5131,7 +5120,7 @@
       <c r="E30" s="162">
         <v>0.88</v>
       </c>
-      <c r="H30" s="246"/>
+      <c r="H30" s="273"/>
     </row>
     <row r="31" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="136" t="s">
@@ -5149,7 +5138,7 @@
       <c r="E31" s="162">
         <v>0</v>
       </c>
-      <c r="H31" s="246"/>
+      <c r="H31" s="273"/>
     </row>
     <row r="32" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="136" t="s">
@@ -5167,7 +5156,7 @@
       <c r="E32" s="158">
         <v>0.12</v>
       </c>
-      <c r="H32" s="246"/>
+      <c r="H32" s="273"/>
     </row>
     <row r="33" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="136" t="s">
@@ -5185,7 +5174,7 @@
       <c r="E33" s="162">
         <v>0.88</v>
       </c>
-      <c r="H33" s="246"/>
+      <c r="H33" s="273"/>
     </row>
     <row r="34" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="136" t="s">
@@ -5203,7 +5192,7 @@
       <c r="E34" s="162">
         <v>0</v>
       </c>
-      <c r="H34" s="246"/>
+      <c r="H34" s="273"/>
     </row>
     <row r="35" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="136" t="s">
@@ -5221,7 +5210,7 @@
       <c r="E35" s="158">
         <v>0.12</v>
       </c>
-      <c r="H35" s="246"/>
+      <c r="H35" s="273"/>
     </row>
     <row r="36" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="136" t="s">
@@ -5239,7 +5228,7 @@
       <c r="E36" s="162">
         <v>0.88</v>
       </c>
-      <c r="H36" s="246"/>
+      <c r="H36" s="273"/>
     </row>
     <row r="37" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="136" t="s">
@@ -5257,7 +5246,7 @@
       <c r="E37" s="162">
         <v>0</v>
       </c>
-      <c r="H37" s="246"/>
+      <c r="H37" s="273"/>
     </row>
     <row r="38" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="136" t="s">
@@ -5275,7 +5264,7 @@
       <c r="E38" s="162">
         <v>0.94</v>
       </c>
-      <c r="H38" s="246"/>
+      <c r="H38" s="273"/>
     </row>
     <row r="39" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="136" t="s">
@@ -5293,7 +5282,7 @@
       <c r="E39" s="162">
         <v>0.06</v>
       </c>
-      <c r="H39" s="246"/>
+      <c r="H39" s="273"/>
     </row>
     <row r="40" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="136" t="s">
@@ -5311,7 +5300,7 @@
       <c r="E40" s="162">
         <v>0</v>
       </c>
-      <c r="H40" s="246"/>
+      <c r="H40" s="273"/>
     </row>
     <row r="41" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="136" t="s">
@@ -5329,7 +5318,7 @@
       <c r="E41" s="162">
         <v>0.94</v>
       </c>
-      <c r="H41" s="246"/>
+      <c r="H41" s="273"/>
     </row>
     <row r="42" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="136" t="s">
@@ -5347,7 +5336,7 @@
       <c r="E42" s="162">
         <v>0.06</v>
       </c>
-      <c r="H42" s="246"/>
+      <c r="H42" s="273"/>
     </row>
     <row r="43" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="136" t="s">
@@ -5365,7 +5354,7 @@
       <c r="E43" s="162">
         <v>0</v>
       </c>
-      <c r="H43" s="246"/>
+      <c r="H43" s="273"/>
     </row>
     <row r="44" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="136" t="s">
@@ -5383,7 +5372,7 @@
       <c r="E44" s="162">
         <v>0.94</v>
       </c>
-      <c r="H44" s="246"/>
+      <c r="H44" s="273"/>
     </row>
     <row r="45" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="136" t="s">
@@ -5401,7 +5390,7 @@
       <c r="E45" s="162">
         <v>0.06</v>
       </c>
-      <c r="H45" s="246"/>
+      <c r="H45" s="273"/>
     </row>
     <row r="46" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="136" t="s">
@@ -5419,7 +5408,7 @@
       <c r="E46" s="162">
         <v>0</v>
       </c>
-      <c r="H46" s="246"/>
+      <c r="H46" s="273"/>
     </row>
     <row r="47" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="136" t="s">
@@ -5437,7 +5426,7 @@
       <c r="E47" s="162">
         <v>0.94</v>
       </c>
-      <c r="H47" s="246"/>
+      <c r="H47" s="273"/>
     </row>
     <row r="48" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="136" t="s">
@@ -5455,7 +5444,7 @@
       <c r="E48" s="162">
         <v>0.06</v>
       </c>
-      <c r="H48" s="246"/>
+      <c r="H48" s="273"/>
     </row>
     <row r="49" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="136" t="s">
@@ -5473,7 +5462,7 @@
       <c r="E49" s="162">
         <v>0</v>
       </c>
-      <c r="H49" s="246"/>
+      <c r="H49" s="273"/>
     </row>
     <row r="50" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="136" t="s">
@@ -5491,7 +5480,7 @@
       <c r="E50" s="162">
         <v>0.94</v>
       </c>
-      <c r="H50" s="246"/>
+      <c r="H50" s="273"/>
     </row>
     <row r="51" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="136" t="s">
@@ -5509,7 +5498,7 @@
       <c r="E51" s="162">
         <v>0.06</v>
       </c>
-      <c r="H51" s="246"/>
+      <c r="H51" s="273"/>
     </row>
     <row r="52" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="136" t="s">
@@ -5527,7 +5516,7 @@
       <c r="E52" s="162">
         <v>0</v>
       </c>
-      <c r="H52" s="246"/>
+      <c r="H52" s="273"/>
     </row>
     <row r="53" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="136" t="s">
@@ -5545,7 +5534,7 @@
       <c r="E53" s="162">
         <v>0.94</v>
       </c>
-      <c r="H53" s="246"/>
+      <c r="H53" s="273"/>
     </row>
     <row r="54" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="136" t="s">
@@ -5563,7 +5552,7 @@
       <c r="E54" s="162">
         <v>0.06</v>
       </c>
-      <c r="H54" s="246"/>
+      <c r="H54" s="273"/>
     </row>
     <row r="55" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="136" t="s">
@@ -5581,7 +5570,7 @@
       <c r="E55" s="162">
         <v>0</v>
       </c>
-      <c r="H55" s="246"/>
+      <c r="H55" s="273"/>
     </row>
     <row r="56" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="136" t="s">
@@ -5599,7 +5588,7 @@
       <c r="E56" s="162">
         <v>0.94</v>
       </c>
-      <c r="H56" s="246"/>
+      <c r="H56" s="273"/>
     </row>
     <row r="57" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="136" t="s">
@@ -5617,7 +5606,7 @@
       <c r="E57" s="162">
         <v>0.06</v>
       </c>
-      <c r="H57" s="246"/>
+      <c r="H57" s="273"/>
     </row>
     <row r="58" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="136" t="s">
@@ -5635,7 +5624,7 @@
       <c r="E58" s="162">
         <v>0</v>
       </c>
-      <c r="H58" s="246"/>
+      <c r="H58" s="273"/>
     </row>
     <row r="59" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="136" t="s">
@@ -5653,7 +5642,7 @@
       <c r="E59" s="162">
         <v>0.94</v>
       </c>
-      <c r="H59" s="246"/>
+      <c r="H59" s="273"/>
     </row>
     <row r="60" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="136" t="s">
@@ -5671,7 +5660,7 @@
       <c r="E60" s="162">
         <v>0.06</v>
       </c>
-      <c r="H60" s="246"/>
+      <c r="H60" s="273"/>
     </row>
     <row r="61" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="136" t="s">
@@ -5689,7 +5678,7 @@
       <c r="E61" s="162">
         <v>0</v>
       </c>
-      <c r="H61" s="246"/>
+      <c r="H61" s="273"/>
     </row>
     <row r="62" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="136" t="s">
@@ -5707,7 +5696,7 @@
       <c r="E62" s="162">
         <v>0.94</v>
       </c>
-      <c r="H62" s="246"/>
+      <c r="H62" s="273"/>
     </row>
     <row r="63" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="136" t="s">
@@ -5725,7 +5714,7 @@
       <c r="E63" s="162">
         <v>0.06</v>
       </c>
-      <c r="H63" s="246"/>
+      <c r="H63" s="273"/>
     </row>
     <row r="64" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="136" t="s">
@@ -5743,7 +5732,7 @@
       <c r="E64" s="162">
         <v>0</v>
       </c>
-      <c r="H64" s="246"/>
+      <c r="H64" s="273"/>
     </row>
     <row r="65" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="136" t="s">
@@ -5761,7 +5750,7 @@
       <c r="E65" s="162">
         <v>0.94</v>
       </c>
-      <c r="H65" s="246"/>
+      <c r="H65" s="273"/>
     </row>
     <row r="66" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="136" t="s">
@@ -5779,7 +5768,7 @@
       <c r="E66" s="162">
         <v>0.06</v>
       </c>
-      <c r="H66" s="246"/>
+      <c r="H66" s="273"/>
     </row>
     <row r="67" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="136" t="s">
@@ -5797,7 +5786,7 @@
       <c r="E67" s="162">
         <v>0</v>
       </c>
-      <c r="H67" s="246"/>
+      <c r="H67" s="273"/>
     </row>
     <row r="68" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="136" t="s">
@@ -5815,7 +5804,7 @@
       <c r="E68" s="162">
         <v>0.94</v>
       </c>
-      <c r="H68" s="246"/>
+      <c r="H68" s="273"/>
     </row>
     <row r="69" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="136" t="s">
@@ -5833,7 +5822,7 @@
       <c r="E69" s="162">
         <v>0.06</v>
       </c>
-      <c r="H69" s="246"/>
+      <c r="H69" s="273"/>
     </row>
     <row r="70" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="136" t="s">
@@ -5851,7 +5840,7 @@
       <c r="E70" s="162">
         <v>0</v>
       </c>
-      <c r="H70" s="246"/>
+      <c r="H70" s="273"/>
     </row>
     <row r="71" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="136" t="s">
@@ -5869,7 +5858,7 @@
       <c r="E71" s="162">
         <v>0.94</v>
       </c>
-      <c r="H71" s="246"/>
+      <c r="H71" s="273"/>
     </row>
     <row r="72" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="136" t="s">
@@ -5887,7 +5876,7 @@
       <c r="E72" s="162">
         <v>0.06</v>
       </c>
-      <c r="H72" s="246"/>
+      <c r="H72" s="273"/>
     </row>
     <row r="73" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="136" t="s">
@@ -5905,7 +5894,7 @@
       <c r="E73" s="162">
         <v>0</v>
       </c>
-      <c r="H73" s="246"/>
+      <c r="H73" s="273"/>
     </row>
     <row r="74" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="136" t="s">
@@ -5923,7 +5912,7 @@
       <c r="E74" s="162">
         <v>0.94</v>
       </c>
-      <c r="H74" s="246"/>
+      <c r="H74" s="273"/>
     </row>
     <row r="75" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="136" t="s">
@@ -5941,7 +5930,7 @@
       <c r="E75" s="162">
         <v>0.06</v>
       </c>
-      <c r="H75" s="246"/>
+      <c r="H75" s="273"/>
     </row>
     <row r="76" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="136" t="s">
@@ -5959,7 +5948,7 @@
       <c r="E76" s="162">
         <v>0</v>
       </c>
-      <c r="H76" s="246"/>
+      <c r="H76" s="273"/>
     </row>
     <row r="77" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="136" t="s">
@@ -5977,7 +5966,7 @@
       <c r="E77" s="162">
         <v>0.94</v>
       </c>
-      <c r="H77" s="246"/>
+      <c r="H77" s="273"/>
     </row>
     <row r="78" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="136" t="s">
@@ -5995,7 +5984,7 @@
       <c r="E78" s="162">
         <v>0.06</v>
       </c>
-      <c r="H78" s="246"/>
+      <c r="H78" s="273"/>
     </row>
     <row r="79" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="136" t="s">
@@ -6013,7 +6002,7 @@
       <c r="E79" s="162">
         <v>0</v>
       </c>
-      <c r="H79" s="246"/>
+      <c r="H79" s="273"/>
     </row>
     <row r="80" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="136" t="s">
@@ -6031,7 +6020,7 @@
       <c r="E80" s="162">
         <v>0.94</v>
       </c>
-      <c r="H80" s="246"/>
+      <c r="H80" s="273"/>
     </row>
     <row r="81" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="136" t="s">
@@ -6049,7 +6038,7 @@
       <c r="E81" s="162">
         <v>0.06</v>
       </c>
-      <c r="H81" s="246"/>
+      <c r="H81" s="273"/>
     </row>
     <row r="82" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="136" t="s">
@@ -6067,7 +6056,7 @@
       <c r="E82" s="162">
         <v>0</v>
       </c>
-      <c r="H82" s="246"/>
+      <c r="H82" s="273"/>
     </row>
     <row r="83" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="136" t="s">
@@ -6085,7 +6074,7 @@
       <c r="E83" s="162">
         <v>0.94</v>
       </c>
-      <c r="H83" s="246"/>
+      <c r="H83" s="273"/>
     </row>
     <row r="84" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="136" t="s">
@@ -6103,7 +6092,7 @@
       <c r="E84" s="162">
         <v>0.06</v>
       </c>
-      <c r="H84" s="246"/>
+      <c r="H84" s="273"/>
     </row>
     <row r="85" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="136" t="s">
@@ -6121,7 +6110,7 @@
       <c r="E85" s="162">
         <v>0</v>
       </c>
-      <c r="H85" s="246"/>
+      <c r="H85" s="273"/>
     </row>
     <row r="86" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="136" t="s">
@@ -6139,7 +6128,7 @@
       <c r="E86" s="162">
         <v>0.94</v>
       </c>
-      <c r="H86" s="246"/>
+      <c r="H86" s="273"/>
     </row>
     <row r="87" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="136" t="s">
@@ -6157,7 +6146,7 @@
       <c r="E87" s="162">
         <v>0.06</v>
       </c>
-      <c r="H87" s="246"/>
+      <c r="H87" s="273"/>
     </row>
     <row r="88" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="136" t="s">
@@ -6175,7 +6164,7 @@
       <c r="E88" s="162">
         <v>0</v>
       </c>
-      <c r="H88" s="246"/>
+      <c r="H88" s="273"/>
     </row>
     <row r="89" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="136" t="s">
@@ -6193,7 +6182,7 @@
       <c r="E89" s="162">
         <v>0.94</v>
       </c>
-      <c r="H89" s="246"/>
+      <c r="H89" s="273"/>
     </row>
     <row r="90" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="136" t="s">
@@ -6211,7 +6200,7 @@
       <c r="E90" s="162">
         <v>0.06</v>
       </c>
-      <c r="H90" s="246"/>
+      <c r="H90" s="273"/>
     </row>
     <row r="91" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="136" t="s">
@@ -6230,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="163"/>
-      <c r="H91" s="246"/>
+      <c r="H91" s="273"/>
     </row>
     <row r="92" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="138" t="s">
@@ -6249,7 +6238,7 @@
         <v>0.96</v>
       </c>
       <c r="F92" s="147"/>
-      <c r="H92" s="247" t="s">
+      <c r="H92" s="274" t="s">
         <v>318</v>
       </c>
     </row>
@@ -6270,7 +6259,7 @@
         <v>0</v>
       </c>
       <c r="F93" s="147"/>
-      <c r="H93" s="247"/>
+      <c r="H93" s="274"/>
     </row>
     <row r="94" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="138" t="s">
@@ -6289,7 +6278,7 @@
         <v>0.04</v>
       </c>
       <c r="F94" s="147"/>
-      <c r="H94" s="247"/>
+      <c r="H94" s="274"/>
     </row>
     <row r="95" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="138" t="s">
@@ -6308,7 +6297,7 @@
         <v>0</v>
       </c>
       <c r="F95" s="147"/>
-      <c r="H95" s="247"/>
+      <c r="H95" s="274"/>
     </row>
     <row r="96" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="138" t="s">
@@ -6327,7 +6316,7 @@
         <v>0.96</v>
       </c>
       <c r="F96" s="147"/>
-      <c r="H96" s="247"/>
+      <c r="H96" s="274"/>
     </row>
     <row r="97" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="138" t="s">
@@ -6346,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="F97" s="147"/>
-      <c r="H97" s="247"/>
+      <c r="H97" s="274"/>
     </row>
     <row r="98" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="138" t="s">
@@ -6365,7 +6354,7 @@
         <v>0.04</v>
       </c>
       <c r="F98" s="147"/>
-      <c r="H98" s="247"/>
+      <c r="H98" s="274"/>
     </row>
     <row r="99" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A99" s="138" t="s">
@@ -6384,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="147"/>
-      <c r="H99" s="247"/>
+      <c r="H99" s="274"/>
     </row>
     <row r="100" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="138" t="s">
@@ -6403,7 +6392,7 @@
         <v>0.96</v>
       </c>
       <c r="F100" s="147"/>
-      <c r="H100" s="247"/>
+      <c r="H100" s="274"/>
     </row>
     <row r="101" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="138" t="s">
@@ -6422,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="147"/>
-      <c r="H101" s="247"/>
+      <c r="H101" s="274"/>
     </row>
     <row r="102" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A102" s="138" t="s">
@@ -6441,7 +6430,7 @@
         <v>0.04</v>
       </c>
       <c r="F102" s="147"/>
-      <c r="H102" s="247"/>
+      <c r="H102" s="274"/>
     </row>
     <row r="103" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="138" t="s">
@@ -6460,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="F103" s="147"/>
-      <c r="H103" s="247"/>
+      <c r="H103" s="274"/>
     </row>
     <row r="104" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="138" t="s">
@@ -6479,7 +6468,7 @@
         <v>0.3</v>
       </c>
       <c r="F104" s="147"/>
-      <c r="H104" s="247"/>
+      <c r="H104" s="274"/>
     </row>
     <row r="105" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A105" s="138" t="s">
@@ -6498,7 +6487,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="147"/>
-      <c r="H105" s="247"/>
+      <c r="H105" s="274"/>
     </row>
     <row r="106" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="138" t="s">
@@ -6517,7 +6506,7 @@
         <v>0.7</v>
       </c>
       <c r="F106" s="147"/>
-      <c r="H106" s="247"/>
+      <c r="H106" s="274"/>
     </row>
     <row r="107" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="138" t="s">
@@ -6536,7 +6525,7 @@
         <v>0</v>
       </c>
       <c r="F107" s="147"/>
-      <c r="H107" s="247"/>
+      <c r="H107" s="274"/>
     </row>
     <row r="108" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="138" t="s">
@@ -6555,7 +6544,7 @@
         <v>0</v>
       </c>
       <c r="F108" s="147"/>
-      <c r="H108" s="247"/>
+      <c r="H108" s="274"/>
     </row>
     <row r="109" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="138" t="s">
@@ -6574,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="F109" s="147"/>
-      <c r="H109" s="247"/>
+      <c r="H109" s="274"/>
     </row>
     <row r="110" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A110" s="138" t="s">
@@ -6593,7 +6582,7 @@
         <v>1</v>
       </c>
       <c r="F110" s="147"/>
-      <c r="H110" s="247"/>
+      <c r="H110" s="274"/>
     </row>
     <row r="111" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="138" t="s">
@@ -6612,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="147"/>
-      <c r="H111" s="247"/>
+      <c r="H111" s="274"/>
     </row>
     <row r="112" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="140" t="s">
@@ -6630,7 +6619,7 @@
       <c r="E112" s="166">
         <v>0.7</v>
       </c>
-      <c r="H112" s="248" t="s">
+      <c r="H112" s="275" t="s">
         <v>306</v>
       </c>
     </row>
@@ -6650,7 +6639,7 @@
       <c r="E113" s="166">
         <v>0</v>
       </c>
-      <c r="H113" s="248"/>
+      <c r="H113" s="275"/>
     </row>
     <row r="114" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" s="140" t="s">
@@ -6668,7 +6657,7 @@
       <c r="E114" s="166">
         <v>0</v>
       </c>
-      <c r="H114" s="248"/>
+      <c r="H114" s="275"/>
     </row>
     <row r="115" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A115" s="140" t="s">
@@ -6686,7 +6675,7 @@
       <c r="E115" s="166">
         <v>0.3</v>
       </c>
-      <c r="H115" s="248"/>
+      <c r="H115" s="275"/>
     </row>
     <row r="116" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="140" t="s">
@@ -6704,7 +6693,7 @@
       <c r="E116" s="166">
         <v>0</v>
       </c>
-      <c r="H116" s="248"/>
+      <c r="H116" s="275"/>
     </row>
     <row r="117" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="140" t="s">
@@ -6722,7 +6711,7 @@
       <c r="E117" s="166">
         <v>0</v>
       </c>
-      <c r="H117" s="248"/>
+      <c r="H117" s="275"/>
     </row>
     <row r="118" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A118" s="140" t="s">
@@ -6740,7 +6729,7 @@
       <c r="E118" s="166">
         <v>0.6</v>
       </c>
-      <c r="H118" s="248"/>
+      <c r="H118" s="275"/>
     </row>
     <row r="119" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="140" t="s">
@@ -6758,7 +6747,7 @@
       <c r="E119" s="166">
         <v>0</v>
       </c>
-      <c r="H119" s="248"/>
+      <c r="H119" s="275"/>
     </row>
     <row r="120" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="140" t="s">
@@ -6776,7 +6765,7 @@
       <c r="E120" s="166">
         <v>0</v>
       </c>
-      <c r="H120" s="248"/>
+      <c r="H120" s="275"/>
     </row>
     <row r="121" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A121" s="140" t="s">
@@ -6794,7 +6783,7 @@
       <c r="E121" s="166">
         <v>0.4</v>
       </c>
-      <c r="H121" s="248"/>
+      <c r="H121" s="275"/>
     </row>
     <row r="122" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" s="140" t="s">
@@ -6812,7 +6801,7 @@
       <c r="E122" s="166">
         <v>0</v>
       </c>
-      <c r="H122" s="248"/>
+      <c r="H122" s="275"/>
     </row>
     <row r="123" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="140" t="s">
@@ -6830,7 +6819,7 @@
       <c r="E123" s="166">
         <v>0</v>
       </c>
-      <c r="H123" s="248"/>
+      <c r="H123" s="275"/>
     </row>
     <row r="124" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="140" t="s">
@@ -6848,7 +6837,7 @@
       <c r="E124" s="166">
         <v>0.42</v>
       </c>
-      <c r="H124" s="248"/>
+      <c r="H124" s="275"/>
     </row>
     <row r="125" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="140" t="s">
@@ -6866,7 +6855,7 @@
       <c r="E125" s="166">
         <v>0</v>
       </c>
-      <c r="H125" s="248"/>
+      <c r="H125" s="275"/>
     </row>
     <row r="126" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="140" t="s">
@@ -6884,7 +6873,7 @@
       <c r="E126" s="166">
         <v>0</v>
       </c>
-      <c r="H126" s="248"/>
+      <c r="H126" s="275"/>
     </row>
     <row r="127" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="140" t="s">
@@ -6902,7 +6891,7 @@
       <c r="E127" s="166">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H127" s="248"/>
+      <c r="H127" s="275"/>
     </row>
     <row r="128" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="140" t="s">
@@ -6920,7 +6909,7 @@
       <c r="E128" s="166">
         <v>0</v>
       </c>
-      <c r="H128" s="248"/>
+      <c r="H128" s="275"/>
     </row>
     <row r="129" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A129" s="140" t="s">
@@ -6938,7 +6927,7 @@
       <c r="E129" s="166">
         <v>0</v>
       </c>
-      <c r="H129" s="248"/>
+      <c r="H129" s="275"/>
     </row>
     <row r="130" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="140" t="s">
@@ -6956,7 +6945,7 @@
       <c r="E130" s="166">
         <v>0.05</v>
       </c>
-      <c r="H130" s="248"/>
+      <c r="H130" s="275"/>
     </row>
     <row r="131" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A131" s="140" t="s">
@@ -6974,7 +6963,7 @@
       <c r="E131" s="166">
         <v>0</v>
       </c>
-      <c r="H131" s="248"/>
+      <c r="H131" s="275"/>
     </row>
     <row r="132" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="140" t="s">
@@ -6992,7 +6981,7 @@
       <c r="E132" s="166">
         <v>0</v>
       </c>
-      <c r="H132" s="248"/>
+      <c r="H132" s="275"/>
     </row>
     <row r="133" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="140" t="s">
@@ -7010,7 +6999,7 @@
       <c r="E133" s="166">
         <v>0.95</v>
       </c>
-      <c r="H133" s="248"/>
+      <c r="H133" s="275"/>
     </row>
     <row r="134" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A134" s="140" t="s">
@@ -7028,7 +7017,7 @@
       <c r="E134" s="166">
         <v>0</v>
       </c>
-      <c r="H134" s="248"/>
+      <c r="H134" s="275"/>
     </row>
     <row r="135" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="140" t="s">
@@ -7046,7 +7035,7 @@
       <c r="E135" s="166">
         <v>0</v>
       </c>
-      <c r="H135" s="248"/>
+      <c r="H135" s="275"/>
     </row>
     <row r="136" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A136" s="140" t="s">
@@ -7064,7 +7053,7 @@
       <c r="E136" s="166">
         <v>0</v>
       </c>
-      <c r="H136" s="248"/>
+      <c r="H136" s="275"/>
     </row>
     <row r="137" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A137" s="140" t="s">
@@ -7082,7 +7071,7 @@
       <c r="E137" s="166">
         <v>0</v>
       </c>
-      <c r="H137" s="248"/>
+      <c r="H137" s="275"/>
     </row>
     <row r="138" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A138" s="140" t="s">
@@ -7100,7 +7089,7 @@
       <c r="E138" s="166">
         <v>0</v>
       </c>
-      <c r="H138" s="248"/>
+      <c r="H138" s="275"/>
     </row>
     <row r="139" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A139" s="140" t="s">
@@ -7118,7 +7107,7 @@
       <c r="E139" s="166">
         <v>0.05</v>
       </c>
-      <c r="H139" s="248"/>
+      <c r="H139" s="275"/>
     </row>
     <row r="140" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A140" s="140" t="s">
@@ -7136,7 +7125,7 @@
       <c r="E140" s="166">
         <v>0.95</v>
       </c>
-      <c r="H140" s="248"/>
+      <c r="H140" s="275"/>
     </row>
     <row r="141" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A141" s="140" t="s">
@@ -7154,7 +7143,7 @@
       <c r="E141" s="166">
         <v>0</v>
       </c>
-      <c r="H141" s="248"/>
+      <c r="H141" s="275"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7200,7 +7189,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D2" s="64"/>
-      <c r="E2" s="249" t="s">
+      <c r="E2" s="276" t="s">
         <v>317</v>
       </c>
     </row>
@@ -7215,7 +7204,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D3" s="64"/>
-      <c r="E3" s="249"/>
+      <c r="E3" s="276"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="136" t="s">
@@ -7228,7 +7217,7 @@
         <v>0.5</v>
       </c>
       <c r="D4" s="64"/>
-      <c r="E4" s="249"/>
+      <c r="E4" s="276"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="136" t="s">
@@ -7241,7 +7230,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="64"/>
-      <c r="E5" s="249"/>
+      <c r="E5" s="276"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="138" t="s">
@@ -7254,7 +7243,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D6" s="64"/>
-      <c r="E6" s="249"/>
+      <c r="E6" s="276"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="138" t="s">
@@ -7267,7 +7256,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D7" s="64"/>
-      <c r="E7" s="249"/>
+      <c r="E7" s="276"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="138" t="s">
@@ -7280,7 +7269,7 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="64"/>
-      <c r="E8" s="249"/>
+      <c r="E8" s="276"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="138" t="s">
@@ -7293,7 +7282,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="64"/>
-      <c r="E9" s="249"/>
+      <c r="E9" s="276"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="140" t="s">
@@ -7306,7 +7295,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D10" s="64"/>
-      <c r="E10" s="249"/>
+      <c r="E10" s="276"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="140" t="s">
@@ -7319,7 +7308,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D11" s="64"/>
-      <c r="E11" s="249"/>
+      <c r="E11" s="276"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="140" t="s">
@@ -7332,7 +7321,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D12" s="64"/>
-      <c r="E12" s="249"/>
+      <c r="E12" s="276"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="140" t="s">
@@ -7345,7 +7334,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="64"/>
-      <c r="E13" s="249"/>
+      <c r="E13" s="276"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" s="64"/>
@@ -7478,84 +7467,84 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="267" t="s">
+      <c r="B2" s="293" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="253" t="s">
+      <c r="C2" s="295" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="269"/>
-      <c r="G2" s="265" t="s">
+      <c r="D2" s="296"/>
+      <c r="E2" s="296"/>
+      <c r="F2" s="297"/>
+      <c r="G2" s="310" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="267" t="s">
+      <c r="H2" s="293" t="s">
         <v>263</v>
       </c>
-      <c r="I2" s="253" t="s">
+      <c r="I2" s="295" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="254"/>
-      <c r="K2" s="255"/>
+      <c r="J2" s="296"/>
+      <c r="K2" s="305"/>
     </row>
     <row r="3" spans="1:21" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="268"/>
-      <c r="C3" s="256"/>
-      <c r="D3" s="257"/>
-      <c r="E3" s="257"/>
-      <c r="F3" s="270"/>
-      <c r="G3" s="266"/>
-      <c r="H3" s="268"/>
-      <c r="I3" s="256"/>
-      <c r="J3" s="257"/>
-      <c r="K3" s="258"/>
+      <c r="B3" s="294"/>
+      <c r="C3" s="298"/>
+      <c r="D3" s="299"/>
+      <c r="E3" s="299"/>
+      <c r="F3" s="300"/>
+      <c r="G3" s="311"/>
+      <c r="H3" s="294"/>
+      <c r="I3" s="298"/>
+      <c r="J3" s="299"/>
+      <c r="K3" s="306"/>
     </row>
     <row r="4" spans="1:21" s="44" customFormat="1" ht="270" x14ac:dyDescent="0.2">
       <c r="A4" s="46"/>
       <c r="B4" s="174" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="271" t="s">
-        <v>322</v>
-      </c>
-      <c r="D4" s="272"/>
-      <c r="E4" s="272"/>
-      <c r="F4" s="273"/>
+      <c r="C4" s="301" t="s">
+        <v>321</v>
+      </c>
+      <c r="D4" s="302"/>
+      <c r="E4" s="302"/>
+      <c r="F4" s="303"/>
       <c r="G4" s="175" t="s">
         <v>270</v>
       </c>
       <c r="H4" s="176" t="s">
         <v>271</v>
       </c>
-      <c r="I4" s="262" t="s">
+      <c r="I4" s="307" t="s">
         <v>295</v>
       </c>
-      <c r="J4" s="263"/>
-      <c r="K4" s="264"/>
+      <c r="J4" s="308"/>
+      <c r="K4" s="309"/>
     </row>
     <row r="5" spans="1:21" s="44" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="46"/>
       <c r="B5" s="92" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="259" t="s">
-        <v>323</v>
-      </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="261"/>
+      <c r="C5" s="277" t="s">
+        <v>322</v>
+      </c>
+      <c r="D5" s="278"/>
+      <c r="E5" s="278"/>
+      <c r="F5" s="304"/>
       <c r="G5" s="177">
         <v>0.8</v>
       </c>
       <c r="H5" s="178" t="s">
         <v>307</v>
       </c>
-      <c r="I5" s="250" t="s">
+      <c r="I5" s="280" t="s">
         <v>269</v>
       </c>
-      <c r="J5" s="251"/>
-      <c r="K5" s="252"/>
+      <c r="J5" s="281"/>
+      <c r="K5" s="282"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -7565,23 +7554,23 @@
       <c r="B6" s="92" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="259" t="s">
-        <v>324</v>
-      </c>
-      <c r="D6" s="260"/>
-      <c r="E6" s="260"/>
-      <c r="F6" s="261"/>
+      <c r="C6" s="277" t="s">
+        <v>323</v>
+      </c>
+      <c r="D6" s="278"/>
+      <c r="E6" s="278"/>
+      <c r="F6" s="304"/>
       <c r="G6" s="177">
         <v>0.8</v>
       </c>
       <c r="H6" s="179" t="s">
         <v>307</v>
       </c>
-      <c r="I6" s="250" t="s">
+      <c r="I6" s="280" t="s">
         <v>268</v>
       </c>
-      <c r="J6" s="251"/>
-      <c r="K6" s="252"/>
+      <c r="J6" s="281"/>
+      <c r="K6" s="282"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -7591,21 +7580,21 @@
       <c r="B7" s="92" t="s">
         <v>297</v>
       </c>
-      <c r="C7" s="259" t="s">
+      <c r="C7" s="277" t="s">
         <v>298</v>
       </c>
-      <c r="D7" s="260"/>
-      <c r="E7" s="260"/>
-      <c r="F7" s="261"/>
+      <c r="D7" s="278"/>
+      <c r="E7" s="278"/>
+      <c r="F7" s="304"/>
       <c r="G7" s="177">
         <v>1</v>
       </c>
       <c r="H7" s="179"/>
-      <c r="I7" s="250" t="s">
+      <c r="I7" s="280" t="s">
         <v>299</v>
       </c>
-      <c r="J7" s="251"/>
-      <c r="K7" s="252"/>
+      <c r="J7" s="281"/>
+      <c r="K7" s="282"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -7615,21 +7604,21 @@
       <c r="B8" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="259" t="s">
+      <c r="C8" s="277" t="s">
         <v>265</v>
       </c>
-      <c r="D8" s="260"/>
-      <c r="E8" s="260"/>
-      <c r="F8" s="261"/>
+      <c r="D8" s="278"/>
+      <c r="E8" s="278"/>
+      <c r="F8" s="304"/>
       <c r="G8" s="177">
         <v>1</v>
       </c>
       <c r="H8" s="178" t="s">
         <v>266</v>
       </c>
-      <c r="I8" s="250"/>
-      <c r="J8" s="251"/>
-      <c r="K8" s="252"/>
+      <c r="I8" s="280"/>
+      <c r="J8" s="281"/>
+      <c r="K8" s="282"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -7639,23 +7628,23 @@
       <c r="B9" s="92" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="259" t="s">
+      <c r="C9" s="277" t="s">
         <v>158</v>
       </c>
-      <c r="D9" s="260"/>
-      <c r="E9" s="260"/>
-      <c r="F9" s="261"/>
+      <c r="D9" s="278"/>
+      <c r="E9" s="278"/>
+      <c r="F9" s="304"/>
       <c r="G9" s="177">
         <v>0.95</v>
       </c>
       <c r="H9" s="178" t="s">
         <v>307</v>
       </c>
-      <c r="I9" s="259" t="s">
+      <c r="I9" s="277" t="s">
         <v>264</v>
       </c>
-      <c r="J9" s="260"/>
-      <c r="K9" s="276"/>
+      <c r="J9" s="278"/>
+      <c r="K9" s="279"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -7665,21 +7654,21 @@
       <c r="B10" s="92" t="s">
         <v>159</v>
       </c>
-      <c r="C10" s="259" t="s">
+      <c r="C10" s="277" t="s">
         <v>162</v>
       </c>
-      <c r="D10" s="260"/>
-      <c r="E10" s="260"/>
-      <c r="F10" s="261"/>
+      <c r="D10" s="278"/>
+      <c r="E10" s="278"/>
+      <c r="F10" s="304"/>
       <c r="G10" s="180">
         <v>0.9</v>
       </c>
       <c r="H10" s="178"/>
-      <c r="I10" s="250" t="s">
+      <c r="I10" s="280" t="s">
         <v>267</v>
       </c>
-      <c r="J10" s="251"/>
-      <c r="K10" s="252"/>
+      <c r="J10" s="281"/>
+      <c r="K10" s="282"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
@@ -7689,21 +7678,21 @@
       <c r="B11" s="92" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="259" t="s">
+      <c r="C11" s="277" t="s">
         <v>161</v>
       </c>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="261"/>
+      <c r="D11" s="278"/>
+      <c r="E11" s="278"/>
+      <c r="F11" s="304"/>
       <c r="G11" s="180">
         <v>0.9</v>
       </c>
       <c r="H11" s="179"/>
-      <c r="I11" s="250" t="s">
+      <c r="I11" s="280" t="s">
         <v>267</v>
       </c>
-      <c r="J11" s="251"/>
-      <c r="K11" s="252"/>
+      <c r="J11" s="281"/>
+      <c r="K11" s="282"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -7734,28 +7723,28 @@
       <c r="U13" s="51"/>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="281" t="s">
+      <c r="B14" s="287" t="s">
         <v>258</v>
       </c>
-      <c r="C14" s="282"/>
-      <c r="D14" s="282"/>
-      <c r="E14" s="282"/>
-      <c r="F14" s="282"/>
-      <c r="G14" s="282"/>
-      <c r="H14" s="282"/>
-      <c r="I14" s="282"/>
-      <c r="J14" s="282"/>
-      <c r="K14" s="282"/>
-      <c r="L14" s="282"/>
-      <c r="M14" s="282"/>
-      <c r="N14" s="282"/>
-      <c r="O14" s="282"/>
-      <c r="P14" s="282"/>
-      <c r="Q14" s="282"/>
-      <c r="R14" s="282"/>
-      <c r="S14" s="282"/>
-      <c r="T14" s="282"/>
-      <c r="U14" s="283"/>
+      <c r="C14" s="288"/>
+      <c r="D14" s="288"/>
+      <c r="E14" s="288"/>
+      <c r="F14" s="288"/>
+      <c r="G14" s="288"/>
+      <c r="H14" s="288"/>
+      <c r="I14" s="288"/>
+      <c r="J14" s="288"/>
+      <c r="K14" s="288"/>
+      <c r="L14" s="288"/>
+      <c r="M14" s="288"/>
+      <c r="N14" s="288"/>
+      <c r="O14" s="288"/>
+      <c r="P14" s="288"/>
+      <c r="Q14" s="288"/>
+      <c r="R14" s="288"/>
+      <c r="S14" s="288"/>
+      <c r="T14" s="288"/>
+      <c r="U14" s="289"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B15" s="52"/>
@@ -7780,34 +7769,34 @@
       <c r="U15" s="55"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B16" s="279" t="s">
+      <c r="B16" s="285" t="s">
         <v>254</v>
       </c>
-      <c r="C16" s="280"/>
-      <c r="D16" s="280"/>
-      <c r="E16" s="280"/>
-      <c r="F16" s="280"/>
-      <c r="G16" s="280"/>
-      <c r="H16" s="280"/>
-      <c r="I16" s="280"/>
-      <c r="J16" s="280"/>
-      <c r="K16" s="280"/>
-      <c r="L16" s="280"/>
-      <c r="M16" s="280"/>
-      <c r="N16" s="280"/>
-      <c r="O16" s="280"/>
-      <c r="P16" s="280"/>
-      <c r="Q16" s="280"/>
-      <c r="R16" s="280"/>
-      <c r="S16" s="280"/>
-      <c r="T16" s="280"/>
-      <c r="U16" s="284"/>
+      <c r="C16" s="286"/>
+      <c r="D16" s="286"/>
+      <c r="E16" s="286"/>
+      <c r="F16" s="286"/>
+      <c r="G16" s="286"/>
+      <c r="H16" s="286"/>
+      <c r="I16" s="286"/>
+      <c r="J16" s="286"/>
+      <c r="K16" s="286"/>
+      <c r="L16" s="286"/>
+      <c r="M16" s="286"/>
+      <c r="N16" s="286"/>
+      <c r="O16" s="286"/>
+      <c r="P16" s="286"/>
+      <c r="Q16" s="286"/>
+      <c r="R16" s="286"/>
+      <c r="S16" s="286"/>
+      <c r="T16" s="286"/>
+      <c r="U16" s="292"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B17" s="274" t="s">
+      <c r="B17" s="290" t="s">
         <v>250</v>
       </c>
-      <c r="C17" s="275"/>
+      <c r="C17" s="291"/>
       <c r="D17" s="181">
         <v>2008</v>
       </c>
@@ -7864,10 +7853,10 @@
       </c>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18" s="274" t="s">
+      <c r="B18" s="290" t="s">
         <v>251</v>
       </c>
-      <c r="C18" s="275"/>
+      <c r="C18" s="291"/>
       <c r="D18" s="59">
         <v>0.86</v>
       </c>
@@ -7924,10 +7913,10 @@
       </c>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B19" s="274" t="s">
+      <c r="B19" s="290" t="s">
         <v>252</v>
       </c>
-      <c r="C19" s="275"/>
+      <c r="C19" s="291"/>
       <c r="D19" s="59">
         <f>78/86</f>
         <v>0.90697674418604646</v>
@@ -7999,10 +7988,10 @@
       </c>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B20" s="274" t="s">
+      <c r="B20" s="290" t="s">
         <v>253</v>
       </c>
-      <c r="C20" s="275"/>
+      <c r="C20" s="291"/>
       <c r="D20" s="59">
         <v>1</v>
       </c>
@@ -8081,17 +8070,17 @@
       <c r="U21" s="55"/>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B22" s="279" t="s">
+      <c r="B22" s="285" t="s">
         <v>257</v>
       </c>
-      <c r="C22" s="280"/>
-      <c r="D22" s="280"/>
-      <c r="E22" s="280"/>
-      <c r="F22" s="280"/>
-      <c r="G22" s="280"/>
-      <c r="H22" s="280"/>
-      <c r="I22" s="280"/>
-      <c r="J22" s="280"/>
+      <c r="C22" s="286"/>
+      <c r="D22" s="286"/>
+      <c r="E22" s="286"/>
+      <c r="F22" s="286"/>
+      <c r="G22" s="286"/>
+      <c r="H22" s="286"/>
+      <c r="I22" s="286"/>
+      <c r="J22" s="286"/>
       <c r="K22" s="184"/>
       <c r="L22" s="184"/>
       <c r="M22" s="184"/>
@@ -8105,10 +8094,10 @@
       <c r="U22" s="185"/>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B23" s="274" t="s">
+      <c r="B23" s="290" t="s">
         <v>250</v>
       </c>
-      <c r="C23" s="275"/>
+      <c r="C23" s="291"/>
       <c r="D23" s="181">
         <v>2019</v>
       </c>
@@ -8143,10 +8132,10 @@
       <c r="U23" s="55"/>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B24" s="274" t="s">
+      <c r="B24" s="290" t="s">
         <v>251</v>
       </c>
-      <c r="C24" s="275"/>
+      <c r="C24" s="291"/>
       <c r="D24" s="59">
         <f>E24</f>
         <v>0.53</v>
@@ -8184,10 +8173,10 @@
       <c r="U24" s="55"/>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B25" s="274" t="s">
+      <c r="B25" s="290" t="s">
         <v>252</v>
       </c>
-      <c r="C25" s="275"/>
+      <c r="C25" s="291"/>
       <c r="D25" s="59">
         <f>E25</f>
         <v>0.35830985915492958</v>
@@ -8225,10 +8214,10 @@
       <c r="U25" s="55"/>
     </row>
     <row r="26" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="277" t="s">
+      <c r="B26" s="283" t="s">
         <v>253</v>
       </c>
-      <c r="C26" s="278"/>
+      <c r="C26" s="284"/>
       <c r="D26" s="186">
         <v>0</v>
       </c>
@@ -8293,6 +8282,26 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="I10:K10"/>
     <mergeCell ref="B26:C26"/>
@@ -8305,26 +8314,6 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B16:U16"/>
     <mergeCell ref="I11:K11"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8370,348 +8359,348 @@
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="196" t="s">
+      <c r="B3" s="211" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="197"/>
-      <c r="D3" s="197"/>
-      <c r="E3" s="197"/>
-      <c r="F3" s="198"/>
+      <c r="C3" s="212"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="213"/>
       <c r="G3" s="75"/>
       <c r="H3" s="76"/>
     </row>
-    <row r="4" spans="2:8" s="286" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="285" t="s">
+    <row r="4" spans="2:8" s="197" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="196" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="286" t="s">
+      <c r="C4" s="197" t="s">
         <v>248</v>
       </c>
-      <c r="D4" s="286">
+      <c r="D4" s="197">
         <v>0.8</v>
       </c>
-      <c r="E4" s="287">
+      <c r="E4" s="198">
         <v>0.65</v>
       </c>
-      <c r="F4" s="288"/>
-      <c r="G4" s="287">
+      <c r="F4" s="199"/>
+      <c r="G4" s="198">
         <v>2</v>
       </c>
-      <c r="H4" s="289">
+      <c r="H4" s="200">
         <f>G4</f>
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="196" t="s">
+      <c r="B5" s="211" t="s">
         <v>260</v>
       </c>
-      <c r="C5" s="197"/>
-      <c r="D5" s="197"/>
-      <c r="E5" s="197"/>
-      <c r="F5" s="198"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="212"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="213"/>
       <c r="G5" s="65"/>
       <c r="H5" s="194"/>
     </row>
-    <row r="6" spans="2:8" s="290" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="285" t="s">
+    <row r="6" spans="2:8" s="317" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="312" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="286" t="s">
+      <c r="C6" s="313" t="s">
         <v>261</v>
       </c>
-      <c r="D6" s="286">
+      <c r="D6" s="313">
         <v>0.8</v>
       </c>
-      <c r="E6" s="287" t="s">
+      <c r="E6" s="314" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="288" t="s">
+      <c r="F6" s="315" t="s">
         <v>272</v>
       </c>
-      <c r="G6" s="287">
+      <c r="G6" s="314">
         <v>3</v>
       </c>
-      <c r="H6" s="289">
+      <c r="H6" s="316">
         <f>H4*G6</f>
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="196" t="s">
+      <c r="B7" s="211" t="s">
         <v>273</v>
       </c>
-      <c r="C7" s="197"/>
-      <c r="D7" s="197"/>
-      <c r="E7" s="197"/>
-      <c r="F7" s="198"/>
+      <c r="C7" s="212"/>
+      <c r="D7" s="212"/>
+      <c r="E7" s="212"/>
+      <c r="F7" s="213"/>
       <c r="G7" s="65"/>
       <c r="H7" s="194"/>
     </row>
-    <row r="8" spans="2:8" s="297" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="291" t="s">
+    <row r="8" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="204" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="292" t="s">
+      <c r="C8" s="205" t="s">
         <v>290</v>
       </c>
-      <c r="D8" s="293">
+      <c r="D8" s="198">
         <v>0.68</v>
       </c>
-      <c r="E8" s="293" t="s">
+      <c r="E8" s="198" t="s">
         <v>292</v>
       </c>
-      <c r="F8" s="294" t="s">
+      <c r="F8" s="217" t="s">
         <v>294</v>
       </c>
-      <c r="G8" s="295">
+      <c r="G8" s="226">
         <v>3</v>
       </c>
-      <c r="H8" s="296">
+      <c r="H8" s="218">
         <f>H6*G8</f>
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="2:8" s="297" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="291" t="s">
+    <row r="9" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="204" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="292" t="s">
+      <c r="C9" s="205" t="s">
         <v>291</v>
       </c>
-      <c r="D9" s="293">
+      <c r="D9" s="198">
         <v>0.76</v>
       </c>
-      <c r="E9" s="293" t="s">
+      <c r="E9" s="198" t="s">
         <v>293</v>
       </c>
-      <c r="F9" s="294"/>
-      <c r="G9" s="295"/>
-      <c r="H9" s="296"/>
-    </row>
-    <row r="10" spans="2:8" s="297" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="298" t="s">
+      <c r="F9" s="217"/>
+      <c r="G9" s="226"/>
+      <c r="H9" s="218"/>
+    </row>
+    <row r="10" spans="2:8" s="201" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="196" t="s">
         <v>164</v>
       </c>
-      <c r="C10" s="292" t="s">
+      <c r="C10" s="205" t="s">
         <v>154</v>
       </c>
-      <c r="D10" s="167">
+      <c r="D10" s="197">
         <v>0.8</v>
       </c>
-      <c r="E10" s="293" t="s">
+      <c r="E10" s="198" t="s">
         <v>274</v>
       </c>
-      <c r="F10" s="294"/>
-      <c r="G10" s="295"/>
-      <c r="H10" s="296"/>
-    </row>
-    <row r="11" spans="2:8" s="297" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="298" t="s">
+      <c r="F10" s="217"/>
+      <c r="G10" s="226"/>
+      <c r="H10" s="218"/>
+    </row>
+    <row r="11" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="196" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="167" t="s">
+      <c r="C11" s="197" t="s">
         <v>155</v>
       </c>
-      <c r="D11" s="167">
+      <c r="D11" s="197">
         <v>0.8</v>
       </c>
-      <c r="E11" s="293" t="s">
+      <c r="E11" s="198" t="s">
         <v>274</v>
       </c>
-      <c r="F11" s="294"/>
-      <c r="G11" s="295"/>
-      <c r="H11" s="296"/>
-    </row>
-    <row r="12" spans="2:8" s="297" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="298" t="s">
+      <c r="F11" s="217"/>
+      <c r="G11" s="226"/>
+      <c r="H11" s="218"/>
+    </row>
+    <row r="12" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="196" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="167" t="s">
+      <c r="C12" s="197" t="s">
         <v>159</v>
       </c>
-      <c r="D12" s="167">
+      <c r="D12" s="197">
         <v>0.9</v>
       </c>
-      <c r="E12" s="293" t="s">
+      <c r="E12" s="198" t="s">
         <v>280</v>
       </c>
-      <c r="F12" s="294"/>
-      <c r="G12" s="295"/>
-      <c r="H12" s="296"/>
-    </row>
-    <row r="13" spans="2:8" s="297" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="298" t="s">
+      <c r="F12" s="217"/>
+      <c r="G12" s="226"/>
+      <c r="H12" s="218"/>
+    </row>
+    <row r="13" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="196" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="167" t="s">
+      <c r="C13" s="197" t="s">
         <v>160</v>
       </c>
-      <c r="D13" s="167">
+      <c r="D13" s="197">
         <v>0.9</v>
       </c>
-      <c r="E13" s="293" t="s">
+      <c r="E13" s="198" t="s">
         <v>275</v>
       </c>
-      <c r="F13" s="294"/>
-      <c r="G13" s="295"/>
-      <c r="H13" s="296"/>
+      <c r="F13" s="217"/>
+      <c r="G13" s="226"/>
+      <c r="H13" s="218"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="196" t="s">
+      <c r="B14" s="211" t="s">
         <v>305</v>
       </c>
-      <c r="C14" s="197"/>
-      <c r="D14" s="197"/>
-      <c r="E14" s="197"/>
-      <c r="F14" s="198"/>
+      <c r="C14" s="212"/>
+      <c r="D14" s="212"/>
+      <c r="E14" s="212"/>
+      <c r="F14" s="213"/>
       <c r="G14" s="65"/>
       <c r="H14" s="194"/>
     </row>
-    <row r="15" spans="2:8" s="304" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="299" t="s">
+    <row r="15" spans="2:8" s="202" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="203" t="s">
         <v>149</v>
       </c>
-      <c r="C15" s="300" t="s">
+      <c r="C15" s="167" t="s">
         <v>276</v>
       </c>
-      <c r="D15" s="300">
-        <v>0</v>
-      </c>
-      <c r="E15" s="300">
+      <c r="D15" s="167">
+        <v>0</v>
+      </c>
+      <c r="E15" s="167">
         <v>0.1</v>
       </c>
-      <c r="F15" s="301" t="s">
+      <c r="F15" s="214" t="s">
         <v>279</v>
       </c>
-      <c r="G15" s="302">
+      <c r="G15" s="215">
         <v>2</v>
       </c>
-      <c r="H15" s="303">
+      <c r="H15" s="216">
         <f>H8*G15</f>
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="2:8" s="304" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="299" t="s">
+    <row r="16" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="203" t="s">
         <v>149</v>
       </c>
-      <c r="C16" s="300" t="s">
+      <c r="C16" s="167" t="s">
         <v>277</v>
       </c>
-      <c r="D16" s="300">
-        <v>0</v>
-      </c>
-      <c r="E16" s="300">
+      <c r="D16" s="167">
+        <v>0</v>
+      </c>
+      <c r="E16" s="167">
         <v>0.1</v>
       </c>
-      <c r="F16" s="301"/>
-      <c r="G16" s="302"/>
-      <c r="H16" s="303"/>
-    </row>
-    <row r="17" spans="2:8" s="304" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="299" t="s">
+      <c r="F16" s="214"/>
+      <c r="G16" s="215"/>
+      <c r="H16" s="216"/>
+    </row>
+    <row r="17" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="203" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="300" t="s">
+      <c r="C17" s="167" t="s">
         <v>278</v>
       </c>
-      <c r="D17" s="300">
-        <v>0</v>
-      </c>
-      <c r="E17" s="300">
+      <c r="D17" s="167">
+        <v>0</v>
+      </c>
+      <c r="E17" s="167">
         <v>0.1</v>
       </c>
-      <c r="F17" s="301"/>
-      <c r="G17" s="302"/>
-      <c r="H17" s="303"/>
+      <c r="F17" s="214"/>
+      <c r="G17" s="215"/>
+      <c r="H17" s="216"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" s="196" t="s">
-        <v>325</v>
-      </c>
-      <c r="C18" s="197"/>
-      <c r="D18" s="197"/>
-      <c r="E18" s="197"/>
-      <c r="F18" s="198"/>
+      <c r="B18" s="211" t="s">
+        <v>324</v>
+      </c>
+      <c r="C18" s="212"/>
+      <c r="D18" s="212"/>
+      <c r="E18" s="212"/>
+      <c r="F18" s="213"/>
       <c r="G18" s="195"/>
       <c r="H18" s="194"/>
     </row>
-    <row r="19" spans="2:8" s="297" customFormat="1" ht="49" x14ac:dyDescent="0.2">
-      <c r="B19" s="298" t="s">
+    <row r="19" spans="2:8" s="201" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+      <c r="B19" s="196" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="167" t="s">
+      <c r="C19" s="197" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="305" t="s">
+      <c r="D19" s="206" t="s">
         <v>308</v>
       </c>
-      <c r="E19" s="305" t="s">
+      <c r="E19" s="206" t="s">
         <v>166</v>
       </c>
-      <c r="F19" s="306" t="s">
-        <v>326</v>
-      </c>
-      <c r="G19" s="307">
+      <c r="F19" s="207" t="s">
+        <v>325</v>
+      </c>
+      <c r="G19" s="208">
         <v>2</v>
       </c>
-      <c r="H19" s="308">
+      <c r="H19" s="200">
         <f>H15*G19</f>
         <v>72</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B20" s="196" t="s">
+      <c r="B20" s="211" t="s">
         <v>319</v>
       </c>
-      <c r="C20" s="197"/>
-      <c r="D20" s="197"/>
-      <c r="E20" s="197"/>
-      <c r="F20" s="198"/>
+      <c r="C20" s="212"/>
+      <c r="D20" s="212"/>
+      <c r="E20" s="212"/>
+      <c r="F20" s="213"/>
       <c r="G20" s="135"/>
       <c r="H20" s="143"/>
     </row>
-    <row r="21" spans="2:8" s="304" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="299" t="s">
+    <row r="21" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="203" t="s">
         <v>140</v>
       </c>
-      <c r="C21" s="300" t="s">
-        <v>327</v>
-      </c>
-      <c r="D21" s="300">
+      <c r="C21" s="167" t="s">
+        <v>326</v>
+      </c>
+      <c r="D21" s="167">
         <v>0.96</v>
       </c>
-      <c r="E21" s="300">
+      <c r="E21" s="167">
         <v>0.9</v>
       </c>
-      <c r="F21" s="309" t="s">
-        <v>321</v>
-      </c>
-      <c r="G21" s="310">
+      <c r="F21" s="224" t="s">
+        <v>328</v>
+      </c>
+      <c r="G21" s="220">
         <v>2</v>
       </c>
-      <c r="H21" s="311">
+      <c r="H21" s="222">
         <f>H19*G21</f>
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="2:8" s="304" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="312" t="s">
+    <row r="22" spans="2:8" s="202" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="209" t="s">
         <v>140</v>
       </c>
-      <c r="C22" s="313" t="s">
+      <c r="C22" s="210" t="s">
         <v>320</v>
       </c>
-      <c r="D22" s="313">
+      <c r="D22" s="210">
         <v>0.7</v>
       </c>
-      <c r="E22" s="313">
+      <c r="E22" s="210">
         <v>0.85</v>
       </c>
-      <c r="F22" s="314"/>
-      <c r="G22" s="315"/>
-      <c r="H22" s="316"/>
+      <c r="F22" s="225"/>
+      <c r="G22" s="221"/>
+      <c r="H22" s="223"/>
     </row>
     <row r="23" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B23" s="8"/>
@@ -8751,46 +8740,46 @@
       <c r="H25" s="8"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C27" s="199" t="s">
+      <c r="C27" s="219" t="s">
         <v>296</v>
       </c>
-      <c r="D27" s="199"/>
-      <c r="E27" s="199"/>
-      <c r="F27" s="199"/>
-      <c r="G27" s="199"/>
+      <c r="D27" s="219"/>
+      <c r="E27" s="219"/>
+      <c r="F27" s="219"/>
+      <c r="G27" s="219"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C28" s="199"/>
-      <c r="D28" s="199"/>
-      <c r="E28" s="199"/>
-      <c r="F28" s="199"/>
-      <c r="G28" s="199"/>
+      <c r="C28" s="219"/>
+      <c r="D28" s="219"/>
+      <c r="E28" s="219"/>
+      <c r="F28" s="219"/>
+      <c r="G28" s="219"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C29" s="199"/>
-      <c r="D29" s="199"/>
-      <c r="E29" s="199"/>
-      <c r="F29" s="199"/>
-      <c r="G29" s="199"/>
+      <c r="C29" s="219"/>
+      <c r="D29" s="219"/>
+      <c r="E29" s="219"/>
+      <c r="F29" s="219"/>
+      <c r="G29" s="219"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="G8:G13"/>
+    <mergeCell ref="C27:G29"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="F21:F22"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="F15:F17"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="H15:H17"/>
     <mergeCell ref="F8:F13"/>
     <mergeCell ref="H8:H13"/>
-    <mergeCell ref="C27:G29"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="G8:G13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/project_documents/parameterDirectory.xlsx
+++ b/project_documents/parameterDirectory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabian/Documents/DPhil Work/Academic Work/EnglandCervicalScreeningProject/project_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49999327-44F8-EB4B-A3A4-71A100E49CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C33E43B-BB4E-E745-9304-EAD4D6D39805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17180" activeTab="7" xr2:uid="{9CDCC384-B02C-4946-8A51-C0AA91FF93D1}"/>
   </bookViews>
@@ -2146,7 +2146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="318">
+  <cellXfs count="316">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2587,12 +2587,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2600,8 +2594,11 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2611,45 +2608,27 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2689,6 +2668,63 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2731,63 +2767,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2801,23 +2780,86 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2839,82 +2881,38 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3363,11 +3361,11 @@
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="227" t="s">
+      <c r="B4" s="220" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="227"/>
-      <c r="D4" s="227"/>
+      <c r="C4" s="220"/>
+      <c r="D4" s="220"/>
     </row>
     <row r="5" spans="2:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -3445,26 +3443,26 @@
       </c>
     </row>
     <row r="13" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="228" t="s">
+      <c r="B13" s="221" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="228"/>
-      <c r="D13" s="228"/>
+      <c r="C13" s="221"/>
+      <c r="D13" s="221"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="228"/>
-      <c r="C14" s="228"/>
-      <c r="D14" s="228"/>
+      <c r="B14" s="221"/>
+      <c r="C14" s="221"/>
+      <c r="D14" s="221"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="228"/>
-      <c r="C15" s="228"/>
-      <c r="D15" s="228"/>
+      <c r="B15" s="221"/>
+      <c r="C15" s="221"/>
+      <c r="D15" s="221"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="228"/>
-      <c r="C16" s="228"/>
-      <c r="D16" s="228"/>
+      <c r="B16" s="221"/>
+      <c r="C16" s="221"/>
+      <c r="D16" s="221"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3495,13 +3493,13 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="231" t="s">
+      <c r="B3" s="224" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="231"/>
-      <c r="D3" s="231"/>
-      <c r="E3" s="231"/>
-      <c r="F3" s="231"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="224"/>
+      <c r="E3" s="224"/>
+      <c r="F3" s="224"/>
     </row>
     <row r="5" spans="2:6" ht="35" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
@@ -3521,7 +3519,7 @@
       </c>
     </row>
     <row r="6" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B6" s="233" t="s">
+      <c r="B6" s="226" t="s">
         <v>177</v>
       </c>
       <c r="C6" s="27" t="s">
@@ -3536,7 +3534,7 @@
       <c r="F6" s="14"/>
     </row>
     <row r="7" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" s="234"/>
+      <c r="B7" s="227"/>
       <c r="C7" s="28" t="s">
         <v>179</v>
       </c>
@@ -3549,7 +3547,7 @@
       <c r="F7" s="15"/>
     </row>
     <row r="8" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B8" s="234"/>
+      <c r="B8" s="227"/>
       <c r="C8" s="28" t="s">
         <v>180</v>
       </c>
@@ -3562,7 +3560,7 @@
       <c r="F8" s="15"/>
     </row>
     <row r="9" spans="2:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="B9" s="234"/>
+      <c r="B9" s="227"/>
       <c r="C9" s="28" t="s">
         <v>181</v>
       </c>
@@ -3575,7 +3573,7 @@
       <c r="F9" s="15"/>
     </row>
     <row r="10" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B10" s="235" t="s">
+      <c r="B10" s="228" t="s">
         <v>173</v>
       </c>
       <c r="C10" s="29" t="s">
@@ -3592,7 +3590,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B11" s="235"/>
+      <c r="B11" s="228"/>
       <c r="C11" s="29" t="s">
         <v>187</v>
       </c>
@@ -3607,7 +3605,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B12" s="235"/>
+      <c r="B12" s="228"/>
       <c r="C12" s="29" t="s">
         <v>188</v>
       </c>
@@ -3622,7 +3620,7 @@
       </c>
     </row>
     <row r="13" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B13" s="236" t="s">
+      <c r="B13" s="229" t="s">
         <v>174</v>
       </c>
       <c r="C13" s="30" t="s">
@@ -3639,7 +3637,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B14" s="236"/>
+      <c r="B14" s="229"/>
       <c r="C14" s="30" t="s">
         <v>113</v>
       </c>
@@ -3654,7 +3652,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B15" s="236"/>
+      <c r="B15" s="229"/>
       <c r="C15" s="30" t="s">
         <v>111</v>
       </c>
@@ -3669,7 +3667,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B16" s="237" t="s">
+      <c r="B16" s="230" t="s">
         <v>175</v>
       </c>
       <c r="C16" s="31" t="s">
@@ -3684,7 +3682,7 @@
       <c r="F16" s="18"/>
     </row>
     <row r="17" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B17" s="237"/>
+      <c r="B17" s="230"/>
       <c r="C17" s="31" t="s">
         <v>133</v>
       </c>
@@ -3699,7 +3697,7 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="135" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="237"/>
+      <c r="B18" s="230"/>
       <c r="C18" s="31" t="s">
         <v>115</v>
       </c>
@@ -3721,7 +3719,7 @@
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B19" s="237"/>
+      <c r="B19" s="230"/>
       <c r="C19" s="31" t="s">
         <v>114</v>
       </c>
@@ -3740,30 +3738,30 @@
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B22" s="238" t="s">
+      <c r="B22" s="231" t="s">
         <v>132</v>
       </c>
       <c r="C22" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="229" t="s">
+      <c r="D22" s="222" t="s">
         <v>216</v>
       </c>
-      <c r="E22" s="230"/>
+      <c r="E22" s="223"/>
     </row>
     <row r="23" spans="2:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="239"/>
+      <c r="B23" s="232"/>
       <c r="C23" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="231" t="s">
+      <c r="D23" s="224" t="s">
         <v>218</v>
       </c>
-      <c r="E23" s="232"/>
+      <c r="E23" s="225"/>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="239"/>
+      <c r="B24" s="232"/>
       <c r="C24" s="8" t="s">
         <v>114</v>
       </c>
@@ -3834,30 +3832,30 @@
   <sheetData>
     <row r="2" spans="1:10" s="66" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="188"/>
-      <c r="B2" s="260" t="s">
+      <c r="B2" s="233" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="264" t="s">
+      <c r="C2" s="237" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="245" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="271"/>
-      <c r="F2" s="272" t="s">
+      <c r="E2" s="246"/>
+      <c r="F2" s="247" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="272"/>
-      <c r="H2" s="272"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="262" t="s">
+      <c r="G2" s="247"/>
+      <c r="H2" s="247"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="235" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="66" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="188"/>
-      <c r="B3" s="261"/>
-      <c r="C3" s="265"/>
+      <c r="B3" s="234"/>
+      <c r="C3" s="238"/>
       <c r="D3" s="11" t="s">
         <v>9</v>
       </c>
@@ -3876,10 +3874,10 @@
       <c r="I3" s="189" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="263"/>
+      <c r="J3" s="236"/>
     </row>
     <row r="4" spans="1:10" s="86" customFormat="1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="255" t="s">
+      <c r="A4" s="249" t="s">
         <v>85</v>
       </c>
       <c r="B4" s="81" t="s">
@@ -3903,7 +3901,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" s="86" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A5" s="255"/>
+      <c r="A5" s="249"/>
       <c r="B5" s="88" t="s">
         <v>18</v>
       </c>
@@ -3925,7 +3923,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" s="86" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A6" s="255"/>
+      <c r="A6" s="249"/>
       <c r="B6" s="88" t="s">
         <v>22</v>
       </c>
@@ -3945,7 +3943,7 @@
       <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" s="86" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="255"/>
+      <c r="A7" s="249"/>
       <c r="B7" s="88" t="s">
         <v>101</v>
       </c>
@@ -3965,7 +3963,7 @@
       <c r="J7" s="89"/>
     </row>
     <row r="8" spans="1:10" s="86" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A8" s="255"/>
+      <c r="A8" s="249"/>
       <c r="B8" s="88" t="s">
         <v>23</v>
       </c>
@@ -4009,7 +4007,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="103" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A10" s="256" t="s">
+      <c r="A10" s="250" t="s">
         <v>87</v>
       </c>
       <c r="B10" s="98" t="s">
@@ -4033,37 +4031,37 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="103" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="256"/>
-      <c r="B11" s="258" t="s">
+      <c r="A11" s="250"/>
+      <c r="B11" s="241" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="266" t="s">
+      <c r="C11" s="239" t="s">
         <v>39</v>
       </c>
       <c r="D11" s="101"/>
-      <c r="E11" s="258" t="s">
+      <c r="E11" s="241" t="s">
         <v>327</v>
       </c>
       <c r="F11" s="101"/>
       <c r="G11" s="102"/>
       <c r="H11" s="102"/>
       <c r="I11" s="98"/>
-      <c r="J11" s="268"/>
+      <c r="J11" s="243"/>
     </row>
     <row r="12" spans="1:10" s="103" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="256"/>
-      <c r="B12" s="259"/>
-      <c r="C12" s="267"/>
+      <c r="A12" s="250"/>
+      <c r="B12" s="242"/>
+      <c r="C12" s="240"/>
       <c r="D12" s="101"/>
-      <c r="E12" s="259"/>
+      <c r="E12" s="242"/>
       <c r="F12" s="101"/>
       <c r="G12" s="102"/>
       <c r="H12" s="102"/>
       <c r="I12" s="98"/>
-      <c r="J12" s="269"/>
+      <c r="J12" s="244"/>
     </row>
     <row r="13" spans="1:10" s="108" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A13" s="257" t="s">
+      <c r="A13" s="251" t="s">
         <v>88</v>
       </c>
       <c r="B13" s="104" t="s">
@@ -4085,7 +4083,7 @@
       <c r="J13" s="106"/>
     </row>
     <row r="14" spans="1:10" s="108" customFormat="1" ht="188" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="257"/>
+      <c r="A14" s="251"/>
       <c r="B14" s="104" t="s">
         <v>35</v>
       </c>
@@ -4107,7 +4105,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" s="108" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="257"/>
+      <c r="A15" s="251"/>
       <c r="B15" s="104" t="s">
         <v>44</v>
       </c>
@@ -4127,7 +4125,7 @@
       <c r="J15" s="106"/>
     </row>
     <row r="16" spans="1:10" s="108" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A16" s="257"/>
+      <c r="A16" s="251"/>
       <c r="B16" s="104" t="s">
         <v>47</v>
       </c>
@@ -4149,7 +4147,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" s="108" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="257"/>
+      <c r="A17" s="251"/>
       <c r="B17" s="104" t="s">
         <v>51</v>
       </c>
@@ -4169,7 +4167,7 @@
       <c r="J17" s="106"/>
     </row>
     <row r="18" spans="1:10" s="108" customFormat="1" ht="135" x14ac:dyDescent="0.2">
-      <c r="A18" s="257"/>
+      <c r="A18" s="251"/>
       <c r="B18" s="104" t="s">
         <v>55</v>
       </c>
@@ -4193,7 +4191,7 @@
       <c r="J18" s="106"/>
     </row>
     <row r="19" spans="1:10" s="108" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A19" s="257"/>
+      <c r="A19" s="251"/>
       <c r="B19" s="104" t="s">
         <v>58</v>
       </c>
@@ -4217,7 +4215,7 @@
       <c r="J19" s="106"/>
     </row>
     <row r="20" spans="1:10" s="108" customFormat="1" ht="115" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="257"/>
+      <c r="A20" s="251"/>
       <c r="B20" s="104" t="s">
         <v>61</v>
       </c>
@@ -4237,51 +4235,51 @@
       <c r="J20" s="110"/>
     </row>
     <row r="21" spans="1:10" s="43" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="257"/>
+      <c r="A21" s="251"/>
       <c r="B21" s="191" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="243" t="s">
+      <c r="C21" s="255" t="s">
         <v>98</v>
       </c>
       <c r="D21" s="110" t="s">
         <v>165</v>
       </c>
-      <c r="E21" s="240" t="s">
+      <c r="E21" s="252" t="s">
         <v>99</v>
       </c>
       <c r="F21" s="72"/>
       <c r="G21" s="73"/>
       <c r="H21" s="73"/>
-      <c r="I21" s="240" t="s">
+      <c r="I21" s="252" t="s">
         <v>167</v>
       </c>
-      <c r="J21" s="246" t="s">
+      <c r="J21" s="258" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="43" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="257"/>
+      <c r="A22" s="251"/>
       <c r="B22" s="192" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="244"/>
+      <c r="C22" s="256"/>
       <c r="D22" s="193" t="s">
         <v>166</v>
       </c>
-      <c r="E22" s="241"/>
+      <c r="E22" s="253"/>
       <c r="F22" s="71"/>
       <c r="G22" s="69"/>
       <c r="H22" s="69"/>
-      <c r="I22" s="241"/>
-      <c r="J22" s="247"/>
+      <c r="I22" s="253"/>
+      <c r="J22" s="259"/>
     </row>
     <row r="23" spans="1:10" s="43" customFormat="1" ht="180" x14ac:dyDescent="0.2">
-      <c r="A23" s="257"/>
+      <c r="A23" s="251"/>
       <c r="B23" s="104" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="245"/>
+      <c r="C23" s="257"/>
       <c r="D23" s="110" t="s">
         <v>308</v>
       </c>
@@ -4291,8 +4289,8 @@
       <c r="F23" s="74"/>
       <c r="G23" s="69"/>
       <c r="H23" s="69"/>
-      <c r="I23" s="242"/>
-      <c r="J23" s="248"/>
+      <c r="I23" s="254"/>
+      <c r="J23" s="260"/>
     </row>
     <row r="24" spans="1:10" s="43" customFormat="1" ht="255" x14ac:dyDescent="0.2">
       <c r="A24" s="190"/>
@@ -4365,7 +4363,7 @@
       <c r="B27" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="251" t="s">
+      <c r="C27" s="263" t="s">
         <v>79</v>
       </c>
       <c r="D27" s="122"/>
@@ -4391,7 +4389,7 @@
       <c r="B28" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="252"/>
+      <c r="C28" s="264"/>
       <c r="D28" s="122">
         <v>50</v>
       </c>
@@ -4409,7 +4407,7 @@
       <c r="B29" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="253"/>
+      <c r="C29" s="265"/>
       <c r="D29" s="122">
         <v>0</v>
       </c>
@@ -4497,7 +4495,7 @@
       <c r="J32" s="122"/>
     </row>
     <row r="33" spans="1:10" s="132" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="254" t="s">
+      <c r="A33" s="248" t="s">
         <v>239</v>
       </c>
       <c r="B33" s="128" t="s">
@@ -4516,12 +4514,12 @@
       <c r="G33" s="131"/>
       <c r="H33" s="131"/>
       <c r="I33" s="128"/>
-      <c r="J33" s="249" t="s">
+      <c r="J33" s="261" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="132" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A34" s="254"/>
+      <c r="A34" s="248"/>
       <c r="B34" s="128" t="s">
         <v>106</v>
       </c>
@@ -4538,10 +4536,21 @@
       <c r="G34" s="131"/>
       <c r="H34" s="131"/>
       <c r="I34" s="128"/>
-      <c r="J34" s="250"/>
+      <c r="J34" s="262"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="J21:J23"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B11:B12"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="C2:C3"/>
@@ -4550,17 +4559,6 @@
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="J21:J23"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="C27:C29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -4614,7 +4612,7 @@
       <c r="E2" s="158">
         <v>0.12</v>
       </c>
-      <c r="H2" s="273" t="s">
+      <c r="H2" s="266" t="s">
         <v>304</v>
       </c>
     </row>
@@ -4634,7 +4632,7 @@
       <c r="E3" s="162">
         <v>0.88</v>
       </c>
-      <c r="H3" s="273"/>
+      <c r="H3" s="266"/>
     </row>
     <row r="4" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="136" t="s">
@@ -4652,7 +4650,7 @@
       <c r="E4" s="162">
         <v>0</v>
       </c>
-      <c r="H4" s="273"/>
+      <c r="H4" s="266"/>
     </row>
     <row r="5" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="136" t="s">
@@ -4670,7 +4668,7 @@
       <c r="E5" s="158">
         <v>0.12</v>
       </c>
-      <c r="H5" s="273"/>
+      <c r="H5" s="266"/>
     </row>
     <row r="6" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="136" t="s">
@@ -4688,7 +4686,7 @@
       <c r="E6" s="162">
         <v>0.88</v>
       </c>
-      <c r="H6" s="273"/>
+      <c r="H6" s="266"/>
     </row>
     <row r="7" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="136" t="s">
@@ -4706,7 +4704,7 @@
       <c r="E7" s="162">
         <v>0</v>
       </c>
-      <c r="H7" s="273"/>
+      <c r="H7" s="266"/>
     </row>
     <row r="8" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="136" t="s">
@@ -4724,7 +4722,7 @@
       <c r="E8" s="158">
         <v>0.12</v>
       </c>
-      <c r="H8" s="273"/>
+      <c r="H8" s="266"/>
     </row>
     <row r="9" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="136" t="s">
@@ -4742,7 +4740,7 @@
       <c r="E9" s="162">
         <v>0.88</v>
       </c>
-      <c r="H9" s="273"/>
+      <c r="H9" s="266"/>
     </row>
     <row r="10" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="136" t="s">
@@ -4760,7 +4758,7 @@
       <c r="E10" s="162">
         <v>0</v>
       </c>
-      <c r="H10" s="273"/>
+      <c r="H10" s="266"/>
     </row>
     <row r="11" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="136" t="s">
@@ -4778,7 +4776,7 @@
       <c r="E11" s="158">
         <v>0.12</v>
       </c>
-      <c r="H11" s="273"/>
+      <c r="H11" s="266"/>
     </row>
     <row r="12" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="136" t="s">
@@ -4796,7 +4794,7 @@
       <c r="E12" s="162">
         <v>0.88</v>
       </c>
-      <c r="H12" s="273"/>
+      <c r="H12" s="266"/>
     </row>
     <row r="13" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="136" t="s">
@@ -4814,7 +4812,7 @@
       <c r="E13" s="162">
         <v>0</v>
       </c>
-      <c r="H13" s="273"/>
+      <c r="H13" s="266"/>
     </row>
     <row r="14" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="136" t="s">
@@ -4832,7 +4830,7 @@
       <c r="E14" s="158">
         <v>0.12</v>
       </c>
-      <c r="H14" s="273"/>
+      <c r="H14" s="266"/>
     </row>
     <row r="15" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="136" t="s">
@@ -4850,7 +4848,7 @@
       <c r="E15" s="162">
         <v>0.88</v>
       </c>
-      <c r="H15" s="273"/>
+      <c r="H15" s="266"/>
     </row>
     <row r="16" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="136" t="s">
@@ -4868,7 +4866,7 @@
       <c r="E16" s="162">
         <v>0</v>
       </c>
-      <c r="H16" s="273"/>
+      <c r="H16" s="266"/>
     </row>
     <row r="17" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="136" t="s">
@@ -4886,7 +4884,7 @@
       <c r="E17" s="158">
         <v>0.12</v>
       </c>
-      <c r="H17" s="273"/>
+      <c r="H17" s="266"/>
     </row>
     <row r="18" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="136" t="s">
@@ -4904,7 +4902,7 @@
       <c r="E18" s="162">
         <v>0.88</v>
       </c>
-      <c r="H18" s="273"/>
+      <c r="H18" s="266"/>
     </row>
     <row r="19" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="136" t="s">
@@ -4922,7 +4920,7 @@
       <c r="E19" s="162">
         <v>0</v>
       </c>
-      <c r="H19" s="273"/>
+      <c r="H19" s="266"/>
     </row>
     <row r="20" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="136" t="s">
@@ -4940,7 +4938,7 @@
       <c r="E20" s="158">
         <v>0.12</v>
       </c>
-      <c r="H20" s="273"/>
+      <c r="H20" s="266"/>
     </row>
     <row r="21" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="136" t="s">
@@ -4958,7 +4956,7 @@
       <c r="E21" s="162">
         <v>0.88</v>
       </c>
-      <c r="H21" s="273"/>
+      <c r="H21" s="266"/>
     </row>
     <row r="22" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="136" t="s">
@@ -4976,7 +4974,7 @@
       <c r="E22" s="162">
         <v>0</v>
       </c>
-      <c r="H22" s="273"/>
+      <c r="H22" s="266"/>
     </row>
     <row r="23" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="136" t="s">
@@ -4994,7 +4992,7 @@
       <c r="E23" s="158">
         <v>0.12</v>
       </c>
-      <c r="H23" s="273"/>
+      <c r="H23" s="266"/>
     </row>
     <row r="24" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="136" t="s">
@@ -5012,7 +5010,7 @@
       <c r="E24" s="162">
         <v>0.88</v>
       </c>
-      <c r="H24" s="273"/>
+      <c r="H24" s="266"/>
     </row>
     <row r="25" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="136" t="s">
@@ -5030,7 +5028,7 @@
       <c r="E25" s="162">
         <v>0</v>
       </c>
-      <c r="H25" s="273"/>
+      <c r="H25" s="266"/>
     </row>
     <row r="26" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="136" t="s">
@@ -5048,7 +5046,7 @@
       <c r="E26" s="158">
         <v>0.12</v>
       </c>
-      <c r="H26" s="273"/>
+      <c r="H26" s="266"/>
     </row>
     <row r="27" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="136" t="s">
@@ -5066,7 +5064,7 @@
       <c r="E27" s="162">
         <v>0.88</v>
       </c>
-      <c r="H27" s="273"/>
+      <c r="H27" s="266"/>
     </row>
     <row r="28" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="136" t="s">
@@ -5084,7 +5082,7 @@
       <c r="E28" s="162">
         <v>0</v>
       </c>
-      <c r="H28" s="273"/>
+      <c r="H28" s="266"/>
     </row>
     <row r="29" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="136" t="s">
@@ -5102,7 +5100,7 @@
       <c r="E29" s="158">
         <v>0.12</v>
       </c>
-      <c r="H29" s="273"/>
+      <c r="H29" s="266"/>
     </row>
     <row r="30" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="136" t="s">
@@ -5120,7 +5118,7 @@
       <c r="E30" s="162">
         <v>0.88</v>
       </c>
-      <c r="H30" s="273"/>
+      <c r="H30" s="266"/>
     </row>
     <row r="31" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="136" t="s">
@@ -5138,7 +5136,7 @@
       <c r="E31" s="162">
         <v>0</v>
       </c>
-      <c r="H31" s="273"/>
+      <c r="H31" s="266"/>
     </row>
     <row r="32" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="136" t="s">
@@ -5156,7 +5154,7 @@
       <c r="E32" s="158">
         <v>0.12</v>
       </c>
-      <c r="H32" s="273"/>
+      <c r="H32" s="266"/>
     </row>
     <row r="33" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="136" t="s">
@@ -5174,7 +5172,7 @@
       <c r="E33" s="162">
         <v>0.88</v>
       </c>
-      <c r="H33" s="273"/>
+      <c r="H33" s="266"/>
     </row>
     <row r="34" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="136" t="s">
@@ -5192,7 +5190,7 @@
       <c r="E34" s="162">
         <v>0</v>
       </c>
-      <c r="H34" s="273"/>
+      <c r="H34" s="266"/>
     </row>
     <row r="35" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="136" t="s">
@@ -5210,7 +5208,7 @@
       <c r="E35" s="158">
         <v>0.12</v>
       </c>
-      <c r="H35" s="273"/>
+      <c r="H35" s="266"/>
     </row>
     <row r="36" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="136" t="s">
@@ -5228,7 +5226,7 @@
       <c r="E36" s="162">
         <v>0.88</v>
       </c>
-      <c r="H36" s="273"/>
+      <c r="H36" s="266"/>
     </row>
     <row r="37" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="136" t="s">
@@ -5246,7 +5244,7 @@
       <c r="E37" s="162">
         <v>0</v>
       </c>
-      <c r="H37" s="273"/>
+      <c r="H37" s="266"/>
     </row>
     <row r="38" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="136" t="s">
@@ -5264,7 +5262,7 @@
       <c r="E38" s="162">
         <v>0.94</v>
       </c>
-      <c r="H38" s="273"/>
+      <c r="H38" s="266"/>
     </row>
     <row r="39" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="136" t="s">
@@ -5282,7 +5280,7 @@
       <c r="E39" s="162">
         <v>0.06</v>
       </c>
-      <c r="H39" s="273"/>
+      <c r="H39" s="266"/>
     </row>
     <row r="40" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="136" t="s">
@@ -5300,7 +5298,7 @@
       <c r="E40" s="162">
         <v>0</v>
       </c>
-      <c r="H40" s="273"/>
+      <c r="H40" s="266"/>
     </row>
     <row r="41" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="136" t="s">
@@ -5318,7 +5316,7 @@
       <c r="E41" s="162">
         <v>0.94</v>
       </c>
-      <c r="H41" s="273"/>
+      <c r="H41" s="266"/>
     </row>
     <row r="42" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="136" t="s">
@@ -5336,7 +5334,7 @@
       <c r="E42" s="162">
         <v>0.06</v>
       </c>
-      <c r="H42" s="273"/>
+      <c r="H42" s="266"/>
     </row>
     <row r="43" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="136" t="s">
@@ -5354,7 +5352,7 @@
       <c r="E43" s="162">
         <v>0</v>
       </c>
-      <c r="H43" s="273"/>
+      <c r="H43" s="266"/>
     </row>
     <row r="44" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="136" t="s">
@@ -5372,7 +5370,7 @@
       <c r="E44" s="162">
         <v>0.94</v>
       </c>
-      <c r="H44" s="273"/>
+      <c r="H44" s="266"/>
     </row>
     <row r="45" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="136" t="s">
@@ -5390,7 +5388,7 @@
       <c r="E45" s="162">
         <v>0.06</v>
       </c>
-      <c r="H45" s="273"/>
+      <c r="H45" s="266"/>
     </row>
     <row r="46" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="136" t="s">
@@ -5408,7 +5406,7 @@
       <c r="E46" s="162">
         <v>0</v>
       </c>
-      <c r="H46" s="273"/>
+      <c r="H46" s="266"/>
     </row>
     <row r="47" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="136" t="s">
@@ -5426,7 +5424,7 @@
       <c r="E47" s="162">
         <v>0.94</v>
       </c>
-      <c r="H47" s="273"/>
+      <c r="H47" s="266"/>
     </row>
     <row r="48" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="136" t="s">
@@ -5444,7 +5442,7 @@
       <c r="E48" s="162">
         <v>0.06</v>
       </c>
-      <c r="H48" s="273"/>
+      <c r="H48" s="266"/>
     </row>
     <row r="49" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="136" t="s">
@@ -5462,7 +5460,7 @@
       <c r="E49" s="162">
         <v>0</v>
       </c>
-      <c r="H49" s="273"/>
+      <c r="H49" s="266"/>
     </row>
     <row r="50" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="136" t="s">
@@ -5480,7 +5478,7 @@
       <c r="E50" s="162">
         <v>0.94</v>
       </c>
-      <c r="H50" s="273"/>
+      <c r="H50" s="266"/>
     </row>
     <row r="51" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="136" t="s">
@@ -5498,7 +5496,7 @@
       <c r="E51" s="162">
         <v>0.06</v>
       </c>
-      <c r="H51" s="273"/>
+      <c r="H51" s="266"/>
     </row>
     <row r="52" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="136" t="s">
@@ -5516,7 +5514,7 @@
       <c r="E52" s="162">
         <v>0</v>
       </c>
-      <c r="H52" s="273"/>
+      <c r="H52" s="266"/>
     </row>
     <row r="53" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="136" t="s">
@@ -5534,7 +5532,7 @@
       <c r="E53" s="162">
         <v>0.94</v>
       </c>
-      <c r="H53" s="273"/>
+      <c r="H53" s="266"/>
     </row>
     <row r="54" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="136" t="s">
@@ -5552,7 +5550,7 @@
       <c r="E54" s="162">
         <v>0.06</v>
       </c>
-      <c r="H54" s="273"/>
+      <c r="H54" s="266"/>
     </row>
     <row r="55" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="136" t="s">
@@ -5570,7 +5568,7 @@
       <c r="E55" s="162">
         <v>0</v>
       </c>
-      <c r="H55" s="273"/>
+      <c r="H55" s="266"/>
     </row>
     <row r="56" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="136" t="s">
@@ -5588,7 +5586,7 @@
       <c r="E56" s="162">
         <v>0.94</v>
       </c>
-      <c r="H56" s="273"/>
+      <c r="H56" s="266"/>
     </row>
     <row r="57" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="136" t="s">
@@ -5606,7 +5604,7 @@
       <c r="E57" s="162">
         <v>0.06</v>
       </c>
-      <c r="H57" s="273"/>
+      <c r="H57" s="266"/>
     </row>
     <row r="58" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="136" t="s">
@@ -5624,7 +5622,7 @@
       <c r="E58" s="162">
         <v>0</v>
       </c>
-      <c r="H58" s="273"/>
+      <c r="H58" s="266"/>
     </row>
     <row r="59" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="136" t="s">
@@ -5642,7 +5640,7 @@
       <c r="E59" s="162">
         <v>0.94</v>
       </c>
-      <c r="H59" s="273"/>
+      <c r="H59" s="266"/>
     </row>
     <row r="60" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="136" t="s">
@@ -5660,7 +5658,7 @@
       <c r="E60" s="162">
         <v>0.06</v>
       </c>
-      <c r="H60" s="273"/>
+      <c r="H60" s="266"/>
     </row>
     <row r="61" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="136" t="s">
@@ -5678,7 +5676,7 @@
       <c r="E61" s="162">
         <v>0</v>
       </c>
-      <c r="H61" s="273"/>
+      <c r="H61" s="266"/>
     </row>
     <row r="62" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="136" t="s">
@@ -5696,7 +5694,7 @@
       <c r="E62" s="162">
         <v>0.94</v>
       </c>
-      <c r="H62" s="273"/>
+      <c r="H62" s="266"/>
     </row>
     <row r="63" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="136" t="s">
@@ -5714,7 +5712,7 @@
       <c r="E63" s="162">
         <v>0.06</v>
       </c>
-      <c r="H63" s="273"/>
+      <c r="H63" s="266"/>
     </row>
     <row r="64" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="136" t="s">
@@ -5732,7 +5730,7 @@
       <c r="E64" s="162">
         <v>0</v>
       </c>
-      <c r="H64" s="273"/>
+      <c r="H64" s="266"/>
     </row>
     <row r="65" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="136" t="s">
@@ -5750,7 +5748,7 @@
       <c r="E65" s="162">
         <v>0.94</v>
       </c>
-      <c r="H65" s="273"/>
+      <c r="H65" s="266"/>
     </row>
     <row r="66" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="136" t="s">
@@ -5768,7 +5766,7 @@
       <c r="E66" s="162">
         <v>0.06</v>
       </c>
-      <c r="H66" s="273"/>
+      <c r="H66" s="266"/>
     </row>
     <row r="67" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="136" t="s">
@@ -5786,7 +5784,7 @@
       <c r="E67" s="162">
         <v>0</v>
       </c>
-      <c r="H67" s="273"/>
+      <c r="H67" s="266"/>
     </row>
     <row r="68" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="136" t="s">
@@ -5804,7 +5802,7 @@
       <c r="E68" s="162">
         <v>0.94</v>
       </c>
-      <c r="H68" s="273"/>
+      <c r="H68" s="266"/>
     </row>
     <row r="69" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="136" t="s">
@@ -5822,7 +5820,7 @@
       <c r="E69" s="162">
         <v>0.06</v>
       </c>
-      <c r="H69" s="273"/>
+      <c r="H69" s="266"/>
     </row>
     <row r="70" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="136" t="s">
@@ -5840,7 +5838,7 @@
       <c r="E70" s="162">
         <v>0</v>
       </c>
-      <c r="H70" s="273"/>
+      <c r="H70" s="266"/>
     </row>
     <row r="71" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="136" t="s">
@@ -5858,7 +5856,7 @@
       <c r="E71" s="162">
         <v>0.94</v>
       </c>
-      <c r="H71" s="273"/>
+      <c r="H71" s="266"/>
     </row>
     <row r="72" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="136" t="s">
@@ -5876,7 +5874,7 @@
       <c r="E72" s="162">
         <v>0.06</v>
       </c>
-      <c r="H72" s="273"/>
+      <c r="H72" s="266"/>
     </row>
     <row r="73" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="136" t="s">
@@ -5894,7 +5892,7 @@
       <c r="E73" s="162">
         <v>0</v>
       </c>
-      <c r="H73" s="273"/>
+      <c r="H73" s="266"/>
     </row>
     <row r="74" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="136" t="s">
@@ -5912,7 +5910,7 @@
       <c r="E74" s="162">
         <v>0.94</v>
       </c>
-      <c r="H74" s="273"/>
+      <c r="H74" s="266"/>
     </row>
     <row r="75" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="136" t="s">
@@ -5930,7 +5928,7 @@
       <c r="E75" s="162">
         <v>0.06</v>
       </c>
-      <c r="H75" s="273"/>
+      <c r="H75" s="266"/>
     </row>
     <row r="76" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="136" t="s">
@@ -5948,7 +5946,7 @@
       <c r="E76" s="162">
         <v>0</v>
       </c>
-      <c r="H76" s="273"/>
+      <c r="H76" s="266"/>
     </row>
     <row r="77" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="136" t="s">
@@ -5966,7 +5964,7 @@
       <c r="E77" s="162">
         <v>0.94</v>
       </c>
-      <c r="H77" s="273"/>
+      <c r="H77" s="266"/>
     </row>
     <row r="78" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="136" t="s">
@@ -5984,7 +5982,7 @@
       <c r="E78" s="162">
         <v>0.06</v>
       </c>
-      <c r="H78" s="273"/>
+      <c r="H78" s="266"/>
     </row>
     <row r="79" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="136" t="s">
@@ -6002,7 +6000,7 @@
       <c r="E79" s="162">
         <v>0</v>
       </c>
-      <c r="H79" s="273"/>
+      <c r="H79" s="266"/>
     </row>
     <row r="80" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="136" t="s">
@@ -6020,7 +6018,7 @@
       <c r="E80" s="162">
         <v>0.94</v>
       </c>
-      <c r="H80" s="273"/>
+      <c r="H80" s="266"/>
     </row>
     <row r="81" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="136" t="s">
@@ -6038,7 +6036,7 @@
       <c r="E81" s="162">
         <v>0.06</v>
       </c>
-      <c r="H81" s="273"/>
+      <c r="H81" s="266"/>
     </row>
     <row r="82" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="136" t="s">
@@ -6056,7 +6054,7 @@
       <c r="E82" s="162">
         <v>0</v>
       </c>
-      <c r="H82" s="273"/>
+      <c r="H82" s="266"/>
     </row>
     <row r="83" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="136" t="s">
@@ -6074,7 +6072,7 @@
       <c r="E83" s="162">
         <v>0.94</v>
       </c>
-      <c r="H83" s="273"/>
+      <c r="H83" s="266"/>
     </row>
     <row r="84" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="136" t="s">
@@ -6092,7 +6090,7 @@
       <c r="E84" s="162">
         <v>0.06</v>
       </c>
-      <c r="H84" s="273"/>
+      <c r="H84" s="266"/>
     </row>
     <row r="85" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="136" t="s">
@@ -6110,7 +6108,7 @@
       <c r="E85" s="162">
         <v>0</v>
       </c>
-      <c r="H85" s="273"/>
+      <c r="H85" s="266"/>
     </row>
     <row r="86" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="136" t="s">
@@ -6128,7 +6126,7 @@
       <c r="E86" s="162">
         <v>0.94</v>
       </c>
-      <c r="H86" s="273"/>
+      <c r="H86" s="266"/>
     </row>
     <row r="87" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="136" t="s">
@@ -6146,7 +6144,7 @@
       <c r="E87" s="162">
         <v>0.06</v>
       </c>
-      <c r="H87" s="273"/>
+      <c r="H87" s="266"/>
     </row>
     <row r="88" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="136" t="s">
@@ -6164,7 +6162,7 @@
       <c r="E88" s="162">
         <v>0</v>
       </c>
-      <c r="H88" s="273"/>
+      <c r="H88" s="266"/>
     </row>
     <row r="89" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="136" t="s">
@@ -6182,7 +6180,7 @@
       <c r="E89" s="162">
         <v>0.94</v>
       </c>
-      <c r="H89" s="273"/>
+      <c r="H89" s="266"/>
     </row>
     <row r="90" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="136" t="s">
@@ -6200,7 +6198,7 @@
       <c r="E90" s="162">
         <v>0.06</v>
       </c>
-      <c r="H90" s="273"/>
+      <c r="H90" s="266"/>
     </row>
     <row r="91" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="136" t="s">
@@ -6219,7 +6217,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="163"/>
-      <c r="H91" s="273"/>
+      <c r="H91" s="266"/>
     </row>
     <row r="92" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="138" t="s">
@@ -6238,7 +6236,7 @@
         <v>0.96</v>
       </c>
       <c r="F92" s="147"/>
-      <c r="H92" s="274" t="s">
+      <c r="H92" s="267" t="s">
         <v>318</v>
       </c>
     </row>
@@ -6259,7 +6257,7 @@
         <v>0</v>
       </c>
       <c r="F93" s="147"/>
-      <c r="H93" s="274"/>
+      <c r="H93" s="267"/>
     </row>
     <row r="94" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="138" t="s">
@@ -6278,7 +6276,7 @@
         <v>0.04</v>
       </c>
       <c r="F94" s="147"/>
-      <c r="H94" s="274"/>
+      <c r="H94" s="267"/>
     </row>
     <row r="95" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="138" t="s">
@@ -6297,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="F95" s="147"/>
-      <c r="H95" s="274"/>
+      <c r="H95" s="267"/>
     </row>
     <row r="96" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="138" t="s">
@@ -6316,7 +6314,7 @@
         <v>0.96</v>
       </c>
       <c r="F96" s="147"/>
-      <c r="H96" s="274"/>
+      <c r="H96" s="267"/>
     </row>
     <row r="97" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="138" t="s">
@@ -6335,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="F97" s="147"/>
-      <c r="H97" s="274"/>
+      <c r="H97" s="267"/>
     </row>
     <row r="98" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="138" t="s">
@@ -6354,7 +6352,7 @@
         <v>0.04</v>
       </c>
       <c r="F98" s="147"/>
-      <c r="H98" s="274"/>
+      <c r="H98" s="267"/>
     </row>
     <row r="99" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A99" s="138" t="s">
@@ -6373,7 +6371,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="147"/>
-      <c r="H99" s="274"/>
+      <c r="H99" s="267"/>
     </row>
     <row r="100" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="138" t="s">
@@ -6392,7 +6390,7 @@
         <v>0.96</v>
       </c>
       <c r="F100" s="147"/>
-      <c r="H100" s="274"/>
+      <c r="H100" s="267"/>
     </row>
     <row r="101" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="138" t="s">
@@ -6411,7 +6409,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="147"/>
-      <c r="H101" s="274"/>
+      <c r="H101" s="267"/>
     </row>
     <row r="102" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A102" s="138" t="s">
@@ -6430,7 +6428,7 @@
         <v>0.04</v>
       </c>
       <c r="F102" s="147"/>
-      <c r="H102" s="274"/>
+      <c r="H102" s="267"/>
     </row>
     <row r="103" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="138" t="s">
@@ -6449,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="F103" s="147"/>
-      <c r="H103" s="274"/>
+      <c r="H103" s="267"/>
     </row>
     <row r="104" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="138" t="s">
@@ -6468,7 +6466,7 @@
         <v>0.3</v>
       </c>
       <c r="F104" s="147"/>
-      <c r="H104" s="274"/>
+      <c r="H104" s="267"/>
     </row>
     <row r="105" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A105" s="138" t="s">
@@ -6487,7 +6485,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="147"/>
-      <c r="H105" s="274"/>
+      <c r="H105" s="267"/>
     </row>
     <row r="106" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="138" t="s">
@@ -6506,7 +6504,7 @@
         <v>0.7</v>
       </c>
       <c r="F106" s="147"/>
-      <c r="H106" s="274"/>
+      <c r="H106" s="267"/>
     </row>
     <row r="107" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="138" t="s">
@@ -6525,7 +6523,7 @@
         <v>0</v>
       </c>
       <c r="F107" s="147"/>
-      <c r="H107" s="274"/>
+      <c r="H107" s="267"/>
     </row>
     <row r="108" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="138" t="s">
@@ -6544,7 +6542,7 @@
         <v>0</v>
       </c>
       <c r="F108" s="147"/>
-      <c r="H108" s="274"/>
+      <c r="H108" s="267"/>
     </row>
     <row r="109" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="138" t="s">
@@ -6563,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="F109" s="147"/>
-      <c r="H109" s="274"/>
+      <c r="H109" s="267"/>
     </row>
     <row r="110" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A110" s="138" t="s">
@@ -6582,7 +6580,7 @@
         <v>1</v>
       </c>
       <c r="F110" s="147"/>
-      <c r="H110" s="274"/>
+      <c r="H110" s="267"/>
     </row>
     <row r="111" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="138" t="s">
@@ -6601,7 +6599,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="147"/>
-      <c r="H111" s="274"/>
+      <c r="H111" s="267"/>
     </row>
     <row r="112" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="140" t="s">
@@ -6619,7 +6617,7 @@
       <c r="E112" s="166">
         <v>0.7</v>
       </c>
-      <c r="H112" s="275" t="s">
+      <c r="H112" s="268" t="s">
         <v>306</v>
       </c>
     </row>
@@ -6639,7 +6637,7 @@
       <c r="E113" s="166">
         <v>0</v>
       </c>
-      <c r="H113" s="275"/>
+      <c r="H113" s="268"/>
     </row>
     <row r="114" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" s="140" t="s">
@@ -6657,7 +6655,7 @@
       <c r="E114" s="166">
         <v>0</v>
       </c>
-      <c r="H114" s="275"/>
+      <c r="H114" s="268"/>
     </row>
     <row r="115" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A115" s="140" t="s">
@@ -6675,7 +6673,7 @@
       <c r="E115" s="166">
         <v>0.3</v>
       </c>
-      <c r="H115" s="275"/>
+      <c r="H115" s="268"/>
     </row>
     <row r="116" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="140" t="s">
@@ -6693,7 +6691,7 @@
       <c r="E116" s="166">
         <v>0</v>
       </c>
-      <c r="H116" s="275"/>
+      <c r="H116" s="268"/>
     </row>
     <row r="117" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="140" t="s">
@@ -6711,7 +6709,7 @@
       <c r="E117" s="166">
         <v>0</v>
       </c>
-      <c r="H117" s="275"/>
+      <c r="H117" s="268"/>
     </row>
     <row r="118" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A118" s="140" t="s">
@@ -6729,7 +6727,7 @@
       <c r="E118" s="166">
         <v>0.6</v>
       </c>
-      <c r="H118" s="275"/>
+      <c r="H118" s="268"/>
     </row>
     <row r="119" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="140" t="s">
@@ -6747,7 +6745,7 @@
       <c r="E119" s="166">
         <v>0</v>
       </c>
-      <c r="H119" s="275"/>
+      <c r="H119" s="268"/>
     </row>
     <row r="120" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="140" t="s">
@@ -6765,7 +6763,7 @@
       <c r="E120" s="166">
         <v>0</v>
       </c>
-      <c r="H120" s="275"/>
+      <c r="H120" s="268"/>
     </row>
     <row r="121" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A121" s="140" t="s">
@@ -6783,7 +6781,7 @@
       <c r="E121" s="166">
         <v>0.4</v>
       </c>
-      <c r="H121" s="275"/>
+      <c r="H121" s="268"/>
     </row>
     <row r="122" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" s="140" t="s">
@@ -6801,7 +6799,7 @@
       <c r="E122" s="166">
         <v>0</v>
       </c>
-      <c r="H122" s="275"/>
+      <c r="H122" s="268"/>
     </row>
     <row r="123" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="140" t="s">
@@ -6819,7 +6817,7 @@
       <c r="E123" s="166">
         <v>0</v>
       </c>
-      <c r="H123" s="275"/>
+      <c r="H123" s="268"/>
     </row>
     <row r="124" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="140" t="s">
@@ -6837,7 +6835,7 @@
       <c r="E124" s="166">
         <v>0.42</v>
       </c>
-      <c r="H124" s="275"/>
+      <c r="H124" s="268"/>
     </row>
     <row r="125" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="140" t="s">
@@ -6855,7 +6853,7 @@
       <c r="E125" s="166">
         <v>0</v>
       </c>
-      <c r="H125" s="275"/>
+      <c r="H125" s="268"/>
     </row>
     <row r="126" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="140" t="s">
@@ -6873,7 +6871,7 @@
       <c r="E126" s="166">
         <v>0</v>
       </c>
-      <c r="H126" s="275"/>
+      <c r="H126" s="268"/>
     </row>
     <row r="127" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="140" t="s">
@@ -6891,7 +6889,7 @@
       <c r="E127" s="166">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H127" s="275"/>
+      <c r="H127" s="268"/>
     </row>
     <row r="128" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="140" t="s">
@@ -6909,7 +6907,7 @@
       <c r="E128" s="166">
         <v>0</v>
       </c>
-      <c r="H128" s="275"/>
+      <c r="H128" s="268"/>
     </row>
     <row r="129" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A129" s="140" t="s">
@@ -6927,7 +6925,7 @@
       <c r="E129" s="166">
         <v>0</v>
       </c>
-      <c r="H129" s="275"/>
+      <c r="H129" s="268"/>
     </row>
     <row r="130" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="140" t="s">
@@ -6945,7 +6943,7 @@
       <c r="E130" s="166">
         <v>0.05</v>
       </c>
-      <c r="H130" s="275"/>
+      <c r="H130" s="268"/>
     </row>
     <row r="131" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A131" s="140" t="s">
@@ -6963,7 +6961,7 @@
       <c r="E131" s="166">
         <v>0</v>
       </c>
-      <c r="H131" s="275"/>
+      <c r="H131" s="268"/>
     </row>
     <row r="132" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="140" t="s">
@@ -6981,7 +6979,7 @@
       <c r="E132" s="166">
         <v>0</v>
       </c>
-      <c r="H132" s="275"/>
+      <c r="H132" s="268"/>
     </row>
     <row r="133" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="140" t="s">
@@ -6999,7 +6997,7 @@
       <c r="E133" s="166">
         <v>0.95</v>
       </c>
-      <c r="H133" s="275"/>
+      <c r="H133" s="268"/>
     </row>
     <row r="134" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A134" s="140" t="s">
@@ -7017,7 +7015,7 @@
       <c r="E134" s="166">
         <v>0</v>
       </c>
-      <c r="H134" s="275"/>
+      <c r="H134" s="268"/>
     </row>
     <row r="135" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="140" t="s">
@@ -7035,7 +7033,7 @@
       <c r="E135" s="166">
         <v>0</v>
       </c>
-      <c r="H135" s="275"/>
+      <c r="H135" s="268"/>
     </row>
     <row r="136" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A136" s="140" t="s">
@@ -7053,7 +7051,7 @@
       <c r="E136" s="166">
         <v>0</v>
       </c>
-      <c r="H136" s="275"/>
+      <c r="H136" s="268"/>
     </row>
     <row r="137" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A137" s="140" t="s">
@@ -7071,7 +7069,7 @@
       <c r="E137" s="166">
         <v>0</v>
       </c>
-      <c r="H137" s="275"/>
+      <c r="H137" s="268"/>
     </row>
     <row r="138" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A138" s="140" t="s">
@@ -7089,7 +7087,7 @@
       <c r="E138" s="166">
         <v>0</v>
       </c>
-      <c r="H138" s="275"/>
+      <c r="H138" s="268"/>
     </row>
     <row r="139" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A139" s="140" t="s">
@@ -7107,7 +7105,7 @@
       <c r="E139" s="166">
         <v>0.05</v>
       </c>
-      <c r="H139" s="275"/>
+      <c r="H139" s="268"/>
     </row>
     <row r="140" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A140" s="140" t="s">
@@ -7125,7 +7123,7 @@
       <c r="E140" s="166">
         <v>0.95</v>
       </c>
-      <c r="H140" s="275"/>
+      <c r="H140" s="268"/>
     </row>
     <row r="141" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A141" s="140" t="s">
@@ -7143,7 +7141,7 @@
       <c r="E141" s="166">
         <v>0</v>
       </c>
-      <c r="H141" s="275"/>
+      <c r="H141" s="268"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7189,7 +7187,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D2" s="64"/>
-      <c r="E2" s="276" t="s">
+      <c r="E2" s="269" t="s">
         <v>317</v>
       </c>
     </row>
@@ -7204,7 +7202,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D3" s="64"/>
-      <c r="E3" s="276"/>
+      <c r="E3" s="269"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="136" t="s">
@@ -7217,7 +7215,7 @@
         <v>0.5</v>
       </c>
       <c r="D4" s="64"/>
-      <c r="E4" s="276"/>
+      <c r="E4" s="269"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="136" t="s">
@@ -7230,7 +7228,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="64"/>
-      <c r="E5" s="276"/>
+      <c r="E5" s="269"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="138" t="s">
@@ -7243,7 +7241,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D6" s="64"/>
-      <c r="E6" s="276"/>
+      <c r="E6" s="269"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="138" t="s">
@@ -7256,7 +7254,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D7" s="64"/>
-      <c r="E7" s="276"/>
+      <c r="E7" s="269"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="138" t="s">
@@ -7269,7 +7267,7 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="64"/>
-      <c r="E8" s="276"/>
+      <c r="E8" s="269"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="138" t="s">
@@ -7282,7 +7280,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="64"/>
-      <c r="E9" s="276"/>
+      <c r="E9" s="269"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="140" t="s">
@@ -7295,7 +7293,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D10" s="64"/>
-      <c r="E10" s="276"/>
+      <c r="E10" s="269"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="140" t="s">
@@ -7308,7 +7306,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D11" s="64"/>
-      <c r="E11" s="276"/>
+      <c r="E11" s="269"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="140" t="s">
@@ -7321,7 +7319,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D12" s="64"/>
-      <c r="E12" s="276"/>
+      <c r="E12" s="269"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="140" t="s">
@@ -7334,7 +7332,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="64"/>
-      <c r="E13" s="276"/>
+      <c r="E13" s="269"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" s="64"/>
@@ -7467,84 +7465,84 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="293" t="s">
+      <c r="B2" s="287" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="295" t="s">
+      <c r="C2" s="273" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="296"/>
-      <c r="E2" s="296"/>
-      <c r="F2" s="297"/>
-      <c r="G2" s="310" t="s">
+      <c r="D2" s="274"/>
+      <c r="E2" s="274"/>
+      <c r="F2" s="289"/>
+      <c r="G2" s="285" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="293" t="s">
+      <c r="H2" s="287" t="s">
         <v>263</v>
       </c>
-      <c r="I2" s="295" t="s">
+      <c r="I2" s="273" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="296"/>
-      <c r="K2" s="305"/>
+      <c r="J2" s="274"/>
+      <c r="K2" s="275"/>
     </row>
     <row r="3" spans="1:21" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="294"/>
-      <c r="C3" s="298"/>
-      <c r="D3" s="299"/>
-      <c r="E3" s="299"/>
-      <c r="F3" s="300"/>
-      <c r="G3" s="311"/>
-      <c r="H3" s="294"/>
-      <c r="I3" s="298"/>
-      <c r="J3" s="299"/>
-      <c r="K3" s="306"/>
+      <c r="B3" s="288"/>
+      <c r="C3" s="276"/>
+      <c r="D3" s="277"/>
+      <c r="E3" s="277"/>
+      <c r="F3" s="290"/>
+      <c r="G3" s="286"/>
+      <c r="H3" s="288"/>
+      <c r="I3" s="276"/>
+      <c r="J3" s="277"/>
+      <c r="K3" s="278"/>
     </row>
     <row r="4" spans="1:21" s="44" customFormat="1" ht="270" x14ac:dyDescent="0.2">
       <c r="A4" s="46"/>
       <c r="B4" s="174" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="301" t="s">
+      <c r="C4" s="291" t="s">
         <v>321</v>
       </c>
-      <c r="D4" s="302"/>
-      <c r="E4" s="302"/>
-      <c r="F4" s="303"/>
+      <c r="D4" s="292"/>
+      <c r="E4" s="292"/>
+      <c r="F4" s="293"/>
       <c r="G4" s="175" t="s">
         <v>270</v>
       </c>
       <c r="H4" s="176" t="s">
         <v>271</v>
       </c>
-      <c r="I4" s="307" t="s">
+      <c r="I4" s="282" t="s">
         <v>295</v>
       </c>
-      <c r="J4" s="308"/>
-      <c r="K4" s="309"/>
+      <c r="J4" s="283"/>
+      <c r="K4" s="284"/>
     </row>
     <row r="5" spans="1:21" s="44" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="46"/>
       <c r="B5" s="92" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="277" t="s">
+      <c r="C5" s="279" t="s">
         <v>322</v>
       </c>
-      <c r="D5" s="278"/>
-      <c r="E5" s="278"/>
-      <c r="F5" s="304"/>
+      <c r="D5" s="280"/>
+      <c r="E5" s="280"/>
+      <c r="F5" s="281"/>
       <c r="G5" s="177">
         <v>0.8</v>
       </c>
       <c r="H5" s="178" t="s">
         <v>307</v>
       </c>
-      <c r="I5" s="280" t="s">
+      <c r="I5" s="270" t="s">
         <v>269</v>
       </c>
-      <c r="J5" s="281"/>
-      <c r="K5" s="282"/>
+      <c r="J5" s="271"/>
+      <c r="K5" s="272"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -7554,23 +7552,23 @@
       <c r="B6" s="92" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="277" t="s">
+      <c r="C6" s="279" t="s">
         <v>323</v>
       </c>
-      <c r="D6" s="278"/>
-      <c r="E6" s="278"/>
-      <c r="F6" s="304"/>
+      <c r="D6" s="280"/>
+      <c r="E6" s="280"/>
+      <c r="F6" s="281"/>
       <c r="G6" s="177">
         <v>0.8</v>
       </c>
       <c r="H6" s="179" t="s">
         <v>307</v>
       </c>
-      <c r="I6" s="280" t="s">
+      <c r="I6" s="270" t="s">
         <v>268</v>
       </c>
-      <c r="J6" s="281"/>
-      <c r="K6" s="282"/>
+      <c r="J6" s="271"/>
+      <c r="K6" s="272"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -7580,21 +7578,21 @@
       <c r="B7" s="92" t="s">
         <v>297</v>
       </c>
-      <c r="C7" s="277" t="s">
+      <c r="C7" s="279" t="s">
         <v>298</v>
       </c>
-      <c r="D7" s="278"/>
-      <c r="E7" s="278"/>
-      <c r="F7" s="304"/>
+      <c r="D7" s="280"/>
+      <c r="E7" s="280"/>
+      <c r="F7" s="281"/>
       <c r="G7" s="177">
         <v>1</v>
       </c>
       <c r="H7" s="179"/>
-      <c r="I7" s="280" t="s">
+      <c r="I7" s="270" t="s">
         <v>299</v>
       </c>
-      <c r="J7" s="281"/>
-      <c r="K7" s="282"/>
+      <c r="J7" s="271"/>
+      <c r="K7" s="272"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -7604,21 +7602,21 @@
       <c r="B8" s="92" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="277" t="s">
+      <c r="C8" s="279" t="s">
         <v>265</v>
       </c>
-      <c r="D8" s="278"/>
-      <c r="E8" s="278"/>
-      <c r="F8" s="304"/>
+      <c r="D8" s="280"/>
+      <c r="E8" s="280"/>
+      <c r="F8" s="281"/>
       <c r="G8" s="177">
         <v>1</v>
       </c>
       <c r="H8" s="178" t="s">
         <v>266</v>
       </c>
-      <c r="I8" s="280"/>
-      <c r="J8" s="281"/>
-      <c r="K8" s="282"/>
+      <c r="I8" s="270"/>
+      <c r="J8" s="271"/>
+      <c r="K8" s="272"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -7628,23 +7626,23 @@
       <c r="B9" s="92" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="277" t="s">
+      <c r="C9" s="279" t="s">
         <v>158</v>
       </c>
-      <c r="D9" s="278"/>
-      <c r="E9" s="278"/>
-      <c r="F9" s="304"/>
+      <c r="D9" s="280"/>
+      <c r="E9" s="280"/>
+      <c r="F9" s="281"/>
       <c r="G9" s="177">
         <v>0.95</v>
       </c>
       <c r="H9" s="178" t="s">
         <v>307</v>
       </c>
-      <c r="I9" s="277" t="s">
+      <c r="I9" s="279" t="s">
         <v>264</v>
       </c>
-      <c r="J9" s="278"/>
-      <c r="K9" s="279"/>
+      <c r="J9" s="280"/>
+      <c r="K9" s="296"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -7654,21 +7652,21 @@
       <c r="B10" s="92" t="s">
         <v>159</v>
       </c>
-      <c r="C10" s="277" t="s">
+      <c r="C10" s="279" t="s">
         <v>162</v>
       </c>
-      <c r="D10" s="278"/>
-      <c r="E10" s="278"/>
-      <c r="F10" s="304"/>
+      <c r="D10" s="280"/>
+      <c r="E10" s="280"/>
+      <c r="F10" s="281"/>
       <c r="G10" s="180">
         <v>0.9</v>
       </c>
       <c r="H10" s="178"/>
-      <c r="I10" s="280" t="s">
+      <c r="I10" s="270" t="s">
         <v>267</v>
       </c>
-      <c r="J10" s="281"/>
-      <c r="K10" s="282"/>
+      <c r="J10" s="271"/>
+      <c r="K10" s="272"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
@@ -7678,21 +7676,21 @@
       <c r="B11" s="92" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="277" t="s">
+      <c r="C11" s="279" t="s">
         <v>161</v>
       </c>
-      <c r="D11" s="278"/>
-      <c r="E11" s="278"/>
-      <c r="F11" s="304"/>
+      <c r="D11" s="280"/>
+      <c r="E11" s="280"/>
+      <c r="F11" s="281"/>
       <c r="G11" s="180">
         <v>0.9</v>
       </c>
       <c r="H11" s="179"/>
-      <c r="I11" s="280" t="s">
+      <c r="I11" s="270" t="s">
         <v>267</v>
       </c>
-      <c r="J11" s="281"/>
-      <c r="K11" s="282"/>
+      <c r="J11" s="271"/>
+      <c r="K11" s="272"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -7723,28 +7721,28 @@
       <c r="U13" s="51"/>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="287" t="s">
+      <c r="B14" s="301" t="s">
         <v>258</v>
       </c>
-      <c r="C14" s="288"/>
-      <c r="D14" s="288"/>
-      <c r="E14" s="288"/>
-      <c r="F14" s="288"/>
-      <c r="G14" s="288"/>
-      <c r="H14" s="288"/>
-      <c r="I14" s="288"/>
-      <c r="J14" s="288"/>
-      <c r="K14" s="288"/>
-      <c r="L14" s="288"/>
-      <c r="M14" s="288"/>
-      <c r="N14" s="288"/>
-      <c r="O14" s="288"/>
-      <c r="P14" s="288"/>
-      <c r="Q14" s="288"/>
-      <c r="R14" s="288"/>
-      <c r="S14" s="288"/>
-      <c r="T14" s="288"/>
-      <c r="U14" s="289"/>
+      <c r="C14" s="302"/>
+      <c r="D14" s="302"/>
+      <c r="E14" s="302"/>
+      <c r="F14" s="302"/>
+      <c r="G14" s="302"/>
+      <c r="H14" s="302"/>
+      <c r="I14" s="302"/>
+      <c r="J14" s="302"/>
+      <c r="K14" s="302"/>
+      <c r="L14" s="302"/>
+      <c r="M14" s="302"/>
+      <c r="N14" s="302"/>
+      <c r="O14" s="302"/>
+      <c r="P14" s="302"/>
+      <c r="Q14" s="302"/>
+      <c r="R14" s="302"/>
+      <c r="S14" s="302"/>
+      <c r="T14" s="302"/>
+      <c r="U14" s="303"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B15" s="52"/>
@@ -7769,34 +7767,34 @@
       <c r="U15" s="55"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B16" s="285" t="s">
+      <c r="B16" s="299" t="s">
         <v>254</v>
       </c>
-      <c r="C16" s="286"/>
-      <c r="D16" s="286"/>
-      <c r="E16" s="286"/>
-      <c r="F16" s="286"/>
-      <c r="G16" s="286"/>
-      <c r="H16" s="286"/>
-      <c r="I16" s="286"/>
-      <c r="J16" s="286"/>
-      <c r="K16" s="286"/>
-      <c r="L16" s="286"/>
-      <c r="M16" s="286"/>
-      <c r="N16" s="286"/>
-      <c r="O16" s="286"/>
-      <c r="P16" s="286"/>
-      <c r="Q16" s="286"/>
-      <c r="R16" s="286"/>
-      <c r="S16" s="286"/>
-      <c r="T16" s="286"/>
-      <c r="U16" s="292"/>
+      <c r="C16" s="300"/>
+      <c r="D16" s="300"/>
+      <c r="E16" s="300"/>
+      <c r="F16" s="300"/>
+      <c r="G16" s="300"/>
+      <c r="H16" s="300"/>
+      <c r="I16" s="300"/>
+      <c r="J16" s="300"/>
+      <c r="K16" s="300"/>
+      <c r="L16" s="300"/>
+      <c r="M16" s="300"/>
+      <c r="N16" s="300"/>
+      <c r="O16" s="300"/>
+      <c r="P16" s="300"/>
+      <c r="Q16" s="300"/>
+      <c r="R16" s="300"/>
+      <c r="S16" s="300"/>
+      <c r="T16" s="300"/>
+      <c r="U16" s="304"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B17" s="290" t="s">
+      <c r="B17" s="294" t="s">
         <v>250</v>
       </c>
-      <c r="C17" s="291"/>
+      <c r="C17" s="295"/>
       <c r="D17" s="181">
         <v>2008</v>
       </c>
@@ -7853,10 +7851,10 @@
       </c>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18" s="290" t="s">
+      <c r="B18" s="294" t="s">
         <v>251</v>
       </c>
-      <c r="C18" s="291"/>
+      <c r="C18" s="295"/>
       <c r="D18" s="59">
         <v>0.86</v>
       </c>
@@ -7913,10 +7911,10 @@
       </c>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B19" s="290" t="s">
+      <c r="B19" s="294" t="s">
         <v>252</v>
       </c>
-      <c r="C19" s="291"/>
+      <c r="C19" s="295"/>
       <c r="D19" s="59">
         <f>78/86</f>
         <v>0.90697674418604646</v>
@@ -7988,10 +7986,10 @@
       </c>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B20" s="290" t="s">
+      <c r="B20" s="294" t="s">
         <v>253</v>
       </c>
-      <c r="C20" s="291"/>
+      <c r="C20" s="295"/>
       <c r="D20" s="59">
         <v>1</v>
       </c>
@@ -8070,17 +8068,17 @@
       <c r="U21" s="55"/>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B22" s="285" t="s">
+      <c r="B22" s="299" t="s">
         <v>257</v>
       </c>
-      <c r="C22" s="286"/>
-      <c r="D22" s="286"/>
-      <c r="E22" s="286"/>
-      <c r="F22" s="286"/>
-      <c r="G22" s="286"/>
-      <c r="H22" s="286"/>
-      <c r="I22" s="286"/>
-      <c r="J22" s="286"/>
+      <c r="C22" s="300"/>
+      <c r="D22" s="300"/>
+      <c r="E22" s="300"/>
+      <c r="F22" s="300"/>
+      <c r="G22" s="300"/>
+      <c r="H22" s="300"/>
+      <c r="I22" s="300"/>
+      <c r="J22" s="300"/>
       <c r="K22" s="184"/>
       <c r="L22" s="184"/>
       <c r="M22" s="184"/>
@@ -8094,10 +8092,10 @@
       <c r="U22" s="185"/>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B23" s="290" t="s">
+      <c r="B23" s="294" t="s">
         <v>250</v>
       </c>
-      <c r="C23" s="291"/>
+      <c r="C23" s="295"/>
       <c r="D23" s="181">
         <v>2019</v>
       </c>
@@ -8132,10 +8130,10 @@
       <c r="U23" s="55"/>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B24" s="290" t="s">
+      <c r="B24" s="294" t="s">
         <v>251</v>
       </c>
-      <c r="C24" s="291"/>
+      <c r="C24" s="295"/>
       <c r="D24" s="59">
         <f>E24</f>
         <v>0.53</v>
@@ -8173,10 +8171,10 @@
       <c r="U24" s="55"/>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B25" s="290" t="s">
+      <c r="B25" s="294" t="s">
         <v>252</v>
       </c>
-      <c r="C25" s="291"/>
+      <c r="C25" s="295"/>
       <c r="D25" s="59">
         <f>E25</f>
         <v>0.35830985915492958</v>
@@ -8214,10 +8212,10 @@
       <c r="U25" s="55"/>
     </row>
     <row r="26" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="283" t="s">
+      <c r="B26" s="297" t="s">
         <v>253</v>
       </c>
-      <c r="C26" s="284"/>
+      <c r="C26" s="298"/>
       <c r="D26" s="186">
         <v>0</v>
       </c>
@@ -8282,26 +8280,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="I10:K10"/>
     <mergeCell ref="B26:C26"/>
@@ -8314,6 +8292,26 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B16:U16"/>
     <mergeCell ref="I11:K11"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8359,13 +8357,13 @@
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="211" t="s">
+      <c r="B3" s="210" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="213"/>
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="212"/>
       <c r="G3" s="75"/>
       <c r="H3" s="76"/>
     </row>
@@ -8392,237 +8390,237 @@
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="211" t="s">
+      <c r="B5" s="210" t="s">
         <v>260</v>
       </c>
-      <c r="C5" s="212"/>
-      <c r="D5" s="212"/>
-      <c r="E5" s="212"/>
-      <c r="F5" s="213"/>
+      <c r="C5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="212"/>
       <c r="G5" s="65"/>
       <c r="H5" s="194"/>
     </row>
-    <row r="6" spans="2:8" s="317" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="312" t="s">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B6" s="207" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="313" t="s">
+      <c r="C6" s="64" t="s">
         <v>261</v>
       </c>
-      <c r="D6" s="313">
+      <c r="D6" s="64">
         <v>0.8</v>
       </c>
-      <c r="E6" s="314" t="s">
+      <c r="E6" s="208" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="315" t="s">
+      <c r="F6" s="209" t="s">
         <v>272</v>
       </c>
-      <c r="G6" s="314">
+      <c r="G6" s="208">
         <v>3</v>
       </c>
-      <c r="H6" s="316">
+      <c r="H6" s="194">
         <f>H4*G6</f>
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="211" t="s">
+      <c r="B7" s="210" t="s">
         <v>273</v>
       </c>
-      <c r="C7" s="212"/>
-      <c r="D7" s="212"/>
-      <c r="E7" s="212"/>
-      <c r="F7" s="213"/>
+      <c r="C7" s="211"/>
+      <c r="D7" s="211"/>
+      <c r="E7" s="211"/>
+      <c r="F7" s="212"/>
       <c r="G7" s="65"/>
       <c r="H7" s="194"/>
     </row>
-    <row r="8" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="204" t="s">
+    <row r="8" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="313" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="205" t="s">
+      <c r="C8" s="314" t="s">
         <v>290</v>
       </c>
-      <c r="D8" s="198">
+      <c r="D8" s="315">
         <v>0.68</v>
       </c>
-      <c r="E8" s="198" t="s">
+      <c r="E8" s="315" t="s">
         <v>292</v>
       </c>
       <c r="F8" s="217" t="s">
         <v>294</v>
       </c>
-      <c r="G8" s="226">
+      <c r="G8" s="215">
         <v>3</v>
       </c>
-      <c r="H8" s="218">
+      <c r="H8" s="216">
         <f>H6*G8</f>
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="204" t="s">
+    <row r="9" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="313" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="205" t="s">
+      <c r="C9" s="314" t="s">
         <v>291</v>
       </c>
-      <c r="D9" s="198">
+      <c r="D9" s="315">
         <v>0.76</v>
       </c>
-      <c r="E9" s="198" t="s">
+      <c r="E9" s="315" t="s">
         <v>293</v>
       </c>
       <c r="F9" s="217"/>
-      <c r="G9" s="226"/>
-      <c r="H9" s="218"/>
-    </row>
-    <row r="10" spans="2:8" s="201" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="196" t="s">
+      <c r="G9" s="215"/>
+      <c r="H9" s="216"/>
+    </row>
+    <row r="10" spans="2:8" s="202" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="203" t="s">
         <v>164</v>
       </c>
-      <c r="C10" s="205" t="s">
+      <c r="C10" s="314" t="s">
         <v>154</v>
       </c>
-      <c r="D10" s="197">
+      <c r="D10" s="167">
         <v>0.8</v>
       </c>
-      <c r="E10" s="198" t="s">
+      <c r="E10" s="315" t="s">
         <v>274</v>
       </c>
       <c r="F10" s="217"/>
-      <c r="G10" s="226"/>
-      <c r="H10" s="218"/>
-    </row>
-    <row r="11" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="196" t="s">
+      <c r="G10" s="215"/>
+      <c r="H10" s="216"/>
+    </row>
+    <row r="11" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="203" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="197" t="s">
+      <c r="C11" s="167" t="s">
         <v>155</v>
       </c>
-      <c r="D11" s="197">
+      <c r="D11" s="167">
         <v>0.8</v>
       </c>
-      <c r="E11" s="198" t="s">
+      <c r="E11" s="315" t="s">
         <v>274</v>
       </c>
       <c r="F11" s="217"/>
-      <c r="G11" s="226"/>
-      <c r="H11" s="218"/>
-    </row>
-    <row r="12" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="196" t="s">
+      <c r="G11" s="215"/>
+      <c r="H11" s="216"/>
+    </row>
+    <row r="12" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="203" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="197" t="s">
+      <c r="C12" s="167" t="s">
         <v>159</v>
       </c>
-      <c r="D12" s="197">
+      <c r="D12" s="167">
         <v>0.9</v>
       </c>
-      <c r="E12" s="198" t="s">
+      <c r="E12" s="315" t="s">
         <v>280</v>
       </c>
       <c r="F12" s="217"/>
-      <c r="G12" s="226"/>
-      <c r="H12" s="218"/>
-    </row>
-    <row r="13" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="196" t="s">
+      <c r="G12" s="215"/>
+      <c r="H12" s="216"/>
+    </row>
+    <row r="13" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="203" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="197" t="s">
+      <c r="C13" s="167" t="s">
         <v>160</v>
       </c>
-      <c r="D13" s="197">
+      <c r="D13" s="167">
         <v>0.9</v>
       </c>
-      <c r="E13" s="198" t="s">
+      <c r="E13" s="315" t="s">
         <v>275</v>
       </c>
       <c r="F13" s="217"/>
-      <c r="G13" s="226"/>
-      <c r="H13" s="218"/>
+      <c r="G13" s="215"/>
+      <c r="H13" s="216"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="211" t="s">
+      <c r="B14" s="210" t="s">
         <v>305</v>
       </c>
-      <c r="C14" s="212"/>
-      <c r="D14" s="212"/>
-      <c r="E14" s="212"/>
-      <c r="F14" s="213"/>
+      <c r="C14" s="211"/>
+      <c r="D14" s="211"/>
+      <c r="E14" s="211"/>
+      <c r="F14" s="212"/>
       <c r="G14" s="65"/>
       <c r="H14" s="194"/>
     </row>
-    <row r="15" spans="2:8" s="202" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="203" t="s">
+    <row r="15" spans="2:8" s="201" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="196" t="s">
         <v>149</v>
       </c>
-      <c r="C15" s="167" t="s">
+      <c r="C15" s="197" t="s">
         <v>276</v>
       </c>
-      <c r="D15" s="167">
-        <v>0</v>
-      </c>
-      <c r="E15" s="167">
+      <c r="D15" s="197">
+        <v>0</v>
+      </c>
+      <c r="E15" s="197">
         <v>0.1</v>
       </c>
-      <c r="F15" s="214" t="s">
+      <c r="F15" s="218" t="s">
         <v>279</v>
       </c>
-      <c r="G15" s="215">
+      <c r="G15" s="311">
         <v>2</v>
       </c>
-      <c r="H15" s="216">
+      <c r="H15" s="312">
         <f>H8*G15</f>
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="203" t="s">
+    <row r="16" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="196" t="s">
         <v>149</v>
       </c>
-      <c r="C16" s="167" t="s">
+      <c r="C16" s="197" t="s">
         <v>277</v>
       </c>
-      <c r="D16" s="167">
-        <v>0</v>
-      </c>
-      <c r="E16" s="167">
+      <c r="D16" s="197">
+        <v>0</v>
+      </c>
+      <c r="E16" s="197">
         <v>0.1</v>
       </c>
-      <c r="F16" s="214"/>
-      <c r="G16" s="215"/>
-      <c r="H16" s="216"/>
-    </row>
-    <row r="17" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="203" t="s">
+      <c r="F16" s="218"/>
+      <c r="G16" s="311"/>
+      <c r="H16" s="312"/>
+    </row>
+    <row r="17" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="196" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="167" t="s">
+      <c r="C17" s="197" t="s">
         <v>278</v>
       </c>
-      <c r="D17" s="167">
-        <v>0</v>
-      </c>
-      <c r="E17" s="167">
+      <c r="D17" s="197">
+        <v>0</v>
+      </c>
+      <c r="E17" s="197">
         <v>0.1</v>
       </c>
-      <c r="F17" s="214"/>
-      <c r="G17" s="215"/>
-      <c r="H17" s="216"/>
+      <c r="F17" s="218"/>
+      <c r="G17" s="311"/>
+      <c r="H17" s="312"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" s="211" t="s">
+      <c r="B18" s="210" t="s">
         <v>324</v>
       </c>
-      <c r="C18" s="212"/>
-      <c r="D18" s="212"/>
-      <c r="E18" s="212"/>
-      <c r="F18" s="213"/>
+      <c r="C18" s="211"/>
+      <c r="D18" s="211"/>
+      <c r="E18" s="211"/>
+      <c r="F18" s="212"/>
       <c r="G18" s="195"/>
       <c r="H18" s="194"/>
     </row>
@@ -8633,16 +8631,16 @@
       <c r="C19" s="197" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="206" t="s">
+      <c r="D19" s="204" t="s">
         <v>308</v>
       </c>
-      <c r="E19" s="206" t="s">
+      <c r="E19" s="204" t="s">
         <v>166</v>
       </c>
-      <c r="F19" s="207" t="s">
+      <c r="F19" s="205" t="s">
         <v>325</v>
       </c>
-      <c r="G19" s="208">
+      <c r="G19" s="206">
         <v>2</v>
       </c>
       <c r="H19" s="200">
@@ -8651,56 +8649,56 @@
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B20" s="211" t="s">
+      <c r="B20" s="210" t="s">
         <v>319</v>
       </c>
-      <c r="C20" s="212"/>
-      <c r="D20" s="212"/>
-      <c r="E20" s="212"/>
-      <c r="F20" s="213"/>
+      <c r="C20" s="211"/>
+      <c r="D20" s="211"/>
+      <c r="E20" s="211"/>
+      <c r="F20" s="212"/>
       <c r="G20" s="135"/>
       <c r="H20" s="143"/>
     </row>
-    <row r="21" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="203" t="s">
+    <row r="21" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="196" t="s">
         <v>140</v>
       </c>
-      <c r="C21" s="167" t="s">
+      <c r="C21" s="197" t="s">
         <v>326</v>
       </c>
-      <c r="D21" s="167">
+      <c r="D21" s="197">
         <v>0.96</v>
       </c>
-      <c r="E21" s="167">
+      <c r="E21" s="197">
         <v>0.9</v>
       </c>
-      <c r="F21" s="224" t="s">
+      <c r="F21" s="305" t="s">
         <v>328</v>
       </c>
-      <c r="G21" s="220">
+      <c r="G21" s="213">
         <v>2</v>
       </c>
-      <c r="H21" s="222">
+      <c r="H21" s="219">
         <f>H19*G21</f>
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="2:8" s="202" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="209" t="s">
+    <row r="22" spans="2:8" s="201" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="306" t="s">
         <v>140</v>
       </c>
-      <c r="C22" s="210" t="s">
+      <c r="C22" s="307" t="s">
         <v>320</v>
       </c>
-      <c r="D22" s="210">
+      <c r="D22" s="307">
         <v>0.7</v>
       </c>
-      <c r="E22" s="210">
+      <c r="E22" s="307">
         <v>0.85</v>
       </c>
-      <c r="F22" s="225"/>
-      <c r="G22" s="221"/>
-      <c r="H22" s="223"/>
+      <c r="F22" s="308"/>
+      <c r="G22" s="309"/>
+      <c r="H22" s="310"/>
     </row>
     <row r="23" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B23" s="8"/>
@@ -8740,46 +8738,46 @@
       <c r="H25" s="8"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C27" s="219" t="s">
+      <c r="C27" s="214" t="s">
         <v>296</v>
       </c>
-      <c r="D27" s="219"/>
-      <c r="E27" s="219"/>
-      <c r="F27" s="219"/>
-      <c r="G27" s="219"/>
+      <c r="D27" s="214"/>
+      <c r="E27" s="214"/>
+      <c r="F27" s="214"/>
+      <c r="G27" s="214"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C28" s="219"/>
-      <c r="D28" s="219"/>
-      <c r="E28" s="219"/>
-      <c r="F28" s="219"/>
-      <c r="G28" s="219"/>
+      <c r="C28" s="214"/>
+      <c r="D28" s="214"/>
+      <c r="E28" s="214"/>
+      <c r="F28" s="214"/>
+      <c r="G28" s="214"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C29" s="219"/>
-      <c r="D29" s="219"/>
-      <c r="E29" s="219"/>
-      <c r="F29" s="219"/>
-      <c r="G29" s="219"/>
+      <c r="C29" s="214"/>
+      <c r="D29" s="214"/>
+      <c r="E29" s="214"/>
+      <c r="F29" s="214"/>
+      <c r="G29" s="214"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="G8:G13"/>
-    <mergeCell ref="C27:G29"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="F21:F22"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="F15:F17"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="H15:H17"/>
     <mergeCell ref="F8:F13"/>
     <mergeCell ref="H8:H13"/>
+    <mergeCell ref="C27:G29"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="G8:G13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/project_documents/parameterDirectory.xlsx
+++ b/project_documents/parameterDirectory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabian/Documents/DPhil Work/Academic Work/EnglandCervicalScreeningProject/project_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C33E43B-BB4E-E745-9304-EAD4D6D39805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4815A5-6FD2-9747-B80F-0C537C8DEF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17180" activeTab="7" xr2:uid="{9CDCC384-B02C-4946-8A51-C0AA91FF93D1}"/>
+    <workbookView xWindow="18820" yWindow="920" windowWidth="10420" windowHeight="16880" firstSheet="6" activeTab="7" xr2:uid="{9CDCC384-B02C-4946-8A51-C0AA91FF93D1}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="323">
   <si>
     <t>This spreadsheet summarises all the parameters used in our modelling, including their names, interpretations, values, and sources</t>
   </si>
@@ -801,12 +801,6 @@
     <t>P(takes 1st dose by age 16)</t>
   </si>
   <si>
-    <t>P(takes 2nd dose by age 16 | took first dose by age 16)</t>
-  </si>
-  <si>
-    <t>P(takes 3rd dose by age 16 | took second dose by age 16)</t>
-  </si>
-  <si>
     <t>GIRLS</t>
   </si>
   <si>
@@ -819,9 +813,6 @@
     <t>BOYS</t>
   </si>
   <si>
-    <t>Girls' uptake in 2008 and 2009 are extrapolated using copying from 2010, as is boys' uptake in 2019 from 2020. Data for first dose and completion is available, so in years where completion of vaccination requires three doses, we assume all those who have two doses additionally have their final dose - given the very small modelled difference between two and three doses, this is negligable as a difference. Data is used until 2021, beyond which we assume fixed rate of future vaccination</t>
-  </si>
-  <si>
     <t>NOTE: 0.8 from 2022 onwards is to be swapped with 0.6 and 0.9 as sensitivity analysis.</t>
   </si>
   <si>
@@ -888,18 +879,6 @@
     <t>0.8, 0.95</t>
   </si>
   <si>
-    <t>Cases</t>
-  </si>
-  <si>
-    <t>Total cases if we do one-v-standard SA</t>
-  </si>
-  <si>
-    <t>Total cases if we do full SA grid</t>
-  </si>
-  <si>
-    <t>Cumulative crossed cases</t>
-  </si>
-  <si>
     <t>HPVsim models each agent as having different states of disease progression, tracking the attribution of a state to a given genotype's infection (e.g. it differentiates between being cancerous due to hpv16 infection and being cancerous due to hi5 infection). Therefore, diagnostic outcome is a random function of (state, genotype) pairs. This sheet defines the function, in the same format as can be directly read by HPVsim - implemented by changing the file data/products_dx in the hpvsim installation used</t>
   </si>
   <si>
@@ -933,9 +912,6 @@
     <t>The denominator in these proportions include those who have opted out of screening. Our modelling doesn't excplitily consider screening opt-outs, instead at each timestep each invited individual has a 0.68 (or 0.76) independnat probability of taking up screening. Further note that we only model primary screening as occuring after an invite from the regular screening porgramme; we justify this as we are modellign changes to the programme itself and not people presenting with issues and being referred to screening - however this means we do not model this 10-15% of primary screenings annually.</t>
   </si>
   <si>
-    <t>NOTE: If I can change a parameter in the sensitivyt analysis (/a batch of them) and still get a good fit with the output of an old calibration, then we can do a sort of reverse sensiiuvty analysis where we see that changing these SA parameters doesn’t change output significnatly and (although this doesnt rule out a newly revealed valley in the loss landscape) - givign us less full calobrations we need to do</t>
-  </si>
-  <si>
     <t>abandon_followup_invites_threshold</t>
   </si>
   <si>
@@ -952,9 +928,6 @@
   </si>
   <si>
     <t>dur_cin' refers to the (randomly-sampled) duration of hpv infection with CIN prior to cancer. It is lognormal(4.5, 20^2) by default in HPVsim; and we are calibrating the mean (par1) of this lognormal distribution</t>
-  </si>
-  <si>
-    <t>f</t>
   </si>
   <si>
     <t>HPV DNA screening. Sensitivity is 0.94, so for precin, cin, and cancerous states there is a 94% probability of positive result. Specificity is 0.88, so for susceptible and latent states (i.e. no detectible infection), we have 12% probablity of a positive result. This data is from the meta-analysis of 10.1016/j.ijgo.2015.07.024; https://pubmed.ncbi.nlm.nih.gov/26851054/</t>
@@ -1114,6 +1087,15 @@
   </si>
   <si>
     <t>These parameters are to be varied together to form two cases, as they are two different ways cytology have been modelled in literature</t>
+  </si>
+  <si>
+    <t>P(takes 1st and 2nd dose by age 16)</t>
+  </si>
+  <si>
+    <t>P(takes 1st, 2nd, and 3rd dose by age 16)</t>
+  </si>
+  <si>
+    <t>Girls' uptake in 2008 and 2009 are extrapolated using copying from 2010, as is boys' uptake in 2019 from 2020. Data for first dose and completion is available, so in years where completion of vaccination requires three doses, we assume all those who have two doses additionally have their final dose - given the very small modelled difference in effect between two and three doses, this is negligable as a difference. Data is used until 2021, beyond which we assume fixed rate of future vaccination</t>
   </si>
 </sst>
 </file>
@@ -1262,7 +1244,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="72">
+  <borders count="70">
     <border>
       <left/>
       <right/>
@@ -2054,21 +2036,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2132,21 +2099,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="316">
+  <cellXfs count="286">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2273,14 +2231,10 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="9" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2306,14 +2260,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2472,9 +2418,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2483,9 +2426,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2552,7 +2492,6 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="9" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2569,64 +2508,13 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2668,6 +2556,66 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2692,12 +2640,6 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2713,60 +2655,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2780,6 +2668,15 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2788,40 +2685,79 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2830,88 +2766,42 @@
     <xf numFmtId="43" fontId="2" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3361,11 +3251,11 @@
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="220"/>
-      <c r="D4" s="220"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
     </row>
     <row r="5" spans="2:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -3389,7 +3279,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="43" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:4" ht="51" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
@@ -3398,7 +3288,7 @@
       </c>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="2:4" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:4" ht="119" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>140</v>
       </c>
@@ -3406,7 +3296,7 @@
         <v>142</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="34" x14ac:dyDescent="0.2">
@@ -3417,7 +3307,7 @@
         <v>150</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="68" x14ac:dyDescent="0.2">
@@ -3428,7 +3318,7 @@
         <v>163</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="34" x14ac:dyDescent="0.2">
@@ -3439,30 +3329,30 @@
         <v>5</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="221" t="s">
+      <c r="B13" s="187" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="221"/>
-      <c r="D13" s="221"/>
+      <c r="C13" s="187"/>
+      <c r="D13" s="187"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="221"/>
-      <c r="C14" s="221"/>
-      <c r="D14" s="221"/>
+      <c r="B14" s="187"/>
+      <c r="C14" s="187"/>
+      <c r="D14" s="187"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="221"/>
-      <c r="C15" s="221"/>
-      <c r="D15" s="221"/>
+      <c r="B15" s="187"/>
+      <c r="C15" s="187"/>
+      <c r="D15" s="187"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="221"/>
-      <c r="C16" s="221"/>
-      <c r="D16" s="221"/>
+      <c r="B16" s="187"/>
+      <c r="C16" s="187"/>
+      <c r="D16" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3493,13 +3383,13 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="224" t="s">
+      <c r="B3" s="190" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="224"/>
-      <c r="D3" s="224"/>
-      <c r="E3" s="224"/>
-      <c r="F3" s="224"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
+      <c r="F3" s="190"/>
     </row>
     <row r="5" spans="2:6" ht="35" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
@@ -3519,7 +3409,7 @@
       </c>
     </row>
     <row r="6" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B6" s="226" t="s">
+      <c r="B6" s="192" t="s">
         <v>177</v>
       </c>
       <c r="C6" s="27" t="s">
@@ -3534,7 +3424,7 @@
       <c r="F6" s="14"/>
     </row>
     <row r="7" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" s="227"/>
+      <c r="B7" s="193"/>
       <c r="C7" s="28" t="s">
         <v>179</v>
       </c>
@@ -3547,7 +3437,7 @@
       <c r="F7" s="15"/>
     </row>
     <row r="8" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B8" s="227"/>
+      <c r="B8" s="193"/>
       <c r="C8" s="28" t="s">
         <v>180</v>
       </c>
@@ -3560,7 +3450,7 @@
       <c r="F8" s="15"/>
     </row>
     <row r="9" spans="2:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="B9" s="227"/>
+      <c r="B9" s="193"/>
       <c r="C9" s="28" t="s">
         <v>181</v>
       </c>
@@ -3573,7 +3463,7 @@
       <c r="F9" s="15"/>
     </row>
     <row r="10" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B10" s="228" t="s">
+      <c r="B10" s="194" t="s">
         <v>173</v>
       </c>
       <c r="C10" s="29" t="s">
@@ -3590,7 +3480,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B11" s="228"/>
+      <c r="B11" s="194"/>
       <c r="C11" s="29" t="s">
         <v>187</v>
       </c>
@@ -3605,7 +3495,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B12" s="228"/>
+      <c r="B12" s="194"/>
       <c r="C12" s="29" t="s">
         <v>188</v>
       </c>
@@ -3620,7 +3510,7 @@
       </c>
     </row>
     <row r="13" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B13" s="229" t="s">
+      <c r="B13" s="195" t="s">
         <v>174</v>
       </c>
       <c r="C13" s="30" t="s">
@@ -3637,7 +3527,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B14" s="229"/>
+      <c r="B14" s="195"/>
       <c r="C14" s="30" t="s">
         <v>113</v>
       </c>
@@ -3652,7 +3542,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B15" s="229"/>
+      <c r="B15" s="195"/>
       <c r="C15" s="30" t="s">
         <v>111</v>
       </c>
@@ -3667,7 +3557,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B16" s="230" t="s">
+      <c r="B16" s="196" t="s">
         <v>175</v>
       </c>
       <c r="C16" s="31" t="s">
@@ -3682,7 +3572,7 @@
       <c r="F16" s="18"/>
     </row>
     <row r="17" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B17" s="230"/>
+      <c r="B17" s="196"/>
       <c r="C17" s="31" t="s">
         <v>133</v>
       </c>
@@ -3697,7 +3587,7 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="135" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="230"/>
+      <c r="B18" s="196"/>
       <c r="C18" s="31" t="s">
         <v>115</v>
       </c>
@@ -3719,7 +3609,7 @@
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B19" s="230"/>
+      <c r="B19" s="196"/>
       <c r="C19" s="31" t="s">
         <v>114</v>
       </c>
@@ -3738,30 +3628,30 @@
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B22" s="231" t="s">
+      <c r="B22" s="197" t="s">
         <v>132</v>
       </c>
       <c r="C22" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="222" t="s">
+      <c r="D22" s="188" t="s">
         <v>216</v>
       </c>
-      <c r="E22" s="223"/>
+      <c r="E22" s="189"/>
     </row>
     <row r="23" spans="2:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="232"/>
+      <c r="B23" s="198"/>
       <c r="C23" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="224" t="s">
+      <c r="D23" s="190" t="s">
         <v>218</v>
       </c>
-      <c r="E23" s="225"/>
+      <c r="E23" s="191"/>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="232"/>
+      <c r="B24" s="198"/>
       <c r="C24" s="8" t="s">
         <v>114</v>
       </c>
@@ -3818,7 +3708,7 @@
   <dimension ref="A2:J34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="188"/>
+    <col min="1" max="1" width="10.83203125" style="177"/>
     <col min="2" max="2" width="14.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53" style="5" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" style="5"/>
@@ -3830,36 +3720,36 @@
     <col min="11" max="16384" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" s="66" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="188"/>
-      <c r="B2" s="233" t="s">
+    <row r="2" spans="1:10" s="64" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="177"/>
+      <c r="B2" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="223" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="245" t="s">
+      <c r="D2" s="229" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="246"/>
-      <c r="F2" s="247" t="s">
+      <c r="E2" s="230"/>
+      <c r="F2" s="231" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="247"/>
-      <c r="H2" s="247"/>
-      <c r="I2" s="246"/>
-      <c r="J2" s="235" t="s">
+      <c r="G2" s="231"/>
+      <c r="H2" s="231"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="221" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="66" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="188"/>
-      <c r="B3" s="234"/>
-      <c r="C3" s="238"/>
+    <row r="3" spans="1:10" s="64" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="177"/>
+      <c r="B3" s="220"/>
+      <c r="C3" s="224"/>
       <c r="D3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="189" t="s">
+      <c r="E3" s="178" t="s">
         <v>25</v>
       </c>
       <c r="F3" s="11" t="s">
@@ -3871,686 +3761,675 @@
       <c r="H3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="189" t="s">
+      <c r="I3" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="236"/>
-    </row>
-    <row r="4" spans="1:10" s="86" customFormat="1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="249" t="s">
+      <c r="J3" s="222"/>
+    </row>
+    <row r="4" spans="1:10" s="78" customFormat="1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="83">
+      <c r="D4" s="75">
         <v>200000</v>
       </c>
-      <c r="E4" s="81" t="s">
+      <c r="E4" s="73" t="s">
+        <v>292</v>
+      </c>
+      <c r="F4" s="76"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="76" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="78" customFormat="1" ht="105" x14ac:dyDescent="0.2">
+      <c r="A5" s="214"/>
+      <c r="B5" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="81">
+        <v>1980</v>
+      </c>
+      <c r="E5" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="81"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="81" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="78" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A6" s="214"/>
+      <c r="B6" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="81">
+        <v>2055</v>
+      </c>
+      <c r="E6" s="80" t="s">
+        <v>301</v>
+      </c>
+      <c r="F6" s="81"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="81"/>
+    </row>
+    <row r="7" spans="1:10" s="78" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A7" s="214"/>
+      <c r="B7" s="80" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="81">
+        <v>20</v>
+      </c>
+      <c r="E7" s="80" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="81"/>
+    </row>
+    <row r="8" spans="1:10" s="78" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A8" s="214"/>
+      <c r="B8" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="79" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="81">
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="80" t="s">
+        <v>302</v>
+      </c>
+      <c r="F8" s="81"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="81"/>
+    </row>
+    <row r="9" spans="1:10" s="89" customFormat="1" ht="139" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="83" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="85" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="84" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="87"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="84"/>
+      <c r="J9" s="87" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="95" customFormat="1" ht="90" x14ac:dyDescent="0.2">
+      <c r="A10" s="215" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="90" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="91" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="92" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="90" t="s">
+        <v>303</v>
+      </c>
+      <c r="F10" s="93"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="90"/>
+      <c r="J10" s="93" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="95" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="215"/>
+      <c r="B11" s="217" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="225" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="93"/>
+      <c r="E11" s="217" t="s">
+        <v>318</v>
+      </c>
+      <c r="F11" s="93"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="90"/>
+      <c r="J11" s="227"/>
+    </row>
+    <row r="12" spans="1:10" s="95" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="215"/>
+      <c r="B12" s="218"/>
+      <c r="C12" s="226"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="218"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="90"/>
+      <c r="J12" s="228"/>
+    </row>
+    <row r="13" spans="1:10" s="100" customFormat="1" ht="105" x14ac:dyDescent="0.2">
+      <c r="A13" s="216" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="96" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="97" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="98" t="s">
         <v>300</v>
       </c>
-      <c r="F4" s="84"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="84" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="86" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A5" s="249"/>
-      <c r="B5" s="88" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="89">
-        <v>1980</v>
-      </c>
-      <c r="E5" s="88" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="89"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="88"/>
-      <c r="J5" s="89" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="86" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A6" s="249"/>
-      <c r="B6" s="88" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="87" t="s">
+      <c r="E13" s="96" t="s">
+        <v>304</v>
+      </c>
+      <c r="F13" s="98"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="98"/>
+    </row>
+    <row r="14" spans="1:10" s="100" customFormat="1" ht="188" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="216"/>
+      <c r="B14" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="97" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="98" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="96" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="98"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="98" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="100" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A15" s="216"/>
+      <c r="B15" s="96" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="97" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="98">
+        <v>0.5</v>
+      </c>
+      <c r="E15" s="96" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="98"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="98"/>
+    </row>
+    <row r="16" spans="1:10" s="100" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A16" s="216"/>
+      <c r="B16" s="96" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="97" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="98">
+        <v>1</v>
+      </c>
+      <c r="E16" s="96" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="98"/>
+      <c r="G16" s="99"/>
+      <c r="H16" s="99"/>
+      <c r="I16" s="96"/>
+      <c r="J16" s="98" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="100" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A17" s="216"/>
+      <c r="B17" s="96" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="98" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="96" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="98"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="96"/>
+      <c r="J17" s="98"/>
+    </row>
+    <row r="18" spans="1:10" s="100" customFormat="1" ht="135" x14ac:dyDescent="0.2">
+      <c r="A18" s="216"/>
+      <c r="B18" s="96" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="97" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="98"/>
+      <c r="E18" s="96"/>
+      <c r="F18" s="98" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" s="99">
+        <v>0</v>
+      </c>
+      <c r="H18" s="99">
+        <v>1</v>
+      </c>
+      <c r="I18" s="96" t="s">
+        <v>305</v>
+      </c>
+      <c r="J18" s="98"/>
+    </row>
+    <row r="19" spans="1:10" s="100" customFormat="1" ht="105" x14ac:dyDescent="0.2">
+      <c r="A19" s="216"/>
+      <c r="B19" s="96" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="97" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="98"/>
+      <c r="E19" s="96"/>
+      <c r="F19" s="98">
+        <v>0.25</v>
+      </c>
+      <c r="G19" s="99">
+        <v>0</v>
+      </c>
+      <c r="H19" s="99">
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="96" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="98"/>
+    </row>
+    <row r="20" spans="1:10" s="100" customFormat="1" ht="115" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="216"/>
+      <c r="B20" s="96" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="101" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="98" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="96" t="s">
+        <v>293</v>
+      </c>
+      <c r="F20" s="98"/>
+      <c r="G20" s="99"/>
+      <c r="H20" s="99"/>
+      <c r="I20" s="96"/>
+      <c r="J20" s="102"/>
+    </row>
+    <row r="21" spans="1:10" s="43" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="216"/>
+      <c r="B21" s="180" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="202" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="102" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" s="199" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" s="70"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="199" t="s">
+        <v>167</v>
+      </c>
+      <c r="J21" s="205" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="43" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="216"/>
+      <c r="B22" s="181" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="203"/>
+      <c r="D22" s="182" t="s">
+        <v>166</v>
+      </c>
+      <c r="E22" s="200"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="200"/>
+      <c r="J22" s="206"/>
+    </row>
+    <row r="23" spans="1:10" s="43" customFormat="1" ht="180" x14ac:dyDescent="0.2">
+      <c r="A23" s="216"/>
+      <c r="B23" s="96" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="204"/>
+      <c r="D23" s="102" t="s">
+        <v>299</v>
+      </c>
+      <c r="E23" s="180" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="72"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="201"/>
+      <c r="J23" s="207"/>
+    </row>
+    <row r="24" spans="1:10" s="43" customFormat="1" ht="255" x14ac:dyDescent="0.2">
+      <c r="A24" s="179"/>
+      <c r="B24" s="96" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="97" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="98" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="96" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="67"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="66"/>
+      <c r="J24" s="98" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="110" customFormat="1" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="103" t="s">
+        <v>232</v>
+      </c>
+      <c r="B25" s="104" t="s">
+        <v>231</v>
+      </c>
+      <c r="C25" s="105" t="s">
+        <v>233</v>
+      </c>
+      <c r="D25" s="106">
+        <v>0</v>
+      </c>
+      <c r="E25" s="107" t="s">
+        <v>219</v>
+      </c>
+      <c r="F25" s="106"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="106"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="109"/>
+    </row>
+    <row r="26" spans="1:10" s="117" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="111" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="112" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="113" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="114" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="114"/>
+      <c r="G26" s="115"/>
+      <c r="H26" s="115"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="116" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" s="117" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+      <c r="A27" s="111"/>
+      <c r="B27" s="112" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="210" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="114"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="114">
+        <v>0.25</v>
+      </c>
+      <c r="G27" s="115">
+        <v>0</v>
+      </c>
+      <c r="H27" s="115">
+        <v>1</v>
+      </c>
+      <c r="I27" s="112" t="s">
+        <v>81</v>
+      </c>
+      <c r="J27" s="116" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" s="117" customFormat="1" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="111"/>
+      <c r="B28" s="112" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="211"/>
+      <c r="D28" s="114">
+        <v>50</v>
+      </c>
+      <c r="E28" s="112" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="114"/>
+      <c r="G28" s="115"/>
+      <c r="H28" s="115"/>
+      <c r="I28" s="112"/>
+      <c r="J28" s="114"/>
+    </row>
+    <row r="29" spans="1:10" s="117" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="111"/>
+      <c r="B29" s="112" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="212"/>
+      <c r="D29" s="114">
+        <v>0</v>
+      </c>
+      <c r="E29" s="112" t="s">
+        <v>84</v>
+      </c>
+      <c r="F29" s="114"/>
+      <c r="G29" s="115"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="112"/>
+      <c r="J29" s="114"/>
+    </row>
+    <row r="30" spans="1:10" s="117" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="111"/>
+      <c r="B30" s="112" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="118" t="s">
+        <v>294</v>
+      </c>
+      <c r="D30" s="114"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="114">
+        <v>5</v>
+      </c>
+      <c r="G30" s="115">
+        <v>1</v>
+      </c>
+      <c r="H30" s="115">
+        <v>12</v>
+      </c>
+      <c r="I30" s="112" t="s">
+        <v>306</v>
+      </c>
+      <c r="J30" s="114" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" s="117" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="111"/>
+      <c r="B31" s="112" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="118" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="114">
         <v>20</v>
       </c>
-      <c r="D6" s="89">
-        <v>2055</v>
-      </c>
-      <c r="E6" s="88" t="s">
-        <v>310</v>
-      </c>
-      <c r="F6" s="89"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="89"/>
-    </row>
-    <row r="7" spans="1:10" s="86" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="249"/>
-      <c r="B7" s="88" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="87" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="89">
-        <v>20</v>
-      </c>
-      <c r="E7" s="88" t="s">
-        <v>103</v>
-      </c>
-      <c r="F7" s="89"/>
-      <c r="G7" s="90"/>
-      <c r="H7" s="90"/>
-      <c r="I7" s="88"/>
-      <c r="J7" s="89"/>
-    </row>
-    <row r="8" spans="1:10" s="86" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A8" s="249"/>
-      <c r="B8" s="88" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="87" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="89">
-        <v>0.25</v>
-      </c>
-      <c r="E8" s="88" t="s">
-        <v>311</v>
-      </c>
-      <c r="F8" s="89"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="89"/>
-    </row>
-    <row r="9" spans="1:10" s="97" customFormat="1" ht="139" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="91" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="92" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="94" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="92" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="95"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="92"/>
-      <c r="J9" s="95" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="103" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A10" s="250" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="98" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="99" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="100" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="98" t="s">
-        <v>312</v>
-      </c>
-      <c r="F10" s="101"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="102"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="101" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="103" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="250"/>
-      <c r="B11" s="241" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="239" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="101"/>
-      <c r="E11" s="241" t="s">
-        <v>327</v>
-      </c>
-      <c r="F11" s="101"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="102"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="243"/>
-    </row>
-    <row r="12" spans="1:10" s="103" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="250"/>
-      <c r="B12" s="242"/>
-      <c r="C12" s="240"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="242"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="102"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="244"/>
-    </row>
-    <row r="13" spans="1:10" s="108" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A13" s="251" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="104" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="105" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="106" t="s">
-        <v>309</v>
-      </c>
-      <c r="E13" s="104" t="s">
-        <v>313</v>
-      </c>
-      <c r="F13" s="106"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="106"/>
-    </row>
-    <row r="14" spans="1:10" s="108" customFormat="1" ht="188" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="251"/>
-      <c r="B14" s="104" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="105" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="106" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="104" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="106"/>
-      <c r="G14" s="107"/>
-      <c r="H14" s="107"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="106" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="108" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="251"/>
-      <c r="B15" s="104" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="105" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="106">
-        <v>0.5</v>
-      </c>
-      <c r="E15" s="104" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="106"/>
-      <c r="G15" s="107"/>
-      <c r="H15" s="107"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="106"/>
-    </row>
-    <row r="16" spans="1:10" s="108" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A16" s="251"/>
-      <c r="B16" s="104" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="105" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="106">
+      <c r="E31" s="112" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="114"/>
+      <c r="G31" s="115"/>
+      <c r="H31" s="115"/>
+      <c r="I31" s="112"/>
+      <c r="J31" s="114"/>
+    </row>
+    <row r="32" spans="1:10" s="117" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A32" s="111"/>
+      <c r="B32" s="112" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="119" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="114" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" s="112" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="114" t="s">
+        <v>74</v>
+      </c>
+      <c r="G32" s="115">
+        <v>0</v>
+      </c>
+      <c r="H32" s="115">
         <v>1</v>
       </c>
-      <c r="E16" s="104" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="106"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="107"/>
-      <c r="I16" s="104"/>
-      <c r="J16" s="106" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" s="108" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="251"/>
-      <c r="B17" s="104" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="105" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="106" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="104" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="106"/>
-      <c r="G17" s="107"/>
-      <c r="H17" s="107"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="106"/>
-    </row>
-    <row r="18" spans="1:10" s="108" customFormat="1" ht="135" x14ac:dyDescent="0.2">
-      <c r="A18" s="251"/>
-      <c r="B18" s="104" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="105" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="106"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="106" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18" s="107">
-        <v>0</v>
-      </c>
-      <c r="H18" s="107">
-        <v>1</v>
-      </c>
-      <c r="I18" s="104" t="s">
-        <v>314</v>
-      </c>
-      <c r="J18" s="106"/>
-    </row>
-    <row r="19" spans="1:10" s="108" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A19" s="251"/>
-      <c r="B19" s="104" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="105" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="106"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="106">
-        <v>0.25</v>
-      </c>
-      <c r="G19" s="107">
-        <v>0</v>
-      </c>
-      <c r="H19" s="107">
-        <v>0.5</v>
-      </c>
-      <c r="I19" s="104" t="s">
-        <v>60</v>
-      </c>
-      <c r="J19" s="106"/>
-    </row>
-    <row r="20" spans="1:10" s="108" customFormat="1" ht="115" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="251"/>
-      <c r="B20" s="104" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="109" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="106" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="104" t="s">
-        <v>301</v>
-      </c>
-      <c r="F20" s="106"/>
-      <c r="G20" s="107"/>
-      <c r="H20" s="107"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="110"/>
-    </row>
-    <row r="21" spans="1:10" s="43" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="251"/>
-      <c r="B21" s="191" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="255" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="110" t="s">
-        <v>165</v>
-      </c>
-      <c r="E21" s="252" t="s">
-        <v>99</v>
-      </c>
-      <c r="F21" s="72"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="252" t="s">
-        <v>167</v>
-      </c>
-      <c r="J21" s="258" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" s="43" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="251"/>
-      <c r="B22" s="192" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="256"/>
-      <c r="D22" s="193" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22" s="253"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="253"/>
-      <c r="J22" s="259"/>
-    </row>
-    <row r="23" spans="1:10" s="43" customFormat="1" ht="180" x14ac:dyDescent="0.2">
-      <c r="A23" s="251"/>
-      <c r="B23" s="104" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="257"/>
-      <c r="D23" s="110" t="s">
-        <v>308</v>
-      </c>
-      <c r="E23" s="191" t="s">
-        <v>100</v>
-      </c>
-      <c r="F23" s="74"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="254"/>
-      <c r="J23" s="260"/>
-    </row>
-    <row r="24" spans="1:10" s="43" customFormat="1" ht="255" x14ac:dyDescent="0.2">
-      <c r="A24" s="190"/>
-      <c r="B24" s="104" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="105" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="104" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24" s="69"/>
-      <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="106" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" s="118" customFormat="1" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="111" t="s">
-        <v>232</v>
-      </c>
-      <c r="B25" s="112" t="s">
-        <v>231</v>
-      </c>
-      <c r="C25" s="113" t="s">
-        <v>233</v>
-      </c>
-      <c r="D25" s="114">
-        <v>0</v>
-      </c>
-      <c r="E25" s="115" t="s">
+      <c r="I32" s="112" t="s">
+        <v>73</v>
+      </c>
+      <c r="J32" s="114"/>
+    </row>
+    <row r="33" spans="1:10" s="124" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="213" t="s">
+        <v>239</v>
+      </c>
+      <c r="B33" s="120" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="121" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" s="122" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="120" t="s">
         <v>219</v>
       </c>
-      <c r="F25" s="114"/>
-      <c r="G25" s="114"/>
-      <c r="H25" s="114"/>
-      <c r="I25" s="116"/>
-      <c r="J25" s="117"/>
-    </row>
-    <row r="26" spans="1:10" s="125" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="119" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" s="120" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="121" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="122" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="120"/>
-      <c r="F26" s="122"/>
-      <c r="G26" s="123"/>
-      <c r="H26" s="123"/>
-      <c r="I26" s="120"/>
-      <c r="J26" s="124" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" s="125" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A27" s="119"/>
-      <c r="B27" s="120" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="263" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="122"/>
-      <c r="E27" s="120"/>
-      <c r="F27" s="122">
-        <v>0.25</v>
-      </c>
-      <c r="G27" s="123">
-        <v>0</v>
-      </c>
-      <c r="H27" s="123">
-        <v>1</v>
-      </c>
-      <c r="I27" s="120" t="s">
-        <v>81</v>
-      </c>
-      <c r="J27" s="124" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" s="125" customFormat="1" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="119"/>
-      <c r="B28" s="120" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="264"/>
-      <c r="D28" s="122">
-        <v>50</v>
-      </c>
-      <c r="E28" s="120" t="s">
-        <v>84</v>
-      </c>
-      <c r="F28" s="122"/>
-      <c r="G28" s="123"/>
-      <c r="H28" s="123"/>
-      <c r="I28" s="120"/>
-      <c r="J28" s="122"/>
-    </row>
-    <row r="29" spans="1:10" s="125" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="119"/>
-      <c r="B29" s="120" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="265"/>
-      <c r="D29" s="122">
-        <v>0</v>
-      </c>
-      <c r="E29" s="120" t="s">
-        <v>84</v>
-      </c>
-      <c r="F29" s="122"/>
-      <c r="G29" s="123"/>
-      <c r="H29" s="123"/>
-      <c r="I29" s="120"/>
-      <c r="J29" s="122"/>
-    </row>
-    <row r="30" spans="1:10" s="125" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="119"/>
-      <c r="B30" s="120" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="126" t="s">
-        <v>302</v>
-      </c>
-      <c r="D30" s="122"/>
-      <c r="E30" s="120"/>
-      <c r="F30" s="122">
-        <v>5</v>
-      </c>
-      <c r="G30" s="123">
-        <v>1</v>
-      </c>
-      <c r="H30" s="123">
-        <v>12</v>
-      </c>
-      <c r="I30" s="120" t="s">
-        <v>315</v>
-      </c>
-      <c r="J30" s="122" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" s="125" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="119"/>
-      <c r="B31" s="120" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" s="126" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" s="122">
-        <v>20</v>
-      </c>
-      <c r="E31" s="120" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31" s="122"/>
-      <c r="G31" s="123"/>
-      <c r="H31" s="123"/>
-      <c r="I31" s="120"/>
-      <c r="J31" s="122"/>
-    </row>
-    <row r="32" spans="1:10" s="125" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A32" s="119"/>
-      <c r="B32" s="120" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" s="127" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" s="122" t="s">
-        <v>71</v>
-      </c>
-      <c r="E32" s="120" t="s">
-        <v>72</v>
-      </c>
-      <c r="F32" s="122" t="s">
-        <v>74</v>
-      </c>
-      <c r="G32" s="123">
-        <v>0</v>
-      </c>
-      <c r="H32" s="123">
-        <v>1</v>
-      </c>
-      <c r="I32" s="120" t="s">
-        <v>73</v>
-      </c>
-      <c r="J32" s="122"/>
-    </row>
-    <row r="33" spans="1:10" s="132" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="248" t="s">
-        <v>239</v>
-      </c>
-      <c r="B33" s="128" t="s">
-        <v>104</v>
-      </c>
-      <c r="C33" s="129" t="s">
-        <v>105</v>
-      </c>
-      <c r="D33" s="130" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" s="128" t="s">
-        <v>219</v>
-      </c>
-      <c r="F33" s="130"/>
-      <c r="G33" s="131"/>
-      <c r="H33" s="131"/>
-      <c r="I33" s="128"/>
-      <c r="J33" s="261" t="s">
+      <c r="F33" s="122"/>
+      <c r="G33" s="123"/>
+      <c r="H33" s="123"/>
+      <c r="I33" s="120"/>
+      <c r="J33" s="208" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="132" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A34" s="248"/>
-      <c r="B34" s="128" t="s">
+    <row r="34" spans="1:10" s="124" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="A34" s="213"/>
+      <c r="B34" s="120" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="129" t="s">
+      <c r="C34" s="121" t="s">
         <v>108</v>
       </c>
-      <c r="D34" s="130" t="s">
+      <c r="D34" s="122" t="s">
         <v>107</v>
       </c>
-      <c r="E34" s="128" t="s">
-        <v>316</v>
-      </c>
-      <c r="F34" s="130"/>
-      <c r="G34" s="131"/>
-      <c r="H34" s="131"/>
-      <c r="I34" s="128"/>
-      <c r="J34" s="262"/>
+      <c r="E34" s="120" t="s">
+        <v>307</v>
+      </c>
+      <c r="F34" s="122"/>
+      <c r="G34" s="123"/>
+      <c r="H34" s="123"/>
+      <c r="I34" s="120"/>
+      <c r="J34" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="J21:J23"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B11:B12"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="C2:C3"/>
@@ -4559,6 +4438,17 @@
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="J21:J23"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="C27:C29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -4571,2577 +4461,2577 @@
   <dimension ref="A1:H141"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="7" width="10.83203125" style="64"/>
-    <col min="8" max="8" width="61.83203125" style="64" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="64"/>
+    <col min="1" max="7" width="10.83203125" style="63"/>
+    <col min="8" max="8" width="61.83203125" style="63" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="63"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="140" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="141" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="152" t="s">
+      <c r="C1" s="142" t="s">
         <v>137</v>
       </c>
-      <c r="D1" s="153" t="s">
+      <c r="D1" s="143" t="s">
         <v>136</v>
       </c>
-      <c r="E1" s="154" t="s">
+      <c r="E1" s="144" t="s">
         <v>135</v>
       </c>
-      <c r="H1" s="155" t="s">
+      <c r="H1" s="145" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="133" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="156" t="s">
+    <row r="2" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="125" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="146" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="157" t="s">
+      <c r="C2" s="147" t="s">
         <v>124</v>
       </c>
-      <c r="D2" s="134" t="s">
+      <c r="D2" s="126" t="s">
         <v>125</v>
       </c>
-      <c r="E2" s="158">
+      <c r="E2" s="148">
         <v>0.12</v>
       </c>
-      <c r="H2" s="266" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B3" s="160" t="s">
+      <c r="H2" s="232" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="161" t="s">
+      <c r="C3" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D3" s="137" t="s">
+      <c r="D3" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="162">
+      <c r="E3" s="152">
         <v>0.88</v>
       </c>
-      <c r="H3" s="266"/>
-    </row>
-    <row r="4" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="160" t="s">
+      <c r="H3" s="232"/>
+    </row>
+    <row r="4" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="161" t="s">
+      <c r="C4" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E4" s="162">
-        <v>0</v>
-      </c>
-      <c r="H4" s="266"/>
-    </row>
-    <row r="5" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" s="160" t="s">
+      <c r="E4" s="152">
+        <v>0</v>
+      </c>
+      <c r="H4" s="232"/>
+    </row>
+    <row r="5" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="161" t="s">
+      <c r="C5" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="137" t="s">
+      <c r="D5" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="158">
+      <c r="E5" s="148">
         <v>0.12</v>
       </c>
-      <c r="H5" s="266"/>
-    </row>
-    <row r="6" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" s="160" t="s">
+      <c r="H5" s="232"/>
+    </row>
+    <row r="6" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="161" t="s">
+      <c r="C6" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="137" t="s">
+      <c r="D6" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="162">
+      <c r="E6" s="152">
         <v>0.88</v>
       </c>
-      <c r="H6" s="266"/>
-    </row>
-    <row r="7" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B7" s="160" t="s">
+      <c r="H6" s="232"/>
+    </row>
+    <row r="7" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="161" t="s">
+      <c r="C7" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D7" s="137" t="s">
+      <c r="D7" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E7" s="162">
-        <v>0</v>
-      </c>
-      <c r="H7" s="266"/>
-    </row>
-    <row r="8" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B8" s="160" t="s">
+      <c r="E7" s="152">
+        <v>0</v>
+      </c>
+      <c r="H7" s="232"/>
+    </row>
+    <row r="8" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="161" t="s">
+      <c r="C8" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D8" s="137" t="s">
+      <c r="D8" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E8" s="158">
+      <c r="E8" s="148">
         <v>0.12</v>
       </c>
-      <c r="H8" s="266"/>
-    </row>
-    <row r="9" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" s="160" t="s">
+      <c r="H8" s="232"/>
+    </row>
+    <row r="9" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="161" t="s">
+      <c r="C9" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="137" t="s">
+      <c r="D9" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="162">
+      <c r="E9" s="152">
         <v>0.88</v>
       </c>
-      <c r="H9" s="266"/>
-    </row>
-    <row r="10" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B10" s="160" t="s">
+      <c r="H9" s="232"/>
+    </row>
+    <row r="10" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="161" t="s">
+      <c r="C10" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="137" t="s">
+      <c r="D10" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E10" s="162">
-        <v>0</v>
-      </c>
-      <c r="H10" s="266"/>
-    </row>
-    <row r="11" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" s="160" t="s">
+      <c r="E10" s="152">
+        <v>0</v>
+      </c>
+      <c r="H10" s="232"/>
+    </row>
+    <row r="11" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C11" s="161" t="s">
+      <c r="C11" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="137" t="s">
+      <c r="D11" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E11" s="158">
+      <c r="E11" s="148">
         <v>0.12</v>
       </c>
-      <c r="H11" s="266"/>
-    </row>
-    <row r="12" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" s="160" t="s">
+      <c r="H11" s="232"/>
+    </row>
+    <row r="12" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C12" s="161" t="s">
+      <c r="C12" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D12" s="137" t="s">
+      <c r="D12" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E12" s="162">
+      <c r="E12" s="152">
         <v>0.88</v>
       </c>
-      <c r="H12" s="266"/>
-    </row>
-    <row r="13" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="160" t="s">
+      <c r="H12" s="232"/>
+    </row>
+    <row r="13" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C13" s="161" t="s">
+      <c r="C13" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D13" s="137" t="s">
+      <c r="D13" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="162">
-        <v>0</v>
-      </c>
-      <c r="H13" s="266"/>
-    </row>
-    <row r="14" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B14" s="160" t="s">
+      <c r="E13" s="152">
+        <v>0</v>
+      </c>
+      <c r="H13" s="232"/>
+    </row>
+    <row r="14" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="161" t="s">
+      <c r="C14" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="137" t="s">
+      <c r="D14" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E14" s="158">
+      <c r="E14" s="148">
         <v>0.12</v>
       </c>
-      <c r="H14" s="266"/>
-    </row>
-    <row r="15" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B15" s="160" t="s">
+      <c r="H14" s="232"/>
+    </row>
+    <row r="15" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="161" t="s">
+      <c r="C15" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D15" s="137" t="s">
+      <c r="D15" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="162">
+      <c r="E15" s="152">
         <v>0.88</v>
       </c>
-      <c r="H15" s="266"/>
-    </row>
-    <row r="16" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" s="160" t="s">
+      <c r="H15" s="232"/>
+    </row>
+    <row r="16" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="161" t="s">
+      <c r="C16" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D16" s="137" t="s">
+      <c r="D16" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E16" s="162">
-        <v>0</v>
-      </c>
-      <c r="H16" s="266"/>
-    </row>
-    <row r="17" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B17" s="160" t="s">
+      <c r="E16" s="152">
+        <v>0</v>
+      </c>
+      <c r="H16" s="232"/>
+    </row>
+    <row r="17" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="161" t="s">
+      <c r="C17" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="137" t="s">
+      <c r="D17" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="158">
+      <c r="E17" s="148">
         <v>0.12</v>
       </c>
-      <c r="H17" s="266"/>
-    </row>
-    <row r="18" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B18" s="160" t="s">
+      <c r="H17" s="232"/>
+    </row>
+    <row r="18" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="161" t="s">
+      <c r="C18" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D18" s="137" t="s">
+      <c r="D18" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E18" s="162">
+      <c r="E18" s="152">
         <v>0.88</v>
       </c>
-      <c r="H18" s="266"/>
-    </row>
-    <row r="19" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B19" s="160" t="s">
+      <c r="H18" s="232"/>
+    </row>
+    <row r="19" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="150" t="s">
         <v>116</v>
       </c>
-      <c r="C19" s="161" t="s">
+      <c r="C19" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D19" s="137" t="s">
+      <c r="D19" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E19" s="162">
-        <v>0</v>
-      </c>
-      <c r="H19" s="266"/>
-    </row>
-    <row r="20" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B20" s="160" t="s">
+      <c r="E19" s="152">
+        <v>0</v>
+      </c>
+      <c r="H19" s="232"/>
+    </row>
+    <row r="20" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="161" t="s">
+      <c r="C20" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="137" t="s">
+      <c r="D20" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E20" s="158">
+      <c r="E20" s="148">
         <v>0.12</v>
       </c>
-      <c r="H20" s="266"/>
-    </row>
-    <row r="21" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B21" s="160" t="s">
+      <c r="H20" s="232"/>
+    </row>
+    <row r="21" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="161" t="s">
+      <c r="C21" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D21" s="137" t="s">
+      <c r="D21" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="162">
+      <c r="E21" s="152">
         <v>0.88</v>
       </c>
-      <c r="H21" s="266"/>
-    </row>
-    <row r="22" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B22" s="160" t="s">
+      <c r="H21" s="232"/>
+    </row>
+    <row r="22" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="161" t="s">
+      <c r="C22" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="137" t="s">
+      <c r="D22" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E22" s="162">
-        <v>0</v>
-      </c>
-      <c r="H22" s="266"/>
-    </row>
-    <row r="23" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B23" s="160" t="s">
+      <c r="E22" s="152">
+        <v>0</v>
+      </c>
+      <c r="H22" s="232"/>
+    </row>
+    <row r="23" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="161" t="s">
+      <c r="C23" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D23" s="137" t="s">
+      <c r="D23" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="158">
+      <c r="E23" s="148">
         <v>0.12</v>
       </c>
-      <c r="H23" s="266"/>
-    </row>
-    <row r="24" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B24" s="160" t="s">
+      <c r="H23" s="232"/>
+    </row>
+    <row r="24" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C24" s="161" t="s">
+      <c r="C24" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D24" s="137" t="s">
+      <c r="D24" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E24" s="162">
+      <c r="E24" s="152">
         <v>0.88</v>
       </c>
-      <c r="H24" s="266"/>
-    </row>
-    <row r="25" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B25" s="160" t="s">
+      <c r="H24" s="232"/>
+    </row>
+    <row r="25" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C25" s="161" t="s">
+      <c r="C25" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D25" s="137" t="s">
+      <c r="D25" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="162">
-        <v>0</v>
-      </c>
-      <c r="H25" s="266"/>
-    </row>
-    <row r="26" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B26" s="160" t="s">
+      <c r="E25" s="152">
+        <v>0</v>
+      </c>
+      <c r="H25" s="232"/>
+    </row>
+    <row r="26" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="161" t="s">
+      <c r="C26" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="137" t="s">
+      <c r="D26" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E26" s="158">
+      <c r="E26" s="148">
         <v>0.12</v>
       </c>
-      <c r="H26" s="266"/>
-    </row>
-    <row r="27" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B27" s="160" t="s">
+      <c r="H26" s="232"/>
+    </row>
+    <row r="27" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C27" s="161" t="s">
+      <c r="C27" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D27" s="137" t="s">
+      <c r="D27" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="162">
+      <c r="E27" s="152">
         <v>0.88</v>
       </c>
-      <c r="H27" s="266"/>
-    </row>
-    <row r="28" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B28" s="160" t="s">
+      <c r="H27" s="232"/>
+    </row>
+    <row r="28" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C28" s="161" t="s">
+      <c r="C28" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="137" t="s">
+      <c r="D28" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E28" s="162">
-        <v>0</v>
-      </c>
-      <c r="H28" s="266"/>
-    </row>
-    <row r="29" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B29" s="160" t="s">
+      <c r="E28" s="152">
+        <v>0</v>
+      </c>
+      <c r="H28" s="232"/>
+    </row>
+    <row r="29" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C29" s="161" t="s">
+      <c r="C29" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="137" t="s">
+      <c r="D29" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E29" s="158">
+      <c r="E29" s="148">
         <v>0.12</v>
       </c>
-      <c r="H29" s="266"/>
-    </row>
-    <row r="30" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B30" s="160" t="s">
+      <c r="H29" s="232"/>
+    </row>
+    <row r="30" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C30" s="161" t="s">
+      <c r="C30" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D30" s="137" t="s">
+      <c r="D30" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="162">
+      <c r="E30" s="152">
         <v>0.88</v>
       </c>
-      <c r="H30" s="266"/>
-    </row>
-    <row r="31" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B31" s="160" t="s">
+      <c r="H30" s="232"/>
+    </row>
+    <row r="31" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C31" s="161" t="s">
+      <c r="C31" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D31" s="137" t="s">
+      <c r="D31" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E31" s="162">
-        <v>0</v>
-      </c>
-      <c r="H31" s="266"/>
-    </row>
-    <row r="32" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B32" s="160" t="s">
+      <c r="E31" s="152">
+        <v>0</v>
+      </c>
+      <c r="H31" s="232"/>
+    </row>
+    <row r="32" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="161" t="s">
+      <c r="C32" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D32" s="137" t="s">
+      <c r="D32" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E32" s="158">
+      <c r="E32" s="148">
         <v>0.12</v>
       </c>
-      <c r="H32" s="266"/>
-    </row>
-    <row r="33" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B33" s="160" t="s">
+      <c r="H32" s="232"/>
+    </row>
+    <row r="33" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C33" s="161" t="s">
+      <c r="C33" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D33" s="137" t="s">
+      <c r="D33" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E33" s="162">
+      <c r="E33" s="152">
         <v>0.88</v>
       </c>
-      <c r="H33" s="266"/>
-    </row>
-    <row r="34" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B34" s="160" t="s">
+      <c r="H33" s="232"/>
+    </row>
+    <row r="34" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C34" s="161" t="s">
+      <c r="C34" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D34" s="137" t="s">
+      <c r="D34" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="162">
-        <v>0</v>
-      </c>
-      <c r="H34" s="266"/>
-    </row>
-    <row r="35" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B35" s="160" t="s">
+      <c r="E34" s="152">
+        <v>0</v>
+      </c>
+      <c r="H34" s="232"/>
+    </row>
+    <row r="35" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C35" s="161" t="s">
+      <c r="C35" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="137" t="s">
+      <c r="D35" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="158">
+      <c r="E35" s="148">
         <v>0.12</v>
       </c>
-      <c r="H35" s="266"/>
-    </row>
-    <row r="36" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B36" s="160" t="s">
+      <c r="H35" s="232"/>
+    </row>
+    <row r="36" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C36" s="161" t="s">
+      <c r="C36" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D36" s="137" t="s">
+      <c r="D36" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E36" s="162">
+      <c r="E36" s="152">
         <v>0.88</v>
       </c>
-      <c r="H36" s="266"/>
-    </row>
-    <row r="37" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B37" s="160" t="s">
+      <c r="H36" s="232"/>
+    </row>
+    <row r="37" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="C37" s="161" t="s">
+      <c r="C37" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D37" s="137" t="s">
+      <c r="D37" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E37" s="162">
-        <v>0</v>
-      </c>
-      <c r="H37" s="266"/>
-    </row>
-    <row r="38" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B38" s="160" t="s">
+      <c r="E37" s="152">
+        <v>0</v>
+      </c>
+      <c r="H37" s="232"/>
+    </row>
+    <row r="38" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C38" s="161" t="s">
+      <c r="C38" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D38" s="137" t="s">
+      <c r="D38" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E38" s="162">
+      <c r="E38" s="152">
         <v>0.94</v>
       </c>
-      <c r="H38" s="266"/>
-    </row>
-    <row r="39" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B39" s="160" t="s">
+      <c r="H38" s="232"/>
+    </row>
+    <row r="39" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="161" t="s">
+      <c r="C39" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D39" s="137" t="s">
+      <c r="D39" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E39" s="162">
+      <c r="E39" s="152">
         <v>0.06</v>
       </c>
-      <c r="H39" s="266"/>
-    </row>
-    <row r="40" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B40" s="160" t="s">
+      <c r="H39" s="232"/>
+    </row>
+    <row r="40" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="161" t="s">
+      <c r="C40" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D40" s="137" t="s">
+      <c r="D40" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E40" s="162">
-        <v>0</v>
-      </c>
-      <c r="H40" s="266"/>
-    </row>
-    <row r="41" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B41" s="160" t="s">
+      <c r="E40" s="152">
+        <v>0</v>
+      </c>
+      <c r="H40" s="232"/>
+    </row>
+    <row r="41" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B41" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C41" s="161" t="s">
+      <c r="C41" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D41" s="137" t="s">
+      <c r="D41" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E41" s="162">
+      <c r="E41" s="152">
         <v>0.94</v>
       </c>
-      <c r="H41" s="266"/>
-    </row>
-    <row r="42" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B42" s="160" t="s">
+      <c r="H41" s="232"/>
+    </row>
+    <row r="42" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C42" s="161" t="s">
+      <c r="C42" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D42" s="137" t="s">
+      <c r="D42" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E42" s="162">
+      <c r="E42" s="152">
         <v>0.06</v>
       </c>
-      <c r="H42" s="266"/>
-    </row>
-    <row r="43" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B43" s="160" t="s">
+      <c r="H42" s="232"/>
+    </row>
+    <row r="43" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C43" s="161" t="s">
+      <c r="C43" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D43" s="137" t="s">
+      <c r="D43" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E43" s="162">
-        <v>0</v>
-      </c>
-      <c r="H43" s="266"/>
-    </row>
-    <row r="44" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B44" s="160" t="s">
+      <c r="E43" s="152">
+        <v>0</v>
+      </c>
+      <c r="H43" s="232"/>
+    </row>
+    <row r="44" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="161" t="s">
+      <c r="C44" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D44" s="137" t="s">
+      <c r="D44" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E44" s="162">
+      <c r="E44" s="152">
         <v>0.94</v>
       </c>
-      <c r="H44" s="266"/>
-    </row>
-    <row r="45" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B45" s="160" t="s">
+      <c r="H44" s="232"/>
+    </row>
+    <row r="45" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="161" t="s">
+      <c r="C45" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D45" s="137" t="s">
+      <c r="D45" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E45" s="162">
+      <c r="E45" s="152">
         <v>0.06</v>
       </c>
-      <c r="H45" s="266"/>
-    </row>
-    <row r="46" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B46" s="160" t="s">
+      <c r="H45" s="232"/>
+    </row>
+    <row r="46" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C46" s="161" t="s">
+      <c r="C46" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D46" s="137" t="s">
+      <c r="D46" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E46" s="162">
-        <v>0</v>
-      </c>
-      <c r="H46" s="266"/>
-    </row>
-    <row r="47" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B47" s="160" t="s">
+      <c r="E46" s="152">
+        <v>0</v>
+      </c>
+      <c r="H46" s="232"/>
+    </row>
+    <row r="47" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C47" s="161" t="s">
+      <c r="C47" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D47" s="137" t="s">
+      <c r="D47" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E47" s="162">
+      <c r="E47" s="152">
         <v>0.94</v>
       </c>
-      <c r="H47" s="266"/>
-    </row>
-    <row r="48" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B48" s="160" t="s">
+      <c r="H47" s="232"/>
+    </row>
+    <row r="48" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C48" s="161" t="s">
+      <c r="C48" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D48" s="137" t="s">
+      <c r="D48" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E48" s="162">
+      <c r="E48" s="152">
         <v>0.06</v>
       </c>
-      <c r="H48" s="266"/>
-    </row>
-    <row r="49" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B49" s="160" t="s">
+      <c r="H48" s="232"/>
+    </row>
+    <row r="49" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C49" s="161" t="s">
+      <c r="C49" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="137" t="s">
+      <c r="D49" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E49" s="162">
-        <v>0</v>
-      </c>
-      <c r="H49" s="266"/>
-    </row>
-    <row r="50" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50" s="160" t="s">
+      <c r="E49" s="152">
+        <v>0</v>
+      </c>
+      <c r="H49" s="232"/>
+    </row>
+    <row r="50" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C50" s="161" t="s">
+      <c r="C50" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D50" s="137" t="s">
+      <c r="D50" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E50" s="162">
+      <c r="E50" s="152">
         <v>0.94</v>
       </c>
-      <c r="H50" s="266"/>
-    </row>
-    <row r="51" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B51" s="160" t="s">
+      <c r="H50" s="232"/>
+    </row>
+    <row r="51" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C51" s="161" t="s">
+      <c r="C51" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D51" s="137" t="s">
+      <c r="D51" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E51" s="162">
+      <c r="E51" s="152">
         <v>0.06</v>
       </c>
-      <c r="H51" s="266"/>
-    </row>
-    <row r="52" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B52" s="160" t="s">
+      <c r="H51" s="232"/>
+    </row>
+    <row r="52" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C52" s="161" t="s">
+      <c r="C52" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D52" s="137" t="s">
+      <c r="D52" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E52" s="162">
-        <v>0</v>
-      </c>
-      <c r="H52" s="266"/>
-    </row>
-    <row r="53" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B53" s="160" t="s">
+      <c r="E52" s="152">
+        <v>0</v>
+      </c>
+      <c r="H52" s="232"/>
+    </row>
+    <row r="53" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C53" s="161" t="s">
+      <c r="C53" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D53" s="137" t="s">
+      <c r="D53" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E53" s="162">
+      <c r="E53" s="152">
         <v>0.94</v>
       </c>
-      <c r="H53" s="266"/>
-    </row>
-    <row r="54" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B54" s="160" t="s">
+      <c r="H53" s="232"/>
+    </row>
+    <row r="54" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B54" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C54" s="161" t="s">
+      <c r="C54" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D54" s="137" t="s">
+      <c r="D54" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E54" s="162">
+      <c r="E54" s="152">
         <v>0.06</v>
       </c>
-      <c r="H54" s="266"/>
-    </row>
-    <row r="55" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B55" s="160" t="s">
+      <c r="H54" s="232"/>
+    </row>
+    <row r="55" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" s="150" t="s">
         <v>114</v>
       </c>
-      <c r="C55" s="161" t="s">
+      <c r="C55" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D55" s="137" t="s">
+      <c r="D55" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E55" s="162">
-        <v>0</v>
-      </c>
-      <c r="H55" s="266"/>
-    </row>
-    <row r="56" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B56" s="160" t="s">
+      <c r="E55" s="152">
+        <v>0</v>
+      </c>
+      <c r="H55" s="232"/>
+    </row>
+    <row r="56" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C56" s="161" t="s">
+      <c r="C56" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D56" s="137" t="s">
+      <c r="D56" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E56" s="162">
+      <c r="E56" s="152">
         <v>0.94</v>
       </c>
-      <c r="H56" s="266"/>
-    </row>
-    <row r="57" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B57" s="160" t="s">
+      <c r="H56" s="232"/>
+    </row>
+    <row r="57" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="161" t="s">
+      <c r="C57" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D57" s="137" t="s">
+      <c r="D57" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E57" s="162">
+      <c r="E57" s="152">
         <v>0.06</v>
       </c>
-      <c r="H57" s="266"/>
-    </row>
-    <row r="58" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B58" s="160" t="s">
+      <c r="H57" s="232"/>
+    </row>
+    <row r="58" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C58" s="161" t="s">
+      <c r="C58" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D58" s="137" t="s">
+      <c r="D58" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E58" s="162">
-        <v>0</v>
-      </c>
-      <c r="H58" s="266"/>
-    </row>
-    <row r="59" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" s="160" t="s">
+      <c r="E58" s="152">
+        <v>0</v>
+      </c>
+      <c r="H58" s="232"/>
+    </row>
+    <row r="59" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C59" s="161" t="s">
+      <c r="C59" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D59" s="137" t="s">
+      <c r="D59" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E59" s="162">
+      <c r="E59" s="152">
         <v>0.94</v>
       </c>
-      <c r="H59" s="266"/>
-    </row>
-    <row r="60" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B60" s="160" t="s">
+      <c r="H59" s="232"/>
+    </row>
+    <row r="60" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C60" s="161" t="s">
+      <c r="C60" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D60" s="137" t="s">
+      <c r="D60" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E60" s="162">
+      <c r="E60" s="152">
         <v>0.06</v>
       </c>
-      <c r="H60" s="266"/>
-    </row>
-    <row r="61" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B61" s="160" t="s">
+      <c r="H60" s="232"/>
+    </row>
+    <row r="61" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B61" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C61" s="161" t="s">
+      <c r="C61" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D61" s="137" t="s">
+      <c r="D61" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E61" s="162">
-        <v>0</v>
-      </c>
-      <c r="H61" s="266"/>
-    </row>
-    <row r="62" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B62" s="160" t="s">
+      <c r="E61" s="152">
+        <v>0</v>
+      </c>
+      <c r="H61" s="232"/>
+    </row>
+    <row r="62" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B62" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C62" s="161" t="s">
+      <c r="C62" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D62" s="137" t="s">
+      <c r="D62" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E62" s="162">
+      <c r="E62" s="152">
         <v>0.94</v>
       </c>
-      <c r="H62" s="266"/>
-    </row>
-    <row r="63" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B63" s="160" t="s">
+      <c r="H62" s="232"/>
+    </row>
+    <row r="63" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C63" s="161" t="s">
+      <c r="C63" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D63" s="137" t="s">
+      <c r="D63" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E63" s="162">
+      <c r="E63" s="152">
         <v>0.06</v>
       </c>
-      <c r="H63" s="266"/>
-    </row>
-    <row r="64" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B64" s="160" t="s">
+      <c r="H63" s="232"/>
+    </row>
+    <row r="64" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C64" s="161" t="s">
+      <c r="C64" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D64" s="137" t="s">
+      <c r="D64" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E64" s="162">
-        <v>0</v>
-      </c>
-      <c r="H64" s="266"/>
-    </row>
-    <row r="65" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B65" s="160" t="s">
+      <c r="E64" s="152">
+        <v>0</v>
+      </c>
+      <c r="H64" s="232"/>
+    </row>
+    <row r="65" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C65" s="161" t="s">
+      <c r="C65" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D65" s="137" t="s">
+      <c r="D65" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E65" s="162">
+      <c r="E65" s="152">
         <v>0.94</v>
       </c>
-      <c r="H65" s="266"/>
-    </row>
-    <row r="66" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B66" s="160" t="s">
+      <c r="H65" s="232"/>
+    </row>
+    <row r="66" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C66" s="161" t="s">
+      <c r="C66" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D66" s="137" t="s">
+      <c r="D66" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E66" s="162">
+      <c r="E66" s="152">
         <v>0.06</v>
       </c>
-      <c r="H66" s="266"/>
-    </row>
-    <row r="67" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B67" s="160" t="s">
+      <c r="H66" s="232"/>
+    </row>
+    <row r="67" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B67" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C67" s="161" t="s">
+      <c r="C67" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D67" s="137" t="s">
+      <c r="D67" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E67" s="162">
-        <v>0</v>
-      </c>
-      <c r="H67" s="266"/>
-    </row>
-    <row r="68" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B68" s="160" t="s">
+      <c r="E67" s="152">
+        <v>0</v>
+      </c>
+      <c r="H67" s="232"/>
+    </row>
+    <row r="68" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B68" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C68" s="161" t="s">
+      <c r="C68" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D68" s="137" t="s">
+      <c r="D68" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E68" s="162">
+      <c r="E68" s="152">
         <v>0.94</v>
       </c>
-      <c r="H68" s="266"/>
-    </row>
-    <row r="69" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B69" s="160" t="s">
+      <c r="H68" s="232"/>
+    </row>
+    <row r="69" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B69" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C69" s="161" t="s">
+      <c r="C69" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D69" s="137" t="s">
+      <c r="D69" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E69" s="162">
+      <c r="E69" s="152">
         <v>0.06</v>
       </c>
-      <c r="H69" s="266"/>
-    </row>
-    <row r="70" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B70" s="160" t="s">
+      <c r="H69" s="232"/>
+    </row>
+    <row r="70" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B70" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C70" s="161" t="s">
+      <c r="C70" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D70" s="137" t="s">
+      <c r="D70" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E70" s="162">
-        <v>0</v>
-      </c>
-      <c r="H70" s="266"/>
-    </row>
-    <row r="71" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B71" s="160" t="s">
+      <c r="E70" s="152">
+        <v>0</v>
+      </c>
+      <c r="H70" s="232"/>
+    </row>
+    <row r="71" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B71" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C71" s="161" t="s">
+      <c r="C71" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D71" s="137" t="s">
+      <c r="D71" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E71" s="162">
+      <c r="E71" s="152">
         <v>0.94</v>
       </c>
-      <c r="H71" s="266"/>
-    </row>
-    <row r="72" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B72" s="160" t="s">
+      <c r="H71" s="232"/>
+    </row>
+    <row r="72" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B72" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C72" s="161" t="s">
+      <c r="C72" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D72" s="137" t="s">
+      <c r="D72" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E72" s="162">
+      <c r="E72" s="152">
         <v>0.06</v>
       </c>
-      <c r="H72" s="266"/>
-    </row>
-    <row r="73" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B73" s="160" t="s">
+      <c r="H72" s="232"/>
+    </row>
+    <row r="73" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B73" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="C73" s="161" t="s">
+      <c r="C73" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D73" s="137" t="s">
+      <c r="D73" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E73" s="162">
-        <v>0</v>
-      </c>
-      <c r="H73" s="266"/>
-    </row>
-    <row r="74" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B74" s="160" t="s">
+      <c r="E73" s="152">
+        <v>0</v>
+      </c>
+      <c r="H73" s="232"/>
+    </row>
+    <row r="74" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B74" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C74" s="161" t="s">
+      <c r="C74" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D74" s="137" t="s">
+      <c r="D74" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E74" s="162">
+      <c r="E74" s="152">
         <v>0.94</v>
       </c>
-      <c r="H74" s="266"/>
-    </row>
-    <row r="75" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B75" s="160" t="s">
+      <c r="H74" s="232"/>
+    </row>
+    <row r="75" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B75" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C75" s="161" t="s">
+      <c r="C75" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D75" s="137" t="s">
+      <c r="D75" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E75" s="162">
+      <c r="E75" s="152">
         <v>0.06</v>
       </c>
-      <c r="H75" s="266"/>
-    </row>
-    <row r="76" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B76" s="160" t="s">
+      <c r="H75" s="232"/>
+    </row>
+    <row r="76" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B76" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C76" s="161" t="s">
+      <c r="C76" s="151" t="s">
         <v>124</v>
       </c>
-      <c r="D76" s="137" t="s">
+      <c r="D76" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E76" s="162">
-        <v>0</v>
-      </c>
-      <c r="H76" s="266"/>
-    </row>
-    <row r="77" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B77" s="160" t="s">
+      <c r="E76" s="152">
+        <v>0</v>
+      </c>
+      <c r="H76" s="232"/>
+    </row>
+    <row r="77" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B77" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C77" s="161" t="s">
+      <c r="C77" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D77" s="137" t="s">
+      <c r="D77" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E77" s="162">
+      <c r="E77" s="152">
         <v>0.94</v>
       </c>
-      <c r="H77" s="266"/>
-    </row>
-    <row r="78" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B78" s="160" t="s">
+      <c r="H77" s="232"/>
+    </row>
+    <row r="78" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B78" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C78" s="161" t="s">
+      <c r="C78" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D78" s="137" t="s">
+      <c r="D78" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E78" s="162">
+      <c r="E78" s="152">
         <v>0.06</v>
       </c>
-      <c r="H78" s="266"/>
-    </row>
-    <row r="79" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B79" s="160" t="s">
+      <c r="H78" s="232"/>
+    </row>
+    <row r="79" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B79" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C79" s="161" t="s">
+      <c r="C79" s="151" t="s">
         <v>123</v>
       </c>
-      <c r="D79" s="137" t="s">
+      <c r="D79" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E79" s="162">
-        <v>0</v>
-      </c>
-      <c r="H79" s="266"/>
-    </row>
-    <row r="80" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B80" s="160" t="s">
+      <c r="E79" s="152">
+        <v>0</v>
+      </c>
+      <c r="H79" s="232"/>
+    </row>
+    <row r="80" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B80" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C80" s="161" t="s">
+      <c r="C80" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D80" s="137" t="s">
+      <c r="D80" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E80" s="162">
+      <c r="E80" s="152">
         <v>0.94</v>
       </c>
-      <c r="H80" s="266"/>
-    </row>
-    <row r="81" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B81" s="160" t="s">
+      <c r="H80" s="232"/>
+    </row>
+    <row r="81" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B81" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C81" s="161" t="s">
+      <c r="C81" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D81" s="137" t="s">
+      <c r="D81" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E81" s="162">
+      <c r="E81" s="152">
         <v>0.06</v>
       </c>
-      <c r="H81" s="266"/>
-    </row>
-    <row r="82" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B82" s="160" t="s">
+      <c r="H81" s="232"/>
+    </row>
+    <row r="82" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B82" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C82" s="161" t="s">
+      <c r="C82" s="151" t="s">
         <v>122</v>
       </c>
-      <c r="D82" s="137" t="s">
+      <c r="D82" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E82" s="162">
-        <v>0</v>
-      </c>
-      <c r="H82" s="266"/>
-    </row>
-    <row r="83" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B83" s="160" t="s">
+      <c r="E82" s="152">
+        <v>0</v>
+      </c>
+      <c r="H82" s="232"/>
+    </row>
+    <row r="83" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B83" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C83" s="161" t="s">
+      <c r="C83" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D83" s="137" t="s">
+      <c r="D83" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E83" s="162">
+      <c r="E83" s="152">
         <v>0.94</v>
       </c>
-      <c r="H83" s="266"/>
-    </row>
-    <row r="84" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B84" s="160" t="s">
+      <c r="H83" s="232"/>
+    </row>
+    <row r="84" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B84" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C84" s="161" t="s">
+      <c r="C84" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D84" s="137" t="s">
+      <c r="D84" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E84" s="162">
+      <c r="E84" s="152">
         <v>0.06</v>
       </c>
-      <c r="H84" s="266"/>
-    </row>
-    <row r="85" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B85" s="160" t="s">
+      <c r="H84" s="232"/>
+    </row>
+    <row r="85" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B85" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C85" s="161" t="s">
+      <c r="C85" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D85" s="137" t="s">
+      <c r="D85" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E85" s="162">
-        <v>0</v>
-      </c>
-      <c r="H85" s="266"/>
-    </row>
-    <row r="86" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B86" s="160" t="s">
+      <c r="E85" s="152">
+        <v>0</v>
+      </c>
+      <c r="H85" s="232"/>
+    </row>
+    <row r="86" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B86" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C86" s="161" t="s">
+      <c r="C86" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D86" s="137" t="s">
+      <c r="D86" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E86" s="162">
+      <c r="E86" s="152">
         <v>0.94</v>
       </c>
-      <c r="H86" s="266"/>
-    </row>
-    <row r="87" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B87" s="160" t="s">
+      <c r="H86" s="232"/>
+    </row>
+    <row r="87" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B87" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C87" s="161" t="s">
+      <c r="C87" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D87" s="137" t="s">
+      <c r="D87" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E87" s="162">
+      <c r="E87" s="152">
         <v>0.06</v>
       </c>
-      <c r="H87" s="266"/>
-    </row>
-    <row r="88" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B88" s="160" t="s">
+      <c r="H87" s="232"/>
+    </row>
+    <row r="88" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B88" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C88" s="161" t="s">
+      <c r="C88" s="151" t="s">
         <v>120</v>
       </c>
-      <c r="D88" s="137" t="s">
+      <c r="D88" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E88" s="162">
-        <v>0</v>
-      </c>
-      <c r="H88" s="266"/>
-    </row>
-    <row r="89" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B89" s="160" t="s">
+      <c r="E88" s="152">
+        <v>0</v>
+      </c>
+      <c r="H88" s="232"/>
+    </row>
+    <row r="89" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B89" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C89" s="161" t="s">
+      <c r="C89" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D89" s="137" t="s">
+      <c r="D89" s="128" t="s">
         <v>125</v>
       </c>
-      <c r="E89" s="162">
+      <c r="E89" s="152">
         <v>0.94</v>
       </c>
-      <c r="H89" s="266"/>
-    </row>
-    <row r="90" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B90" s="160" t="s">
+      <c r="H89" s="232"/>
+    </row>
+    <row r="90" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B90" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C90" s="161" t="s">
+      <c r="C90" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D90" s="137" t="s">
+      <c r="D90" s="128" t="s">
         <v>119</v>
       </c>
-      <c r="E90" s="162">
+      <c r="E90" s="152">
         <v>0.06</v>
       </c>
-      <c r="H90" s="266"/>
-    </row>
-    <row r="91" spans="1:8" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="136" t="s">
-        <v>126</v>
-      </c>
-      <c r="B91" s="160" t="s">
+      <c r="H90" s="232"/>
+    </row>
+    <row r="91" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="B91" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="C91" s="161" t="s">
+      <c r="C91" s="151" t="s">
         <v>118</v>
       </c>
-      <c r="D91" s="137" t="s">
+      <c r="D91" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="E91" s="162">
-        <v>0</v>
-      </c>
-      <c r="F91" s="163"/>
-      <c r="H91" s="266"/>
-    </row>
-    <row r="92" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="138" t="s">
+      <c r="E91" s="152">
+        <v>0</v>
+      </c>
+      <c r="F91" s="153"/>
+      <c r="H91" s="232"/>
+    </row>
+    <row r="92" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B92" s="144" t="s">
+      <c r="B92" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="C92" s="145" t="s">
+      <c r="C92" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D92" s="139" t="s">
+      <c r="D92" s="130" t="s">
         <v>132</v>
       </c>
-      <c r="E92" s="146">
+      <c r="E92" s="136">
         <v>0.96</v>
       </c>
-      <c r="F92" s="147"/>
-      <c r="H92" s="267" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="138" t="s">
+      <c r="F92" s="137"/>
+      <c r="H92" s="233" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B93" s="144" t="s">
+      <c r="B93" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="C93" s="145" t="s">
+      <c r="C93" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D93" s="139" t="s">
+      <c r="D93" s="130" t="s">
         <v>131</v>
       </c>
-      <c r="E93" s="146">
-        <v>0</v>
-      </c>
-      <c r="F93" s="147"/>
-      <c r="H93" s="267"/>
-    </row>
-    <row r="94" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="138" t="s">
+      <c r="E93" s="136">
+        <v>0</v>
+      </c>
+      <c r="F93" s="137"/>
+      <c r="H93" s="233"/>
+    </row>
+    <row r="94" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B94" s="144" t="s">
+      <c r="B94" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="C94" s="145" t="s">
+      <c r="C94" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D94" s="139" t="s">
+      <c r="D94" s="130" t="s">
         <v>133</v>
       </c>
-      <c r="E94" s="146">
+      <c r="E94" s="136">
         <v>0.04</v>
       </c>
-      <c r="F94" s="147"/>
-      <c r="H94" s="267"/>
-    </row>
-    <row r="95" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="138" t="s">
+      <c r="F94" s="137"/>
+      <c r="H94" s="233"/>
+    </row>
+    <row r="95" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B95" s="144" t="s">
+      <c r="B95" s="134" t="s">
         <v>116</v>
       </c>
-      <c r="C95" s="145" t="s">
+      <c r="C95" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D95" s="139" t="s">
+      <c r="D95" s="130" t="s">
         <v>117</v>
       </c>
-      <c r="E95" s="146">
-        <v>0</v>
-      </c>
-      <c r="F95" s="147"/>
-      <c r="H95" s="267"/>
-    </row>
-    <row r="96" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="138" t="s">
+      <c r="E95" s="136">
+        <v>0</v>
+      </c>
+      <c r="F95" s="137"/>
+      <c r="H95" s="233"/>
+    </row>
+    <row r="96" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B96" s="144" t="s">
+      <c r="B96" s="134" t="s">
         <v>115</v>
       </c>
-      <c r="C96" s="145" t="s">
+      <c r="C96" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D96" s="139" t="s">
+      <c r="D96" s="130" t="s">
         <v>132</v>
       </c>
-      <c r="E96" s="146">
+      <c r="E96" s="136">
         <v>0.96</v>
       </c>
-      <c r="F96" s="147"/>
-      <c r="H96" s="267"/>
-    </row>
-    <row r="97" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="138" t="s">
+      <c r="F96" s="137"/>
+      <c r="H96" s="233"/>
+    </row>
+    <row r="97" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B97" s="144" t="s">
+      <c r="B97" s="134" t="s">
         <v>115</v>
       </c>
-      <c r="C97" s="145" t="s">
+      <c r="C97" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D97" s="139" t="s">
+      <c r="D97" s="130" t="s">
         <v>131</v>
       </c>
-      <c r="E97" s="146">
-        <v>0</v>
-      </c>
-      <c r="F97" s="147"/>
-      <c r="H97" s="267"/>
-    </row>
-    <row r="98" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="138" t="s">
+      <c r="E97" s="136">
+        <v>0</v>
+      </c>
+      <c r="F97" s="137"/>
+      <c r="H97" s="233"/>
+    </row>
+    <row r="98" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B98" s="144" t="s">
+      <c r="B98" s="134" t="s">
         <v>115</v>
       </c>
-      <c r="C98" s="145" t="s">
+      <c r="C98" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D98" s="139" t="s">
+      <c r="D98" s="130" t="s">
         <v>133</v>
       </c>
-      <c r="E98" s="146">
+      <c r="E98" s="136">
         <v>0.04</v>
       </c>
-      <c r="F98" s="147"/>
-      <c r="H98" s="267"/>
-    </row>
-    <row r="99" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="138" t="s">
+      <c r="F98" s="137"/>
+      <c r="H98" s="233"/>
+    </row>
+    <row r="99" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B99" s="144" t="s">
+      <c r="B99" s="134" t="s">
         <v>115</v>
       </c>
-      <c r="C99" s="145" t="s">
+      <c r="C99" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D99" s="139" t="s">
+      <c r="D99" s="130" t="s">
         <v>117</v>
       </c>
-      <c r="E99" s="146">
-        <v>0</v>
-      </c>
-      <c r="F99" s="147"/>
-      <c r="H99" s="267"/>
-    </row>
-    <row r="100" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="138" t="s">
+      <c r="E99" s="136">
+        <v>0</v>
+      </c>
+      <c r="F99" s="137"/>
+      <c r="H99" s="233"/>
+    </row>
+    <row r="100" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B100" s="144" t="s">
+      <c r="B100" s="134" t="s">
         <v>114</v>
       </c>
-      <c r="C100" s="145" t="s">
+      <c r="C100" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D100" s="139" t="s">
+      <c r="D100" s="130" t="s">
         <v>132</v>
       </c>
-      <c r="E100" s="146">
+      <c r="E100" s="136">
         <v>0.96</v>
       </c>
-      <c r="F100" s="147"/>
-      <c r="H100" s="267"/>
-    </row>
-    <row r="101" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="138" t="s">
+      <c r="F100" s="137"/>
+      <c r="H100" s="233"/>
+    </row>
+    <row r="101" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B101" s="144" t="s">
+      <c r="B101" s="134" t="s">
         <v>114</v>
       </c>
-      <c r="C101" s="145" t="s">
+      <c r="C101" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="139" t="s">
+      <c r="D101" s="130" t="s">
         <v>131</v>
       </c>
-      <c r="E101" s="146">
-        <v>0</v>
-      </c>
-      <c r="F101" s="147"/>
-      <c r="H101" s="267"/>
-    </row>
-    <row r="102" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="138" t="s">
+      <c r="E101" s="136">
+        <v>0</v>
+      </c>
+      <c r="F101" s="137"/>
+      <c r="H101" s="233"/>
+    </row>
+    <row r="102" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B102" s="144" t="s">
+      <c r="B102" s="134" t="s">
         <v>114</v>
       </c>
-      <c r="C102" s="145" t="s">
+      <c r="C102" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D102" s="139" t="s">
+      <c r="D102" s="130" t="s">
         <v>133</v>
       </c>
-      <c r="E102" s="146">
+      <c r="E102" s="136">
         <v>0.04</v>
       </c>
-      <c r="F102" s="147"/>
-      <c r="H102" s="267"/>
-    </row>
-    <row r="103" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="138" t="s">
+      <c r="F102" s="137"/>
+      <c r="H102" s="233"/>
+    </row>
+    <row r="103" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B103" s="144" t="s">
+      <c r="B103" s="134" t="s">
         <v>114</v>
       </c>
-      <c r="C103" s="145" t="s">
+      <c r="C103" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D103" s="139" t="s">
+      <c r="D103" s="130" t="s">
         <v>117</v>
       </c>
-      <c r="E103" s="146">
-        <v>0</v>
-      </c>
-      <c r="F103" s="147"/>
-      <c r="H103" s="267"/>
-    </row>
-    <row r="104" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="138" t="s">
+      <c r="E103" s="136">
+        <v>0</v>
+      </c>
+      <c r="F103" s="137"/>
+      <c r="H103" s="233"/>
+    </row>
+    <row r="104" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B104" s="144" t="s">
+      <c r="B104" s="134" t="s">
         <v>113</v>
       </c>
-      <c r="C104" s="145" t="s">
+      <c r="C104" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D104" s="139" t="s">
+      <c r="D104" s="130" t="s">
         <v>132</v>
       </c>
-      <c r="E104" s="146">
+      <c r="E104" s="136">
         <v>0.3</v>
       </c>
-      <c r="F104" s="147"/>
-      <c r="H104" s="267"/>
-    </row>
-    <row r="105" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="138" t="s">
+      <c r="F104" s="137"/>
+      <c r="H104" s="233"/>
+    </row>
+    <row r="105" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B105" s="144" t="s">
+      <c r="B105" s="134" t="s">
         <v>113</v>
       </c>
-      <c r="C105" s="145" t="s">
+      <c r="C105" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D105" s="139" t="s">
+      <c r="D105" s="130" t="s">
         <v>131</v>
       </c>
-      <c r="E105" s="146">
-        <v>0</v>
-      </c>
-      <c r="F105" s="147"/>
-      <c r="H105" s="267"/>
-    </row>
-    <row r="106" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="138" t="s">
+      <c r="E105" s="136">
+        <v>0</v>
+      </c>
+      <c r="F105" s="137"/>
+      <c r="H105" s="233"/>
+    </row>
+    <row r="106" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B106" s="144" t="s">
+      <c r="B106" s="134" t="s">
         <v>113</v>
       </c>
-      <c r="C106" s="145" t="s">
+      <c r="C106" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D106" s="139" t="s">
+      <c r="D106" s="130" t="s">
         <v>133</v>
       </c>
-      <c r="E106" s="146">
+      <c r="E106" s="136">
         <v>0.7</v>
       </c>
-      <c r="F106" s="147"/>
-      <c r="H106" s="267"/>
-    </row>
-    <row r="107" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="138" t="s">
+      <c r="F106" s="137"/>
+      <c r="H106" s="233"/>
+    </row>
+    <row r="107" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B107" s="144" t="s">
+      <c r="B107" s="134" t="s">
         <v>113</v>
       </c>
-      <c r="C107" s="145" t="s">
+      <c r="C107" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D107" s="139" t="s">
+      <c r="D107" s="130" t="s">
         <v>117</v>
       </c>
-      <c r="E107" s="146">
-        <v>0</v>
-      </c>
-      <c r="F107" s="147"/>
-      <c r="H107" s="267"/>
-    </row>
-    <row r="108" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="138" t="s">
+      <c r="E107" s="136">
+        <v>0</v>
+      </c>
+      <c r="F107" s="137"/>
+      <c r="H107" s="233"/>
+    </row>
+    <row r="108" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B108" s="144" t="s">
+      <c r="B108" s="134" t="s">
         <v>111</v>
       </c>
-      <c r="C108" s="145" t="s">
+      <c r="C108" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D108" s="139" t="s">
+      <c r="D108" s="130" t="s">
         <v>132</v>
       </c>
-      <c r="E108" s="146">
-        <v>0</v>
-      </c>
-      <c r="F108" s="147"/>
-      <c r="H108" s="267"/>
-    </row>
-    <row r="109" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="138" t="s">
+      <c r="E108" s="136">
+        <v>0</v>
+      </c>
+      <c r="F108" s="137"/>
+      <c r="H108" s="233"/>
+    </row>
+    <row r="109" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B109" s="144" t="s">
+      <c r="B109" s="134" t="s">
         <v>111</v>
       </c>
-      <c r="C109" s="145" t="s">
+      <c r="C109" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D109" s="139" t="s">
+      <c r="D109" s="130" t="s">
         <v>131</v>
       </c>
-      <c r="E109" s="146">
-        <v>0</v>
-      </c>
-      <c r="F109" s="147"/>
-      <c r="H109" s="267"/>
-    </row>
-    <row r="110" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="138" t="s">
+      <c r="E109" s="136">
+        <v>0</v>
+      </c>
+      <c r="F109" s="137"/>
+      <c r="H109" s="233"/>
+    </row>
+    <row r="110" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B110" s="144" t="s">
+      <c r="B110" s="134" t="s">
         <v>111</v>
       </c>
-      <c r="C110" s="145" t="s">
+      <c r="C110" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D110" s="139" t="s">
+      <c r="D110" s="130" t="s">
         <v>133</v>
       </c>
-      <c r="E110" s="146">
+      <c r="E110" s="136">
         <v>1</v>
       </c>
-      <c r="F110" s="147"/>
-      <c r="H110" s="267"/>
-    </row>
-    <row r="111" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="138" t="s">
+      <c r="F110" s="137"/>
+      <c r="H110" s="233"/>
+    </row>
+    <row r="111" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B111" s="144" t="s">
+      <c r="B111" s="134" t="s">
         <v>111</v>
       </c>
-      <c r="C111" s="145" t="s">
+      <c r="C111" s="135" t="s">
         <v>110</v>
       </c>
-      <c r="D111" s="139" t="s">
+      <c r="D111" s="130" t="s">
         <v>117</v>
       </c>
-      <c r="E111" s="146">
-        <v>0</v>
-      </c>
-      <c r="F111" s="147"/>
-      <c r="H111" s="267"/>
-    </row>
-    <row r="112" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="140" t="s">
+      <c r="E111" s="136">
+        <v>0</v>
+      </c>
+      <c r="F111" s="137"/>
+      <c r="H111" s="233"/>
+    </row>
+    <row r="112" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B112" s="164" t="s">
+      <c r="B112" s="154" t="s">
         <v>116</v>
       </c>
-      <c r="C112" s="165" t="s">
+      <c r="C112" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D112" s="141" t="s">
+      <c r="D112" s="132" t="s">
         <v>132</v>
       </c>
-      <c r="E112" s="166">
+      <c r="E112" s="156">
         <v>0.7</v>
       </c>
-      <c r="H112" s="268" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="140" t="s">
+      <c r="H112" s="234" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B113" s="164" t="s">
+      <c r="B113" s="154" t="s">
         <v>116</v>
       </c>
-      <c r="C113" s="165" t="s">
+      <c r="C113" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D113" s="141" t="s">
+      <c r="D113" s="132" t="s">
         <v>131</v>
       </c>
-      <c r="E113" s="166">
-        <v>0</v>
-      </c>
-      <c r="H113" s="268"/>
-    </row>
-    <row r="114" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="140" t="s">
+      <c r="E113" s="156">
+        <v>0</v>
+      </c>
+      <c r="H113" s="234"/>
+    </row>
+    <row r="114" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B114" s="164" t="s">
+      <c r="B114" s="154" t="s">
         <v>116</v>
       </c>
-      <c r="C114" s="165" t="s">
+      <c r="C114" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D114" s="141" t="s">
+      <c r="D114" s="132" t="s">
         <v>130</v>
       </c>
-      <c r="E114" s="166">
-        <v>0</v>
-      </c>
-      <c r="H114" s="268"/>
-    </row>
-    <row r="115" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="140" t="s">
+      <c r="E114" s="156">
+        <v>0</v>
+      </c>
+      <c r="H114" s="234"/>
+    </row>
+    <row r="115" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B115" s="164" t="s">
+      <c r="B115" s="154" t="s">
         <v>116</v>
       </c>
-      <c r="C115" s="165" t="s">
+      <c r="C115" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D115" s="141" t="s">
+      <c r="D115" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="E115" s="166">
+      <c r="E115" s="156">
         <v>0.3</v>
       </c>
-      <c r="H115" s="268"/>
-    </row>
-    <row r="116" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="140" t="s">
+      <c r="H115" s="234"/>
+    </row>
+    <row r="116" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B116" s="164" t="s">
+      <c r="B116" s="154" t="s">
         <v>116</v>
       </c>
-      <c r="C116" s="165" t="s">
+      <c r="C116" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D116" s="141" t="s">
+      <c r="D116" s="132" t="s">
         <v>128</v>
       </c>
-      <c r="E116" s="166">
-        <v>0</v>
-      </c>
-      <c r="H116" s="268"/>
-    </row>
-    <row r="117" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="140" t="s">
+      <c r="E116" s="156">
+        <v>0</v>
+      </c>
+      <c r="H116" s="234"/>
+    </row>
+    <row r="117" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B117" s="164" t="s">
+      <c r="B117" s="154" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="165" t="s">
+      <c r="C117" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D117" s="141" t="s">
+      <c r="D117" s="132" t="s">
         <v>117</v>
       </c>
-      <c r="E117" s="166">
-        <v>0</v>
-      </c>
-      <c r="H117" s="268"/>
-    </row>
-    <row r="118" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="140" t="s">
+      <c r="E117" s="156">
+        <v>0</v>
+      </c>
+      <c r="H117" s="234"/>
+    </row>
+    <row r="118" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B118" s="164" t="s">
+      <c r="B118" s="154" t="s">
         <v>115</v>
       </c>
-      <c r="C118" s="165" t="s">
+      <c r="C118" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D118" s="141" t="s">
+      <c r="D118" s="132" t="s">
         <v>132</v>
       </c>
-      <c r="E118" s="166">
+      <c r="E118" s="156">
         <v>0.6</v>
       </c>
-      <c r="H118" s="268"/>
-    </row>
-    <row r="119" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="140" t="s">
+      <c r="H118" s="234"/>
+    </row>
+    <row r="119" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B119" s="164" t="s">
+      <c r="B119" s="154" t="s">
         <v>115</v>
       </c>
-      <c r="C119" s="165" t="s">
+      <c r="C119" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D119" s="141" t="s">
+      <c r="D119" s="132" t="s">
         <v>131</v>
       </c>
-      <c r="E119" s="166">
-        <v>0</v>
-      </c>
-      <c r="H119" s="268"/>
-    </row>
-    <row r="120" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="140" t="s">
+      <c r="E119" s="156">
+        <v>0</v>
+      </c>
+      <c r="H119" s="234"/>
+    </row>
+    <row r="120" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B120" s="164" t="s">
+      <c r="B120" s="154" t="s">
         <v>115</v>
       </c>
-      <c r="C120" s="165" t="s">
+      <c r="C120" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D120" s="141" t="s">
+      <c r="D120" s="132" t="s">
         <v>130</v>
       </c>
-      <c r="E120" s="166">
-        <v>0</v>
-      </c>
-      <c r="H120" s="268"/>
-    </row>
-    <row r="121" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="140" t="s">
+      <c r="E120" s="156">
+        <v>0</v>
+      </c>
+      <c r="H120" s="234"/>
+    </row>
+    <row r="121" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B121" s="164" t="s">
+      <c r="B121" s="154" t="s">
         <v>115</v>
       </c>
-      <c r="C121" s="165" t="s">
+      <c r="C121" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D121" s="141" t="s">
+      <c r="D121" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="E121" s="166">
+      <c r="E121" s="156">
         <v>0.4</v>
       </c>
-      <c r="H121" s="268"/>
-    </row>
-    <row r="122" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="140" t="s">
+      <c r="H121" s="234"/>
+    </row>
+    <row r="122" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B122" s="164" t="s">
+      <c r="B122" s="154" t="s">
         <v>115</v>
       </c>
-      <c r="C122" s="165" t="s">
+      <c r="C122" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D122" s="141" t="s">
+      <c r="D122" s="132" t="s">
         <v>128</v>
       </c>
-      <c r="E122" s="166">
-        <v>0</v>
-      </c>
-      <c r="H122" s="268"/>
-    </row>
-    <row r="123" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="140" t="s">
+      <c r="E122" s="156">
+        <v>0</v>
+      </c>
+      <c r="H122" s="234"/>
+    </row>
+    <row r="123" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B123" s="164" t="s">
+      <c r="B123" s="154" t="s">
         <v>115</v>
       </c>
-      <c r="C123" s="165" t="s">
+      <c r="C123" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D123" s="141" t="s">
+      <c r="D123" s="132" t="s">
         <v>117</v>
       </c>
-      <c r="E123" s="166">
-        <v>0</v>
-      </c>
-      <c r="H123" s="268"/>
-    </row>
-    <row r="124" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="140" t="s">
+      <c r="E123" s="156">
+        <v>0</v>
+      </c>
+      <c r="H123" s="234"/>
+    </row>
+    <row r="124" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B124" s="164" t="s">
+      <c r="B124" s="154" t="s">
         <v>114</v>
       </c>
-      <c r="C124" s="165" t="s">
+      <c r="C124" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D124" s="141" t="s">
+      <c r="D124" s="132" t="s">
         <v>132</v>
       </c>
-      <c r="E124" s="166">
+      <c r="E124" s="156">
         <v>0.42</v>
       </c>
-      <c r="H124" s="268"/>
-    </row>
-    <row r="125" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="140" t="s">
+      <c r="H124" s="234"/>
+    </row>
+    <row r="125" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B125" s="164" t="s">
+      <c r="B125" s="154" t="s">
         <v>114</v>
       </c>
-      <c r="C125" s="165" t="s">
+      <c r="C125" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D125" s="141" t="s">
+      <c r="D125" s="132" t="s">
         <v>131</v>
       </c>
-      <c r="E125" s="166">
-        <v>0</v>
-      </c>
-      <c r="H125" s="268"/>
-    </row>
-    <row r="126" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="140" t="s">
+      <c r="E125" s="156">
+        <v>0</v>
+      </c>
+      <c r="H125" s="234"/>
+    </row>
+    <row r="126" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B126" s="164" t="s">
+      <c r="B126" s="154" t="s">
         <v>114</v>
       </c>
-      <c r="C126" s="165" t="s">
+      <c r="C126" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D126" s="141" t="s">
+      <c r="D126" s="132" t="s">
         <v>130</v>
       </c>
-      <c r="E126" s="166">
-        <v>0</v>
-      </c>
-      <c r="H126" s="268"/>
-    </row>
-    <row r="127" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="140" t="s">
+      <c r="E126" s="156">
+        <v>0</v>
+      </c>
+      <c r="H126" s="234"/>
+    </row>
+    <row r="127" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B127" s="164" t="s">
+      <c r="B127" s="154" t="s">
         <v>114</v>
       </c>
-      <c r="C127" s="165" t="s">
+      <c r="C127" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D127" s="141" t="s">
+      <c r="D127" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="E127" s="166">
+      <c r="E127" s="156">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H127" s="268"/>
-    </row>
-    <row r="128" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="140" t="s">
+      <c r="H127" s="234"/>
+    </row>
+    <row r="128" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B128" s="164" t="s">
+      <c r="B128" s="154" t="s">
         <v>114</v>
       </c>
-      <c r="C128" s="165" t="s">
+      <c r="C128" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D128" s="141" t="s">
+      <c r="D128" s="132" t="s">
         <v>128</v>
       </c>
-      <c r="E128" s="166">
-        <v>0</v>
-      </c>
-      <c r="H128" s="268"/>
-    </row>
-    <row r="129" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="140" t="s">
+      <c r="E128" s="156">
+        <v>0</v>
+      </c>
+      <c r="H128" s="234"/>
+    </row>
+    <row r="129" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B129" s="164" t="s">
+      <c r="B129" s="154" t="s">
         <v>114</v>
       </c>
-      <c r="C129" s="165" t="s">
+      <c r="C129" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D129" s="141" t="s">
+      <c r="D129" s="132" t="s">
         <v>117</v>
       </c>
-      <c r="E129" s="166">
-        <v>0</v>
-      </c>
-      <c r="H129" s="268"/>
-    </row>
-    <row r="130" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="140" t="s">
+      <c r="E129" s="156">
+        <v>0</v>
+      </c>
+      <c r="H129" s="234"/>
+    </row>
+    <row r="130" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B130" s="164" t="s">
+      <c r="B130" s="154" t="s">
         <v>113</v>
       </c>
-      <c r="C130" s="165" t="s">
+      <c r="C130" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D130" s="141" t="s">
+      <c r="D130" s="132" t="s">
         <v>132</v>
       </c>
-      <c r="E130" s="166">
+      <c r="E130" s="156">
         <v>0.05</v>
       </c>
-      <c r="H130" s="268"/>
-    </row>
-    <row r="131" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="140" t="s">
+      <c r="H130" s="234"/>
+    </row>
+    <row r="131" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B131" s="164" t="s">
+      <c r="B131" s="154" t="s">
         <v>113</v>
       </c>
-      <c r="C131" s="165" t="s">
+      <c r="C131" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D131" s="141" t="s">
+      <c r="D131" s="132" t="s">
         <v>131</v>
       </c>
-      <c r="E131" s="166">
-        <v>0</v>
-      </c>
-      <c r="H131" s="268"/>
-    </row>
-    <row r="132" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="140" t="s">
+      <c r="E131" s="156">
+        <v>0</v>
+      </c>
+      <c r="H131" s="234"/>
+    </row>
+    <row r="132" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B132" s="164" t="s">
+      <c r="B132" s="154" t="s">
         <v>113</v>
       </c>
-      <c r="C132" s="165" t="s">
+      <c r="C132" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D132" s="141" t="s">
+      <c r="D132" s="132" t="s">
         <v>130</v>
       </c>
-      <c r="E132" s="166">
-        <v>0</v>
-      </c>
-      <c r="H132" s="268"/>
-    </row>
-    <row r="133" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="140" t="s">
+      <c r="E132" s="156">
+        <v>0</v>
+      </c>
+      <c r="H132" s="234"/>
+    </row>
+    <row r="133" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B133" s="164" t="s">
+      <c r="B133" s="154" t="s">
         <v>113</v>
       </c>
-      <c r="C133" s="165" t="s">
+      <c r="C133" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D133" s="141" t="s">
+      <c r="D133" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="E133" s="166">
+      <c r="E133" s="156">
         <v>0.95</v>
       </c>
-      <c r="H133" s="268"/>
-    </row>
-    <row r="134" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="140" t="s">
+      <c r="H133" s="234"/>
+    </row>
+    <row r="134" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B134" s="164" t="s">
+      <c r="B134" s="154" t="s">
         <v>113</v>
       </c>
-      <c r="C134" s="165" t="s">
+      <c r="C134" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D134" s="141" t="s">
+      <c r="D134" s="132" t="s">
         <v>128</v>
       </c>
-      <c r="E134" s="166">
-        <v>0</v>
-      </c>
-      <c r="H134" s="268"/>
-    </row>
-    <row r="135" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="140" t="s">
+      <c r="E134" s="156">
+        <v>0</v>
+      </c>
+      <c r="H134" s="234"/>
+    </row>
+    <row r="135" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B135" s="164" t="s">
+      <c r="B135" s="154" t="s">
         <v>113</v>
       </c>
-      <c r="C135" s="165" t="s">
+      <c r="C135" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D135" s="141" t="s">
+      <c r="D135" s="132" t="s">
         <v>117</v>
       </c>
-      <c r="E135" s="166">
-        <v>0</v>
-      </c>
-      <c r="H135" s="268"/>
-    </row>
-    <row r="136" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="140" t="s">
+      <c r="E135" s="156">
+        <v>0</v>
+      </c>
+      <c r="H135" s="234"/>
+    </row>
+    <row r="136" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B136" s="164" t="s">
+      <c r="B136" s="154" t="s">
         <v>111</v>
       </c>
-      <c r="C136" s="165" t="s">
+      <c r="C136" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D136" s="141" t="s">
+      <c r="D136" s="132" t="s">
         <v>132</v>
       </c>
-      <c r="E136" s="166">
-        <v>0</v>
-      </c>
-      <c r="H136" s="268"/>
-    </row>
-    <row r="137" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="140" t="s">
+      <c r="E136" s="156">
+        <v>0</v>
+      </c>
+      <c r="H136" s="234"/>
+    </row>
+    <row r="137" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B137" s="164" t="s">
+      <c r="B137" s="154" t="s">
         <v>111</v>
       </c>
-      <c r="C137" s="165" t="s">
+      <c r="C137" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D137" s="141" t="s">
+      <c r="D137" s="132" t="s">
         <v>131</v>
       </c>
-      <c r="E137" s="166">
-        <v>0</v>
-      </c>
-      <c r="H137" s="268"/>
-    </row>
-    <row r="138" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="140" t="s">
+      <c r="E137" s="156">
+        <v>0</v>
+      </c>
+      <c r="H137" s="234"/>
+    </row>
+    <row r="138" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B138" s="164" t="s">
+      <c r="B138" s="154" t="s">
         <v>111</v>
       </c>
-      <c r="C138" s="165" t="s">
+      <c r="C138" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D138" s="141" t="s">
+      <c r="D138" s="132" t="s">
         <v>130</v>
       </c>
-      <c r="E138" s="166">
-        <v>0</v>
-      </c>
-      <c r="H138" s="268"/>
-    </row>
-    <row r="139" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="140" t="s">
+      <c r="E138" s="156">
+        <v>0</v>
+      </c>
+      <c r="H138" s="234"/>
+    </row>
+    <row r="139" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B139" s="164" t="s">
+      <c r="B139" s="154" t="s">
         <v>111</v>
       </c>
-      <c r="C139" s="165" t="s">
+      <c r="C139" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D139" s="141" t="s">
+      <c r="D139" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="E139" s="166">
+      <c r="E139" s="156">
         <v>0.05</v>
       </c>
-      <c r="H139" s="268"/>
-    </row>
-    <row r="140" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="140" t="s">
+      <c r="H139" s="234"/>
+    </row>
+    <row r="140" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B140" s="164" t="s">
+      <c r="B140" s="154" t="s">
         <v>111</v>
       </c>
-      <c r="C140" s="165" t="s">
+      <c r="C140" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D140" s="141" t="s">
+      <c r="D140" s="132" t="s">
         <v>128</v>
       </c>
-      <c r="E140" s="166">
+      <c r="E140" s="156">
         <v>0.95</v>
       </c>
-      <c r="H140" s="268"/>
-    </row>
-    <row r="141" spans="1:8" s="167" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="140" t="s">
+      <c r="H140" s="234"/>
+    </row>
+    <row r="141" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="B141" s="164" t="s">
+      <c r="B141" s="154" t="s">
         <v>111</v>
       </c>
-      <c r="C141" s="165" t="s">
+      <c r="C141" s="155" t="s">
         <v>110</v>
       </c>
-      <c r="D141" s="141" t="s">
+      <c r="D141" s="132" t="s">
         <v>117</v>
       </c>
-      <c r="E141" s="166">
-        <v>0</v>
-      </c>
-      <c r="H141" s="268"/>
+      <c r="E141" s="156">
+        <v>0</v>
+      </c>
+      <c r="H141" s="234"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7177,165 +7067,165 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="133" t="s">
+      <c r="A2" s="125" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="125" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="134">
+      <c r="C2" s="126">
         <v>0.96499999999999997</v>
       </c>
-      <c r="D2" s="64"/>
-      <c r="E2" s="269" t="s">
-        <v>317</v>
+      <c r="D2" s="63"/>
+      <c r="E2" s="235" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="136" t="s">
+      <c r="A3" s="127" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="136" t="s">
+      <c r="B3" s="127" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="137">
+      <c r="C3" s="128">
         <v>0.96499999999999997</v>
       </c>
-      <c r="D3" s="64"/>
-      <c r="E3" s="269"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="235"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="136" t="s">
+      <c r="A4" s="127" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="136" t="s">
+      <c r="B4" s="127" t="s">
         <v>122</v>
       </c>
-      <c r="C4" s="137">
+      <c r="C4" s="128">
         <v>0.5</v>
       </c>
-      <c r="D4" s="64"/>
-      <c r="E4" s="269"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="235"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="136" t="s">
+      <c r="A5" s="127" t="s">
         <v>147</v>
       </c>
-      <c r="B5" s="136" t="s">
+      <c r="B5" s="127" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="137">
-        <v>0</v>
-      </c>
-      <c r="D5" s="64"/>
-      <c r="E5" s="269"/>
+      <c r="C5" s="128">
+        <v>0</v>
+      </c>
+      <c r="D5" s="63"/>
+      <c r="E5" s="235"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="138" t="s">
+      <c r="A6" s="129" t="s">
         <v>146</v>
       </c>
-      <c r="B6" s="138" t="s">
+      <c r="B6" s="129" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="139">
+      <c r="C6" s="130">
         <v>0.96499999999999997</v>
       </c>
-      <c r="D6" s="64"/>
-      <c r="E6" s="269"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="235"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="138" t="s">
+      <c r="A7" s="129" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="138" t="s">
+      <c r="B7" s="129" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="139">
+      <c r="C7" s="130">
         <v>0.96499999999999997</v>
       </c>
-      <c r="D7" s="64"/>
-      <c r="E7" s="269"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="235"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="138" t="s">
+      <c r="A8" s="129" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="138" t="s">
+      <c r="B8" s="129" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="139">
+      <c r="C8" s="130">
         <v>0.5</v>
       </c>
-      <c r="D8" s="64"/>
-      <c r="E8" s="269"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="235"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="138" t="s">
+      <c r="A9" s="129" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="138" t="s">
+      <c r="B9" s="129" t="s">
         <v>121</v>
       </c>
-      <c r="C9" s="139">
-        <v>0</v>
-      </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="269"/>
+      <c r="C9" s="130">
+        <v>0</v>
+      </c>
+      <c r="D9" s="63"/>
+      <c r="E9" s="235"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="140" t="s">
+      <c r="A10" s="131" t="s">
         <v>145</v>
       </c>
-      <c r="B10" s="140" t="s">
+      <c r="B10" s="131" t="s">
         <v>124</v>
       </c>
-      <c r="C10" s="141">
+      <c r="C10" s="132">
         <v>0.96499999999999997</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="269"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="235"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="140" t="s">
+      <c r="A11" s="131" t="s">
         <v>145</v>
       </c>
-      <c r="B11" s="140" t="s">
+      <c r="B11" s="131" t="s">
         <v>123</v>
       </c>
-      <c r="C11" s="141">
+      <c r="C11" s="132">
         <v>0.96499999999999997</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="269"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="235"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="140" t="s">
+      <c r="A12" s="131" t="s">
         <v>145</v>
       </c>
-      <c r="B12" s="140" t="s">
+      <c r="B12" s="131" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="141">
+      <c r="C12" s="132">
         <v>0.96499999999999997</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="269"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="235"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="140" t="s">
+      <c r="A13" s="131" t="s">
         <v>145</v>
       </c>
-      <c r="B13" s="140" t="s">
+      <c r="B13" s="131" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="141">
-        <v>0</v>
-      </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="269"/>
+      <c r="C13" s="132">
+        <v>0</v>
+      </c>
+      <c r="D13" s="63"/>
+      <c r="E13" s="235"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B18" s="64"/>
+      <c r="B18" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7350,99 +7240,99 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23" style="64" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="10.83203125" style="64"/>
-    <col min="6" max="6" width="112.6640625" style="64" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="64"/>
+    <col min="1" max="1" width="23" style="63" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="10.83203125" style="63"/>
+    <col min="6" max="6" width="112.6640625" style="63" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="63"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="140" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="153" t="s">
+      <c r="B1" s="143" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="168" t="s">
+      <c r="C1" s="158" t="s">
         <v>137</v>
       </c>
-      <c r="D1" s="153" t="s">
+      <c r="D1" s="143" t="s">
         <v>144</v>
       </c>
-      <c r="F1" s="155" t="s">
+      <c r="F1" s="145" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="133" t="s">
+    <row r="2" spans="1:6" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="125" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="126" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="169" t="s">
+      <c r="C2" s="159" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="134">
-        <v>0</v>
-      </c>
-      <c r="F2" s="170" t="s">
+      <c r="D2" s="126">
+        <v>0</v>
+      </c>
+      <c r="F2" s="160" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="136" t="s">
+    <row r="3" spans="1:6" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="127" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="128" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="171" t="s">
+      <c r="C3" s="161" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="137">
+      <c r="D3" s="128">
         <v>0.95</v>
       </c>
-      <c r="F3" s="172" t="s">
+      <c r="F3" s="162" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="159" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="136" t="s">
+    <row r="4" spans="1:6" s="149" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="127" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="137" t="s">
+      <c r="B4" s="128" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="171" t="s">
+      <c r="C4" s="161" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="137">
-        <v>0</v>
-      </c>
-      <c r="F4" s="172" t="s">
+      <c r="D4" s="128">
+        <v>0</v>
+      </c>
+      <c r="F4" s="162" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="148" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="138" t="s">
+    <row r="5" spans="1:6" s="138" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="129" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="139" t="s">
+      <c r="B5" s="130" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="173" t="s">
+      <c r="C5" s="163" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="139">
+      <c r="D5" s="130">
         <v>0.8</v>
       </c>
-      <c r="F5" s="149" t="s">
+      <c r="F5" s="139" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F6" s="142"/>
+      <c r="F6" s="133"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7451,7 +7341,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93012449-ECC5-8E4E-B073-CC1B32FCDD86}">
-  <dimension ref="A2:U31"/>
+  <dimension ref="A2:U26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.1640625" style="6" customWidth="1"/>
@@ -7465,232 +7355,232 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="287" t="s">
+      <c r="B2" s="250" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="273" t="s">
+      <c r="C2" s="252" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="274"/>
-      <c r="E2" s="274"/>
-      <c r="F2" s="289"/>
-      <c r="G2" s="285" t="s">
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="267" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="287" t="s">
-        <v>263</v>
-      </c>
-      <c r="I2" s="273" t="s">
+      <c r="H2" s="250" t="s">
+        <v>260</v>
+      </c>
+      <c r="I2" s="252" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="274"/>
-      <c r="K2" s="275"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="262"/>
     </row>
     <row r="3" spans="1:21" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="288"/>
-      <c r="C3" s="276"/>
-      <c r="D3" s="277"/>
-      <c r="E3" s="277"/>
-      <c r="F3" s="290"/>
-      <c r="G3" s="286"/>
-      <c r="H3" s="288"/>
-      <c r="I3" s="276"/>
-      <c r="J3" s="277"/>
-      <c r="K3" s="278"/>
+      <c r="B3" s="251"/>
+      <c r="C3" s="255"/>
+      <c r="D3" s="256"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="257"/>
+      <c r="G3" s="268"/>
+      <c r="H3" s="251"/>
+      <c r="I3" s="255"/>
+      <c r="J3" s="256"/>
+      <c r="K3" s="263"/>
     </row>
     <row r="4" spans="1:21" s="44" customFormat="1" ht="270" x14ac:dyDescent="0.2">
       <c r="A4" s="46"/>
-      <c r="B4" s="174" t="s">
+      <c r="B4" s="164" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="291" t="s">
-        <v>321</v>
-      </c>
-      <c r="D4" s="292"/>
-      <c r="E4" s="292"/>
-      <c r="F4" s="293"/>
-      <c r="G4" s="175" t="s">
-        <v>270</v>
-      </c>
-      <c r="H4" s="176" t="s">
-        <v>271</v>
-      </c>
-      <c r="I4" s="282" t="s">
-        <v>295</v>
-      </c>
-      <c r="J4" s="283"/>
-      <c r="K4" s="284"/>
+      <c r="C4" s="258" t="s">
+        <v>312</v>
+      </c>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="260"/>
+      <c r="G4" s="165" t="s">
+        <v>267</v>
+      </c>
+      <c r="H4" s="166" t="s">
+        <v>268</v>
+      </c>
+      <c r="I4" s="264" t="s">
+        <v>288</v>
+      </c>
+      <c r="J4" s="265"/>
+      <c r="K4" s="266"/>
     </row>
     <row r="5" spans="1:21" s="44" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="46"/>
-      <c r="B5" s="92" t="s">
+      <c r="B5" s="84" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="279" t="s">
-        <v>322</v>
-      </c>
-      <c r="D5" s="280"/>
-      <c r="E5" s="280"/>
-      <c r="F5" s="281"/>
-      <c r="G5" s="177">
+      <c r="C5" s="236" t="s">
+        <v>313</v>
+      </c>
+      <c r="D5" s="237"/>
+      <c r="E5" s="237"/>
+      <c r="F5" s="261"/>
+      <c r="G5" s="167">
         <v>0.8</v>
       </c>
-      <c r="H5" s="178" t="s">
-        <v>307</v>
-      </c>
-      <c r="I5" s="270" t="s">
-        <v>269</v>
-      </c>
-      <c r="J5" s="271"/>
-      <c r="K5" s="272"/>
+      <c r="H5" s="168" t="s">
+        <v>298</v>
+      </c>
+      <c r="I5" s="239" t="s">
+        <v>266</v>
+      </c>
+      <c r="J5" s="240"/>
+      <c r="K5" s="241"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
     </row>
     <row r="6" spans="1:21" s="44" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="46"/>
-      <c r="B6" s="92" t="s">
+      <c r="B6" s="84" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="279" t="s">
-        <v>323</v>
-      </c>
-      <c r="D6" s="280"/>
-      <c r="E6" s="280"/>
-      <c r="F6" s="281"/>
-      <c r="G6" s="177">
+      <c r="C6" s="236" t="s">
+        <v>314</v>
+      </c>
+      <c r="D6" s="237"/>
+      <c r="E6" s="237"/>
+      <c r="F6" s="261"/>
+      <c r="G6" s="167">
         <v>0.8</v>
       </c>
-      <c r="H6" s="179" t="s">
-        <v>307</v>
-      </c>
-      <c r="I6" s="270" t="s">
-        <v>268</v>
-      </c>
-      <c r="J6" s="271"/>
-      <c r="K6" s="272"/>
+      <c r="H6" s="169" t="s">
+        <v>298</v>
+      </c>
+      <c r="I6" s="239" t="s">
+        <v>265</v>
+      </c>
+      <c r="J6" s="240"/>
+      <c r="K6" s="241"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
     </row>
     <row r="7" spans="1:21" s="44" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="46"/>
-      <c r="B7" s="92" t="s">
-        <v>297</v>
-      </c>
-      <c r="C7" s="279" t="s">
-        <v>298</v>
-      </c>
-      <c r="D7" s="280"/>
-      <c r="E7" s="280"/>
-      <c r="F7" s="281"/>
-      <c r="G7" s="177">
+      <c r="B7" s="84" t="s">
+        <v>289</v>
+      </c>
+      <c r="C7" s="236" t="s">
+        <v>290</v>
+      </c>
+      <c r="D7" s="237"/>
+      <c r="E7" s="237"/>
+      <c r="F7" s="261"/>
+      <c r="G7" s="167">
         <v>1</v>
       </c>
-      <c r="H7" s="179"/>
-      <c r="I7" s="270" t="s">
-        <v>299</v>
-      </c>
-      <c r="J7" s="271"/>
-      <c r="K7" s="272"/>
+      <c r="H7" s="169"/>
+      <c r="I7" s="239" t="s">
+        <v>291</v>
+      </c>
+      <c r="J7" s="240"/>
+      <c r="K7" s="241"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:21" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A8" s="46"/>
-      <c r="B8" s="92" t="s">
+      <c r="B8" s="84" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="279" t="s">
-        <v>265</v>
-      </c>
-      <c r="D8" s="280"/>
-      <c r="E8" s="280"/>
-      <c r="F8" s="281"/>
-      <c r="G8" s="177">
+      <c r="C8" s="236" t="s">
+        <v>262</v>
+      </c>
+      <c r="D8" s="237"/>
+      <c r="E8" s="237"/>
+      <c r="F8" s="261"/>
+      <c r="G8" s="167">
         <v>1</v>
       </c>
-      <c r="H8" s="178" t="s">
-        <v>266</v>
-      </c>
-      <c r="I8" s="270"/>
-      <c r="J8" s="271"/>
-      <c r="K8" s="272"/>
+      <c r="H8" s="168" t="s">
+        <v>263</v>
+      </c>
+      <c r="I8" s="239"/>
+      <c r="J8" s="240"/>
+      <c r="K8" s="241"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="1:21" s="44" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="46"/>
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="84" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="279" t="s">
+      <c r="C9" s="236" t="s">
         <v>158</v>
       </c>
-      <c r="D9" s="280"/>
-      <c r="E9" s="280"/>
-      <c r="F9" s="281"/>
-      <c r="G9" s="177">
+      <c r="D9" s="237"/>
+      <c r="E9" s="237"/>
+      <c r="F9" s="261"/>
+      <c r="G9" s="167">
         <v>0.95</v>
       </c>
-      <c r="H9" s="178" t="s">
-        <v>307</v>
-      </c>
-      <c r="I9" s="279" t="s">
-        <v>264</v>
-      </c>
-      <c r="J9" s="280"/>
-      <c r="K9" s="296"/>
+      <c r="H9" s="168" t="s">
+        <v>298</v>
+      </c>
+      <c r="I9" s="236" t="s">
+        <v>261</v>
+      </c>
+      <c r="J9" s="237"/>
+      <c r="K9" s="238"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:21" s="44" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="47"/>
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="84" t="s">
         <v>159</v>
       </c>
-      <c r="C10" s="279" t="s">
+      <c r="C10" s="236" t="s">
         <v>162</v>
       </c>
-      <c r="D10" s="280"/>
-      <c r="E10" s="280"/>
-      <c r="F10" s="281"/>
-      <c r="G10" s="180">
+      <c r="D10" s="237"/>
+      <c r="E10" s="237"/>
+      <c r="F10" s="261"/>
+      <c r="G10" s="170">
         <v>0.9</v>
       </c>
-      <c r="H10" s="178"/>
-      <c r="I10" s="270" t="s">
-        <v>267</v>
-      </c>
-      <c r="J10" s="271"/>
-      <c r="K10" s="272"/>
+      <c r="H10" s="168"/>
+      <c r="I10" s="239" t="s">
+        <v>264</v>
+      </c>
+      <c r="J10" s="240"/>
+      <c r="K10" s="241"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
     </row>
     <row r="11" spans="1:21" s="44" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="46"/>
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="84" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="279" t="s">
+      <c r="C11" s="236" t="s">
         <v>161</v>
       </c>
-      <c r="D11" s="280"/>
-      <c r="E11" s="280"/>
-      <c r="F11" s="281"/>
-      <c r="G11" s="180">
+      <c r="D11" s="237"/>
+      <c r="E11" s="237"/>
+      <c r="F11" s="261"/>
+      <c r="G11" s="170">
         <v>0.9</v>
       </c>
-      <c r="H11" s="179"/>
-      <c r="I11" s="270" t="s">
-        <v>267</v>
-      </c>
-      <c r="J11" s="271"/>
-      <c r="K11" s="272"/>
+      <c r="H11" s="169"/>
+      <c r="I11" s="239" t="s">
+        <v>264</v>
+      </c>
+      <c r="J11" s="240"/>
+      <c r="K11" s="241"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -7698,7 +7588,7 @@
     <row r="12" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B13" s="48" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C13" s="49"/>
       <c r="D13" s="49"/>
@@ -7721,28 +7611,28 @@
       <c r="U13" s="51"/>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="301" t="s">
-        <v>258</v>
-      </c>
-      <c r="C14" s="302"/>
-      <c r="D14" s="302"/>
-      <c r="E14" s="302"/>
-      <c r="F14" s="302"/>
-      <c r="G14" s="302"/>
-      <c r="H14" s="302"/>
-      <c r="I14" s="302"/>
-      <c r="J14" s="302"/>
-      <c r="K14" s="302"/>
-      <c r="L14" s="302"/>
-      <c r="M14" s="302"/>
-      <c r="N14" s="302"/>
-      <c r="O14" s="302"/>
-      <c r="P14" s="302"/>
-      <c r="Q14" s="302"/>
-      <c r="R14" s="302"/>
-      <c r="S14" s="302"/>
-      <c r="T14" s="302"/>
-      <c r="U14" s="303"/>
+      <c r="B14" s="244" t="s">
+        <v>322</v>
+      </c>
+      <c r="C14" s="245"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
+      <c r="F14" s="245"/>
+      <c r="G14" s="245"/>
+      <c r="H14" s="245"/>
+      <c r="I14" s="245"/>
+      <c r="J14" s="245"/>
+      <c r="K14" s="245"/>
+      <c r="L14" s="245"/>
+      <c r="M14" s="245"/>
+      <c r="N14" s="245"/>
+      <c r="O14" s="245"/>
+      <c r="P14" s="245"/>
+      <c r="Q14" s="245"/>
+      <c r="R14" s="245"/>
+      <c r="S14" s="245"/>
+      <c r="T14" s="245"/>
+      <c r="U14" s="246"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B15" s="52"/>
@@ -7767,94 +7657,94 @@
       <c r="U15" s="55"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B16" s="299" t="s">
+      <c r="B16" s="242" t="s">
+        <v>252</v>
+      </c>
+      <c r="C16" s="243"/>
+      <c r="D16" s="243"/>
+      <c r="E16" s="243"/>
+      <c r="F16" s="243"/>
+      <c r="G16" s="243"/>
+      <c r="H16" s="243"/>
+      <c r="I16" s="243"/>
+      <c r="J16" s="243"/>
+      <c r="K16" s="243"/>
+      <c r="L16" s="243"/>
+      <c r="M16" s="243"/>
+      <c r="N16" s="243"/>
+      <c r="O16" s="243"/>
+      <c r="P16" s="243"/>
+      <c r="Q16" s="243"/>
+      <c r="R16" s="243"/>
+      <c r="S16" s="243"/>
+      <c r="T16" s="243"/>
+      <c r="U16" s="249"/>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B17" s="247" t="s">
+        <v>250</v>
+      </c>
+      <c r="C17" s="248"/>
+      <c r="D17" s="171">
+        <v>2008</v>
+      </c>
+      <c r="E17" s="171">
+        <v>2009</v>
+      </c>
+      <c r="F17" s="171">
+        <v>2010</v>
+      </c>
+      <c r="G17" s="171">
+        <v>2011</v>
+      </c>
+      <c r="H17" s="171">
+        <v>2012</v>
+      </c>
+      <c r="I17" s="171">
+        <v>2013</v>
+      </c>
+      <c r="J17" s="171">
+        <v>2014</v>
+      </c>
+      <c r="K17" s="171">
+        <v>2015</v>
+      </c>
+      <c r="L17" s="171">
+        <v>2016</v>
+      </c>
+      <c r="M17" s="171">
+        <v>2017</v>
+      </c>
+      <c r="N17" s="171">
+        <v>2018</v>
+      </c>
+      <c r="O17" s="171">
+        <v>2019</v>
+      </c>
+      <c r="P17" s="171">
+        <v>2020</v>
+      </c>
+      <c r="Q17" s="171">
+        <v>2021</v>
+      </c>
+      <c r="R17" s="171">
+        <v>2022</v>
+      </c>
+      <c r="S17" s="171">
+        <v>2023</v>
+      </c>
+      <c r="T17" s="171">
+        <v>2024</v>
+      </c>
+      <c r="U17" s="172" t="s">
         <v>254</v>
       </c>
-      <c r="C16" s="300"/>
-      <c r="D16" s="300"/>
-      <c r="E16" s="300"/>
-      <c r="F16" s="300"/>
-      <c r="G16" s="300"/>
-      <c r="H16" s="300"/>
-      <c r="I16" s="300"/>
-      <c r="J16" s="300"/>
-      <c r="K16" s="300"/>
-      <c r="L16" s="300"/>
-      <c r="M16" s="300"/>
-      <c r="N16" s="300"/>
-      <c r="O16" s="300"/>
-      <c r="P16" s="300"/>
-      <c r="Q16" s="300"/>
-      <c r="R16" s="300"/>
-      <c r="S16" s="300"/>
-      <c r="T16" s="300"/>
-      <c r="U16" s="304"/>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B17" s="294" t="s">
-        <v>250</v>
-      </c>
-      <c r="C17" s="295"/>
-      <c r="D17" s="181">
-        <v>2008</v>
-      </c>
-      <c r="E17" s="181">
-        <v>2009</v>
-      </c>
-      <c r="F17" s="181">
-        <v>2010</v>
-      </c>
-      <c r="G17" s="181">
-        <v>2011</v>
-      </c>
-      <c r="H17" s="181">
-        <v>2012</v>
-      </c>
-      <c r="I17" s="181">
-        <v>2013</v>
-      </c>
-      <c r="J17" s="181">
-        <v>2014</v>
-      </c>
-      <c r="K17" s="181">
-        <v>2015</v>
-      </c>
-      <c r="L17" s="181">
-        <v>2016</v>
-      </c>
-      <c r="M17" s="181">
-        <v>2017</v>
-      </c>
-      <c r="N17" s="181">
-        <v>2018</v>
-      </c>
-      <c r="O17" s="181">
-        <v>2019</v>
-      </c>
-      <c r="P17" s="181">
-        <v>2020</v>
-      </c>
-      <c r="Q17" s="181">
-        <v>2021</v>
-      </c>
-      <c r="R17" s="181">
-        <v>2022</v>
-      </c>
-      <c r="S17" s="181">
-        <v>2023</v>
-      </c>
-      <c r="T17" s="181">
-        <v>2024</v>
-      </c>
-      <c r="U17" s="182" t="s">
-        <v>256</v>
-      </c>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18" s="294" t="s">
+      <c r="B18" s="247" t="s">
         <v>251</v>
       </c>
-      <c r="C18" s="295"/>
+      <c r="C18" s="248"/>
       <c r="D18" s="59">
         <v>0.86</v>
       </c>
@@ -7906,74 +7796,60 @@
       <c r="T18" s="59">
         <v>0.8</v>
       </c>
-      <c r="U18" s="183">
+      <c r="U18" s="173">
         <v>0.8</v>
       </c>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B19" s="294" t="s">
-        <v>252</v>
-      </c>
-      <c r="C19" s="295"/>
+      <c r="B19" s="247" t="s">
+        <v>320</v>
+      </c>
+      <c r="C19" s="248"/>
       <c r="D19" s="59">
-        <f>78/86</f>
-        <v>0.90697674418604646</v>
+        <v>0.78</v>
       </c>
       <c r="E19" s="59">
-        <f>78/86</f>
-        <v>0.90697674418604646</v>
+        <v>0.78</v>
       </c>
       <c r="F19" s="59">
-        <f>78/86</f>
-        <v>0.90697674418604646</v>
+        <f>0.78</f>
+        <v>0.78</v>
       </c>
       <c r="G19" s="59">
-        <f>83/89</f>
-        <v>0.93258426966292129</v>
+        <v>0.83</v>
       </c>
       <c r="H19" s="59">
-        <f>0.87/H18</f>
-        <v>0.95604395604395598</v>
+        <v>0.87</v>
       </c>
       <c r="I19" s="59">
-        <f>0.84/I18</f>
-        <v>0.93333333333333324</v>
+        <v>0.84</v>
       </c>
       <c r="J19" s="59">
-        <f>0.85/J18</f>
-        <v>0.94444444444444442</v>
+        <v>0.85</v>
       </c>
       <c r="K19" s="59">
-        <f>0.84/K18</f>
-        <v>0.95454545454545447</v>
+        <v>0.84</v>
       </c>
       <c r="L19" s="59">
-        <f>0.83/L18</f>
-        <v>0.96511627906976738</v>
+        <v>0.83</v>
       </c>
       <c r="M19" s="59">
-        <f>0.82/M18</f>
-        <v>0.95348837209302317</v>
+        <v>0.82</v>
       </c>
       <c r="N19" s="59">
-        <f>0.82/N18</f>
-        <v>0.96470588235294119</v>
+        <v>0.82</v>
       </c>
       <c r="O19" s="59">
-        <f>0.82/O18</f>
-        <v>0.96470588235294119</v>
+        <v>0.82</v>
       </c>
       <c r="P19" s="59">
-        <f>0.59/P18</f>
-        <v>0.98333333333333328</v>
+        <v>0.59</v>
       </c>
       <c r="Q19" s="59">
-        <f>0.59/0.77</f>
-        <v>0.76623376623376616</v>
+        <v>0.59</v>
       </c>
       <c r="R19" s="59">
-        <f>0.5/0.6</f>
-        <v>0.83333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="S19" s="59">
         <v>0</v>
@@ -7981,32 +7857,32 @@
       <c r="T19" s="59">
         <v>0</v>
       </c>
-      <c r="U19" s="183">
+      <c r="U19" s="173">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B20" s="294" t="s">
-        <v>253</v>
-      </c>
-      <c r="C20" s="295"/>
+      <c r="B20" s="247" t="s">
+        <v>321</v>
+      </c>
+      <c r="C20" s="248"/>
       <c r="D20" s="59">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="E20" s="59">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="F20" s="59">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="G20" s="59">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="H20" s="59">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="I20" s="59">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="J20" s="59">
         <v>0</v>
@@ -8041,7 +7917,7 @@
       <c r="T20" s="59">
         <v>0</v>
       </c>
-      <c r="U20" s="183">
+      <c r="U20" s="173">
         <v>0</v>
       </c>
     </row>
@@ -8068,54 +7944,54 @@
       <c r="U21" s="55"/>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B22" s="299" t="s">
-        <v>257</v>
-      </c>
-      <c r="C22" s="300"/>
-      <c r="D22" s="300"/>
-      <c r="E22" s="300"/>
-      <c r="F22" s="300"/>
-      <c r="G22" s="300"/>
-      <c r="H22" s="300"/>
-      <c r="I22" s="300"/>
-      <c r="J22" s="300"/>
-      <c r="K22" s="184"/>
-      <c r="L22" s="184"/>
-      <c r="M22" s="184"/>
-      <c r="N22" s="184"/>
-      <c r="O22" s="184"/>
-      <c r="P22" s="184"/>
-      <c r="Q22" s="184"/>
-      <c r="R22" s="184"/>
-      <c r="S22" s="184"/>
-      <c r="T22" s="184"/>
-      <c r="U22" s="185"/>
+      <c r="B22" s="242" t="s">
+        <v>255</v>
+      </c>
+      <c r="C22" s="243"/>
+      <c r="D22" s="243"/>
+      <c r="E22" s="243"/>
+      <c r="F22" s="243"/>
+      <c r="G22" s="243"/>
+      <c r="H22" s="243"/>
+      <c r="I22" s="243"/>
+      <c r="J22" s="243"/>
+      <c r="K22" s="174"/>
+      <c r="L22" s="174"/>
+      <c r="M22" s="174"/>
+      <c r="N22" s="174"/>
+      <c r="O22" s="174"/>
+      <c r="P22" s="174"/>
+      <c r="Q22" s="174"/>
+      <c r="R22" s="174"/>
+      <c r="S22" s="174"/>
+      <c r="T22" s="174"/>
+      <c r="U22" s="175"/>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B23" s="294" t="s">
+      <c r="B23" s="247" t="s">
         <v>250</v>
       </c>
-      <c r="C23" s="295"/>
-      <c r="D23" s="181">
+      <c r="C23" s="248"/>
+      <c r="D23" s="171">
         <v>2019</v>
       </c>
-      <c r="E23" s="181">
+      <c r="E23" s="171">
         <v>2020</v>
       </c>
-      <c r="F23" s="181">
+      <c r="F23" s="171">
         <v>2021</v>
       </c>
-      <c r="G23" s="181">
+      <c r="G23" s="171">
         <v>2022</v>
       </c>
-      <c r="H23" s="181">
+      <c r="H23" s="171">
         <v>2023</v>
       </c>
-      <c r="I23" s="181">
+      <c r="I23" s="171">
         <v>2024</v>
       </c>
-      <c r="J23" s="67" t="s">
-        <v>256</v>
+      <c r="J23" s="65" t="s">
+        <v>254</v>
       </c>
       <c r="K23" s="53"/>
       <c r="L23" s="53"/>
@@ -8130,10 +8006,10 @@
       <c r="U23" s="55"/>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B24" s="294" t="s">
+      <c r="B24" s="247" t="s">
         <v>251</v>
       </c>
-      <c r="C24" s="295"/>
+      <c r="C24" s="248"/>
       <c r="D24" s="59">
         <f>E24</f>
         <v>0.53</v>
@@ -8159,8 +8035,8 @@
       <c r="K24" s="53"/>
       <c r="L24" s="53"/>
       <c r="M24" s="53"/>
-      <c r="N24" s="184" t="s">
-        <v>259</v>
+      <c r="N24" s="174" t="s">
+        <v>256</v>
       </c>
       <c r="O24" s="53"/>
       <c r="P24" s="53"/>
@@ -8171,10 +8047,10 @@
       <c r="U24" s="55"/>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B25" s="294" t="s">
-        <v>252</v>
-      </c>
-      <c r="C25" s="295"/>
+      <c r="B25" s="247" t="s">
+        <v>320</v>
+      </c>
+      <c r="C25" s="248"/>
       <c r="D25" s="59">
         <f>E25</f>
         <v>0.35830985915492958</v>
@@ -8212,29 +8088,29 @@
       <c r="U25" s="55"/>
     </row>
     <row r="26" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="297" t="s">
-        <v>253</v>
-      </c>
-      <c r="C26" s="298"/>
-      <c r="D26" s="186">
-        <v>0</v>
-      </c>
-      <c r="E26" s="186">
-        <v>0</v>
-      </c>
-      <c r="F26" s="186">
-        <v>0</v>
-      </c>
-      <c r="G26" s="186">
-        <v>0</v>
-      </c>
-      <c r="H26" s="186">
-        <v>0</v>
-      </c>
-      <c r="I26" s="186">
-        <v>0</v>
-      </c>
-      <c r="J26" s="186">
+      <c r="B26" s="247" t="s">
+        <v>321</v>
+      </c>
+      <c r="C26" s="248"/>
+      <c r="D26" s="176">
+        <v>0</v>
+      </c>
+      <c r="E26" s="176">
+        <v>0</v>
+      </c>
+      <c r="F26" s="176">
+        <v>0</v>
+      </c>
+      <c r="G26" s="176">
+        <v>0</v>
+      </c>
+      <c r="H26" s="176">
+        <v>0</v>
+      </c>
+      <c r="I26" s="176">
+        <v>0</v>
+      </c>
+      <c r="J26" s="176">
         <v>0</v>
       </c>
       <c r="K26" s="57"/>
@@ -8249,37 +8125,28 @@
       <c r="T26" s="57"/>
       <c r="U26" s="58"/>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="M28" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="E29" s="187"/>
-      <c r="F29" s="187"/>
-      <c r="G29" s="187"/>
-      <c r="H29" s="187"/>
-      <c r="I29" s="187"/>
-      <c r="J29" s="187"/>
-    </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="E30" s="187"/>
-      <c r="F30" s="187"/>
-      <c r="G30" s="187"/>
-      <c r="H30" s="187"/>
-      <c r="I30" s="187"/>
-      <c r="J30" s="187"/>
-    </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="E31" s="187"/>
-      <c r="F31" s="187"/>
-      <c r="G31" s="187"/>
-      <c r="H31" s="187"/>
-      <c r="I31" s="187"/>
-      <c r="J31" s="187"/>
-    </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="I10:K10"/>
     <mergeCell ref="B26:C26"/>
@@ -8292,26 +8159,6 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B16:U16"/>
     <mergeCell ref="I11:K11"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8320,7 +8167,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E92792FA-EF80-0944-A988-9D9A31764F29}">
-  <dimension ref="B1:H29"/>
+  <dimension ref="B1:F23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
@@ -8328,12 +8175,10 @@
     <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.6640625" customWidth="1"/>
-    <col min="8" max="8" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:6" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="60" t="s">
         <v>247</v>
       </c>
@@ -8349,435 +8194,299 @@
       <c r="F2" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="61" t="s">
-        <v>281</v>
-      </c>
-      <c r="H2" s="63" t="s">
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B3" s="183" t="s">
+        <v>243</v>
+      </c>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="185"/>
+    </row>
+    <row r="4" spans="2:6" s="270" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="269" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="270" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" s="270">
+        <v>0.8</v>
+      </c>
+      <c r="E4" s="271">
+        <v>0.65</v>
+      </c>
+      <c r="F4" s="272"/>
+    </row>
+    <row r="5" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="273" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" s="274"/>
+      <c r="D5" s="274"/>
+      <c r="E5" s="274"/>
+      <c r="F5" s="275"/>
+    </row>
+    <row r="6" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="269" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="270" t="s">
+        <v>258</v>
+      </c>
+      <c r="D6" s="270">
+        <v>0.8</v>
+      </c>
+      <c r="E6" s="271" t="s">
+        <v>259</v>
+      </c>
+      <c r="F6" s="272" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="273" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" s="274"/>
+      <c r="D7" s="274"/>
+      <c r="E7" s="274"/>
+      <c r="F7" s="275"/>
+    </row>
+    <row r="8" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="277" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="278" t="s">
+        <v>283</v>
+      </c>
+      <c r="D8" s="271">
+        <v>0.68</v>
+      </c>
+      <c r="E8" s="271" t="s">
+        <v>285</v>
+      </c>
+      <c r="F8" s="279" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="277" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="278" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="210" t="s">
-        <v>243</v>
-      </c>
-      <c r="C3" s="211"/>
-      <c r="D3" s="211"/>
-      <c r="E3" s="211"/>
-      <c r="F3" s="212"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="76"/>
-    </row>
-    <row r="4" spans="2:8" s="197" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="196" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="197" t="s">
-        <v>248</v>
-      </c>
-      <c r="D4" s="197">
+      <c r="D9" s="271">
+        <v>0.76</v>
+      </c>
+      <c r="E9" s="271" t="s">
+        <v>286</v>
+      </c>
+      <c r="F9" s="279"/>
+    </row>
+    <row r="10" spans="2:6" s="276" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="269" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" s="278" t="s">
+        <v>154</v>
+      </c>
+      <c r="D10" s="270">
         <v>0.8</v>
       </c>
-      <c r="E4" s="198">
-        <v>0.65</v>
-      </c>
-      <c r="F4" s="199"/>
-      <c r="G4" s="198">
-        <v>2</v>
-      </c>
-      <c r="H4" s="200">
-        <f>G4</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="210" t="s">
-        <v>260</v>
-      </c>
-      <c r="C5" s="211"/>
-      <c r="D5" s="211"/>
-      <c r="E5" s="211"/>
-      <c r="F5" s="212"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="194"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B6" s="207" t="s">
+      <c r="E10" s="271" t="s">
+        <v>271</v>
+      </c>
+      <c r="F10" s="279"/>
+    </row>
+    <row r="11" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="269" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="64" t="s">
-        <v>261</v>
-      </c>
-      <c r="D6" s="64">
+      <c r="C11" s="270" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="270">
         <v>0.8</v>
       </c>
-      <c r="E6" s="208" t="s">
-        <v>262</v>
-      </c>
-      <c r="F6" s="209" t="s">
+      <c r="E11" s="271" t="s">
+        <v>271</v>
+      </c>
+      <c r="F11" s="279"/>
+    </row>
+    <row r="12" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="269" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" s="270" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" s="270">
+        <v>0.9</v>
+      </c>
+      <c r="E12" s="271" t="s">
+        <v>277</v>
+      </c>
+      <c r="F12" s="279"/>
+    </row>
+    <row r="13" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="269" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" s="270" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" s="270">
+        <v>0.9</v>
+      </c>
+      <c r="E13" s="271" t="s">
         <v>272</v>
       </c>
-      <c r="G6" s="208">
-        <v>3</v>
-      </c>
-      <c r="H6" s="194">
-        <f>H4*G6</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="210" t="s">
+      <c r="F13" s="279"/>
+    </row>
+    <row r="14" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="273" t="s">
+        <v>296</v>
+      </c>
+      <c r="C14" s="274"/>
+      <c r="D14" s="274"/>
+      <c r="E14" s="274"/>
+      <c r="F14" s="275"/>
+    </row>
+    <row r="15" spans="2:6" s="276" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="269" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="270" t="s">
         <v>273</v>
       </c>
-      <c r="C7" s="211"/>
-      <c r="D7" s="211"/>
-      <c r="E7" s="211"/>
-      <c r="F7" s="212"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="194"/>
-    </row>
-    <row r="8" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="313" t="s">
-        <v>164</v>
-      </c>
-      <c r="C8" s="314" t="s">
-        <v>290</v>
-      </c>
-      <c r="D8" s="315">
-        <v>0.68</v>
-      </c>
-      <c r="E8" s="315" t="s">
-        <v>292</v>
-      </c>
-      <c r="F8" s="217" t="s">
-        <v>294</v>
-      </c>
-      <c r="G8" s="215">
-        <v>3</v>
-      </c>
-      <c r="H8" s="216">
-        <f>H6*G8</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="313" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="314" t="s">
-        <v>291</v>
-      </c>
-      <c r="D9" s="315">
-        <v>0.76</v>
-      </c>
-      <c r="E9" s="315" t="s">
-        <v>293</v>
-      </c>
-      <c r="F9" s="217"/>
-      <c r="G9" s="215"/>
-      <c r="H9" s="216"/>
-    </row>
-    <row r="10" spans="2:8" s="202" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="203" t="s">
-        <v>164</v>
-      </c>
-      <c r="C10" s="314" t="s">
-        <v>154</v>
-      </c>
-      <c r="D10" s="167">
-        <v>0.8</v>
-      </c>
-      <c r="E10" s="315" t="s">
+      <c r="D15" s="270">
+        <v>0</v>
+      </c>
+      <c r="E15" s="270">
+        <v>0.1</v>
+      </c>
+      <c r="F15" s="279" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="269" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="270" t="s">
         <v>274</v>
       </c>
-      <c r="F10" s="217"/>
-      <c r="G10" s="215"/>
-      <c r="H10" s="216"/>
-    </row>
-    <row r="11" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="203" t="s">
-        <v>164</v>
-      </c>
-      <c r="C11" s="167" t="s">
-        <v>155</v>
-      </c>
-      <c r="D11" s="167">
-        <v>0.8</v>
-      </c>
-      <c r="E11" s="315" t="s">
-        <v>274</v>
-      </c>
-      <c r="F11" s="217"/>
-      <c r="G11" s="215"/>
-      <c r="H11" s="216"/>
-    </row>
-    <row r="12" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="203" t="s">
-        <v>164</v>
-      </c>
-      <c r="C12" s="167" t="s">
-        <v>159</v>
-      </c>
-      <c r="D12" s="167">
+      <c r="D16" s="270">
+        <v>0</v>
+      </c>
+      <c r="E16" s="270">
+        <v>0.1</v>
+      </c>
+      <c r="F16" s="279"/>
+    </row>
+    <row r="17" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="269" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" s="270" t="s">
+        <v>275</v>
+      </c>
+      <c r="D17" s="270">
+        <v>0</v>
+      </c>
+      <c r="E17" s="270">
+        <v>0.1</v>
+      </c>
+      <c r="F17" s="279"/>
+    </row>
+    <row r="18" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="273" t="s">
+        <v>315</v>
+      </c>
+      <c r="C18" s="274"/>
+      <c r="D18" s="274"/>
+      <c r="E18" s="274"/>
+      <c r="F18" s="275"/>
+    </row>
+    <row r="19" spans="2:6" s="276" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+      <c r="B19" s="269" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="270" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="280" t="s">
+        <v>299</v>
+      </c>
+      <c r="E19" s="280" t="s">
+        <v>166</v>
+      </c>
+      <c r="F19" s="281" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="273" t="s">
+        <v>310</v>
+      </c>
+      <c r="C20" s="274"/>
+      <c r="D20" s="274"/>
+      <c r="E20" s="274"/>
+      <c r="F20" s="275"/>
+    </row>
+    <row r="21" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="269" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="270" t="s">
+        <v>317</v>
+      </c>
+      <c r="D21" s="270">
+        <v>0.96</v>
+      </c>
+      <c r="E21" s="270">
         <v>0.9</v>
       </c>
-      <c r="E12" s="315" t="s">
-        <v>280</v>
-      </c>
-      <c r="F12" s="217"/>
-      <c r="G12" s="215"/>
-      <c r="H12" s="216"/>
-    </row>
-    <row r="13" spans="2:8" s="202" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="203" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="167" t="s">
-        <v>160</v>
-      </c>
-      <c r="D13" s="167">
-        <v>0.9</v>
-      </c>
-      <c r="E13" s="315" t="s">
-        <v>275</v>
-      </c>
-      <c r="F13" s="217"/>
-      <c r="G13" s="215"/>
-      <c r="H13" s="216"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="210" t="s">
-        <v>305</v>
-      </c>
-      <c r="C14" s="211"/>
-      <c r="D14" s="211"/>
-      <c r="E14" s="211"/>
-      <c r="F14" s="212"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="194"/>
-    </row>
-    <row r="15" spans="2:8" s="201" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="196" t="s">
-        <v>149</v>
-      </c>
-      <c r="C15" s="197" t="s">
-        <v>276</v>
-      </c>
-      <c r="D15" s="197">
-        <v>0</v>
-      </c>
-      <c r="E15" s="197">
-        <v>0.1</v>
-      </c>
-      <c r="F15" s="218" t="s">
-        <v>279</v>
-      </c>
-      <c r="G15" s="311">
-        <v>2</v>
-      </c>
-      <c r="H15" s="312">
-        <f>H8*G15</f>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="196" t="s">
-        <v>149</v>
-      </c>
-      <c r="C16" s="197" t="s">
-        <v>277</v>
-      </c>
-      <c r="D16" s="197">
-        <v>0</v>
-      </c>
-      <c r="E16" s="197">
-        <v>0.1</v>
-      </c>
-      <c r="F16" s="218"/>
-      <c r="G16" s="311"/>
-      <c r="H16" s="312"/>
-    </row>
-    <row r="17" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="196" t="s">
-        <v>149</v>
-      </c>
-      <c r="C17" s="197" t="s">
-        <v>278</v>
-      </c>
-      <c r="D17" s="197">
-        <v>0</v>
-      </c>
-      <c r="E17" s="197">
-        <v>0.1</v>
-      </c>
-      <c r="F17" s="218"/>
-      <c r="G17" s="311"/>
-      <c r="H17" s="312"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" s="210" t="s">
-        <v>324</v>
-      </c>
-      <c r="C18" s="211"/>
-      <c r="D18" s="211"/>
-      <c r="E18" s="211"/>
-      <c r="F18" s="212"/>
-      <c r="G18" s="195"/>
-      <c r="H18" s="194"/>
-    </row>
-    <row r="19" spans="2:8" s="201" customFormat="1" ht="49" x14ac:dyDescent="0.2">
-      <c r="B19" s="196" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="197" t="s">
-        <v>96</v>
-      </c>
-      <c r="D19" s="204" t="s">
-        <v>308</v>
-      </c>
-      <c r="E19" s="204" t="s">
-        <v>166</v>
-      </c>
-      <c r="F19" s="205" t="s">
-        <v>325</v>
-      </c>
-      <c r="G19" s="206">
-        <v>2</v>
-      </c>
-      <c r="H19" s="200">
-        <f>H15*G19</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B20" s="210" t="s">
+      <c r="F21" s="282" t="s">
         <v>319</v>
       </c>
-      <c r="C20" s="211"/>
-      <c r="D20" s="211"/>
-      <c r="E20" s="211"/>
-      <c r="F20" s="212"/>
-      <c r="G20" s="135"/>
-      <c r="H20" s="143"/>
-    </row>
-    <row r="21" spans="2:8" s="201" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="196" t="s">
+    </row>
+    <row r="22" spans="2:6" s="276" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="283" t="s">
         <v>140</v>
       </c>
-      <c r="C21" s="197" t="s">
-        <v>326</v>
-      </c>
-      <c r="D21" s="197">
-        <v>0.96</v>
-      </c>
-      <c r="E21" s="197">
-        <v>0.9</v>
-      </c>
-      <c r="F21" s="305" t="s">
-        <v>328</v>
-      </c>
-      <c r="G21" s="213">
-        <v>2</v>
-      </c>
-      <c r="H21" s="219">
-        <f>H19*G21</f>
-        <v>144</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" s="201" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="306" t="s">
-        <v>140</v>
-      </c>
-      <c r="C22" s="307" t="s">
-        <v>320</v>
-      </c>
-      <c r="D22" s="307">
+      <c r="C22" s="284" t="s">
+        <v>311</v>
+      </c>
+      <c r="D22" s="284">
         <v>0.7</v>
       </c>
-      <c r="E22" s="307">
+      <c r="E22" s="284">
         <v>0.85</v>
       </c>
-      <c r="F22" s="308"/>
-      <c r="G22" s="309"/>
-      <c r="H22" s="310"/>
-    </row>
-    <row r="23" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F22" s="285"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="78" t="s">
-        <v>282</v>
-      </c>
-      <c r="G24" s="79">
-        <f>G4+G6+G8+G15+G19+G21-COUNT(G3:G22)</f>
-        <v>8</v>
-      </c>
-      <c r="H24" s="8"/>
-    </row>
-    <row r="25" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="77" t="s">
-        <v>283</v>
-      </c>
-      <c r="G25" s="80">
-        <f>H21</f>
-        <v>144</v>
-      </c>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C27" s="214" t="s">
-        <v>296</v>
-      </c>
-      <c r="D27" s="214"/>
-      <c r="E27" s="214"/>
-      <c r="F27" s="214"/>
-      <c r="G27" s="214"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C28" s="214"/>
-      <c r="D28" s="214"/>
-      <c r="E28" s="214"/>
-      <c r="F28" s="214"/>
-      <c r="G28" s="214"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C29" s="214"/>
-      <c r="D29" s="214"/>
-      <c r="E29" s="214"/>
-      <c r="F29" s="214"/>
-      <c r="G29" s="214"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="F8:F13"/>
-    <mergeCell ref="H8:H13"/>
-    <mergeCell ref="C27:G29"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="F21:F22"/>
+  <mergeCells count="9">
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="G8:G13"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F8:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/project_documents/parameterDirectory.xlsx
+++ b/project_documents/parameterDirectory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabian/Documents/DPhil Work/Academic Work/EnglandCervicalScreeningProject/project_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4815A5-6FD2-9747-B80F-0C537C8DEF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25532B27-1E5C-8449-9D95-5DCBC66D86F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18820" yWindow="920" windowWidth="10420" windowHeight="16880" firstSheet="6" activeTab="7" xr2:uid="{9CDCC384-B02C-4946-8A51-C0AA91FF93D1}"/>
+    <workbookView xWindow="14780" yWindow="920" windowWidth="14480" windowHeight="16880" activeTab="7" xr2:uid="{9CDCC384-B02C-4946-8A51-C0AA91FF93D1}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -2104,7 +2104,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="281">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2508,6 +2508,29 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2517,6 +2540,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2685,6 +2711,12 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2700,12 +2732,6 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2765,43 +2791,6 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3251,11 +3240,11 @@
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="186" t="s">
+      <c r="B4" s="198" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
+      <c r="C4" s="198"/>
+      <c r="D4" s="198"/>
     </row>
     <row r="5" spans="2:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -3333,26 +3322,26 @@
       </c>
     </row>
     <row r="13" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="187" t="s">
+      <c r="B13" s="199" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="187"/>
-      <c r="D13" s="187"/>
+      <c r="C13" s="199"/>
+      <c r="D13" s="199"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="187"/>
-      <c r="C14" s="187"/>
-      <c r="D14" s="187"/>
+      <c r="B14" s="199"/>
+      <c r="C14" s="199"/>
+      <c r="D14" s="199"/>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="187"/>
-      <c r="C15" s="187"/>
-      <c r="D15" s="187"/>
+      <c r="B15" s="199"/>
+      <c r="C15" s="199"/>
+      <c r="D15" s="199"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="187"/>
-      <c r="C16" s="187"/>
-      <c r="D16" s="187"/>
+      <c r="B16" s="199"/>
+      <c r="C16" s="199"/>
+      <c r="D16" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3383,13 +3372,13 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="190" t="s">
+      <c r="B3" s="202" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
+      <c r="C3" s="202"/>
+      <c r="D3" s="202"/>
+      <c r="E3" s="202"/>
+      <c r="F3" s="202"/>
     </row>
     <row r="5" spans="2:6" ht="35" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
@@ -3409,7 +3398,7 @@
       </c>
     </row>
     <row r="6" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B6" s="192" t="s">
+      <c r="B6" s="204" t="s">
         <v>177</v>
       </c>
       <c r="C6" s="27" t="s">
@@ -3424,7 +3413,7 @@
       <c r="F6" s="14"/>
     </row>
     <row r="7" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" s="193"/>
+      <c r="B7" s="205"/>
       <c r="C7" s="28" t="s">
         <v>179</v>
       </c>
@@ -3437,7 +3426,7 @@
       <c r="F7" s="15"/>
     </row>
     <row r="8" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B8" s="193"/>
+      <c r="B8" s="205"/>
       <c r="C8" s="28" t="s">
         <v>180</v>
       </c>
@@ -3450,7 +3439,7 @@
       <c r="F8" s="15"/>
     </row>
     <row r="9" spans="2:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="B9" s="193"/>
+      <c r="B9" s="205"/>
       <c r="C9" s="28" t="s">
         <v>181</v>
       </c>
@@ -3463,7 +3452,7 @@
       <c r="F9" s="15"/>
     </row>
     <row r="10" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B10" s="194" t="s">
+      <c r="B10" s="206" t="s">
         <v>173</v>
       </c>
       <c r="C10" s="29" t="s">
@@ -3480,7 +3469,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B11" s="194"/>
+      <c r="B11" s="206"/>
       <c r="C11" s="29" t="s">
         <v>187</v>
       </c>
@@ -3495,7 +3484,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B12" s="194"/>
+      <c r="B12" s="206"/>
       <c r="C12" s="29" t="s">
         <v>188</v>
       </c>
@@ -3510,7 +3499,7 @@
       </c>
     </row>
     <row r="13" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B13" s="195" t="s">
+      <c r="B13" s="207" t="s">
         <v>174</v>
       </c>
       <c r="C13" s="30" t="s">
@@ -3527,7 +3516,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B14" s="195"/>
+      <c r="B14" s="207"/>
       <c r="C14" s="30" t="s">
         <v>113</v>
       </c>
@@ -3542,7 +3531,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B15" s="195"/>
+      <c r="B15" s="207"/>
       <c r="C15" s="30" t="s">
         <v>111</v>
       </c>
@@ -3557,7 +3546,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="B16" s="196" t="s">
+      <c r="B16" s="208" t="s">
         <v>175</v>
       </c>
       <c r="C16" s="31" t="s">
@@ -3572,7 +3561,7 @@
       <c r="F16" s="18"/>
     </row>
     <row r="17" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B17" s="196"/>
+      <c r="B17" s="208"/>
       <c r="C17" s="31" t="s">
         <v>133</v>
       </c>
@@ -3587,7 +3576,7 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="135" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="196"/>
+      <c r="B18" s="208"/>
       <c r="C18" s="31" t="s">
         <v>115</v>
       </c>
@@ -3609,7 +3598,7 @@
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B19" s="196"/>
+      <c r="B19" s="208"/>
       <c r="C19" s="31" t="s">
         <v>114</v>
       </c>
@@ -3628,30 +3617,30 @@
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B22" s="197" t="s">
+      <c r="B22" s="209" t="s">
         <v>132</v>
       </c>
       <c r="C22" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="188" t="s">
+      <c r="D22" s="200" t="s">
         <v>216</v>
       </c>
-      <c r="E22" s="189"/>
+      <c r="E22" s="201"/>
     </row>
     <row r="23" spans="2:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="198"/>
+      <c r="B23" s="210"/>
       <c r="C23" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="190" t="s">
+      <c r="D23" s="202" t="s">
         <v>218</v>
       </c>
-      <c r="E23" s="191"/>
+      <c r="E23" s="203"/>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="198"/>
+      <c r="B24" s="210"/>
       <c r="C24" s="8" t="s">
         <v>114</v>
       </c>
@@ -3722,30 +3711,30 @@
   <sheetData>
     <row r="2" spans="1:10" s="64" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="177"/>
-      <c r="B2" s="219" t="s">
+      <c r="B2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="223" t="s">
+      <c r="C2" s="235" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="229" t="s">
+      <c r="D2" s="241" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="230"/>
-      <c r="F2" s="231" t="s">
+      <c r="E2" s="242"/>
+      <c r="F2" s="243" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="231"/>
-      <c r="H2" s="231"/>
-      <c r="I2" s="230"/>
-      <c r="J2" s="221" t="s">
+      <c r="G2" s="243"/>
+      <c r="H2" s="243"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="233" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="64" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="177"/>
-      <c r="B3" s="220"/>
-      <c r="C3" s="224"/>
+      <c r="B3" s="232"/>
+      <c r="C3" s="236"/>
       <c r="D3" s="11" t="s">
         <v>9</v>
       </c>
@@ -3764,10 +3753,10 @@
       <c r="I3" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="222"/>
+      <c r="J3" s="234"/>
     </row>
     <row r="4" spans="1:10" s="78" customFormat="1" ht="91" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="214" t="s">
+      <c r="A4" s="226" t="s">
         <v>85</v>
       </c>
       <c r="B4" s="73" t="s">
@@ -3791,7 +3780,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" s="78" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A5" s="214"/>
+      <c r="A5" s="226"/>
       <c r="B5" s="80" t="s">
         <v>18</v>
       </c>
@@ -3813,7 +3802,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" s="78" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A6" s="214"/>
+      <c r="A6" s="226"/>
       <c r="B6" s="80" t="s">
         <v>22</v>
       </c>
@@ -3833,7 +3822,7 @@
       <c r="J6" s="81"/>
     </row>
     <row r="7" spans="1:10" s="78" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="214"/>
+      <c r="A7" s="226"/>
       <c r="B7" s="80" t="s">
         <v>101</v>
       </c>
@@ -3853,7 +3842,7 @@
       <c r="J7" s="81"/>
     </row>
     <row r="8" spans="1:10" s="78" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A8" s="214"/>
+      <c r="A8" s="226"/>
       <c r="B8" s="80" t="s">
         <v>23</v>
       </c>
@@ -3897,7 +3886,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="95" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A10" s="215" t="s">
+      <c r="A10" s="227" t="s">
         <v>87</v>
       </c>
       <c r="B10" s="90" t="s">
@@ -3921,37 +3910,37 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="95" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="215"/>
-      <c r="B11" s="217" t="s">
+      <c r="A11" s="227"/>
+      <c r="B11" s="229" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="225" t="s">
+      <c r="C11" s="237" t="s">
         <v>39</v>
       </c>
       <c r="D11" s="93"/>
-      <c r="E11" s="217" t="s">
+      <c r="E11" s="229" t="s">
         <v>318</v>
       </c>
       <c r="F11" s="93"/>
       <c r="G11" s="94"/>
       <c r="H11" s="94"/>
       <c r="I11" s="90"/>
-      <c r="J11" s="227"/>
+      <c r="J11" s="239"/>
     </row>
     <row r="12" spans="1:10" s="95" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="215"/>
-      <c r="B12" s="218"/>
-      <c r="C12" s="226"/>
+      <c r="A12" s="227"/>
+      <c r="B12" s="230"/>
+      <c r="C12" s="238"/>
       <c r="D12" s="93"/>
-      <c r="E12" s="218"/>
+      <c r="E12" s="230"/>
       <c r="F12" s="93"/>
       <c r="G12" s="94"/>
       <c r="H12" s="94"/>
       <c r="I12" s="90"/>
-      <c r="J12" s="228"/>
+      <c r="J12" s="240"/>
     </row>
     <row r="13" spans="1:10" s="100" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A13" s="216" t="s">
+      <c r="A13" s="228" t="s">
         <v>88</v>
       </c>
       <c r="B13" s="96" t="s">
@@ -3973,7 +3962,7 @@
       <c r="J13" s="98"/>
     </row>
     <row r="14" spans="1:10" s="100" customFormat="1" ht="188" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="216"/>
+      <c r="A14" s="228"/>
       <c r="B14" s="96" t="s">
         <v>35</v>
       </c>
@@ -3995,7 +3984,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" s="100" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="216"/>
+      <c r="A15" s="228"/>
       <c r="B15" s="96" t="s">
         <v>44</v>
       </c>
@@ -4015,7 +4004,7 @@
       <c r="J15" s="98"/>
     </row>
     <row r="16" spans="1:10" s="100" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A16" s="216"/>
+      <c r="A16" s="228"/>
       <c r="B16" s="96" t="s">
         <v>47</v>
       </c>
@@ -4037,7 +4026,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" s="100" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="216"/>
+      <c r="A17" s="228"/>
       <c r="B17" s="96" t="s">
         <v>51</v>
       </c>
@@ -4057,7 +4046,7 @@
       <c r="J17" s="98"/>
     </row>
     <row r="18" spans="1:10" s="100" customFormat="1" ht="135" x14ac:dyDescent="0.2">
-      <c r="A18" s="216"/>
+      <c r="A18" s="228"/>
       <c r="B18" s="96" t="s">
         <v>55</v>
       </c>
@@ -4081,7 +4070,7 @@
       <c r="J18" s="98"/>
     </row>
     <row r="19" spans="1:10" s="100" customFormat="1" ht="105" x14ac:dyDescent="0.2">
-      <c r="A19" s="216"/>
+      <c r="A19" s="228"/>
       <c r="B19" s="96" t="s">
         <v>58</v>
       </c>
@@ -4105,7 +4094,7 @@
       <c r="J19" s="98"/>
     </row>
     <row r="20" spans="1:10" s="100" customFormat="1" ht="115" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="216"/>
+      <c r="A20" s="228"/>
       <c r="B20" s="96" t="s">
         <v>61</v>
       </c>
@@ -4125,51 +4114,51 @@
       <c r="J20" s="102"/>
     </row>
     <row r="21" spans="1:10" s="43" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="216"/>
+      <c r="A21" s="228"/>
       <c r="B21" s="180" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="202" t="s">
+      <c r="C21" s="214" t="s">
         <v>98</v>
       </c>
       <c r="D21" s="102" t="s">
         <v>165</v>
       </c>
-      <c r="E21" s="199" t="s">
+      <c r="E21" s="211" t="s">
         <v>99</v>
       </c>
       <c r="F21" s="70"/>
       <c r="G21" s="71"/>
       <c r="H21" s="71"/>
-      <c r="I21" s="199" t="s">
+      <c r="I21" s="211" t="s">
         <v>167</v>
       </c>
-      <c r="J21" s="205" t="s">
+      <c r="J21" s="217" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="43" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="216"/>
+      <c r="A22" s="228"/>
       <c r="B22" s="181" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="203"/>
+      <c r="C22" s="215"/>
       <c r="D22" s="182" t="s">
         <v>166</v>
       </c>
-      <c r="E22" s="200"/>
+      <c r="E22" s="212"/>
       <c r="F22" s="69"/>
       <c r="G22" s="67"/>
       <c r="H22" s="67"/>
-      <c r="I22" s="200"/>
-      <c r="J22" s="206"/>
+      <c r="I22" s="212"/>
+      <c r="J22" s="218"/>
     </row>
     <row r="23" spans="1:10" s="43" customFormat="1" ht="180" x14ac:dyDescent="0.2">
-      <c r="A23" s="216"/>
+      <c r="A23" s="228"/>
       <c r="B23" s="96" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="204"/>
+      <c r="C23" s="216"/>
       <c r="D23" s="102" t="s">
         <v>299</v>
       </c>
@@ -4179,8 +4168,8 @@
       <c r="F23" s="72"/>
       <c r="G23" s="67"/>
       <c r="H23" s="67"/>
-      <c r="I23" s="201"/>
-      <c r="J23" s="207"/>
+      <c r="I23" s="213"/>
+      <c r="J23" s="219"/>
     </row>
     <row r="24" spans="1:10" s="43" customFormat="1" ht="255" x14ac:dyDescent="0.2">
       <c r="A24" s="179"/>
@@ -4253,7 +4242,7 @@
       <c r="B27" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="210" t="s">
+      <c r="C27" s="222" t="s">
         <v>79</v>
       </c>
       <c r="D27" s="114"/>
@@ -4279,7 +4268,7 @@
       <c r="B28" s="112" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="211"/>
+      <c r="C28" s="223"/>
       <c r="D28" s="114">
         <v>50</v>
       </c>
@@ -4297,7 +4286,7 @@
       <c r="B29" s="112" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="212"/>
+      <c r="C29" s="224"/>
       <c r="D29" s="114">
         <v>0</v>
       </c>
@@ -4385,7 +4374,7 @@
       <c r="J32" s="114"/>
     </row>
     <row r="33" spans="1:10" s="124" customFormat="1" ht="180" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="213" t="s">
+      <c r="A33" s="225" t="s">
         <v>239</v>
       </c>
       <c r="B33" s="120" t="s">
@@ -4404,12 +4393,12 @@
       <c r="G33" s="123"/>
       <c r="H33" s="123"/>
       <c r="I33" s="120"/>
-      <c r="J33" s="208" t="s">
+      <c r="J33" s="220" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="124" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A34" s="213"/>
+      <c r="A34" s="225"/>
       <c r="B34" s="120" t="s">
         <v>106</v>
       </c>
@@ -4426,7 +4415,7 @@
       <c r="G34" s="123"/>
       <c r="H34" s="123"/>
       <c r="I34" s="120"/>
-      <c r="J34" s="209"/>
+      <c r="J34" s="221"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4502,7 +4491,7 @@
       <c r="E2" s="148">
         <v>0.12</v>
       </c>
-      <c r="H2" s="232" t="s">
+      <c r="H2" s="244" t="s">
         <v>295</v>
       </c>
     </row>
@@ -4522,7 +4511,7 @@
       <c r="E3" s="152">
         <v>0.88</v>
       </c>
-      <c r="H3" s="232"/>
+      <c r="H3" s="244"/>
     </row>
     <row r="4" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="127" t="s">
@@ -4540,7 +4529,7 @@
       <c r="E4" s="152">
         <v>0</v>
       </c>
-      <c r="H4" s="232"/>
+      <c r="H4" s="244"/>
     </row>
     <row r="5" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="127" t="s">
@@ -4558,7 +4547,7 @@
       <c r="E5" s="148">
         <v>0.12</v>
       </c>
-      <c r="H5" s="232"/>
+      <c r="H5" s="244"/>
     </row>
     <row r="6" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="127" t="s">
@@ -4576,7 +4565,7 @@
       <c r="E6" s="152">
         <v>0.88</v>
       </c>
-      <c r="H6" s="232"/>
+      <c r="H6" s="244"/>
     </row>
     <row r="7" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="127" t="s">
@@ -4594,7 +4583,7 @@
       <c r="E7" s="152">
         <v>0</v>
       </c>
-      <c r="H7" s="232"/>
+      <c r="H7" s="244"/>
     </row>
     <row r="8" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="127" t="s">
@@ -4612,7 +4601,7 @@
       <c r="E8" s="148">
         <v>0.12</v>
       </c>
-      <c r="H8" s="232"/>
+      <c r="H8" s="244"/>
     </row>
     <row r="9" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="127" t="s">
@@ -4630,7 +4619,7 @@
       <c r="E9" s="152">
         <v>0.88</v>
       </c>
-      <c r="H9" s="232"/>
+      <c r="H9" s="244"/>
     </row>
     <row r="10" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="127" t="s">
@@ -4648,7 +4637,7 @@
       <c r="E10" s="152">
         <v>0</v>
       </c>
-      <c r="H10" s="232"/>
+      <c r="H10" s="244"/>
     </row>
     <row r="11" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="127" t="s">
@@ -4666,7 +4655,7 @@
       <c r="E11" s="148">
         <v>0.12</v>
       </c>
-      <c r="H11" s="232"/>
+      <c r="H11" s="244"/>
     </row>
     <row r="12" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="127" t="s">
@@ -4684,7 +4673,7 @@
       <c r="E12" s="152">
         <v>0.88</v>
       </c>
-      <c r="H12" s="232"/>
+      <c r="H12" s="244"/>
     </row>
     <row r="13" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="127" t="s">
@@ -4702,7 +4691,7 @@
       <c r="E13" s="152">
         <v>0</v>
       </c>
-      <c r="H13" s="232"/>
+      <c r="H13" s="244"/>
     </row>
     <row r="14" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="127" t="s">
@@ -4720,7 +4709,7 @@
       <c r="E14" s="148">
         <v>0.12</v>
       </c>
-      <c r="H14" s="232"/>
+      <c r="H14" s="244"/>
     </row>
     <row r="15" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="127" t="s">
@@ -4738,7 +4727,7 @@
       <c r="E15" s="152">
         <v>0.88</v>
       </c>
-      <c r="H15" s="232"/>
+      <c r="H15" s="244"/>
     </row>
     <row r="16" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="127" t="s">
@@ -4756,7 +4745,7 @@
       <c r="E16" s="152">
         <v>0</v>
       </c>
-      <c r="H16" s="232"/>
+      <c r="H16" s="244"/>
     </row>
     <row r="17" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="127" t="s">
@@ -4774,7 +4763,7 @@
       <c r="E17" s="148">
         <v>0.12</v>
       </c>
-      <c r="H17" s="232"/>
+      <c r="H17" s="244"/>
     </row>
     <row r="18" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="127" t="s">
@@ -4792,7 +4781,7 @@
       <c r="E18" s="152">
         <v>0.88</v>
       </c>
-      <c r="H18" s="232"/>
+      <c r="H18" s="244"/>
     </row>
     <row r="19" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="127" t="s">
@@ -4810,7 +4799,7 @@
       <c r="E19" s="152">
         <v>0</v>
       </c>
-      <c r="H19" s="232"/>
+      <c r="H19" s="244"/>
     </row>
     <row r="20" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="127" t="s">
@@ -4828,7 +4817,7 @@
       <c r="E20" s="148">
         <v>0.12</v>
       </c>
-      <c r="H20" s="232"/>
+      <c r="H20" s="244"/>
     </row>
     <row r="21" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="127" t="s">
@@ -4846,7 +4835,7 @@
       <c r="E21" s="152">
         <v>0.88</v>
       </c>
-      <c r="H21" s="232"/>
+      <c r="H21" s="244"/>
     </row>
     <row r="22" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="127" t="s">
@@ -4864,7 +4853,7 @@
       <c r="E22" s="152">
         <v>0</v>
       </c>
-      <c r="H22" s="232"/>
+      <c r="H22" s="244"/>
     </row>
     <row r="23" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="127" t="s">
@@ -4882,7 +4871,7 @@
       <c r="E23" s="148">
         <v>0.12</v>
       </c>
-      <c r="H23" s="232"/>
+      <c r="H23" s="244"/>
     </row>
     <row r="24" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="127" t="s">
@@ -4900,7 +4889,7 @@
       <c r="E24" s="152">
         <v>0.88</v>
       </c>
-      <c r="H24" s="232"/>
+      <c r="H24" s="244"/>
     </row>
     <row r="25" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="127" t="s">
@@ -4918,7 +4907,7 @@
       <c r="E25" s="152">
         <v>0</v>
       </c>
-      <c r="H25" s="232"/>
+      <c r="H25" s="244"/>
     </row>
     <row r="26" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="127" t="s">
@@ -4936,7 +4925,7 @@
       <c r="E26" s="148">
         <v>0.12</v>
       </c>
-      <c r="H26" s="232"/>
+      <c r="H26" s="244"/>
     </row>
     <row r="27" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="127" t="s">
@@ -4954,7 +4943,7 @@
       <c r="E27" s="152">
         <v>0.88</v>
       </c>
-      <c r="H27" s="232"/>
+      <c r="H27" s="244"/>
     </row>
     <row r="28" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="127" t="s">
@@ -4972,7 +4961,7 @@
       <c r="E28" s="152">
         <v>0</v>
       </c>
-      <c r="H28" s="232"/>
+      <c r="H28" s="244"/>
     </row>
     <row r="29" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="127" t="s">
@@ -4990,7 +4979,7 @@
       <c r="E29" s="148">
         <v>0.12</v>
       </c>
-      <c r="H29" s="232"/>
+      <c r="H29" s="244"/>
     </row>
     <row r="30" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="127" t="s">
@@ -5008,7 +4997,7 @@
       <c r="E30" s="152">
         <v>0.88</v>
       </c>
-      <c r="H30" s="232"/>
+      <c r="H30" s="244"/>
     </row>
     <row r="31" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="127" t="s">
@@ -5026,7 +5015,7 @@
       <c r="E31" s="152">
         <v>0</v>
       </c>
-      <c r="H31" s="232"/>
+      <c r="H31" s="244"/>
     </row>
     <row r="32" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="127" t="s">
@@ -5044,7 +5033,7 @@
       <c r="E32" s="148">
         <v>0.12</v>
       </c>
-      <c r="H32" s="232"/>
+      <c r="H32" s="244"/>
     </row>
     <row r="33" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="127" t="s">
@@ -5062,7 +5051,7 @@
       <c r="E33" s="152">
         <v>0.88</v>
       </c>
-      <c r="H33" s="232"/>
+      <c r="H33" s="244"/>
     </row>
     <row r="34" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="127" t="s">
@@ -5080,7 +5069,7 @@
       <c r="E34" s="152">
         <v>0</v>
       </c>
-      <c r="H34" s="232"/>
+      <c r="H34" s="244"/>
     </row>
     <row r="35" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="127" t="s">
@@ -5098,7 +5087,7 @@
       <c r="E35" s="148">
         <v>0.12</v>
       </c>
-      <c r="H35" s="232"/>
+      <c r="H35" s="244"/>
     </row>
     <row r="36" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="127" t="s">
@@ -5116,7 +5105,7 @@
       <c r="E36" s="152">
         <v>0.88</v>
       </c>
-      <c r="H36" s="232"/>
+      <c r="H36" s="244"/>
     </row>
     <row r="37" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="127" t="s">
@@ -5134,7 +5123,7 @@
       <c r="E37" s="152">
         <v>0</v>
       </c>
-      <c r="H37" s="232"/>
+      <c r="H37" s="244"/>
     </row>
     <row r="38" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="127" t="s">
@@ -5152,7 +5141,7 @@
       <c r="E38" s="152">
         <v>0.94</v>
       </c>
-      <c r="H38" s="232"/>
+      <c r="H38" s="244"/>
     </row>
     <row r="39" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="127" t="s">
@@ -5170,7 +5159,7 @@
       <c r="E39" s="152">
         <v>0.06</v>
       </c>
-      <c r="H39" s="232"/>
+      <c r="H39" s="244"/>
     </row>
     <row r="40" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="127" t="s">
@@ -5188,7 +5177,7 @@
       <c r="E40" s="152">
         <v>0</v>
       </c>
-      <c r="H40" s="232"/>
+      <c r="H40" s="244"/>
     </row>
     <row r="41" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="127" t="s">
@@ -5206,7 +5195,7 @@
       <c r="E41" s="152">
         <v>0.94</v>
       </c>
-      <c r="H41" s="232"/>
+      <c r="H41" s="244"/>
     </row>
     <row r="42" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="127" t="s">
@@ -5224,7 +5213,7 @@
       <c r="E42" s="152">
         <v>0.06</v>
       </c>
-      <c r="H42" s="232"/>
+      <c r="H42" s="244"/>
     </row>
     <row r="43" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="127" t="s">
@@ -5242,7 +5231,7 @@
       <c r="E43" s="152">
         <v>0</v>
       </c>
-      <c r="H43" s="232"/>
+      <c r="H43" s="244"/>
     </row>
     <row r="44" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="127" t="s">
@@ -5260,7 +5249,7 @@
       <c r="E44" s="152">
         <v>0.94</v>
       </c>
-      <c r="H44" s="232"/>
+      <c r="H44" s="244"/>
     </row>
     <row r="45" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="127" t="s">
@@ -5278,7 +5267,7 @@
       <c r="E45" s="152">
         <v>0.06</v>
       </c>
-      <c r="H45" s="232"/>
+      <c r="H45" s="244"/>
     </row>
     <row r="46" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="127" t="s">
@@ -5296,7 +5285,7 @@
       <c r="E46" s="152">
         <v>0</v>
       </c>
-      <c r="H46" s="232"/>
+      <c r="H46" s="244"/>
     </row>
     <row r="47" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="127" t="s">
@@ -5314,7 +5303,7 @@
       <c r="E47" s="152">
         <v>0.94</v>
       </c>
-      <c r="H47" s="232"/>
+      <c r="H47" s="244"/>
     </row>
     <row r="48" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="127" t="s">
@@ -5332,7 +5321,7 @@
       <c r="E48" s="152">
         <v>0.06</v>
       </c>
-      <c r="H48" s="232"/>
+      <c r="H48" s="244"/>
     </row>
     <row r="49" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="127" t="s">
@@ -5350,7 +5339,7 @@
       <c r="E49" s="152">
         <v>0</v>
       </c>
-      <c r="H49" s="232"/>
+      <c r="H49" s="244"/>
     </row>
     <row r="50" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="127" t="s">
@@ -5368,7 +5357,7 @@
       <c r="E50" s="152">
         <v>0.94</v>
       </c>
-      <c r="H50" s="232"/>
+      <c r="H50" s="244"/>
     </row>
     <row r="51" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="127" t="s">
@@ -5386,7 +5375,7 @@
       <c r="E51" s="152">
         <v>0.06</v>
       </c>
-      <c r="H51" s="232"/>
+      <c r="H51" s="244"/>
     </row>
     <row r="52" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="127" t="s">
@@ -5404,7 +5393,7 @@
       <c r="E52" s="152">
         <v>0</v>
       </c>
-      <c r="H52" s="232"/>
+      <c r="H52" s="244"/>
     </row>
     <row r="53" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="127" t="s">
@@ -5422,7 +5411,7 @@
       <c r="E53" s="152">
         <v>0.94</v>
       </c>
-      <c r="H53" s="232"/>
+      <c r="H53" s="244"/>
     </row>
     <row r="54" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="127" t="s">
@@ -5440,7 +5429,7 @@
       <c r="E54" s="152">
         <v>0.06</v>
       </c>
-      <c r="H54" s="232"/>
+      <c r="H54" s="244"/>
     </row>
     <row r="55" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="127" t="s">
@@ -5458,7 +5447,7 @@
       <c r="E55" s="152">
         <v>0</v>
       </c>
-      <c r="H55" s="232"/>
+      <c r="H55" s="244"/>
     </row>
     <row r="56" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="127" t="s">
@@ -5476,7 +5465,7 @@
       <c r="E56" s="152">
         <v>0.94</v>
       </c>
-      <c r="H56" s="232"/>
+      <c r="H56" s="244"/>
     </row>
     <row r="57" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="127" t="s">
@@ -5494,7 +5483,7 @@
       <c r="E57" s="152">
         <v>0.06</v>
       </c>
-      <c r="H57" s="232"/>
+      <c r="H57" s="244"/>
     </row>
     <row r="58" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="127" t="s">
@@ -5512,7 +5501,7 @@
       <c r="E58" s="152">
         <v>0</v>
       </c>
-      <c r="H58" s="232"/>
+      <c r="H58" s="244"/>
     </row>
     <row r="59" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="127" t="s">
@@ -5530,7 +5519,7 @@
       <c r="E59" s="152">
         <v>0.94</v>
       </c>
-      <c r="H59" s="232"/>
+      <c r="H59" s="244"/>
     </row>
     <row r="60" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="127" t="s">
@@ -5548,7 +5537,7 @@
       <c r="E60" s="152">
         <v>0.06</v>
       </c>
-      <c r="H60" s="232"/>
+      <c r="H60" s="244"/>
     </row>
     <row r="61" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="127" t="s">
@@ -5566,7 +5555,7 @@
       <c r="E61" s="152">
         <v>0</v>
       </c>
-      <c r="H61" s="232"/>
+      <c r="H61" s="244"/>
     </row>
     <row r="62" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="127" t="s">
@@ -5584,7 +5573,7 @@
       <c r="E62" s="152">
         <v>0.94</v>
       </c>
-      <c r="H62" s="232"/>
+      <c r="H62" s="244"/>
     </row>
     <row r="63" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="127" t="s">
@@ -5602,7 +5591,7 @@
       <c r="E63" s="152">
         <v>0.06</v>
       </c>
-      <c r="H63" s="232"/>
+      <c r="H63" s="244"/>
     </row>
     <row r="64" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="127" t="s">
@@ -5620,7 +5609,7 @@
       <c r="E64" s="152">
         <v>0</v>
       </c>
-      <c r="H64" s="232"/>
+      <c r="H64" s="244"/>
     </row>
     <row r="65" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="127" t="s">
@@ -5638,7 +5627,7 @@
       <c r="E65" s="152">
         <v>0.94</v>
       </c>
-      <c r="H65" s="232"/>
+      <c r="H65" s="244"/>
     </row>
     <row r="66" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="127" t="s">
@@ -5656,7 +5645,7 @@
       <c r="E66" s="152">
         <v>0.06</v>
       </c>
-      <c r="H66" s="232"/>
+      <c r="H66" s="244"/>
     </row>
     <row r="67" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="127" t="s">
@@ -5674,7 +5663,7 @@
       <c r="E67" s="152">
         <v>0</v>
       </c>
-      <c r="H67" s="232"/>
+      <c r="H67" s="244"/>
     </row>
     <row r="68" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="127" t="s">
@@ -5692,7 +5681,7 @@
       <c r="E68" s="152">
         <v>0.94</v>
       </c>
-      <c r="H68" s="232"/>
+      <c r="H68" s="244"/>
     </row>
     <row r="69" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="127" t="s">
@@ -5710,7 +5699,7 @@
       <c r="E69" s="152">
         <v>0.06</v>
       </c>
-      <c r="H69" s="232"/>
+      <c r="H69" s="244"/>
     </row>
     <row r="70" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="127" t="s">
@@ -5728,7 +5717,7 @@
       <c r="E70" s="152">
         <v>0</v>
       </c>
-      <c r="H70" s="232"/>
+      <c r="H70" s="244"/>
     </row>
     <row r="71" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="127" t="s">
@@ -5746,7 +5735,7 @@
       <c r="E71" s="152">
         <v>0.94</v>
       </c>
-      <c r="H71" s="232"/>
+      <c r="H71" s="244"/>
     </row>
     <row r="72" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="127" t="s">
@@ -5764,7 +5753,7 @@
       <c r="E72" s="152">
         <v>0.06</v>
       </c>
-      <c r="H72" s="232"/>
+      <c r="H72" s="244"/>
     </row>
     <row r="73" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="127" t="s">
@@ -5782,7 +5771,7 @@
       <c r="E73" s="152">
         <v>0</v>
       </c>
-      <c r="H73" s="232"/>
+      <c r="H73" s="244"/>
     </row>
     <row r="74" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="127" t="s">
@@ -5800,7 +5789,7 @@
       <c r="E74" s="152">
         <v>0.94</v>
       </c>
-      <c r="H74" s="232"/>
+      <c r="H74" s="244"/>
     </row>
     <row r="75" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="127" t="s">
@@ -5818,7 +5807,7 @@
       <c r="E75" s="152">
         <v>0.06</v>
       </c>
-      <c r="H75" s="232"/>
+      <c r="H75" s="244"/>
     </row>
     <row r="76" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="127" t="s">
@@ -5836,7 +5825,7 @@
       <c r="E76" s="152">
         <v>0</v>
       </c>
-      <c r="H76" s="232"/>
+      <c r="H76" s="244"/>
     </row>
     <row r="77" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="127" t="s">
@@ -5854,7 +5843,7 @@
       <c r="E77" s="152">
         <v>0.94</v>
       </c>
-      <c r="H77" s="232"/>
+      <c r="H77" s="244"/>
     </row>
     <row r="78" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="127" t="s">
@@ -5872,7 +5861,7 @@
       <c r="E78" s="152">
         <v>0.06</v>
       </c>
-      <c r="H78" s="232"/>
+      <c r="H78" s="244"/>
     </row>
     <row r="79" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="127" t="s">
@@ -5890,7 +5879,7 @@
       <c r="E79" s="152">
         <v>0</v>
       </c>
-      <c r="H79" s="232"/>
+      <c r="H79" s="244"/>
     </row>
     <row r="80" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="127" t="s">
@@ -5908,7 +5897,7 @@
       <c r="E80" s="152">
         <v>0.94</v>
       </c>
-      <c r="H80" s="232"/>
+      <c r="H80" s="244"/>
     </row>
     <row r="81" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="127" t="s">
@@ -5926,7 +5915,7 @@
       <c r="E81" s="152">
         <v>0.06</v>
       </c>
-      <c r="H81" s="232"/>
+      <c r="H81" s="244"/>
     </row>
     <row r="82" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="127" t="s">
@@ -5944,7 +5933,7 @@
       <c r="E82" s="152">
         <v>0</v>
       </c>
-      <c r="H82" s="232"/>
+      <c r="H82" s="244"/>
     </row>
     <row r="83" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="127" t="s">
@@ -5962,7 +5951,7 @@
       <c r="E83" s="152">
         <v>0.94</v>
       </c>
-      <c r="H83" s="232"/>
+      <c r="H83" s="244"/>
     </row>
     <row r="84" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="127" t="s">
@@ -5980,7 +5969,7 @@
       <c r="E84" s="152">
         <v>0.06</v>
       </c>
-      <c r="H84" s="232"/>
+      <c r="H84" s="244"/>
     </row>
     <row r="85" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="127" t="s">
@@ -5998,7 +5987,7 @@
       <c r="E85" s="152">
         <v>0</v>
       </c>
-      <c r="H85" s="232"/>
+      <c r="H85" s="244"/>
     </row>
     <row r="86" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="127" t="s">
@@ -6016,7 +6005,7 @@
       <c r="E86" s="152">
         <v>0.94</v>
       </c>
-      <c r="H86" s="232"/>
+      <c r="H86" s="244"/>
     </row>
     <row r="87" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="127" t="s">
@@ -6034,7 +6023,7 @@
       <c r="E87" s="152">
         <v>0.06</v>
       </c>
-      <c r="H87" s="232"/>
+      <c r="H87" s="244"/>
     </row>
     <row r="88" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="127" t="s">
@@ -6052,7 +6041,7 @@
       <c r="E88" s="152">
         <v>0</v>
       </c>
-      <c r="H88" s="232"/>
+      <c r="H88" s="244"/>
     </row>
     <row r="89" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="127" t="s">
@@ -6070,7 +6059,7 @@
       <c r="E89" s="152">
         <v>0.94</v>
       </c>
-      <c r="H89" s="232"/>
+      <c r="H89" s="244"/>
     </row>
     <row r="90" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="127" t="s">
@@ -6088,7 +6077,7 @@
       <c r="E90" s="152">
         <v>0.06</v>
       </c>
-      <c r="H90" s="232"/>
+      <c r="H90" s="244"/>
     </row>
     <row r="91" spans="1:8" s="149" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="127" t="s">
@@ -6107,7 +6096,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="153"/>
-      <c r="H91" s="232"/>
+      <c r="H91" s="244"/>
     </row>
     <row r="92" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="129" t="s">
@@ -6126,7 +6115,7 @@
         <v>0.96</v>
       </c>
       <c r="F92" s="137"/>
-      <c r="H92" s="233" t="s">
+      <c r="H92" s="245" t="s">
         <v>309</v>
       </c>
     </row>
@@ -6147,7 +6136,7 @@
         <v>0</v>
       </c>
       <c r="F93" s="137"/>
-      <c r="H93" s="233"/>
+      <c r="H93" s="245"/>
     </row>
     <row r="94" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="129" t="s">
@@ -6166,7 +6155,7 @@
         <v>0.04</v>
       </c>
       <c r="F94" s="137"/>
-      <c r="H94" s="233"/>
+      <c r="H94" s="245"/>
     </row>
     <row r="95" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="129" t="s">
@@ -6185,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="F95" s="137"/>
-      <c r="H95" s="233"/>
+      <c r="H95" s="245"/>
     </row>
     <row r="96" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="129" t="s">
@@ -6204,7 +6193,7 @@
         <v>0.96</v>
       </c>
       <c r="F96" s="137"/>
-      <c r="H96" s="233"/>
+      <c r="H96" s="245"/>
     </row>
     <row r="97" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="129" t="s">
@@ -6223,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="F97" s="137"/>
-      <c r="H97" s="233"/>
+      <c r="H97" s="245"/>
     </row>
     <row r="98" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="129" t="s">
@@ -6242,7 +6231,7 @@
         <v>0.04</v>
       </c>
       <c r="F98" s="137"/>
-      <c r="H98" s="233"/>
+      <c r="H98" s="245"/>
     </row>
     <row r="99" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A99" s="129" t="s">
@@ -6261,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="137"/>
-      <c r="H99" s="233"/>
+      <c r="H99" s="245"/>
     </row>
     <row r="100" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="129" t="s">
@@ -6280,7 +6269,7 @@
         <v>0.96</v>
       </c>
       <c r="F100" s="137"/>
-      <c r="H100" s="233"/>
+      <c r="H100" s="245"/>
     </row>
     <row r="101" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="129" t="s">
@@ -6299,7 +6288,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="137"/>
-      <c r="H101" s="233"/>
+      <c r="H101" s="245"/>
     </row>
     <row r="102" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A102" s="129" t="s">
@@ -6318,7 +6307,7 @@
         <v>0.04</v>
       </c>
       <c r="F102" s="137"/>
-      <c r="H102" s="233"/>
+      <c r="H102" s="245"/>
     </row>
     <row r="103" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="129" t="s">
@@ -6337,7 +6326,7 @@
         <v>0</v>
       </c>
       <c r="F103" s="137"/>
-      <c r="H103" s="233"/>
+      <c r="H103" s="245"/>
     </row>
     <row r="104" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="129" t="s">
@@ -6356,7 +6345,7 @@
         <v>0.3</v>
       </c>
       <c r="F104" s="137"/>
-      <c r="H104" s="233"/>
+      <c r="H104" s="245"/>
     </row>
     <row r="105" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A105" s="129" t="s">
@@ -6375,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="137"/>
-      <c r="H105" s="233"/>
+      <c r="H105" s="245"/>
     </row>
     <row r="106" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="129" t="s">
@@ -6394,7 +6383,7 @@
         <v>0.7</v>
       </c>
       <c r="F106" s="137"/>
-      <c r="H106" s="233"/>
+      <c r="H106" s="245"/>
     </row>
     <row r="107" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="129" t="s">
@@ -6413,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="F107" s="137"/>
-      <c r="H107" s="233"/>
+      <c r="H107" s="245"/>
     </row>
     <row r="108" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="129" t="s">
@@ -6432,7 +6421,7 @@
         <v>0</v>
       </c>
       <c r="F108" s="137"/>
-      <c r="H108" s="233"/>
+      <c r="H108" s="245"/>
     </row>
     <row r="109" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="129" t="s">
@@ -6451,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="F109" s="137"/>
-      <c r="H109" s="233"/>
+      <c r="H109" s="245"/>
     </row>
     <row r="110" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A110" s="129" t="s">
@@ -6470,7 +6459,7 @@
         <v>1</v>
       </c>
       <c r="F110" s="137"/>
-      <c r="H110" s="233"/>
+      <c r="H110" s="245"/>
     </row>
     <row r="111" spans="1:8" s="138" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="129" t="s">
@@ -6489,7 +6478,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="137"/>
-      <c r="H111" s="233"/>
+      <c r="H111" s="245"/>
     </row>
     <row r="112" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="131" t="s">
@@ -6507,7 +6496,7 @@
       <c r="E112" s="156">
         <v>0.7</v>
       </c>
-      <c r="H112" s="234" t="s">
+      <c r="H112" s="246" t="s">
         <v>297</v>
       </c>
     </row>
@@ -6527,7 +6516,7 @@
       <c r="E113" s="156">
         <v>0</v>
       </c>
-      <c r="H113" s="234"/>
+      <c r="H113" s="246"/>
     </row>
     <row r="114" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" s="131" t="s">
@@ -6545,7 +6534,7 @@
       <c r="E114" s="156">
         <v>0</v>
       </c>
-      <c r="H114" s="234"/>
+      <c r="H114" s="246"/>
     </row>
     <row r="115" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A115" s="131" t="s">
@@ -6563,7 +6552,7 @@
       <c r="E115" s="156">
         <v>0.3</v>
       </c>
-      <c r="H115" s="234"/>
+      <c r="H115" s="246"/>
     </row>
     <row r="116" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="131" t="s">
@@ -6581,7 +6570,7 @@
       <c r="E116" s="156">
         <v>0</v>
       </c>
-      <c r="H116" s="234"/>
+      <c r="H116" s="246"/>
     </row>
     <row r="117" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="131" t="s">
@@ -6599,7 +6588,7 @@
       <c r="E117" s="156">
         <v>0</v>
       </c>
-      <c r="H117" s="234"/>
+      <c r="H117" s="246"/>
     </row>
     <row r="118" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A118" s="131" t="s">
@@ -6617,7 +6606,7 @@
       <c r="E118" s="156">
         <v>0.6</v>
       </c>
-      <c r="H118" s="234"/>
+      <c r="H118" s="246"/>
     </row>
     <row r="119" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="131" t="s">
@@ -6635,7 +6624,7 @@
       <c r="E119" s="156">
         <v>0</v>
       </c>
-      <c r="H119" s="234"/>
+      <c r="H119" s="246"/>
     </row>
     <row r="120" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="131" t="s">
@@ -6653,7 +6642,7 @@
       <c r="E120" s="156">
         <v>0</v>
       </c>
-      <c r="H120" s="234"/>
+      <c r="H120" s="246"/>
     </row>
     <row r="121" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A121" s="131" t="s">
@@ -6671,7 +6660,7 @@
       <c r="E121" s="156">
         <v>0.4</v>
       </c>
-      <c r="H121" s="234"/>
+      <c r="H121" s="246"/>
     </row>
     <row r="122" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" s="131" t="s">
@@ -6689,7 +6678,7 @@
       <c r="E122" s="156">
         <v>0</v>
       </c>
-      <c r="H122" s="234"/>
+      <c r="H122" s="246"/>
     </row>
     <row r="123" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="131" t="s">
@@ -6707,7 +6696,7 @@
       <c r="E123" s="156">
         <v>0</v>
       </c>
-      <c r="H123" s="234"/>
+      <c r="H123" s="246"/>
     </row>
     <row r="124" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="131" t="s">
@@ -6725,7 +6714,7 @@
       <c r="E124" s="156">
         <v>0.42</v>
       </c>
-      <c r="H124" s="234"/>
+      <c r="H124" s="246"/>
     </row>
     <row r="125" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="131" t="s">
@@ -6743,7 +6732,7 @@
       <c r="E125" s="156">
         <v>0</v>
       </c>
-      <c r="H125" s="234"/>
+      <c r="H125" s="246"/>
     </row>
     <row r="126" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="131" t="s">
@@ -6761,7 +6750,7 @@
       <c r="E126" s="156">
         <v>0</v>
       </c>
-      <c r="H126" s="234"/>
+      <c r="H126" s="246"/>
     </row>
     <row r="127" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="131" t="s">
@@ -6779,7 +6768,7 @@
       <c r="E127" s="156">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H127" s="234"/>
+      <c r="H127" s="246"/>
     </row>
     <row r="128" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="131" t="s">
@@ -6797,7 +6786,7 @@
       <c r="E128" s="156">
         <v>0</v>
       </c>
-      <c r="H128" s="234"/>
+      <c r="H128" s="246"/>
     </row>
     <row r="129" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A129" s="131" t="s">
@@ -6815,7 +6804,7 @@
       <c r="E129" s="156">
         <v>0</v>
       </c>
-      <c r="H129" s="234"/>
+      <c r="H129" s="246"/>
     </row>
     <row r="130" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="131" t="s">
@@ -6833,7 +6822,7 @@
       <c r="E130" s="156">
         <v>0.05</v>
       </c>
-      <c r="H130" s="234"/>
+      <c r="H130" s="246"/>
     </row>
     <row r="131" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A131" s="131" t="s">
@@ -6851,7 +6840,7 @@
       <c r="E131" s="156">
         <v>0</v>
       </c>
-      <c r="H131" s="234"/>
+      <c r="H131" s="246"/>
     </row>
     <row r="132" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="131" t="s">
@@ -6869,7 +6858,7 @@
       <c r="E132" s="156">
         <v>0</v>
       </c>
-      <c r="H132" s="234"/>
+      <c r="H132" s="246"/>
     </row>
     <row r="133" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="131" t="s">
@@ -6887,7 +6876,7 @@
       <c r="E133" s="156">
         <v>0.95</v>
       </c>
-      <c r="H133" s="234"/>
+      <c r="H133" s="246"/>
     </row>
     <row r="134" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A134" s="131" t="s">
@@ -6905,7 +6894,7 @@
       <c r="E134" s="156">
         <v>0</v>
       </c>
-      <c r="H134" s="234"/>
+      <c r="H134" s="246"/>
     </row>
     <row r="135" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="131" t="s">
@@ -6923,7 +6912,7 @@
       <c r="E135" s="156">
         <v>0</v>
       </c>
-      <c r="H135" s="234"/>
+      <c r="H135" s="246"/>
     </row>
     <row r="136" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A136" s="131" t="s">
@@ -6941,7 +6930,7 @@
       <c r="E136" s="156">
         <v>0</v>
       </c>
-      <c r="H136" s="234"/>
+      <c r="H136" s="246"/>
     </row>
     <row r="137" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A137" s="131" t="s">
@@ -6959,7 +6948,7 @@
       <c r="E137" s="156">
         <v>0</v>
       </c>
-      <c r="H137" s="234"/>
+      <c r="H137" s="246"/>
     </row>
     <row r="138" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A138" s="131" t="s">
@@ -6977,7 +6966,7 @@
       <c r="E138" s="156">
         <v>0</v>
       </c>
-      <c r="H138" s="234"/>
+      <c r="H138" s="246"/>
     </row>
     <row r="139" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A139" s="131" t="s">
@@ -6995,7 +6984,7 @@
       <c r="E139" s="156">
         <v>0.05</v>
       </c>
-      <c r="H139" s="234"/>
+      <c r="H139" s="246"/>
     </row>
     <row r="140" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A140" s="131" t="s">
@@ -7013,7 +7002,7 @@
       <c r="E140" s="156">
         <v>0.95</v>
       </c>
-      <c r="H140" s="234"/>
+      <c r="H140" s="246"/>
     </row>
     <row r="141" spans="1:8" s="157" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A141" s="131" t="s">
@@ -7031,7 +7020,7 @@
       <c r="E141" s="156">
         <v>0</v>
       </c>
-      <c r="H141" s="234"/>
+      <c r="H141" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7077,7 +7066,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D2" s="63"/>
-      <c r="E2" s="235" t="s">
+      <c r="E2" s="247" t="s">
         <v>308</v>
       </c>
     </row>
@@ -7092,7 +7081,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D3" s="63"/>
-      <c r="E3" s="235"/>
+      <c r="E3" s="247"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="127" t="s">
@@ -7105,7 +7094,7 @@
         <v>0.5</v>
       </c>
       <c r="D4" s="63"/>
-      <c r="E4" s="235"/>
+      <c r="E4" s="247"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="127" t="s">
@@ -7118,7 +7107,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="63"/>
-      <c r="E5" s="235"/>
+      <c r="E5" s="247"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="129" t="s">
@@ -7131,7 +7120,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D6" s="63"/>
-      <c r="E6" s="235"/>
+      <c r="E6" s="247"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="129" t="s">
@@ -7144,7 +7133,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D7" s="63"/>
-      <c r="E7" s="235"/>
+      <c r="E7" s="247"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="129" t="s">
@@ -7157,7 +7146,7 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="63"/>
-      <c r="E8" s="235"/>
+      <c r="E8" s="247"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="129" t="s">
@@ -7170,7 +7159,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="63"/>
-      <c r="E9" s="235"/>
+      <c r="E9" s="247"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="131" t="s">
@@ -7183,7 +7172,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D10" s="63"/>
-      <c r="E10" s="235"/>
+      <c r="E10" s="247"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="131" t="s">
@@ -7196,7 +7185,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D11" s="63"/>
-      <c r="E11" s="235"/>
+      <c r="E11" s="247"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="131" t="s">
@@ -7209,7 +7198,7 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="D12" s="63"/>
-      <c r="E12" s="235"/>
+      <c r="E12" s="247"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="131" t="s">
@@ -7222,7 +7211,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="63"/>
-      <c r="E13" s="235"/>
+      <c r="E13" s="247"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" s="63"/>
@@ -7355,84 +7344,84 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="250" t="s">
+      <c r="B2" s="262" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="264" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="253"/>
-      <c r="E2" s="253"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="267" t="s">
+      <c r="D2" s="265"/>
+      <c r="E2" s="265"/>
+      <c r="F2" s="266"/>
+      <c r="G2" s="279" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="250" t="s">
+      <c r="H2" s="262" t="s">
         <v>260</v>
       </c>
-      <c r="I2" s="252" t="s">
+      <c r="I2" s="264" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="253"/>
-      <c r="K2" s="262"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="274"/>
     </row>
     <row r="3" spans="1:21" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="251"/>
-      <c r="C3" s="255"/>
-      <c r="D3" s="256"/>
-      <c r="E3" s="256"/>
-      <c r="F3" s="257"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="251"/>
-      <c r="I3" s="255"/>
-      <c r="J3" s="256"/>
-      <c r="K3" s="263"/>
+      <c r="B3" s="263"/>
+      <c r="C3" s="267"/>
+      <c r="D3" s="268"/>
+      <c r="E3" s="268"/>
+      <c r="F3" s="269"/>
+      <c r="G3" s="280"/>
+      <c r="H3" s="263"/>
+      <c r="I3" s="267"/>
+      <c r="J3" s="268"/>
+      <c r="K3" s="275"/>
     </row>
     <row r="4" spans="1:21" s="44" customFormat="1" ht="270" x14ac:dyDescent="0.2">
       <c r="A4" s="46"/>
       <c r="B4" s="164" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="258" t="s">
+      <c r="C4" s="270" t="s">
         <v>312</v>
       </c>
-      <c r="D4" s="259"/>
-      <c r="E4" s="259"/>
-      <c r="F4" s="260"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="272"/>
       <c r="G4" s="165" t="s">
         <v>267</v>
       </c>
       <c r="H4" s="166" t="s">
         <v>268</v>
       </c>
-      <c r="I4" s="264" t="s">
+      <c r="I4" s="276" t="s">
         <v>288</v>
       </c>
-      <c r="J4" s="265"/>
-      <c r="K4" s="266"/>
+      <c r="J4" s="277"/>
+      <c r="K4" s="278"/>
     </row>
     <row r="5" spans="1:21" s="44" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="46"/>
       <c r="B5" s="84" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="236" t="s">
+      <c r="C5" s="248" t="s">
         <v>313</v>
       </c>
-      <c r="D5" s="237"/>
-      <c r="E5" s="237"/>
-      <c r="F5" s="261"/>
+      <c r="D5" s="249"/>
+      <c r="E5" s="249"/>
+      <c r="F5" s="273"/>
       <c r="G5" s="167">
         <v>0.8</v>
       </c>
       <c r="H5" s="168" t="s">
         <v>298</v>
       </c>
-      <c r="I5" s="239" t="s">
+      <c r="I5" s="251" t="s">
         <v>266</v>
       </c>
-      <c r="J5" s="240"/>
-      <c r="K5" s="241"/>
+      <c r="J5" s="252"/>
+      <c r="K5" s="253"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -7442,23 +7431,23 @@
       <c r="B6" s="84" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="236" t="s">
+      <c r="C6" s="248" t="s">
         <v>314</v>
       </c>
-      <c r="D6" s="237"/>
-      <c r="E6" s="237"/>
-      <c r="F6" s="261"/>
+      <c r="D6" s="249"/>
+      <c r="E6" s="249"/>
+      <c r="F6" s="273"/>
       <c r="G6" s="167">
         <v>0.8</v>
       </c>
       <c r="H6" s="169" t="s">
         <v>298</v>
       </c>
-      <c r="I6" s="239" t="s">
+      <c r="I6" s="251" t="s">
         <v>265</v>
       </c>
-      <c r="J6" s="240"/>
-      <c r="K6" s="241"/>
+      <c r="J6" s="252"/>
+      <c r="K6" s="253"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -7468,21 +7457,21 @@
       <c r="B7" s="84" t="s">
         <v>289</v>
       </c>
-      <c r="C7" s="236" t="s">
+      <c r="C7" s="248" t="s">
         <v>290</v>
       </c>
-      <c r="D7" s="237"/>
-      <c r="E7" s="237"/>
-      <c r="F7" s="261"/>
+      <c r="D7" s="249"/>
+      <c r="E7" s="249"/>
+      <c r="F7" s="273"/>
       <c r="G7" s="167">
         <v>1</v>
       </c>
       <c r="H7" s="169"/>
-      <c r="I7" s="239" t="s">
+      <c r="I7" s="251" t="s">
         <v>291</v>
       </c>
-      <c r="J7" s="240"/>
-      <c r="K7" s="241"/>
+      <c r="J7" s="252"/>
+      <c r="K7" s="253"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -7492,21 +7481,21 @@
       <c r="B8" s="84" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="236" t="s">
+      <c r="C8" s="248" t="s">
         <v>262</v>
       </c>
-      <c r="D8" s="237"/>
-      <c r="E8" s="237"/>
-      <c r="F8" s="261"/>
+      <c r="D8" s="249"/>
+      <c r="E8" s="249"/>
+      <c r="F8" s="273"/>
       <c r="G8" s="167">
         <v>1</v>
       </c>
       <c r="H8" s="168" t="s">
         <v>263</v>
       </c>
-      <c r="I8" s="239"/>
-      <c r="J8" s="240"/>
-      <c r="K8" s="241"/>
+      <c r="I8" s="251"/>
+      <c r="J8" s="252"/>
+      <c r="K8" s="253"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -7516,23 +7505,23 @@
       <c r="B9" s="84" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="236" t="s">
+      <c r="C9" s="248" t="s">
         <v>158</v>
       </c>
-      <c r="D9" s="237"/>
-      <c r="E9" s="237"/>
-      <c r="F9" s="261"/>
+      <c r="D9" s="249"/>
+      <c r="E9" s="249"/>
+      <c r="F9" s="273"/>
       <c r="G9" s="167">
         <v>0.95</v>
       </c>
       <c r="H9" s="168" t="s">
         <v>298</v>
       </c>
-      <c r="I9" s="236" t="s">
+      <c r="I9" s="248" t="s">
         <v>261</v>
       </c>
-      <c r="J9" s="237"/>
-      <c r="K9" s="238"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="250"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -7542,21 +7531,21 @@
       <c r="B10" s="84" t="s">
         <v>159</v>
       </c>
-      <c r="C10" s="236" t="s">
+      <c r="C10" s="248" t="s">
         <v>162</v>
       </c>
-      <c r="D10" s="237"/>
-      <c r="E10" s="237"/>
-      <c r="F10" s="261"/>
+      <c r="D10" s="249"/>
+      <c r="E10" s="249"/>
+      <c r="F10" s="273"/>
       <c r="G10" s="170">
         <v>0.9</v>
       </c>
       <c r="H10" s="168"/>
-      <c r="I10" s="239" t="s">
+      <c r="I10" s="251" t="s">
         <v>264</v>
       </c>
-      <c r="J10" s="240"/>
-      <c r="K10" s="241"/>
+      <c r="J10" s="252"/>
+      <c r="K10" s="253"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
@@ -7566,21 +7555,21 @@
       <c r="B11" s="84" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="236" t="s">
+      <c r="C11" s="248" t="s">
         <v>161</v>
       </c>
-      <c r="D11" s="237"/>
-      <c r="E11" s="237"/>
-      <c r="F11" s="261"/>
+      <c r="D11" s="249"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="273"/>
       <c r="G11" s="170">
         <v>0.9</v>
       </c>
       <c r="H11" s="169"/>
-      <c r="I11" s="239" t="s">
+      <c r="I11" s="251" t="s">
         <v>264</v>
       </c>
-      <c r="J11" s="240"/>
-      <c r="K11" s="241"/>
+      <c r="J11" s="252"/>
+      <c r="K11" s="253"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -7611,28 +7600,28 @@
       <c r="U13" s="51"/>
     </row>
     <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="244" t="s">
+      <c r="B14" s="258" t="s">
         <v>322</v>
       </c>
-      <c r="C14" s="245"/>
-      <c r="D14" s="245"/>
-      <c r="E14" s="245"/>
-      <c r="F14" s="245"/>
-      <c r="G14" s="245"/>
-      <c r="H14" s="245"/>
-      <c r="I14" s="245"/>
-      <c r="J14" s="245"/>
-      <c r="K14" s="245"/>
-      <c r="L14" s="245"/>
-      <c r="M14" s="245"/>
-      <c r="N14" s="245"/>
-      <c r="O14" s="245"/>
-      <c r="P14" s="245"/>
-      <c r="Q14" s="245"/>
-      <c r="R14" s="245"/>
-      <c r="S14" s="245"/>
-      <c r="T14" s="245"/>
-      <c r="U14" s="246"/>
+      <c r="C14" s="259"/>
+      <c r="D14" s="259"/>
+      <c r="E14" s="259"/>
+      <c r="F14" s="259"/>
+      <c r="G14" s="259"/>
+      <c r="H14" s="259"/>
+      <c r="I14" s="259"/>
+      <c r="J14" s="259"/>
+      <c r="K14" s="259"/>
+      <c r="L14" s="259"/>
+      <c r="M14" s="259"/>
+      <c r="N14" s="259"/>
+      <c r="O14" s="259"/>
+      <c r="P14" s="259"/>
+      <c r="Q14" s="259"/>
+      <c r="R14" s="259"/>
+      <c r="S14" s="259"/>
+      <c r="T14" s="259"/>
+      <c r="U14" s="260"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B15" s="52"/>
@@ -7657,34 +7646,34 @@
       <c r="U15" s="55"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B16" s="242" t="s">
+      <c r="B16" s="256" t="s">
         <v>252</v>
       </c>
-      <c r="C16" s="243"/>
-      <c r="D16" s="243"/>
-      <c r="E16" s="243"/>
-      <c r="F16" s="243"/>
-      <c r="G16" s="243"/>
-      <c r="H16" s="243"/>
-      <c r="I16" s="243"/>
-      <c r="J16" s="243"/>
-      <c r="K16" s="243"/>
-      <c r="L16" s="243"/>
-      <c r="M16" s="243"/>
-      <c r="N16" s="243"/>
-      <c r="O16" s="243"/>
-      <c r="P16" s="243"/>
-      <c r="Q16" s="243"/>
-      <c r="R16" s="243"/>
-      <c r="S16" s="243"/>
-      <c r="T16" s="243"/>
-      <c r="U16" s="249"/>
+      <c r="C16" s="257"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="257"/>
+      <c r="F16" s="257"/>
+      <c r="G16" s="257"/>
+      <c r="H16" s="257"/>
+      <c r="I16" s="257"/>
+      <c r="J16" s="257"/>
+      <c r="K16" s="257"/>
+      <c r="L16" s="257"/>
+      <c r="M16" s="257"/>
+      <c r="N16" s="257"/>
+      <c r="O16" s="257"/>
+      <c r="P16" s="257"/>
+      <c r="Q16" s="257"/>
+      <c r="R16" s="257"/>
+      <c r="S16" s="257"/>
+      <c r="T16" s="257"/>
+      <c r="U16" s="261"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B17" s="247" t="s">
+      <c r="B17" s="254" t="s">
         <v>250</v>
       </c>
-      <c r="C17" s="248"/>
+      <c r="C17" s="255"/>
       <c r="D17" s="171">
         <v>2008</v>
       </c>
@@ -7741,10 +7730,10 @@
       </c>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B18" s="247" t="s">
+      <c r="B18" s="254" t="s">
         <v>251</v>
       </c>
-      <c r="C18" s="248"/>
+      <c r="C18" s="255"/>
       <c r="D18" s="59">
         <v>0.86</v>
       </c>
@@ -7801,10 +7790,10 @@
       </c>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B19" s="247" t="s">
+      <c r="B19" s="254" t="s">
         <v>320</v>
       </c>
-      <c r="C19" s="248"/>
+      <c r="C19" s="255"/>
       <c r="D19" s="59">
         <v>0.78</v>
       </c>
@@ -7862,10 +7851,10 @@
       </c>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B20" s="247" t="s">
+      <c r="B20" s="254" t="s">
         <v>321</v>
       </c>
-      <c r="C20" s="248"/>
+      <c r="C20" s="255"/>
       <c r="D20" s="59">
         <v>0.78</v>
       </c>
@@ -7944,17 +7933,17 @@
       <c r="U21" s="55"/>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B22" s="242" t="s">
+      <c r="B22" s="256" t="s">
         <v>255</v>
       </c>
-      <c r="C22" s="243"/>
-      <c r="D22" s="243"/>
-      <c r="E22" s="243"/>
-      <c r="F22" s="243"/>
-      <c r="G22" s="243"/>
-      <c r="H22" s="243"/>
-      <c r="I22" s="243"/>
-      <c r="J22" s="243"/>
+      <c r="C22" s="257"/>
+      <c r="D22" s="257"/>
+      <c r="E22" s="257"/>
+      <c r="F22" s="257"/>
+      <c r="G22" s="257"/>
+      <c r="H22" s="257"/>
+      <c r="I22" s="257"/>
+      <c r="J22" s="257"/>
       <c r="K22" s="174"/>
       <c r="L22" s="174"/>
       <c r="M22" s="174"/>
@@ -7968,10 +7957,10 @@
       <c r="U22" s="175"/>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B23" s="247" t="s">
+      <c r="B23" s="254" t="s">
         <v>250</v>
       </c>
-      <c r="C23" s="248"/>
+      <c r="C23" s="255"/>
       <c r="D23" s="171">
         <v>2019</v>
       </c>
@@ -8006,10 +7995,10 @@
       <c r="U23" s="55"/>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B24" s="247" t="s">
+      <c r="B24" s="254" t="s">
         <v>251</v>
       </c>
-      <c r="C24" s="248"/>
+      <c r="C24" s="255"/>
       <c r="D24" s="59">
         <f>E24</f>
         <v>0.53</v>
@@ -8047,10 +8036,10 @@
       <c r="U24" s="55"/>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B25" s="247" t="s">
+      <c r="B25" s="254" t="s">
         <v>320</v>
       </c>
-      <c r="C25" s="248"/>
+      <c r="C25" s="255"/>
       <c r="D25" s="59">
         <f>E25</f>
         <v>0.35830985915492958</v>
@@ -8088,10 +8077,10 @@
       <c r="U25" s="55"/>
     </row>
     <row r="26" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="247" t="s">
+      <c r="B26" s="254" t="s">
         <v>321</v>
       </c>
-      <c r="C26" s="248"/>
+      <c r="C26" s="255"/>
       <c r="D26" s="176">
         <v>0</v>
       </c>
@@ -8196,278 +8185,278 @@
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="194" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="185"/>
-    </row>
-    <row r="4" spans="2:6" s="270" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="269" t="s">
+      <c r="C3" s="195"/>
+      <c r="D3" s="195"/>
+      <c r="E3" s="195"/>
+      <c r="F3" s="196"/>
+    </row>
+    <row r="4" spans="2:6" s="63" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="183" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="270" t="s">
+      <c r="C4" s="63" t="s">
         <v>248</v>
       </c>
-      <c r="D4" s="270">
+      <c r="D4" s="63">
         <v>0.8</v>
       </c>
-      <c r="E4" s="271">
+      <c r="E4" s="184">
         <v>0.65</v>
       </c>
-      <c r="F4" s="272"/>
-    </row>
-    <row r="5" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="273" t="s">
+      <c r="F4" s="185"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B5" s="194" t="s">
         <v>257</v>
       </c>
-      <c r="C5" s="274"/>
-      <c r="D5" s="274"/>
-      <c r="E5" s="274"/>
-      <c r="F5" s="275"/>
-    </row>
-    <row r="6" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="269" t="s">
+      <c r="C5" s="195"/>
+      <c r="D5" s="195"/>
+      <c r="E5" s="195"/>
+      <c r="F5" s="196"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B6" s="183" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="270" t="s">
+      <c r="C6" s="63" t="s">
         <v>258</v>
       </c>
-      <c r="D6" s="270">
+      <c r="D6" s="63">
         <v>0.8</v>
       </c>
-      <c r="E6" s="271" t="s">
+      <c r="E6" s="184" t="s">
         <v>259</v>
       </c>
-      <c r="F6" s="272" t="s">
+      <c r="F6" s="185" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="7" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="273" t="s">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B7" s="194" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="274"/>
-      <c r="D7" s="274"/>
-      <c r="E7" s="274"/>
-      <c r="F7" s="275"/>
-    </row>
-    <row r="8" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="277" t="s">
+      <c r="C7" s="195"/>
+      <c r="D7" s="195"/>
+      <c r="E7" s="195"/>
+      <c r="F7" s="196"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B8" s="186" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="278" t="s">
+      <c r="C8" s="187" t="s">
         <v>283</v>
       </c>
-      <c r="D8" s="271">
+      <c r="D8" s="184">
         <v>0.68</v>
       </c>
-      <c r="E8" s="271" t="s">
+      <c r="E8" s="184" t="s">
         <v>285</v>
       </c>
-      <c r="F8" s="279" t="s">
+      <c r="F8" s="197" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="9" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="277" t="s">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B9" s="186" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="278" t="s">
+      <c r="C9" s="187" t="s">
         <v>284</v>
       </c>
-      <c r="D9" s="271">
+      <c r="D9" s="184">
         <v>0.76</v>
       </c>
-      <c r="E9" s="271" t="s">
+      <c r="E9" s="184" t="s">
         <v>286</v>
       </c>
-      <c r="F9" s="279"/>
-    </row>
-    <row r="10" spans="2:6" s="276" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="269" t="s">
+      <c r="F9" s="197"/>
+    </row>
+    <row r="10" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="183" t="s">
         <v>164</v>
       </c>
-      <c r="C10" s="278" t="s">
+      <c r="C10" s="187" t="s">
         <v>154</v>
       </c>
-      <c r="D10" s="270">
+      <c r="D10" s="63">
         <v>0.8</v>
       </c>
-      <c r="E10" s="271" t="s">
+      <c r="E10" s="184" t="s">
         <v>271</v>
       </c>
-      <c r="F10" s="279"/>
-    </row>
-    <row r="11" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="269" t="s">
+      <c r="F10" s="197"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B11" s="183" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="270" t="s">
+      <c r="C11" s="63" t="s">
         <v>155</v>
       </c>
-      <c r="D11" s="270">
+      <c r="D11" s="63">
         <v>0.8</v>
       </c>
-      <c r="E11" s="271" t="s">
+      <c r="E11" s="184" t="s">
         <v>271</v>
       </c>
-      <c r="F11" s="279"/>
-    </row>
-    <row r="12" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="269" t="s">
+      <c r="F11" s="197"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="183" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="270" t="s">
+      <c r="C12" s="63" t="s">
         <v>159</v>
       </c>
-      <c r="D12" s="270">
+      <c r="D12" s="63">
         <v>0.9</v>
       </c>
-      <c r="E12" s="271" t="s">
+      <c r="E12" s="184" t="s">
         <v>277</v>
       </c>
-      <c r="F12" s="279"/>
-    </row>
-    <row r="13" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="269" t="s">
+      <c r="F12" s="197"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B13" s="183" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="270" t="s">
+      <c r="C13" s="63" t="s">
         <v>160</v>
       </c>
-      <c r="D13" s="270">
+      <c r="D13" s="63">
         <v>0.9</v>
       </c>
-      <c r="E13" s="271" t="s">
+      <c r="E13" s="184" t="s">
         <v>272</v>
       </c>
-      <c r="F13" s="279"/>
-    </row>
-    <row r="14" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="273" t="s">
+      <c r="F13" s="197"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B14" s="194" t="s">
         <v>296</v>
       </c>
-      <c r="C14" s="274"/>
-      <c r="D14" s="274"/>
-      <c r="E14" s="274"/>
-      <c r="F14" s="275"/>
-    </row>
-    <row r="15" spans="2:6" s="276" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="269" t="s">
+      <c r="C14" s="195"/>
+      <c r="D14" s="195"/>
+      <c r="E14" s="195"/>
+      <c r="F14" s="196"/>
+    </row>
+    <row r="15" spans="2:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="183" t="s">
         <v>149</v>
       </c>
-      <c r="C15" s="270" t="s">
+      <c r="C15" s="63" t="s">
         <v>273</v>
       </c>
-      <c r="D15" s="270">
-        <v>0</v>
-      </c>
-      <c r="E15" s="270">
+      <c r="D15" s="63">
+        <v>0</v>
+      </c>
+      <c r="E15" s="63">
         <v>0.1</v>
       </c>
-      <c r="F15" s="279" t="s">
+      <c r="F15" s="197" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="269" t="s">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B16" s="183" t="s">
         <v>149</v>
       </c>
-      <c r="C16" s="270" t="s">
+      <c r="C16" s="63" t="s">
         <v>274</v>
       </c>
-      <c r="D16" s="270">
-        <v>0</v>
-      </c>
-      <c r="E16" s="270">
+      <c r="D16" s="63">
+        <v>0</v>
+      </c>
+      <c r="E16" s="63">
         <v>0.1</v>
       </c>
-      <c r="F16" s="279"/>
-    </row>
-    <row r="17" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="269" t="s">
+      <c r="F16" s="197"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B17" s="183" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="270" t="s">
+      <c r="C17" s="63" t="s">
         <v>275</v>
       </c>
-      <c r="D17" s="270">
-        <v>0</v>
-      </c>
-      <c r="E17" s="270">
+      <c r="D17" s="63">
+        <v>0</v>
+      </c>
+      <c r="E17" s="63">
         <v>0.1</v>
       </c>
-      <c r="F17" s="279"/>
-    </row>
-    <row r="18" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="273" t="s">
+      <c r="F17" s="197"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B18" s="194" t="s">
         <v>315</v>
       </c>
-      <c r="C18" s="274"/>
-      <c r="D18" s="274"/>
-      <c r="E18" s="274"/>
-      <c r="F18" s="275"/>
-    </row>
-    <row r="19" spans="2:6" s="276" customFormat="1" ht="49" x14ac:dyDescent="0.2">
-      <c r="B19" s="269" t="s">
+      <c r="C18" s="195"/>
+      <c r="D18" s="195"/>
+      <c r="E18" s="195"/>
+      <c r="F18" s="196"/>
+    </row>
+    <row r="19" spans="2:6" ht="49" x14ac:dyDescent="0.2">
+      <c r="B19" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="270" t="s">
+      <c r="C19" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="280" t="s">
+      <c r="D19" s="188" t="s">
         <v>299</v>
       </c>
-      <c r="E19" s="280" t="s">
+      <c r="E19" s="188" t="s">
         <v>166</v>
       </c>
-      <c r="F19" s="281" t="s">
+      <c r="F19" s="189" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="20" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="273" t="s">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B20" s="194" t="s">
         <v>310</v>
       </c>
-      <c r="C20" s="274"/>
-      <c r="D20" s="274"/>
-      <c r="E20" s="274"/>
-      <c r="F20" s="275"/>
-    </row>
-    <row r="21" spans="2:6" s="276" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="269" t="s">
+      <c r="C20" s="195"/>
+      <c r="D20" s="195"/>
+      <c r="E20" s="195"/>
+      <c r="F20" s="196"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B21" s="183" t="s">
         <v>140</v>
       </c>
-      <c r="C21" s="270" t="s">
+      <c r="C21" s="63" t="s">
         <v>317</v>
       </c>
-      <c r="D21" s="270">
+      <c r="D21" s="63">
         <v>0.96</v>
       </c>
-      <c r="E21" s="270">
+      <c r="E21" s="63">
         <v>0.9</v>
       </c>
-      <c r="F21" s="282" t="s">
+      <c r="F21" s="192" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="22" spans="2:6" s="276" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="283" t="s">
+    <row r="22" spans="2:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="190" t="s">
         <v>140</v>
       </c>
-      <c r="C22" s="284" t="s">
+      <c r="C22" s="191" t="s">
         <v>311</v>
       </c>
-      <c r="D22" s="284">
+      <c r="D22" s="191">
         <v>0.7</v>
       </c>
-      <c r="E22" s="284">
+      <c r="E22" s="191">
         <v>0.85</v>
       </c>
-      <c r="F22" s="285"/>
+      <c r="F22" s="193"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" s="8"/>
@@ -8478,7 +8467,6 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B14:F14"/>
@@ -8487,6 +8475,7 @@
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="F15:F17"/>
     <mergeCell ref="F8:F13"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
